--- a/hardware information/AeroSense v2/05_BOM/BOM_EN.xlsx
+++ b/hardware information/AeroSense v2/05_BOM/BOM_EN.xlsx
@@ -2,11 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R38e55dd7ded24f54"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Printed" sheetId="2" r:id="R1473929d5e2f47d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purchase" sheetId="3" r:id="Rb23f3a49e7d34f95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCB" sheetId="4" r:id="R71b9ef60aa2b42c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Print_batches" sheetId="5" r:id="R121e9cf825bf424f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R5278591a199a4ca9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Printed" sheetId="2" r:id="R88776f9981d3405b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purchase" sheetId="3" r:id="R20cc217bab2c4402"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCB" sheetId="4" r:id="R2eedbb3898f843e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Print_batches" sheetId="5" r:id="R8256ab50c3dc471c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="6" r:id="Rb7d20f5631534357"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,10 +18,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="5">
     <x:numFmt numFmtId="200" formatCode="#,##0.00;(#,##0.00);0.00"/>
+    <x:numFmt numFmtId="201" formatCode="&quot;$&quot;#,##0.00;(&quot;$&quot;#,##0.00);&quot;$&quot;0.00"/>
+    <x:numFmt numFmtId="202" formatCode="0.000"/>
+    <x:numFmt numFmtId="203" formatCode="&quot;$&quot;0.000000"/>
+    <x:numFmt numFmtId="204" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="6">
+  <x:fonts count="8">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -53,8 +58,20 @@
       <x:color rgb="FF243746"/>
       <x:name val="Microsoft JhengHei"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="14"/>
+      <x:color rgb="FF263D50"/>
+      <x:name val="Microsoft JhengHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF263D50"/>
+      <x:name val="Microsoft JhengHei"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -71,6 +88,31 @@
         <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE9EFF3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF263D50"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF263D50"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDFE8EE"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -78,7 +120,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="17">
+  <x:cellXfs count="37">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -124,6 +166,66 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -330,10 +432,10 @@
   <x:cols>
     <x:col min="1" max="1" width="46" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="3" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="4" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="38" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="23" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="4" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="46" hidden="0" customWidth="1"/>
   </x:cols>
@@ -350,7 +452,7 @@
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>AeroSense materials and cost</x:v>
+        <x:v>AeroSense materials and cost (USD)</x:v>
       </x:c>
       <x:c r="B2" s="2"/>
       <x:c r="C2" s="2"/>
@@ -362,7 +464,7 @@
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
       <x:c r="A3" s="4" t="str">
-        <x:v>Dual-currency budget. Listings, proxies and allowances are identified.</x:v>
+        <x:v>All cost inputs and totals in USD. Original quotation currencies are retained in source notes.</x:v>
       </x:c>
       <x:c r="B3" s="2"/>
       <x:c r="C3" s="2"/>
@@ -377,11 +479,9 @@
         <x:v>Item</x:v>
       </x:c>
       <x:c r="B4" s="8" t="str">
-        <x:v>NTD</x:v>
-      </x:c>
-      <x:c r="C4" s="8" t="str">
         <x:v>USD</x:v>
       </x:c>
+      <x:c r="C4"/>
       <x:c r="D4" s="2"/>
       <x:c r="E4" s="10" t="str">
         <x:v>Input</x:v>
@@ -392,28 +492,25 @@
       <x:c r="G4" s="2"/>
       <x:c r="H4" s="2"/>
     </x:row>
-    <x:row r="5" ht="110" customHeight="1">
+    <x:row r="5" ht="165" customHeight="1">
       <x:c r="A5" s="10" t="str">
         <x:v>Required printing</x:v>
       </x:c>
-      <x:c r="B5" s="12" t="n">
+      <x:c r="B5" s="24" t="n">
         <x:f>IF(ISNUMBER(Print_batches!K8),Print_batches!K8,"Unconfirmed")</x:f>
-        <x:v>1115.3856</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="n">
-        <x:f>IF(ISNUMBER(Print_batches!L8),Print_batches!L8,"Unconfirmed")</x:f>
-        <x:v>35.069504794843574</x:v>
-      </x:c>
+        <x:v>35.06950479484358</x:v>
+      </x:c>
+      <x:c r="C5"/>
       <x:c r="D5" s="2"/>
       <x:c r="E5" s="10" t="str">
-        <x:v>NTD per USD</x:v>
-      </x:c>
-      <x:c r="F5" s="11" t="n">
+        <x:v>Conversion snapshot: NTD per USD</x:v>
+      </x:c>
+      <x:c r="F5" s="20" t="n">
         <x:v>31.805</x:v>
       </x:c>
       <x:c r="G5" s="2"/>
       <x:c r="H5" s="10" t="str">
-        <x:v>2026-10-05 15:13 displayed snapshot: USD spot buy 31.705, sell 31.805. Budget conversion uses sell 31.805, not an October 8 live execution quote.
+        <x:v>Retained budget FX: 1 USD = 31.805 NTD, 2026-10-05 15:13; recorded 2026-10-08. Source quote: NTD 131,250 / 2 boards. Fixed USD inputs; changing this snapshot label does not reprice them.
 https://www.bot.com.tw/tw/personal-banking/foreign-exchange</x:v>
       </x:c>
     </x:row>
@@ -421,20 +518,17 @@
       <x:c r="A6" s="10" t="str">
         <x:v>Required purchases at used quantity</x:v>
       </x:c>
-      <x:c r="B6" s="12" t="n">
-        <x:f>IF(COUNTIFS(Purchase!G5:G30,"Required",Purchase!W5:W30,"OK")=COUNTIF(Purchase!G5:G30,"Required"),SUMIFS(Purchase!N5:N30,Purchase!G5:G30,"Required"),"Unconfirmed")</x:f>
-        <x:v>13133.4052</x:v>
-      </x:c>
-      <x:c r="C6" s="12" t="n">
-        <x:f>IF(COUNTIFS(Purchase!G5:G30,"Required",Purchase!W5:W30,"OK")=COUNTIF(Purchase!G5:G30,"Required"),SUMIFS(Purchase!O5:O30,Purchase!G5:G30,"Required"),"Unconfirmed")</x:f>
+      <x:c r="B6" s="24" t="n">
+        <x:f>IF(COUNTIFS(Purchase!G5:G30,"Required",Purchase!R5:R30,"OK")=COUNTIF(Purchase!G5:G30,"Required"),SUMIFS(Purchase!K5:K30,Purchase!G5:G30,"Required"),"Unconfirmed")</x:f>
         <x:v>412.9352365980192</x:v>
       </x:c>
+      <x:c r="C6"/>
       <x:c r="D6" s="2"/>
       <x:c r="E6" s="10" t="str">
-        <x:v>PCB quote for two NTD</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="n">
-        <x:v>131250</x:v>
+        <x:v>PCB quote for two (USD)</x:v>
+      </x:c>
+      <x:c r="F6" s="19" t="n">
+        <x:v>4126.709636849552</x:v>
       </x:c>
       <x:c r="G6" s="2"/>
       <x:c r="H6" s="2"/>
@@ -443,19 +537,16 @@
       <x:c r="A7" s="15" t="str">
         <x:v>Required budget excluding PCB</x:v>
       </x:c>
-      <x:c r="B7" s="16" t="n">
+      <x:c r="B7" s="26" t="n">
         <x:f>IF(COUNT(B5:B6)=2,SUM(B5:B6),"Unconfirmed")</x:f>
-        <x:v>14248.790799999999</x:v>
-      </x:c>
-      <x:c r="C7" s="16" t="n">
-        <x:f>IF(COUNT(C5:C6)=2,SUM(C5:C6),"Unconfirmed")</x:f>
         <x:v>448.00474139286274</x:v>
       </x:c>
+      <x:c r="C7"/>
       <x:c r="D7" s="2"/>
       <x:c r="E7" s="10" t="str">
         <x:v>Quoted board count</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="n">
+      <x:c r="F7" s="18" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G7" s="2"/>
@@ -465,17 +556,14 @@
       <x:c r="A8" s="10" t="str">
         <x:v>PCB allocation from this quote</x:v>
       </x:c>
-      <x:c r="B8" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER($F$6),$F$6&gt;=0,ISNUMBER($F$7),$F$7&gt;0,ISNUMBER($F$5),$F$5&gt;0),$F$6/$F$7,"Unconfirmed")</x:f>
-        <x:v>65625</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER($F$6),$F$6&gt;=0,ISNUMBER($F$7),$F$7&gt;0,ISNUMBER($F$5),$F$5&gt;0),$F$6/$F$7/$F$5,"Unconfirmed")</x:f>
+      <x:c r="B8" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER($F$6),$F$6&gt;=0,ISNUMBER($F$7),$F$7&gt;0),$F$6/$F$7,"Unconfirmed")</x:f>
         <x:v>2063.354818424776</x:v>
       </x:c>
+      <x:c r="C8"/>
       <x:c r="D8" s="2"/>
       <x:c r="E8" s="10" t="str">
-        <x:v>FX snapshot</x:v>
+        <x:v>FX snapshot date</x:v>
       </x:c>
       <x:c r="F8" s="10" t="str">
         <x:v>2026-10-05 15:13</x:v>
@@ -487,14 +575,11 @@
       <x:c r="A9" s="15" t="str">
         <x:v>Required device budget</x:v>
       </x:c>
-      <x:c r="B9" s="16" t="n">
+      <x:c r="B9" s="26" t="n">
         <x:f>IF(COUNT(B7:B8)=2,SUM(B7:B8),"Unconfirmed")</x:f>
-        <x:v>79873.7908</x:v>
-      </x:c>
-      <x:c r="C9" s="16" t="n">
-        <x:f>IF(COUNT(C7:C8)=2,SUM(C7:C8),"Unconfirmed")</x:f>
         <x:v>2511.359559817639</x:v>
       </x:c>
+      <x:c r="C9"/>
       <x:c r="D9" s="2"/>
       <x:c r="E9" s="2"/>
       <x:c r="F9" s="2"/>
@@ -505,14 +590,11 @@
       <x:c r="A10" s="10" t="str">
         <x:v>Required purchases in whole packs</x:v>
       </x:c>
-      <x:c r="B10" s="12" t="n">
-        <x:f>IF(COUNTIFS(Purchase!G5:G30,"Required",Purchase!W5:W30,"OK")=COUNTIF(Purchase!G5:G30,"Required"),SUMIFS(Purchase!Q5:Q30,Purchase!G5:G30,"Required"),"Unconfirmed")</x:f>
-        <x:v>16300.4507</x:v>
-      </x:c>
-      <x:c r="C10" s="12" t="n">
-        <x:f>IF(COUNTIFS(Purchase!G5:G30,"Required",Purchase!W5:W30,"OK")=COUNTIF(Purchase!G5:G30,"Required"),SUMIFS(Purchase!R5:R30,Purchase!G5:G30,"Required"),"Unconfirmed")</x:f>
+      <x:c r="B10" s="24" t="n">
+        <x:f>IF(COUNTIFS(Purchase!G5:G30,"Required",Purchase!R5:R30,"OK")=COUNTIF(Purchase!G5:G30,"Required"),SUMIFS(Purchase!M5:M30,Purchase!G5:G30,"Required"),"Unconfirmed")</x:f>
         <x:v>512.5122056280459</x:v>
       </x:c>
+      <x:c r="C10"/>
       <x:c r="D10" s="2"/>
       <x:c r="E10" s="2"/>
       <x:c r="F10" s="2"/>
@@ -523,14 +605,11 @@
       <x:c r="A11" s="10" t="str">
         <x:v>Developer equipment budget</x:v>
       </x:c>
-      <x:c r="B11" s="12" t="n">
-        <x:f>IF(COUNTIFS(Purchase!G5:G30,"Developer",Purchase!W5:W30,"OK")=COUNTIF(Purchase!G5:G30,"Developer"),SUMIFS(Purchase!N5:N30,Purchase!G5:G30,"Developer"),"Unconfirmed")</x:f>
-        <x:v>38612.18275</x:v>
-      </x:c>
-      <x:c r="C11" s="12" t="n">
-        <x:f>IF(COUNTIFS(Purchase!G5:G30,"Developer",Purchase!W5:W30,"OK")=COUNTIF(Purchase!G5:G30,"Developer"),SUMIFS(Purchase!O5:O30,Purchase!G5:G30,"Developer"),"Unconfirmed")</x:f>
+      <x:c r="B11" s="24" t="n">
+        <x:f>IF(COUNTIFS(Purchase!G5:G30,"Developer",Purchase!R5:R30,"OK")=COUNTIF(Purchase!G5:G30,"Developer"),SUMIFS(Purchase!K5:K30,Purchase!G5:G30,"Developer"),"Unconfirmed")</x:f>
         <x:v>1214.0286983178744</x:v>
       </x:c>
+      <x:c r="C11"/>
       <x:c r="D11" s="2"/>
       <x:c r="E11" s="10" t="str">
         <x:v>Required: prints, PCB and assembly materials. Developer: external gas delivery, testing and flashing equipment; borrow where possible.</x:v>
@@ -543,14 +622,11 @@
       <x:c r="A12" s="10" t="str">
         <x:v>Developer new-purchase budget</x:v>
       </x:c>
-      <x:c r="B12" s="12" t="n">
-        <x:f>IF(COUNTIFS(Purchase!G5:G30,"Developer",Purchase!W5:W30,"OK")=COUNTIF(Purchase!G5:G30,"Developer"),SUMIFS(Purchase!Q5:Q30,Purchase!G5:G30,"Developer"),"Unconfirmed")</x:f>
-        <x:v>38612.18275</x:v>
-      </x:c>
-      <x:c r="C12" s="12" t="n">
-        <x:f>IF(COUNTIFS(Purchase!G5:G30,"Developer",Purchase!W5:W30,"OK")=COUNTIF(Purchase!G5:G30,"Developer"),SUMIFS(Purchase!R5:R30,Purchase!G5:G30,"Developer"),"Unconfirmed")</x:f>
+      <x:c r="B12" s="24" t="n">
+        <x:f>IF(COUNTIFS(Purchase!G5:G30,"Developer",Purchase!R5:R30,"OK")=COUNTIF(Purchase!G5:G30,"Developer"),SUMIFS(Purchase!M5:M30,Purchase!G5:G30,"Developer"),"Unconfirmed")</x:f>
         <x:v>1214.0286983178744</x:v>
       </x:c>
+      <x:c r="C12"/>
       <x:c r="D12" s="2"/>
       <x:c r="E12" s="2"/>
       <x:c r="F12" s="2"/>
@@ -561,14 +637,11 @@
       <x:c r="A13" s="10" t="str">
         <x:v>Future allowance</x:v>
       </x:c>
-      <x:c r="B13" s="12" t="n">
-        <x:f>IF(COUNTIFS(Purchase!G5:G30,"Future",Purchase!W5:W30,"OK")=COUNTIF(Purchase!G5:G30,"Future"),SUMIFS(Purchase!N5:N30,Purchase!G5:G30,"Future"),"Unconfirmed")</x:f>
-        <x:v>7500</x:v>
-      </x:c>
-      <x:c r="C13" s="12" t="n">
-        <x:f>IF(COUNTIFS(Purchase!G5:G30,"Future",Purchase!W5:W30,"OK")=COUNTIF(Purchase!G5:G30,"Future"),SUMIFS(Purchase!O5:O30,Purchase!G5:G30,"Future"),"Unconfirmed")</x:f>
+      <x:c r="B13" s="24" t="n">
+        <x:f>IF(COUNTIFS(Purchase!G5:G30,"Future",Purchase!R5:R30,"OK")=COUNTIF(Purchase!G5:G30,"Future"),SUMIFS(Purchase!K5:K30,Purchase!G5:G30,"Future"),"Unconfirmed")</x:f>
         <x:v>235.8119792485458</x:v>
       </x:c>
+      <x:c r="C13"/>
       <x:c r="D13" s="2"/>
       <x:c r="E13" s="10" t="str">
         <x:v>L01 gas delivery and L04 flow measurement remain necessary for gas experiments.</x:v>
@@ -581,14 +654,11 @@
       <x:c r="A14" s="10" t="str">
         <x:v>PCB priced-material subtotal</x:v>
       </x:c>
-      <x:c r="B14" s="12" t="n">
-        <x:f>PCB!L68</x:f>
-        <x:v>1954</x:v>
-      </x:c>
-      <x:c r="C14" s="12" t="n">
-        <x:f>PCB!M68</x:f>
+      <x:c r="B14" s="24" t="n">
+        <x:f>PCB!K68</x:f>
         <x:v>61.436880993554496</x:v>
       </x:c>
+      <x:c r="C14"/>
       <x:c r="D14" s="2"/>
       <x:c r="E14" s="2"/>
       <x:c r="F14" s="2"/>
@@ -599,14 +669,11 @@
       <x:c r="A15" s="10" t="str">
         <x:v>PCB unpriced rows</x:v>
       </x:c>
-      <x:c r="B15" s="10" t="n">
+      <x:c r="B15" s="27" t="n">
         <x:f>ROWS(PCB!J5:J65)-COUNT(PCB!J5:J65)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C15" s="10" t="n">
-        <x:f>ROWS(PCB!J5:J65)-COUNT(PCB!J5:J65)</x:f>
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="C15"/>
       <x:c r="D15" s="2"/>
       <x:c r="E15" s="10" t="str">
         <x:v>Future items are excluded from current budgets. PDMS, valves and environment sensing are not integrated.</x:v>
@@ -622,9 +689,7 @@
       <x:c r="B16" s="15" t="str">
         <x:v>Custom filter and other details pending</x:v>
       </x:c>
-      <x:c r="C16" s="15" t="str">
-        <x:v>Custom filter and other details pending</x:v>
-      </x:c>
+      <x:c r="C16"/>
       <x:c r="D16" s="2"/>
       <x:c r="E16" s="2"/>
       <x:c r="F16" s="2"/>
@@ -659,7 +724,7 @@
       <x:c r="C19" s="2"/>
       <x:c r="D19" s="2"/>
       <x:c r="E19" s="10" t="str">
-        <x:v>Device budget includes NTD 12,000 for a custom filter. The 12.5 mm reference filter is too large and too thick.</x:v>
+        <x:v>Device budget includes USD 377.30 for a custom filter. The 12.5 mm reference filter is too large and too thick.</x:v>
       </x:c>
       <x:c r="F19" s="2"/>
       <x:c r="G19" s="2"/>
@@ -703,7 +768,7 @@
       <x:c r="C23" s="2"/>
       <x:c r="D23" s="2"/>
       <x:c r="E23" s="10" t="str">
-        <x:v>PCB quote: NTD 131,250 for two including design/setup. NTD 65,625 is an allocation, not production pricing. Do not add component costs again.</x:v>
+        <x:v>PCB quote: USD 4,126.71 for two including design/setup. USD 2,063.35 is an allocation, not production pricing. Do not add component costs again.</x:v>
       </x:c>
       <x:c r="F23" s="2"/>
       <x:c r="G23" s="2"/>
@@ -752,34 +817,38 @@
       <x:c r="H27" s="2"/>
     </x:row>
     <x:row r="28" ht="28" customHeight="1">
-      <x:c r="A28" s="2"/>
-      <x:c r="B28" s="2"/>
-      <x:c r="C28" s="2"/>
-      <x:c r="D28" s="2"/>
-      <x:c r="E28" s="2"/>
-      <x:c r="F28" s="2"/>
-      <x:c r="G28" s="2"/>
-      <x:c r="H28" s="2"/>
+      <x:c r="A28" s="10" t="str">
+        <x:v>USD values retain full precision; displayed cents are rounded only for reading.</x:v>
+      </x:c>
+      <x:c r="B28" s="10"/>
+      <x:c r="C28" s="10"/>
+      <x:c r="D28" s="10"/>
+      <x:c r="E28" s="10"/>
+      <x:c r="F28" s="10"/>
+      <x:c r="G28" s="10"/>
+      <x:c r="H28" s="10"/>
     </x:row>
     <x:row r="29" ht="28" customHeight="1">
-      <x:c r="A29" s="2"/>
-      <x:c r="B29" s="2"/>
-      <x:c r="C29" s="2"/>
-      <x:c r="D29" s="2"/>
-      <x:c r="E29" s="2"/>
-      <x:c r="F29" s="2"/>
-      <x:c r="G29" s="2"/>
-      <x:c r="H29" s="2"/>
+      <x:c r="A29" s="10"/>
+      <x:c r="B29" s="10"/>
+      <x:c r="C29" s="10"/>
+      <x:c r="D29" s="10"/>
+      <x:c r="E29" s="10"/>
+      <x:c r="F29" s="10"/>
+      <x:c r="G29" s="10"/>
+      <x:c r="H29" s="10"/>
     </x:row>
     <x:row r="30" ht="28" customHeight="1">
-      <x:c r="A30" s="2"/>
-      <x:c r="B30" s="2"/>
-      <x:c r="C30" s="2"/>
-      <x:c r="D30" s="2"/>
-      <x:c r="E30" s="2"/>
-      <x:c r="F30" s="2"/>
-      <x:c r="G30" s="2"/>
-      <x:c r="H30" s="2"/>
+      <x:c r="A30" s="10" t="str">
+        <x:v>New FX basis: reprice USD input cells directly. The FX snapshot label does not recalculate costs; see Notes.</x:v>
+      </x:c>
+      <x:c r="B30" s="10"/>
+      <x:c r="C30" s="10"/>
+      <x:c r="D30" s="10"/>
+      <x:c r="E30" s="10"/>
+      <x:c r="F30" s="10"/>
+      <x:c r="G30" s="10"/>
+      <x:c r="H30" s="10"/>
     </x:row>
     <x:row r="31" ht="28" customHeight="1">
       <x:c r="A31" s="2"/>
@@ -1691,6 +1760,8 @@
     <x:mergeCell ref="E21:H21"/>
     <x:mergeCell ref="E23:H23"/>
     <x:mergeCell ref="E25:H25"/>
+    <x:mergeCell ref="A28:H28"/>
+    <x:mergeCell ref="A30:H30"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -3628,17 +3699,17 @@
     <x:col min="5" max="5" width="8" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="9" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="19" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="12" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="12" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="13" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="16" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="13" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="15" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="16" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="15" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="16" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="16" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="20" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="4" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="58" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="60" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="18" hidden="0" customWidth="1"/>
     <x:col min="19" max="19" width="20" hidden="0" customWidth="1"/>
     <x:col min="20" max="20" width="4" hidden="0" customWidth="1"/>
     <x:col min="21" max="21" width="58" hidden="0" customWidth="1"/>
@@ -3700,7 +3771,7 @@
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
       <x:c r="A3" s="4" t="str">
-        <x:v>Yellow inputs are editable. Owned quantities can include borrowed items.</x:v>
+        <x:v>All prices in USD. Yellow inputs are editable; Owned qty can include borrowed items.</x:v>
       </x:c>
       <x:c r="B3" s="2"/>
       <x:c r="C3" s="2"/>
@@ -3726,73 +3797,63 @@
       <x:c r="W3" s="2"/>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
-      <x:c r="A4" s="8" t="str">
+      <x:c r="A4" s="23" t="str">
         <x:v>ID</x:v>
       </x:c>
-      <x:c r="B4" s="8" t="str">
+      <x:c r="B4" s="23" t="str">
         <x:v>Name</x:v>
       </x:c>
-      <x:c r="C4" s="8" t="str">
+      <x:c r="C4" s="23" t="str">
         <x:v>Specification</x:v>
       </x:c>
-      <x:c r="D4" s="8" t="str">
+      <x:c r="D4" s="23" t="str">
         <x:v>Purpose and location</x:v>
       </x:c>
-      <x:c r="E4" s="8" t="str">
+      <x:c r="E4" s="23" t="str">
         <x:v>Qty</x:v>
       </x:c>
-      <x:c r="F4" s="8" t="str">
+      <x:c r="F4" s="23" t="str">
         <x:v>Unit</x:v>
       </x:c>
-      <x:c r="G4" s="8" t="str">
+      <x:c r="G4" s="23" t="str">
         <x:v>Class</x:v>
       </x:c>
-      <x:c r="H4" s="8" t="str">
-        <x:v>Source unit price</x:v>
-      </x:c>
-      <x:c r="I4" s="8" t="str">
-        <x:v>Currency</x:v>
-      </x:c>
-      <x:c r="J4" s="8" t="str">
+      <x:c r="H4" s="23" t="str">
+        <x:v>Unit USD</x:v>
+      </x:c>
+      <x:c r="I4" s="23" t="str">
         <x:v>Pack units</x:v>
       </x:c>
-      <x:c r="K4" s="8" t="str">
+      <x:c r="J4" s="23" t="str">
         <x:v>Owned qty</x:v>
       </x:c>
-      <x:c r="L4" s="8" t="str">
-        <x:v>Unit NTD</x:v>
-      </x:c>
-      <x:c r="M4" s="8" t="str">
-        <x:v>Unit USD</x:v>
-      </x:c>
-      <x:c r="N4" s="8" t="str">
-        <x:v>Used NTD</x:v>
-      </x:c>
-      <x:c r="O4" s="8" t="str">
+      <x:c r="K4" s="23" t="str">
         <x:v>Used USD</x:v>
       </x:c>
-      <x:c r="P4" s="8" t="str">
+      <x:c r="L4" s="23" t="str">
         <x:v>Packs to buy</x:v>
       </x:c>
-      <x:c r="Q4" s="8" t="str">
-        <x:v>New NTD</x:v>
-      </x:c>
-      <x:c r="R4" s="8" t="str">
+      <x:c r="M4" s="23" t="str">
         <x:v>New USD</x:v>
       </x:c>
-      <x:c r="S4" s="8" t="str">
+      <x:c r="N4" s="23" t="str">
         <x:v>Price type</x:v>
       </x:c>
-      <x:c r="T4" s="8" t="str"/>
-      <x:c r="U4" s="8" t="str">
+      <x:c r="O4" s="23" t="str"/>
+      <x:c r="P4" s="23" t="str">
         <x:v>Compatibility limits</x:v>
       </x:c>
-      <x:c r="V4" s="8" t="str">
-        <x:v>Price sources</x:v>
-      </x:c>
-      <x:c r="W4" s="8" t="str">
+      <x:c r="Q4" s="23" t="str">
+        <x:v>Price sources / original quotations</x:v>
+      </x:c>
+      <x:c r="R4" s="23" t="str">
         <x:v>Calculation state</x:v>
       </x:c>
+      <x:c r="S4"/>
+      <x:c r="T4"/>
+      <x:c r="U4"/>
+      <x:c r="V4"/>
+      <x:c r="W4"/>
     </x:row>
     <x:row r="5" ht="108" customHeight="1">
       <x:c r="A5" s="10" t="str">
@@ -3817,64 +3878,51 @@
       <x:c r="G5" s="10" t="str">
         <x:v>Required</x:v>
       </x:c>
-      <x:c r="H5" s="14" t="n">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="I5" s="11" t="str">
-        <x:v>NTD</x:v>
-      </x:c>
-      <x:c r="J5" s="11" t="n">
+      <x:c r="H5" s="19" t="n">
+        <x:v>5.062097154535451</x:v>
+      </x:c>
+      <x:c r="I5" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K5" s="11" t="n">
+      <x:c r="J5" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L5" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H5),H5&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I5="NTD",I5="USD")),IF(I5="USD",H5*Summary!$F$5,H5),"")</x:f>
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="M5" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H5),H5&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I5="NTD",I5="USD")),IF(I5="USD",H5,H5/Summary!$F$5),"")</x:f>
+      <x:c r="K5" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(E5),E5&gt;=0,ISNUMBER(H5),H5&gt;=0),E5*H5,"")</x:f>
         <x:v>5.062097154535451</x:v>
       </x:c>
-      <x:c r="N5" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E5),E5&gt;=0,ISNUMBER(L5)),E5*L5,"")</x:f>
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="O5" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E5),E5&gt;=0,ISNUMBER(M5)),E5*M5,"")</x:f>
+      <x:c r="L5" s="10" t="n">
+        <x:f>IF(AND(ISNUMBER(E5),E5&gt;=0,ISNUMBER(I5),I5&gt;0,ISNUMBER(J5),J5&gt;=0),ROUNDUP(MAX(0,E5-J5)/I5,0),"")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M5" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(L5),ISNUMBER(H5),H5&gt;=0),L5*I5*H5,"")</x:f>
         <x:v>5.062097154535451</x:v>
       </x:c>
-      <x:c r="P5" s="10" t="n">
-        <x:f>IF(AND(ISNUMBER(E5),E5&gt;=0,ISNUMBER(J5),J5&gt;0,ISNUMBER(K5),K5&gt;=0),ROUNDUP(MAX(0,E5-K5)/J5,0),"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q5" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P5),ISNUMBER(L5)),P5*J5*L5,"")</x:f>
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="R5" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P5),ISNUMBER(M5)),P5*J5*M5,"")</x:f>
-        <x:v>5.062097154535451</x:v>
-      </x:c>
-      <x:c r="S5" s="10" t="str">
+      <x:c r="N5" s="10" t="str">
         <x:v>Listed</x:v>
       </x:c>
-      <x:c r="T5" s="10" t="str"/>
-      <x:c r="U5" s="10" t="str">
+      <x:c r="O5" s="10" t="str"/>
+      <x:c r="P5" s="10" t="str">
         <x:v>Cradle opening40.6 mm; candidate frame40±0.5 leaves only0.05 mm/side at maximum size before print error. Measure frame/pitch/thickness/wires. Vendor must approve5 V connection and startup-current margin; battery-mode5 V capability is unverified. Never use GPIO or an arbitrary3.3 V rail.</x:v>
       </x:c>
-      <x:c r="V5" s="10" t="str">
+      <x:c r="Q5" s="10" t="str">
         <x:v>FAN
+Original unit input: NTD 161. Converted at 31.805 NTD/USD.
 NTD 161 at quantity 1. Listed out of stock. Shipping and local tax not added.
 https://www.digikey.tw/en/products/detail/sunon-fans/MF40100V1-1000U-A99/6198732</x:v>
       </x:c>
-      <x:c r="W5" s="10" t="str">
-        <x:f>IF(AND(ISNUMBER(N5),ISNUMBER(Q5)),"OK","Missing")</x:f>
+      <x:c r="R5" s="10" t="str">
+        <x:f>IF(AND(ISNUMBER(K5),ISNUMBER(M5)),"OK","Missing")</x:f>
         <x:v>OK</x:v>
       </x:c>
-    </x:row>
-    <x:row r="6" ht="123" customHeight="1">
+      <x:c r="S5"/>
+      <x:c r="T5"/>
+      <x:c r="U5"/>
+      <x:c r="V5"/>
+      <x:c r="W5"/>
+    </x:row>
+    <x:row r="6" ht="138" customHeight="1">
       <x:c r="A6" s="10" t="str">
         <x:v>H01</x:v>
       </x:c>
@@ -3897,64 +3945,51 @@
       <x:c r="G6" s="10" t="str">
         <x:v>Required</x:v>
       </x:c>
-      <x:c r="H6" s="14" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="I6" s="11" t="str">
-        <x:v>NTD</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
+      <x:c r="H6" s="19" t="n">
+        <x:v>0.09432479169941833</x:v>
+      </x:c>
+      <x:c r="I6" s="18" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="K6" s="11" t="n">
+      <x:c r="J6" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L6" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H6),H6&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I6="NTD",I6="USD")),IF(I6="USD",H6*Summary!$F$5,H6),"")</x:f>
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="M6" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H6),H6&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I6="NTD",I6="USD")),IF(I6="USD",H6,H6/Summary!$F$5),"")</x:f>
-        <x:v>0.09432479169941833</x:v>
-      </x:c>
-      <x:c r="N6" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E6),E6&gt;=0,ISNUMBER(L6)),E6*L6,"")</x:f>
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="O6" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E6),E6&gt;=0,ISNUMBER(M6)),E6*M6,"")</x:f>
+      <x:c r="K6" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(E6),E6&gt;=0,ISNUMBER(H6),H6&gt;=0),E6*H6,"")</x:f>
         <x:v>0.37729916679767334</x:v>
       </x:c>
-      <x:c r="P6" s="10" t="n">
-        <x:f>IF(AND(ISNUMBER(E6),E6&gt;=0,ISNUMBER(J6),J6&gt;0,ISNUMBER(K6),K6&gt;=0),ROUNDUP(MAX(0,E6-K6)/J6,0),"")</x:f>
+      <x:c r="L6" s="10" t="n">
+        <x:f>IF(AND(ISNUMBER(E6),E6&gt;=0,ISNUMBER(I6),I6&gt;0,ISNUMBER(J6),J6&gt;=0),ROUNDUP(MAX(0,E6-J6)/I6,0),"")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Q6" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P6),ISNUMBER(L6)),P6*J6*L6,"")</x:f>
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="R6" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P6),ISNUMBER(M6)),P6*J6*M6,"")</x:f>
+      <x:c r="M6" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(L6),ISNUMBER(H6),H6&gt;=0),L6*I6*H6,"")</x:f>
         <x:v>1.8864958339883666</x:v>
       </x:c>
-      <x:c r="S6" s="10" t="str">
+      <x:c r="N6" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="T6" s="10" t="str"/>
-      <x:c r="U6" s="10" t="str">
+      <x:c r="O6" s="10" t="str"/>
+      <x:c r="P6" s="10" t="str">
         <x:v>With0.5 mm washer, nominal under-headZ40.1/tipZ32.1; nut pocketZ33.5–36.2. Verify actual PCB hole, copper keep-out and head clearance. No validated tightening torque for the resin; screw material/finish remain to be specified.</x:v>
       </x:c>
-      <x:c r="V6" s="10" t="str">
+      <x:c r="Q6" s="10" t="str">
         <x:v>FASTENER
+Original unit input: NTD 3. Converted at 31.805 NTD/USD.
 Listing shows small M3 fasteners around NTD 3 individually. Listed flat-head type is NOT the specified socket cap. Budget allowances 3/4/6 NTD for M3x8/16/35 cap screws, 2 for nuts and 1 for washers; local exact-type prices unverified.
 https://www.ruten.com.tw/item/21306183365097/</x:v>
       </x:c>
-      <x:c r="W6" s="10" t="str">
-        <x:f>IF(AND(ISNUMBER(N6),ISNUMBER(Q6)),"OK","Missing")</x:f>
+      <x:c r="R6" s="10" t="str">
+        <x:f>IF(AND(ISNUMBER(K6),ISNUMBER(M6)),"OK","Missing")</x:f>
         <x:v>OK</x:v>
       </x:c>
-    </x:row>
-    <x:row r="7" ht="123" customHeight="1">
+      <x:c r="S6"/>
+      <x:c r="T6"/>
+      <x:c r="U6"/>
+      <x:c r="V6"/>
+      <x:c r="W6"/>
+    </x:row>
+    <x:row r="7" ht="138" customHeight="1">
       <x:c r="A7" s="10" t="str">
         <x:v>H02</x:v>
       </x:c>
@@ -3977,64 +4012,51 @@
       <x:c r="G7" s="10" t="str">
         <x:v>Required</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="I7" s="11" t="str">
-        <x:v>NTD</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="n">
+      <x:c r="H7" s="19" t="n">
+        <x:v>0.1257663889325578</x:v>
+      </x:c>
+      <x:c r="I7" s="18" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="n">
+      <x:c r="J7" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L7" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H7),H7&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I7="NTD",I7="USD")),IF(I7="USD",H7*Summary!$F$5,H7),"")</x:f>
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="M7" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H7),H7&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I7="NTD",I7="USD")),IF(I7="USD",H7,H7/Summary!$F$5),"")</x:f>
-        <x:v>0.1257663889325578</x:v>
-      </x:c>
-      <x:c r="N7" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E7),E7&gt;=0,ISNUMBER(L7)),E7*L7,"")</x:f>
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="O7" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E7),E7&gt;=0,ISNUMBER(M7)),E7*M7,"")</x:f>
+      <x:c r="K7" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(E7),E7&gt;=0,ISNUMBER(H7),H7&gt;=0),E7*H7,"")</x:f>
         <x:v>0.2515327778651156</x:v>
       </x:c>
-      <x:c r="P7" s="10" t="n">
-        <x:f>IF(AND(ISNUMBER(E7),E7&gt;=0,ISNUMBER(J7),J7&gt;0,ISNUMBER(K7),K7&gt;=0),ROUNDUP(MAX(0,E7-K7)/J7,0),"")</x:f>
+      <x:c r="L7" s="10" t="n">
+        <x:f>IF(AND(ISNUMBER(E7),E7&gt;=0,ISNUMBER(I7),I7&gt;0,ISNUMBER(J7),J7&gt;=0),ROUNDUP(MAX(0,E7-J7)/I7,0),"")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Q7" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P7),ISNUMBER(L7)),P7*J7*L7,"")</x:f>
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="R7" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P7),ISNUMBER(M7)),P7*J7*M7,"")</x:f>
+      <x:c r="M7" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(L7),ISNUMBER(H7),H7&gt;=0),L7*I7*H7,"")</x:f>
         <x:v>2.5153277786511556</x:v>
       </x:c>
-      <x:c r="S7" s="10" t="str">
+      <x:c r="N7" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="T7" s="10" t="str"/>
-      <x:c r="U7" s="10" t="str">
+      <x:c r="O7" s="10" t="str"/>
+      <x:c r="P7" s="10" t="str">
         <x:v>For nominal10 mm fan plus0.5 mm washer, under-headZ16.5/tipZ0.5; nut pocketZ0.3–3. Confirm real tolerances: tip must remain above foot planeZ0 and engage the nut. No validated tightening torque for the resin; screw material/finish remain to be specified.</x:v>
       </x:c>
-      <x:c r="V7" s="10" t="str">
+      <x:c r="Q7" s="10" t="str">
         <x:v>FASTENER
+Original unit input: NTD 4. Converted at 31.805 NTD/USD.
 Listing shows small M3 fasteners around NTD 3 individually. Listed flat-head type is NOT the specified socket cap. Budget allowances 3/4/6 NTD for M3x8/16/35 cap screws, 2 for nuts and 1 for washers; local exact-type prices unverified.
 https://www.ruten.com.tw/item/21306183365097/</x:v>
       </x:c>
-      <x:c r="W7" s="10" t="str">
-        <x:f>IF(AND(ISNUMBER(N7),ISNUMBER(Q7)),"OK","Missing")</x:f>
+      <x:c r="R7" s="10" t="str">
+        <x:f>IF(AND(ISNUMBER(K7),ISNUMBER(M7)),"OK","Missing")</x:f>
         <x:v>OK</x:v>
       </x:c>
-    </x:row>
-    <x:row r="8" ht="123" customHeight="1">
+      <x:c r="S7"/>
+      <x:c r="T7"/>
+      <x:c r="U7"/>
+      <x:c r="V7"/>
+      <x:c r="W7"/>
+    </x:row>
+    <x:row r="8" ht="138" customHeight="1">
       <x:c r="A8" s="10" t="str">
         <x:v>H03</x:v>
       </x:c>
@@ -4057,64 +4079,51 @@
       <x:c r="G8" s="10" t="str">
         <x:v>Required</x:v>
       </x:c>
-      <x:c r="H8" s="14" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="I8" s="11" t="str">
-        <x:v>NTD</x:v>
-      </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="H8" s="19" t="n">
+        <x:v>0.18864958339883667</x:v>
+      </x:c>
+      <x:c r="I8" s="18" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K8" s="11" t="n">
+      <x:c r="J8" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L8" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H8),H8&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I8="NTD",I8="USD")),IF(I8="USD",H8*Summary!$F$5,H8),"")</x:f>
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="M8" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H8),H8&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I8="NTD",I8="USD")),IF(I8="USD",H8,H8/Summary!$F$5),"")</x:f>
-        <x:v>0.18864958339883667</x:v>
-      </x:c>
-      <x:c r="N8" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E8),E8&gt;=0,ISNUMBER(L8)),E8*L8,"")</x:f>
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="O8" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E8),E8&gt;=0,ISNUMBER(M8)),E8*M8,"")</x:f>
+      <x:c r="K8" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(E8),E8&gt;=0,ISNUMBER(H8),H8&gt;=0),E8*H8,"")</x:f>
         <x:v>0.37729916679767334</x:v>
       </x:c>
-      <x:c r="P8" s="10" t="n">
-        <x:f>IF(AND(ISNUMBER(E8),E8&gt;=0,ISNUMBER(J8),J8&gt;0,ISNUMBER(K8),K8&gt;=0),ROUNDUP(MAX(0,E8-K8)/J8,0),"")</x:f>
+      <x:c r="L8" s="10" t="n">
+        <x:f>IF(AND(ISNUMBER(E8),E8&gt;=0,ISNUMBER(I8),I8&gt;0,ISNUMBER(J8),J8&gt;=0),ROUNDUP(MAX(0,E8-J8)/I8,0),"")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Q8" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P8),ISNUMBER(L8)),P8*J8*L8,"")</x:f>
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="R8" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P8),ISNUMBER(M8)),P8*J8*M8,"")</x:f>
+      <x:c r="M8" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(L8),ISNUMBER(H8),H8&gt;=0),L8*I8*H8,"")</x:f>
         <x:v>1.8864958339883666</x:v>
       </x:c>
-      <x:c r="S8" s="10" t="str">
+      <x:c r="N8" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="T8" s="10" t="str"/>
-      <x:c r="U8" s="10" t="str">
+      <x:c r="O8" s="10" t="str"/>
+      <x:c r="P8" s="10" t="str">
         <x:v>Existing stack without extra washer: under-headZ66/tipZ31; nut pocketZ33.2–35.9. Head projects beyond66-mm body height. Verify supplier thread length and physical stop; do not over-tighten to force sealing. No validated tightening torque for the resin; screw material/finish remain to be specified.</x:v>
       </x:c>
-      <x:c r="V8" s="10" t="str">
+      <x:c r="Q8" s="10" t="str">
         <x:v>FASTENER
+Original unit input: NTD 6. Converted at 31.805 NTD/USD.
 Listing shows small M3 fasteners around NTD 3 individually. Listed flat-head type is NOT the specified socket cap. Budget allowances 3/4/6 NTD for M3x8/16/35 cap screws, 2 for nuts and 1 for washers; local exact-type prices unverified.
 https://www.ruten.com.tw/item/21306183365097/</x:v>
       </x:c>
-      <x:c r="W8" s="10" t="str">
-        <x:f>IF(AND(ISNUMBER(N8),ISNUMBER(Q8)),"OK","Missing")</x:f>
+      <x:c r="R8" s="10" t="str">
+        <x:f>IF(AND(ISNUMBER(K8),ISNUMBER(M8)),"OK","Missing")</x:f>
         <x:v>OK</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9" ht="123" customHeight="1">
+      <x:c r="S8"/>
+      <x:c r="T8"/>
+      <x:c r="U8"/>
+      <x:c r="V8"/>
+      <x:c r="W8"/>
+    </x:row>
+    <x:row r="9" ht="138" customHeight="1">
       <x:c r="A9" s="10" t="str">
         <x:v>H04</x:v>
       </x:c>
@@ -4137,64 +4146,51 @@
       <x:c r="G9" s="10" t="str">
         <x:v>Required</x:v>
       </x:c>
-      <x:c r="H9" s="14" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I9" s="11" t="str">
-        <x:v>NTD</x:v>
-      </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="H9" s="19" t="n">
+        <x:v>0.0628831944662789</x:v>
+      </x:c>
+      <x:c r="I9" s="18" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="K9" s="11" t="n">
+      <x:c r="J9" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L9" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H9),H9&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I9="NTD",I9="USD")),IF(I9="USD",H9*Summary!$F$5,H9),"")</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M9" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H9),H9&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I9="NTD",I9="USD")),IF(I9="USD",H9,H9/Summary!$F$5),"")</x:f>
-        <x:v>0.0628831944662789</x:v>
-      </x:c>
-      <x:c r="N9" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E9),E9&gt;=0,ISNUMBER(L9)),E9*L9,"")</x:f>
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="O9" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E9),E9&gt;=0,ISNUMBER(M9)),E9*M9,"")</x:f>
+      <x:c r="K9" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(E9),E9&gt;=0,ISNUMBER(H9),H9&gt;=0),E9*H9,"")</x:f>
         <x:v>0.5030655557302312</x:v>
       </x:c>
-      <x:c r="P9" s="10" t="n">
-        <x:f>IF(AND(ISNUMBER(E9),E9&gt;=0,ISNUMBER(J9),J9&gt;0,ISNUMBER(K9),K9&gt;=0),ROUNDUP(MAX(0,E9-K9)/J9,0),"")</x:f>
+      <x:c r="L9" s="10" t="n">
+        <x:f>IF(AND(ISNUMBER(E9),E9&gt;=0,ISNUMBER(I9),I9&gt;0,ISNUMBER(J9),J9&gt;=0),ROUNDUP(MAX(0,E9-J9)/I9,0),"")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Q9" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P9),ISNUMBER(L9)),P9*J9*L9,"")</x:f>
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="R9" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P9),ISNUMBER(M9)),P9*J9*M9,"")</x:f>
+      <x:c r="M9" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(L9),ISNUMBER(H9),H9&gt;=0),L9*I9*H9,"")</x:f>
         <x:v>1.2576638893255778</x:v>
       </x:c>
-      <x:c r="S9" s="10" t="str">
+      <x:c r="N9" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="T9" s="10" t="str"/>
-      <x:c r="U9" s="10" t="str">
+      <x:c r="O9" s="10" t="str"/>
+      <x:c r="P9" s="10" t="str">
         <x:v>CAD hex circumradius3.3 gives5.716 mm across flats; pocket height 2.7. Relative to5.5×2.4 nut, total width allowance0.216 and height 0.3 mm; test printed pockets. Match material/finish to screws; do not force or substitute self-tapping.</x:v>
       </x:c>
-      <x:c r="V9" s="10" t="str">
+      <x:c r="Q9" s="10" t="str">
         <x:v>FASTENER
+Original unit input: NTD 2. Converted at 31.805 NTD/USD.
 Listing shows small M3 fasteners around NTD 3 individually. Listed flat-head type is NOT the specified socket cap. Budget allowances 3/4/6 NTD for M3x8/16/35 cap screws, 2 for nuts and 1 for washers; local exact-type prices unverified.
 https://www.ruten.com.tw/item/21306183365097/</x:v>
       </x:c>
-      <x:c r="W9" s="10" t="str">
-        <x:f>IF(AND(ISNUMBER(N9),ISNUMBER(Q9)),"OK","Missing")</x:f>
+      <x:c r="R9" s="10" t="str">
+        <x:f>IF(AND(ISNUMBER(K9),ISNUMBER(M9)),"OK","Missing")</x:f>
         <x:v>OK</x:v>
       </x:c>
-    </x:row>
-    <x:row r="10" ht="123" customHeight="1">
+      <x:c r="S9"/>
+      <x:c r="T9"/>
+      <x:c r="U9"/>
+      <x:c r="V9"/>
+      <x:c r="W9"/>
+    </x:row>
+    <x:row r="10" ht="138" customHeight="1">
       <x:c r="A10" s="10" t="str">
         <x:v>H05</x:v>
       </x:c>
@@ -4217,64 +4213,51 @@
       <x:c r="G10" s="10" t="str">
         <x:v>Required</x:v>
       </x:c>
-      <x:c r="H10" s="14" t="n">
+      <x:c r="H10" s="19" t="n">
+        <x:v>0.03144159723313945</x:v>
+      </x:c>
+      <x:c r="I10" s="18" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J10" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K10" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(E10),E10&gt;=0,ISNUMBER(H10),H10&gt;=0),E10*H10,"")</x:f>
+        <x:v>0.1886495833988367</x:v>
+      </x:c>
+      <x:c r="L10" s="10" t="n">
+        <x:f>IF(AND(ISNUMBER(E10),E10&gt;=0,ISNUMBER(I10),I10&gt;0,ISNUMBER(J10),J10&gt;=0),ROUNDUP(MAX(0,E10-J10)/I10,0),"")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I10" s="11" t="str">
-        <x:v>NTD</x:v>
-      </x:c>
-      <x:c r="J10" s="11" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="K10" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L10" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H10),H10&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I10="NTD",I10="USD")),IF(I10="USD",H10*Summary!$F$5,H10),"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M10" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H10),H10&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I10="NTD",I10="USD")),IF(I10="USD",H10,H10/Summary!$F$5),"")</x:f>
-        <x:v>0.03144159723313945</x:v>
-      </x:c>
-      <x:c r="N10" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E10),E10&gt;=0,ISNUMBER(L10)),E10*L10,"")</x:f>
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="O10" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E10),E10&gt;=0,ISNUMBER(M10)),E10*M10,"")</x:f>
-        <x:v>0.1886495833988367</x:v>
-      </x:c>
-      <x:c r="P10" s="10" t="n">
-        <x:f>IF(AND(ISNUMBER(E10),E10&gt;=0,ISNUMBER(J10),J10&gt;0,ISNUMBER(K10),K10&gt;=0),ROUNDUP(MAX(0,E10-K10)/J10,0),"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q10" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P10),ISNUMBER(L10)),P10*J10*L10,"")</x:f>
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="R10" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P10),ISNUMBER(M10)),P10*J10*M10,"")</x:f>
+      <x:c r="M10" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(L10),ISNUMBER(H10),H10&gt;=0),L10*I10*H10,"")</x:f>
         <x:v>0.6288319446627889</x:v>
       </x:c>
-      <x:c r="S10" s="10" t="str">
+      <x:c r="N10" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="T10" s="10" t="str"/>
-      <x:c r="U10" s="10" t="str">
+      <x:c r="O10" s="10" t="str"/>
+      <x:c r="P10" s="10" t="str">
         <x:v>OD7 mm is a procurement reference; PCB copper keep-out remains unverified. Metal must not touch exposed copper. Conductive versus insulating material requires vendor approval; insulating washers also need creep/thickness checks. A thicker substitute changes the screw stack.</x:v>
       </x:c>
-      <x:c r="V10" s="10" t="str">
+      <x:c r="Q10" s="10" t="str">
         <x:v>FASTENER
+Original unit input: NTD 1. Converted at 31.805 NTD/USD.
 Listing shows small M3 fasteners around NTD 3 individually. Listed flat-head type is NOT the specified socket cap. Budget allowances 3/4/6 NTD for M3x8/16/35 cap screws, 2 for nuts and 1 for washers; local exact-type prices unverified.
 https://www.ruten.com.tw/item/21306183365097/</x:v>
       </x:c>
-      <x:c r="W10" s="10" t="str">
-        <x:f>IF(AND(ISNUMBER(N10),ISNUMBER(Q10)),"OK","Missing")</x:f>
+      <x:c r="R10" s="10" t="str">
+        <x:f>IF(AND(ISNUMBER(K10),ISNUMBER(M10)),"OK","Missing")</x:f>
         <x:v>OK</x:v>
       </x:c>
-    </x:row>
-    <x:row r="11" ht="123" customHeight="1">
+      <x:c r="S10"/>
+      <x:c r="T10"/>
+      <x:c r="U10"/>
+      <x:c r="V10"/>
+      <x:c r="W10"/>
+    </x:row>
+    <x:row r="11" ht="138" customHeight="1">
       <x:c r="A11" s="10" t="str">
         <x:v>E01</x:v>
       </x:c>
@@ -4297,64 +4280,51 @@
       <x:c r="G11" s="10" t="str">
         <x:v>Required</x:v>
       </x:c>
-      <x:c r="H11" s="14" t="n">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="I11" s="11" t="str">
-        <x:v>NTD</x:v>
-      </x:c>
-      <x:c r="J11" s="11" t="n">
+      <x:c r="H11" s="19" t="n">
+        <x:v>2.5153277786511556</x:v>
+      </x:c>
+      <x:c r="I11" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K11" s="11" t="n">
+      <x:c r="J11" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L11" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H11),H11&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I11="NTD",I11="USD")),IF(I11="USD",H11*Summary!$F$5,H11),"")</x:f>
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="M11" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H11),H11&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I11="NTD",I11="USD")),IF(I11="USD",H11,H11/Summary!$F$5),"")</x:f>
+      <x:c r="K11" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(E11),E11&gt;=0,ISNUMBER(H11),H11&gt;=0),E11*H11,"")</x:f>
         <x:v>2.5153277786511556</x:v>
       </x:c>
-      <x:c r="N11" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E11),E11&gt;=0,ISNUMBER(L11)),E11*L11,"")</x:f>
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="O11" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E11),E11&gt;=0,ISNUMBER(M11)),E11*M11,"")</x:f>
+      <x:c r="L11" s="10" t="n">
+        <x:f>IF(AND(ISNUMBER(E11),E11&gt;=0,ISNUMBER(I11),I11&gt;0,ISNUMBER(J11),J11&gt;=0),ROUNDUP(MAX(0,E11-J11)/I11,0),"")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M11" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(L11),ISNUMBER(H11),H11&gt;=0),L11*I11*H11,"")</x:f>
         <x:v>2.5153277786511556</x:v>
       </x:c>
-      <x:c r="P11" s="10" t="n">
-        <x:f>IF(AND(ISNUMBER(E11),E11&gt;=0,ISNUMBER(J11),J11&gt;0,ISNUMBER(K11),K11&gt;=0),ROUNDUP(MAX(0,E11-K11)/J11,0),"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q11" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P11),ISNUMBER(L11)),P11*J11*L11,"")</x:f>
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="R11" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P11),ISNUMBER(M11)),P11*J11*M11,"")</x:f>
-        <x:v>2.5153277786511556</x:v>
-      </x:c>
-      <x:c r="S11" s="10" t="str">
+      <x:c r="N11" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="T11" s="10" t="str"/>
-      <x:c r="U11" s="10" t="str">
+      <x:c r="O11" s="10" t="str"/>
+      <x:c r="P11" s="10" t="str">
         <x:v>Use only vendor-approved5 V/GND. A TPS61023 boost architecture is drawn, but missing passives/current margin prevent a battery-mode5 V claim. Do not connect to GPIO/arbitrary3.3 V. No added boost module is specified.</x:v>
       </x:c>
-      <x:c r="V11" s="10" t="str">
+      <x:c r="Q11" s="10" t="str">
         <x:v>TOOLS
+Original unit input: NTD 80. Converted at 31.805 NTD/USD.
 Engineering allowances only: hand tools/calipers NTD 1500; DMM 800; scope 10000; pipette/tips 4000; print/post-cure supplies 300. Borrow existing printer, wash/cure equipment, PC, phone, biosafety/cell facilities. Their capital replacement prices are outside this BOM.
 </x:v>
       </x:c>
-      <x:c r="W11" s="10" t="str">
-        <x:f>IF(AND(ISNUMBER(N11),ISNUMBER(Q11)),"OK","Missing")</x:f>
+      <x:c r="R11" s="10" t="str">
+        <x:f>IF(AND(ISNUMBER(K11),ISNUMBER(M11)),"OK","Missing")</x:f>
         <x:v>OK</x:v>
       </x:c>
-    </x:row>
-    <x:row r="12" ht="108" customHeight="1">
+      <x:c r="S11"/>
+      <x:c r="T11"/>
+      <x:c r="U11"/>
+      <x:c r="V11"/>
+      <x:c r="W11"/>
+    </x:row>
+    <x:row r="12" ht="123" customHeight="1">
       <x:c r="A12" s="10" t="str">
         <x:v>S01</x:v>
       </x:c>
@@ -4377,62 +4347,49 @@
       <x:c r="G12" s="10" t="str">
         <x:v>Required</x:v>
       </x:c>
-      <x:c r="H12" s="14" t="n">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="I12" s="11" t="str">
-        <x:v>NTD</x:v>
-      </x:c>
-      <x:c r="J12" s="11" t="n">
+      <x:c r="H12" s="19" t="n">
+        <x:v>4.716239584970917</x:v>
+      </x:c>
+      <x:c r="I12" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K12" s="11" t="n">
+      <x:c r="J12" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L12" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H12),H12&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I12="NTD",I12="USD")),IF(I12="USD",H12*Summary!$F$5,H12),"")</x:f>
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="M12" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H12),H12&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I12="NTD",I12="USD")),IF(I12="USD",H12,H12/Summary!$F$5),"")</x:f>
+      <x:c r="K12" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(E12),E12&gt;=0,ISNUMBER(H12),H12&gt;=0),E12*H12,"")</x:f>
         <x:v>4.716239584970917</x:v>
       </x:c>
-      <x:c r="N12" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E12),E12&gt;=0,ISNUMBER(L12)),E12*L12,"")</x:f>
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="O12" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E12),E12&gt;=0,ISNUMBER(M12)),E12*M12,"")</x:f>
+      <x:c r="L12" s="10" t="n">
+        <x:f>IF(AND(ISNUMBER(E12),E12&gt;=0,ISNUMBER(I12),I12&gt;0,ISNUMBER(J12),J12&gt;=0),ROUNDUP(MAX(0,E12-J12)/I12,0),"")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M12" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(L12),ISNUMBER(H12),H12&gt;=0),L12*I12*H12,"")</x:f>
         <x:v>4.716239584970917</x:v>
       </x:c>
-      <x:c r="P12" s="10" t="n">
-        <x:f>IF(AND(ISNUMBER(E12),E12&gt;=0,ISNUMBER(J12),J12&gt;0,ISNUMBER(K12),K12&gt;=0),ROUNDUP(MAX(0,E12-K12)/J12,0),"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q12" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P12),ISNUMBER(L12)),P12*J12*L12,"")</x:f>
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="R12" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P12),ISNUMBER(M12)),P12*J12*M12,"")</x:f>
-        <x:v>4.716239584970917</x:v>
-      </x:c>
-      <x:c r="S12" s="10" t="str">
+      <x:c r="N12" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="T12" s="10" t="str"/>
-      <x:c r="U12" s="10" t="str">
+      <x:c r="O12" s="10" t="str"/>
+      <x:c r="P12" s="10" t="str">
         <x:v>Hardness, compression set, thickness tolerance, VOC sorption/permeation, cleaning and cell-environment compatibility remain unqualified. PD ring minimum wall 0.3 mm and tiny aperture alignment margin require the100% SVG and real PD window. Black appearance does not prove opacity or gas sealing.</x:v>
       </x:c>
-      <x:c r="V12" s="10" t="str">
+      <x:c r="Q12" s="10" t="str">
         <x:v>SEAL
+Original unit input: NTD 150. Converted at 31.805 NTD/USD.
 0.8 mm selectable stock; exact price unavailable. NTD 150 per small sheet is an engineering allowance, not a verified selling price. Hardness and VOC compatibility unqualified.
 https://www.ruten.com.tw/item/22517308416481/</x:v>
       </x:c>
-      <x:c r="W12" s="10" t="str">
-        <x:f>IF(AND(ISNUMBER(N12),ISNUMBER(Q12)),"OK","Missing")</x:f>
+      <x:c r="R12" s="10" t="str">
+        <x:f>IF(AND(ISNUMBER(K12),ISNUMBER(M12)),"OK","Missing")</x:f>
         <x:v>OK</x:v>
       </x:c>
+      <x:c r="S12"/>
+      <x:c r="T12"/>
+      <x:c r="U12"/>
+      <x:c r="V12"/>
+      <x:c r="W12"/>
     </x:row>
     <x:row r="13" ht="108" customHeight="1">
       <x:c r="A13" s="10" t="str">
@@ -4457,64 +4414,51 @@
       <x:c r="G13" s="10" t="str">
         <x:v>Required</x:v>
       </x:c>
-      <x:c r="H13" s="14" t="n">
+      <x:c r="H13" s="19" t="n">
         <x:v>8.74</x:v>
       </x:c>
-      <x:c r="I13" s="11" t="str">
-        <x:v>USD</x:v>
-      </x:c>
-      <x:c r="J13" s="11" t="n">
+      <x:c r="I13" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K13" s="11" t="n">
+      <x:c r="J13" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L13" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H13),H13&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I13="NTD",I13="USD")),IF(I13="USD",H13*Summary!$F$5,H13),"")</x:f>
-        <x:v>277.9757</x:v>
-      </x:c>
-      <x:c r="M13" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H13),H13&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I13="NTD",I13="USD")),IF(I13="USD",H13,H13/Summary!$F$5),"")</x:f>
+      <x:c r="K13" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(E13),E13&gt;=0,ISNUMBER(H13),H13&gt;=0),E13*H13,"")</x:f>
         <x:v>8.74</x:v>
       </x:c>
-      <x:c r="N13" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E13),E13&gt;=0,ISNUMBER(L13)),E13*L13,"")</x:f>
-        <x:v>277.9757</x:v>
-      </x:c>
-      <x:c r="O13" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E13),E13&gt;=0,ISNUMBER(M13)),E13*M13,"")</x:f>
+      <x:c r="L13" s="10" t="n">
+        <x:f>IF(AND(ISNUMBER(E13),E13&gt;=0,ISNUMBER(I13),I13&gt;0,ISNUMBER(J13),J13&gt;=0),ROUNDUP(MAX(0,E13-J13)/I13,0),"")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M13" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(L13),ISNUMBER(H13),H13&gt;=0),L13*I13*H13,"")</x:f>
         <x:v>8.74</x:v>
       </x:c>
-      <x:c r="P13" s="10" t="n">
-        <x:f>IF(AND(ISNUMBER(E13),E13&gt;=0,ISNUMBER(J13),J13&gt;0,ISNUMBER(K13),K13&gt;=0),ROUNDUP(MAX(0,E13-K13)/J13,0),"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q13" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P13),ISNUMBER(L13)),P13*J13*L13,"")</x:f>
-        <x:v>277.9757</x:v>
-      </x:c>
-      <x:c r="R13" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P13),ISNUMBER(M13)),P13*J13*M13,"")</x:f>
-        <x:v>8.74</x:v>
-      </x:c>
-      <x:c r="S13" s="10" t="str">
+      <x:c r="N13" s="10" t="str">
         <x:v>Proxy</x:v>
       </x:c>
-      <x:c r="T13" s="10" t="str"/>
-      <x:c r="U13" s="10" t="str">
+      <x:c r="O13" s="10" t="str"/>
+      <x:c r="P13" s="10" t="str">
         <x:v>J1 connects BAT/GND, but holder dimensions/polarity and charge-setting R1–R3/TS R9 values are missing. Do not specify18650 chemistry/protection from photographs. TPS61023 output is labeled5 V but R6/R8 and other values are absent; vendor must confirm power and fan capability in both modes.</x:v>
       </x:c>
-      <x:c r="V13" s="10" t="str">
+      <x:c r="Q13" s="10" t="str">
         <x:v>POWER
+Original unit input: USD 8.74. No conversion.
 USD 8.74, 5.1 V 3 A with cable. Price benchmark only; vendor must confirm input and charging configuration. Current budget uses external power, not an unconfirmed battery.
 https://www.adafruit.com/product/4298</x:v>
       </x:c>
-      <x:c r="W13" s="10" t="str">
-        <x:f>IF(AND(ISNUMBER(N13),ISNUMBER(Q13)),"OK","Missing")</x:f>
+      <x:c r="R13" s="10" t="str">
+        <x:f>IF(AND(ISNUMBER(K13),ISNUMBER(M13)),"OK","Missing")</x:f>
         <x:v>OK</x:v>
       </x:c>
-    </x:row>
-    <x:row r="14" ht="123" customHeight="1">
+      <x:c r="S13"/>
+      <x:c r="T13"/>
+      <x:c r="U13"/>
+      <x:c r="V13"/>
+      <x:c r="W13"/>
+    </x:row>
+    <x:row r="14" ht="138" customHeight="1">
       <x:c r="A14" s="10" t="str">
         <x:v>G01</x:v>
       </x:c>
@@ -4537,64 +4481,51 @@
       <x:c r="G14" s="10" t="str">
         <x:v>Required</x:v>
       </x:c>
-      <x:c r="H14" s="14" t="n">
+      <x:c r="H14" s="19" t="n">
         <x:v>0.95</x:v>
       </x:c>
-      <x:c r="I14" s="11" t="str">
-        <x:v>USD</x:v>
-      </x:c>
-      <x:c r="J14" s="11" t="n">
+      <x:c r="I14" s="18" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="K14" s="11" t="n">
+      <x:c r="J14" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L14" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H14),H14&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I14="NTD",I14="USD")),IF(I14="USD",H14*Summary!$F$5,H14),"")</x:f>
-        <x:v>30.21475</x:v>
-      </x:c>
-      <x:c r="M14" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H14),H14&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I14="NTD",I14="USD")),IF(I14="USD",H14,H14/Summary!$F$5),"")</x:f>
-        <x:v>0.95</x:v>
-      </x:c>
-      <x:c r="N14" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E14),E14&gt;=0,ISNUMBER(L14)),E14*L14,"")</x:f>
-        <x:v>60.4295</x:v>
-      </x:c>
-      <x:c r="O14" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E14),E14&gt;=0,ISNUMBER(M14)),E14*M14,"")</x:f>
+      <x:c r="K14" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(E14),E14&gt;=0,ISNUMBER(H14),H14&gt;=0),E14*H14,"")</x:f>
         <x:v>1.9</x:v>
       </x:c>
-      <x:c r="P14" s="10" t="n">
-        <x:f>IF(AND(ISNUMBER(E14),E14&gt;=0,ISNUMBER(J14),J14&gt;0,ISNUMBER(K14),K14&gt;=0),ROUNDUP(MAX(0,E14-K14)/J14,0),"")</x:f>
+      <x:c r="L14" s="10" t="n">
+        <x:f>IF(AND(ISNUMBER(E14),E14&gt;=0,ISNUMBER(I14),I14&gt;0,ISNUMBER(J14),J14&gt;=0),ROUNDUP(MAX(0,E14-J14)/I14,0),"")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Q14" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P14),ISNUMBER(L14)),P14*J14*L14,"")</x:f>
-        <x:v>3021.475</x:v>
-      </x:c>
-      <x:c r="R14" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P14),ISNUMBER(M14)),P14*J14*M14,"")</x:f>
+      <x:c r="M14" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(L14),ISNUMBER(H14),H14&gt;=0),L14*I14*H14,"")</x:f>
         <x:v>95</x:v>
       </x:c>
-      <x:c r="S14" s="10" t="str">
+      <x:c r="N14" s="10" t="str">
         <x:v>Proxy</x:v>
       </x:c>
-      <x:c r="T14" s="10" t="str"/>
-      <x:c r="U14" s="10" t="str">
+      <x:c r="O14" s="10" t="str"/>
+      <x:c r="P14" s="10" t="str">
         <x:v>Obtain air pressure drop near3 mL/min, direction, pressure limits, wetting behavior, fittings and cleaning/sterilization information; measure target-VOC recovery/lag. Pore size does not prove zero VOC sorption or absolute containment. Price proxy ANP1322 is 0.22 um and nonsterile; it is not a qualified replacement for the specified 0.2 um gas filter.</x:v>
       </x:c>
-      <x:c r="V14" s="10" t="str">
+      <x:c r="Q14" s="10" t="str">
         <x:v>GASFILTER
+Original unit input: USD 0.95. No conversion.
 USD 95 per 100. Hydrophobic PTFE, 13 mm, 0.22 um, NONSTERILE, air venting listed. Price proxy for 0.2 um gas-filter requirement, not certified sterile replacement. Two used per device; buying a box costs 100 filters.
 https://www.gilson.com/default/catalog/product/view/id/1204/</x:v>
       </x:c>
-      <x:c r="W14" s="10" t="str">
-        <x:f>IF(AND(ISNUMBER(N14),ISNUMBER(Q14)),"OK","Missing")</x:f>
+      <x:c r="R14" s="10" t="str">
+        <x:f>IF(AND(ISNUMBER(K14),ISNUMBER(M14)),"OK","Missing")</x:f>
         <x:v>OK</x:v>
       </x:c>
-    </x:row>
-    <x:row r="15" ht="108" customHeight="1">
+      <x:c r="S14"/>
+      <x:c r="T14"/>
+      <x:c r="U14"/>
+      <x:c r="V14"/>
+      <x:c r="W14"/>
+    </x:row>
+    <x:row r="15" ht="123" customHeight="1">
       <x:c r="A15" s="10" t="str">
         <x:v>G02</x:v>
       </x:c>
@@ -4617,64 +4548,51 @@
       <x:c r="G15" s="10" t="str">
         <x:v>Required</x:v>
       </x:c>
-      <x:c r="H15" s="14" t="n">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="I15" s="11" t="str">
-        <x:v>NTD</x:v>
-      </x:c>
-      <x:c r="J15" s="11" t="n">
+      <x:c r="H15" s="19" t="n">
+        <x:v>6.288319446627889</x:v>
+      </x:c>
+      <x:c r="I15" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K15" s="11" t="n">
+      <x:c r="J15" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L15" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H15),H15&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I15="NTD",I15="USD")),IF(I15="USD",H15*Summary!$F$5,H15),"")</x:f>
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="M15" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H15),H15&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I15="NTD",I15="USD")),IF(I15="USD",H15,H15/Summary!$F$5),"")</x:f>
+      <x:c r="K15" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(E15),E15&gt;=0,ISNUMBER(H15),H15&gt;=0),E15*H15,"")</x:f>
         <x:v>6.288319446627889</x:v>
       </x:c>
-      <x:c r="N15" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E15),E15&gt;=0,ISNUMBER(L15)),E15*L15,"")</x:f>
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="O15" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E15),E15&gt;=0,ISNUMBER(M15)),E15*M15,"")</x:f>
+      <x:c r="L15" s="10" t="n">
+        <x:f>IF(AND(ISNUMBER(E15),E15&gt;=0,ISNUMBER(I15),I15&gt;0,ISNUMBER(J15),J15&gt;=0),ROUNDUP(MAX(0,E15-J15)/I15,0),"")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M15" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(L15),ISNUMBER(H15),H15&gt;=0),L15*I15*H15,"")</x:f>
         <x:v>6.288319446627889</x:v>
       </x:c>
-      <x:c r="P15" s="10" t="n">
-        <x:f>IF(AND(ISNUMBER(E15),E15&gt;=0,ISNUMBER(J15),J15&gt;0,ISNUMBER(K15),K15&gt;=0),ROUNDUP(MAX(0,E15-K15)/J15,0),"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q15" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P15),ISNUMBER(L15)),P15*J15*L15,"")</x:f>
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="R15" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P15),ISNUMBER(M15)),P15*J15*M15,"")</x:f>
-        <x:v>6.288319446627889</x:v>
-      </x:c>
-      <x:c r="S15" s="10" t="str">
+      <x:c r="N15" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="T15" s="10" t="str"/>
-      <x:c r="U15" s="10" t="str">
+      <x:c r="O15" s="10" t="str"/>
+      <x:c r="P15" s="10" t="str">
         <x:v>Verify wall/bend radius, tolerances and VOC recovery.1 m of ID2-mm tubing holds about3.14 mL; at3 mL/min nominal residence alone is about63 s. Chamber ~50-s t90 is not complete-system response time.</x:v>
       </x:c>
-      <x:c r="V15" s="10" t="str">
+      <x:c r="Q15" s="10" t="str">
         <x:v>PTFE
+Original unit input: NTD 200. Converted at 31.805 NTD/USD.
 Search listing USD 4.99; sold length not verified. NTD 200 per 1 m is a separate allowance. Printer-feed tubing is not qualified analytical tubing.
 https://tinkersphere.com/3d-printer-parts-supplies/2015-ptfe-teflon-tube-2mm-id-3mm-od-for-175-mm-filament.html</x:v>
       </x:c>
-      <x:c r="W15" s="10" t="str">
-        <x:f>IF(AND(ISNUMBER(N15),ISNUMBER(Q15)),"OK","Missing")</x:f>
+      <x:c r="R15" s="10" t="str">
+        <x:f>IF(AND(ISNUMBER(K15),ISNUMBER(M15)),"OK","Missing")</x:f>
         <x:v>OK</x:v>
       </x:c>
-    </x:row>
-    <x:row r="16" ht="108" customHeight="1">
+      <x:c r="S15"/>
+      <x:c r="T15"/>
+      <x:c r="U15"/>
+      <x:c r="V15"/>
+      <x:c r="W15"/>
+    </x:row>
+    <x:row r="16" ht="123" customHeight="1">
       <x:c r="A16" s="10" t="str">
         <x:v>G03</x:v>
       </x:c>
@@ -4697,64 +4615,51 @@
       <x:c r="G16" s="10" t="str">
         <x:v>Required</x:v>
       </x:c>
-      <x:c r="H16" s="14" t="n">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="I16" s="11" t="str">
-        <x:v>NTD</x:v>
-      </x:c>
-      <x:c r="J16" s="11" t="n">
+      <x:c r="H16" s="19" t="n">
+        <x:v>4.716239584970917</x:v>
+      </x:c>
+      <x:c r="I16" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K16" s="11" t="n">
+      <x:c r="J16" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L16" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H16),H16&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I16="NTD",I16="USD")),IF(I16="USD",H16*Summary!$F$5,H16),"")</x:f>
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="M16" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H16),H16&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I16="NTD",I16="USD")),IF(I16="USD",H16,H16/Summary!$F$5),"")</x:f>
+      <x:c r="K16" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(E16),E16&gt;=0,ISNUMBER(H16),H16&gt;=0),E16*H16,"")</x:f>
         <x:v>4.716239584970917</x:v>
       </x:c>
-      <x:c r="N16" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E16),E16&gt;=0,ISNUMBER(L16)),E16*L16,"")</x:f>
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="O16" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E16),E16&gt;=0,ISNUMBER(M16)),E16*M16,"")</x:f>
+      <x:c r="L16" s="10" t="n">
+        <x:f>IF(AND(ISNUMBER(E16),E16&gt;=0,ISNUMBER(I16),I16&gt;0,ISNUMBER(J16),J16&gt;=0),ROUNDUP(MAX(0,E16-J16)/I16,0),"")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M16" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(L16),ISNUMBER(H16),H16&gt;=0),L16*I16*H16,"")</x:f>
         <x:v>4.716239584970917</x:v>
       </x:c>
-      <x:c r="P16" s="10" t="n">
-        <x:f>IF(AND(ISNUMBER(E16),E16&gt;=0,ISNUMBER(J16),J16&gt;0,ISNUMBER(K16),K16&gt;=0),ROUNDUP(MAX(0,E16-K16)/J16,0),"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q16" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P16),ISNUMBER(L16)),P16*J16*L16,"")</x:f>
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="R16" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P16),ISNUMBER(M16)),P16*J16*M16,"")</x:f>
-        <x:v>4.716239584970917</x:v>
-      </x:c>
-      <x:c r="S16" s="10" t="str">
+      <x:c r="N16" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="T16" s="10" t="str"/>
-      <x:c r="U16" s="10" t="str">
+      <x:c r="O16" s="10" t="str"/>
+      <x:c r="P16" s="10" t="str">
         <x:v>Coupling must pass4-mm ridge without splitting nominal0.5-mm printed wall. Tip-to-rib insertion length is about4.8 mm, not the full10-mm tail. Side slot height 7 mm also limits OD/bend. Off-board test retention, leaks, VOC sorption and unrestricted outlet.</x:v>
       </x:c>
-      <x:c r="V16" s="10" t="str">
+      <x:c r="Q16" s="10" t="str">
         <x:v>COUPLER
+Original unit input: NTD 150. Converted at 31.805 NTD/USD.
 Related tubing listed USD 2.50 per metre. Budget NTD 150 includes short flexible couplers and matching adapters. Exact ID/OD, Luer interfaces and VOC recovery must be checked; no fit guarantee.
 https://www.adafruit.com/product/4699</x:v>
       </x:c>
-      <x:c r="W16" s="10" t="str">
-        <x:f>IF(AND(ISNUMBER(N16),ISNUMBER(Q16)),"OK","Missing")</x:f>
+      <x:c r="R16" s="10" t="str">
+        <x:f>IF(AND(ISNUMBER(K16),ISNUMBER(M16)),"OK","Missing")</x:f>
         <x:v>OK</x:v>
       </x:c>
-    </x:row>
-    <x:row r="17" ht="138" customHeight="1">
+      <x:c r="S16"/>
+      <x:c r="T16"/>
+      <x:c r="U16"/>
+      <x:c r="V16"/>
+      <x:c r="W16"/>
+    </x:row>
+    <x:row r="17" ht="168" customHeight="1">
       <x:c r="A17" s="10" t="str">
         <x:v>O01</x:v>
       </x:c>
@@ -4777,62 +4682,49 @@
       <x:c r="G17" s="10" t="str">
         <x:v>Required</x:v>
       </x:c>
-      <x:c r="H17" s="14" t="n">
-        <x:v>12000</x:v>
-      </x:c>
-      <x:c r="I17" s="11" t="str">
-        <x:v>NTD</x:v>
-      </x:c>
-      <x:c r="J17" s="11" t="n">
+      <x:c r="H17" s="19" t="n">
+        <x:v>377.2991667976733</x:v>
+      </x:c>
+      <x:c r="I17" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K17" s="11" t="n">
+      <x:c r="J17" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L17" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H17),H17&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I17="NTD",I17="USD")),IF(I17="USD",H17*Summary!$F$5,H17),"")</x:f>
-        <x:v>12000</x:v>
-      </x:c>
-      <x:c r="M17" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H17),H17&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I17="NTD",I17="USD")),IF(I17="USD",H17,H17/Summary!$F$5),"")</x:f>
+      <x:c r="K17" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(E17),E17&gt;=0,ISNUMBER(H17),H17&gt;=0),E17*H17,"")</x:f>
         <x:v>377.2991667976733</x:v>
       </x:c>
-      <x:c r="N17" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E17),E17&gt;=0,ISNUMBER(L17)),E17*L17,"")</x:f>
-        <x:v>12000</x:v>
-      </x:c>
-      <x:c r="O17" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E17),E17&gt;=0,ISNUMBER(M17)),E17*M17,"")</x:f>
+      <x:c r="L17" s="10" t="n">
+        <x:f>IF(AND(ISNUMBER(E17),E17&gt;=0,ISNUMBER(I17),I17&gt;0,ISNUMBER(J17),J17&gt;=0),ROUNDUP(MAX(0,E17-J17)/I17,0),"")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M17" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(L17),ISNUMBER(H17),H17&gt;=0),L17*I17*H17,"")</x:f>
         <x:v>377.2991667976733</x:v>
       </x:c>
-      <x:c r="P17" s="10" t="n">
-        <x:f>IF(AND(ISNUMBER(E17),E17&gt;=0,ISNUMBER(J17),J17&gt;0,ISNUMBER(K17),K17&gt;=0),ROUNDUP(MAX(0,E17-K17)/J17,0),"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q17" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P17),ISNUMBER(L17)),P17*J17*L17,"")</x:f>
-        <x:v>12000</x:v>
-      </x:c>
-      <x:c r="R17" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P17),ISNUMBER(M17)),P17*J17*M17,"")</x:f>
-        <x:v>377.2991667976733</x:v>
-      </x:c>
-      <x:c r="S17" s="10" t="str">
+      <x:c r="N17" s="10" t="str">
         <x:v>Custom allowance</x:v>
       </x:c>
-      <x:c r="T17" s="10" t="str"/>
-      <x:c r="U17" s="10" t="str">
+      <x:c r="O17" s="10" t="str"/>
+      <x:c r="P17" s="10" t="str">
         <x:v>No selected MPN. Model OD3/4/5 at470/520 nm and0.9 normal green transmission are design-study assumptions, not verified purchased performance. Collection includes large angles; obtain0–65° and higher-angle data/limits. Interference-filter spectral shift is not represented by the absorptive proxy. Verify edge coating, orientation, flatness, thickness and PD-seal fit.</x:v>
       </x:c>
-      <x:c r="V17" s="10" t="str">
+      <x:c r="Q17" s="10" t="str">
         <x:v>OPTIC
+Original unit input: NTD 12000. Converted at 31.805 NTD/USD.
 USD 284, 12.5 mm diameter, substrate 2.00 +/-0.25 mm, mounted. Does NOT fit 5.2x4.2x1.0 mm seat. NTD 12000 is a custom thin-filter budget allowance, not a quote or available drop-in part. Cutting this stock part does not solve its thickness mismatch.
 https://www.edmundoptics.com/p/520nm-cwl-125mm-dia-36nm-bandwidth-od-6-fluorescence-filter/21556/</x:v>
       </x:c>
-      <x:c r="W17" s="10" t="str">
-        <x:f>IF(AND(ISNUMBER(N17),ISNUMBER(Q17)),"OK","Missing")</x:f>
+      <x:c r="R17" s="10" t="str">
+        <x:f>IF(AND(ISNUMBER(K17),ISNUMBER(M17)),"OK","Missing")</x:f>
         <x:v>OK</x:v>
       </x:c>
+      <x:c r="S17"/>
+      <x:c r="T17"/>
+      <x:c r="U17"/>
+      <x:c r="V17"/>
+      <x:c r="W17"/>
     </x:row>
     <x:row r="18" ht="93" customHeight="1">
       <x:c r="A18" s="10" t="str">
@@ -4857,64 +4749,51 @@
       <x:c r="G18" s="10" t="str">
         <x:v>Developer</x:v>
       </x:c>
-      <x:c r="H18" s="14" t="n">
+      <x:c r="H18" s="19" t="n">
         <x:v>5.95</x:v>
       </x:c>
-      <x:c r="I18" s="11" t="str">
-        <x:v>USD</x:v>
-      </x:c>
-      <x:c r="J18" s="11" t="n">
+      <x:c r="I18" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K18" s="11" t="n">
+      <x:c r="J18" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L18" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H18),H18&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I18="NTD",I18="USD")),IF(I18="USD",H18*Summary!$F$5,H18),"")</x:f>
-        <x:v>189.23975000000002</x:v>
-      </x:c>
-      <x:c r="M18" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H18),H18&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I18="NTD",I18="USD")),IF(I18="USD",H18,H18/Summary!$F$5),"")</x:f>
+      <x:c r="K18" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(E18),E18&gt;=0,ISNUMBER(H18),H18&gt;=0),E18*H18,"")</x:f>
         <x:v>5.95</x:v>
       </x:c>
-      <x:c r="N18" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E18),E18&gt;=0,ISNUMBER(L18)),E18*L18,"")</x:f>
-        <x:v>189.23975000000002</x:v>
-      </x:c>
-      <x:c r="O18" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E18),E18&gt;=0,ISNUMBER(M18)),E18*M18,"")</x:f>
+      <x:c r="L18" s="10" t="n">
+        <x:f>IF(AND(ISNUMBER(E18),E18&gt;=0,ISNUMBER(I18),I18&gt;0,ISNUMBER(J18),J18&gt;=0),ROUNDUP(MAX(0,E18-J18)/I18,0),"")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M18" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(L18),ISNUMBER(H18),H18&gt;=0),L18*I18*H18,"")</x:f>
         <x:v>5.95</x:v>
       </x:c>
-      <x:c r="P18" s="10" t="n">
-        <x:f>IF(AND(ISNUMBER(E18),E18&gt;=0,ISNUMBER(J18),J18&gt;0,ISNUMBER(K18),K18&gt;=0),ROUNDUP(MAX(0,E18-K18)/J18,0),"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q18" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P18),ISNUMBER(L18)),P18*J18*L18,"")</x:f>
-        <x:v>189.23975000000002</x:v>
-      </x:c>
-      <x:c r="R18" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P18),ISNUMBER(M18)),P18*J18*M18,"")</x:f>
-        <x:v>5.95</x:v>
-      </x:c>
-      <x:c r="S18" s="10" t="str">
+      <x:c r="N18" s="10" t="str">
         <x:v>Listed</x:v>
       </x:c>
-      <x:c r="T18" s="10" t="str"/>
-      <x:c r="U18" s="10" t="str">
+      <x:c r="O18" s="10" t="str"/>
+      <x:c r="P18" s="10" t="str">
         <x:v>Confirm physical J3 pin1 and terminal pitch. Leave adapterVCC disconnected with normal board power. J2 has no USB–UART bridge; never apply5 V UART signalling to ESP32.</x:v>
       </x:c>
-      <x:c r="V18" s="10" t="str">
+      <x:c r="Q18" s="10" t="str">
         <x:v>UART
+Original unit input: USD 5.95. No conversion.
 USD 5.95 each. Signals 3.3 V; power wire 5 V. Leave VCC disconnected at J3. Cable and jumper wires separate.
 https://www.adafruit.com/product/5335</x:v>
       </x:c>
-      <x:c r="W18" s="10" t="str">
-        <x:f>IF(AND(ISNUMBER(N18),ISNUMBER(Q18)),"OK","Missing")</x:f>
+      <x:c r="R18" s="10" t="str">
+        <x:f>IF(AND(ISNUMBER(K18),ISNUMBER(M18)),"OK","Missing")</x:f>
         <x:v>OK</x:v>
       </x:c>
-    </x:row>
-    <x:row r="19" ht="123" customHeight="1">
+      <x:c r="S18"/>
+      <x:c r="T18"/>
+      <x:c r="U18"/>
+      <x:c r="V18"/>
+      <x:c r="W18"/>
+    </x:row>
+    <x:row r="19" ht="153" customHeight="1">
       <x:c r="A19" s="10" t="str">
         <x:v>L01</x:v>
       </x:c>
@@ -4937,64 +4816,51 @@
       <x:c r="G19" s="10" t="str">
         <x:v>Developer</x:v>
       </x:c>
-      <x:c r="H19" s="14" t="n">
-        <x:v>5000</x:v>
-      </x:c>
-      <x:c r="I19" s="11" t="str">
-        <x:v>NTD</x:v>
-      </x:c>
-      <x:c r="J19" s="11" t="n">
+      <x:c r="H19" s="19" t="n">
+        <x:v>157.2079861656972</x:v>
+      </x:c>
+      <x:c r="I19" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K19" s="11" t="n">
+      <x:c r="J19" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L19" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H19),H19&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I19="NTD",I19="USD")),IF(I19="USD",H19*Summary!$F$5,H19),"")</x:f>
-        <x:v>5000</x:v>
-      </x:c>
-      <x:c r="M19" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H19),H19&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I19="NTD",I19="USD")),IF(I19="USD",H19,H19/Summary!$F$5),"")</x:f>
+      <x:c r="K19" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(E19),E19&gt;=0,ISNUMBER(H19),H19&gt;=0),E19*H19,"")</x:f>
         <x:v>157.2079861656972</x:v>
       </x:c>
-      <x:c r="N19" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E19),E19&gt;=0,ISNUMBER(L19)),E19*L19,"")</x:f>
-        <x:v>5000</x:v>
-      </x:c>
-      <x:c r="O19" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E19),E19&gt;=0,ISNUMBER(M19)),E19*M19,"")</x:f>
+      <x:c r="L19" s="10" t="n">
+        <x:f>IF(AND(ISNUMBER(E19),E19&gt;=0,ISNUMBER(I19),I19&gt;0,ISNUMBER(J19),J19&gt;=0),ROUNDUP(MAX(0,E19-J19)/I19,0),"")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M19" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(L19),ISNUMBER(H19),H19&gt;=0),L19*I19*H19,"")</x:f>
         <x:v>157.2079861656972</x:v>
       </x:c>
-      <x:c r="P19" s="10" t="n">
-        <x:f>IF(AND(ISNUMBER(E19),E19&gt;=0,ISNUMBER(J19),J19&gt;0,ISNUMBER(K19),K19&gt;=0),ROUNDUP(MAX(0,E19-K19)/J19,0),"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q19" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P19),ISNUMBER(L19)),P19*J19*L19,"")</x:f>
-        <x:v>5000</x:v>
-      </x:c>
-      <x:c r="R19" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P19),ISNUMBER(M19)),P19*J19*M19,"")</x:f>
-        <x:v>157.2079861656972</x:v>
-      </x:c>
-      <x:c r="S19" s="10" t="str">
+      <x:c r="N19" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="T19" s="10" t="str"/>
-      <x:c r="U19" s="10" t="str">
+      <x:c r="O19" s="10" t="str"/>
+      <x:c r="P19" s="10" t="str">
         <x:v>3 mL/min is a conditional fixed-CAD candidate, not a cell-safety limit. Measure assembled system; steady inlet/outlet volume rates match at common temperature/pressure. Chamber CFD excludes filters/tubing. Do not expose wells directly to pump maximum suction; baffle is not pressure regulation.</x:v>
       </x:c>
-      <x:c r="V19" s="10" t="str">
+      <x:c r="Q19" s="10" t="str">
         <x:v>PUMP
+Original unit input: NTD 5000. Converted at 31.805 NTD/USD.
 USD 7.95 for pump alone. 2.5 L/min, intermittent duty; NOT a selected 3 mL/min continuous source. NTD 5000 system allowance requires a qualified controlled source, bypass/regulation, pressure protection, fittings and supply. Borrow a suitable lab system first.
 https://www.adafruit.com/product/4699</x:v>
       </x:c>
-      <x:c r="W19" s="10" t="str">
-        <x:f>IF(AND(ISNUMBER(N19),ISNUMBER(Q19)),"OK","Missing")</x:f>
+      <x:c r="R19" s="10" t="str">
+        <x:f>IF(AND(ISNUMBER(K19),ISNUMBER(M19)),"OK","Missing")</x:f>
         <x:v>OK</x:v>
       </x:c>
-    </x:row>
-    <x:row r="20" ht="123" customHeight="1">
+      <x:c r="S19"/>
+      <x:c r="T19"/>
+      <x:c r="U19"/>
+      <x:c r="V19"/>
+      <x:c r="W19"/>
+    </x:row>
+    <x:row r="20" ht="153" customHeight="1">
       <x:c r="A20" s="10" t="str">
         <x:v>L02</x:v>
       </x:c>
@@ -5017,64 +4883,51 @@
       <x:c r="G20" s="10" t="str">
         <x:v>Developer</x:v>
       </x:c>
-      <x:c r="H20" s="14" t="n">
-        <x:v>1500</x:v>
-      </x:c>
-      <x:c r="I20" s="11" t="str">
-        <x:v>NTD</x:v>
-      </x:c>
-      <x:c r="J20" s="11" t="n">
+      <x:c r="H20" s="19" t="n">
+        <x:v>47.16239584970916</x:v>
+      </x:c>
+      <x:c r="I20" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K20" s="11" t="n">
+      <x:c r="J20" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L20" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H20),H20&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I20="NTD",I20="USD")),IF(I20="USD",H20*Summary!$F$5,H20),"")</x:f>
-        <x:v>1500</x:v>
-      </x:c>
-      <x:c r="M20" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H20),H20&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I20="NTD",I20="USD")),IF(I20="USD",H20,H20/Summary!$F$5),"")</x:f>
+      <x:c r="K20" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(E20),E20&gt;=0,ISNUMBER(H20),H20&gt;=0),E20*H20,"")</x:f>
         <x:v>47.16239584970916</x:v>
       </x:c>
-      <x:c r="N20" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E20),E20&gt;=0,ISNUMBER(L20)),E20*L20,"")</x:f>
-        <x:v>1500</x:v>
-      </x:c>
-      <x:c r="O20" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E20),E20&gt;=0,ISNUMBER(M20)),E20*M20,"")</x:f>
+      <x:c r="L20" s="10" t="n">
+        <x:f>IF(AND(ISNUMBER(E20),E20&gt;=0,ISNUMBER(I20),I20&gt;0,ISNUMBER(J20),J20&gt;=0),ROUNDUP(MAX(0,E20-J20)/I20,0),"")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M20" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(L20),ISNUMBER(H20),H20&gt;=0),L20*I20*H20,"")</x:f>
         <x:v>47.16239584970916</x:v>
       </x:c>
-      <x:c r="P20" s="10" t="n">
-        <x:f>IF(AND(ISNUMBER(E20),E20&gt;=0,ISNUMBER(J20),J20&gt;0,ISNUMBER(K20),K20&gt;=0),ROUNDUP(MAX(0,E20-K20)/J20,0),"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q20" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P20),ISNUMBER(L20)),P20*J20*L20,"")</x:f>
-        <x:v>1500</x:v>
-      </x:c>
-      <x:c r="R20" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P20),ISNUMBER(M20)),P20*J20*M20,"")</x:f>
-        <x:v>47.16239584970916</x:v>
-      </x:c>
-      <x:c r="S20" s="10" t="str">
+      <x:c r="N20" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="T20" s="10" t="str"/>
-      <x:c r="U20" s="10" t="str">
+      <x:c r="O20" s="10" t="str"/>
+      <x:c r="P20" s="10" t="str">
         <x:v>Use resin-validated settings, no universal exposure/torque claim. Must measure/clean0.8-mm gaskets, 0.5-mm well floors and small bores. Existing equipment is declared as owned/borrowed rather than free.</x:v>
       </x:c>
-      <x:c r="V20" s="10" t="str">
+      <x:c r="Q20" s="10" t="str">
         <x:v>TOOLS
+Original unit input: NTD 1500. Converted at 31.805 NTD/USD.
 Engineering allowances only: hand tools/calipers NTD 1500; DMM 800; scope 10000; pipette/tips 4000; print/post-cure supplies 300. Borrow existing printer, wash/cure equipment, PC, phone, biosafety/cell facilities. Their capital replacement prices are outside this BOM.
 </x:v>
       </x:c>
-      <x:c r="W20" s="10" t="str">
-        <x:f>IF(AND(ISNUMBER(N20),ISNUMBER(Q20)),"OK","Missing")</x:f>
+      <x:c r="R20" s="10" t="str">
+        <x:f>IF(AND(ISNUMBER(K20),ISNUMBER(M20)),"OK","Missing")</x:f>
         <x:v>OK</x:v>
       </x:c>
-    </x:row>
-    <x:row r="21" ht="108" customHeight="1">
+      <x:c r="S20"/>
+      <x:c r="T20"/>
+      <x:c r="U20"/>
+      <x:c r="V20"/>
+      <x:c r="W20"/>
+    </x:row>
+    <x:row r="21" ht="123" customHeight="1">
       <x:c r="A21" s="10" t="str">
         <x:v>L03</x:v>
       </x:c>
@@ -5097,64 +4950,51 @@
       <x:c r="G21" s="10" t="str">
         <x:v>Developer</x:v>
       </x:c>
-      <x:c r="H21" s="14" t="n">
+      <x:c r="H21" s="19" t="n">
         <x:v>52.6</x:v>
       </x:c>
-      <x:c r="I21" s="11" t="str">
-        <x:v>USD</x:v>
-      </x:c>
-      <x:c r="J21" s="11" t="n">
+      <x:c r="I21" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K21" s="11" t="n">
+      <x:c r="J21" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L21" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H21),H21&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I21="NTD",I21="USD")),IF(I21="USD",H21*Summary!$F$5,H21),"")</x:f>
-        <x:v>1672.943</x:v>
-      </x:c>
-      <x:c r="M21" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H21),H21&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I21="NTD",I21="USD")),IF(I21="USD",H21,H21/Summary!$F$5),"")</x:f>
+      <x:c r="K21" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(E21),E21&gt;=0,ISNUMBER(H21),H21&gt;=0),E21*H21,"")</x:f>
         <x:v>52.6</x:v>
       </x:c>
-      <x:c r="N21" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E21),E21&gt;=0,ISNUMBER(L21)),E21*L21,"")</x:f>
-        <x:v>1672.943</x:v>
-      </x:c>
-      <x:c r="O21" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E21),E21&gt;=0,ISNUMBER(M21)),E21*M21,"")</x:f>
+      <x:c r="L21" s="10" t="n">
+        <x:f>IF(AND(ISNUMBER(E21),E21&gt;=0,ISNUMBER(I21),I21&gt;0,ISNUMBER(J21),J21&gt;=0),ROUNDUP(MAX(0,E21-J21)/I21,0),"")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M21" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(L21),ISNUMBER(H21),H21&gt;=0),L21*I21*H21,"")</x:f>
         <x:v>52.6</x:v>
       </x:c>
-      <x:c r="P21" s="10" t="n">
-        <x:f>IF(AND(ISNUMBER(E21),E21&gt;=0,ISNUMBER(J21),J21&gt;0,ISNUMBER(K21),K21&gt;=0),ROUNDUP(MAX(0,E21-K21)/J21,0),"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q21" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P21),ISNUMBER(L21)),P21*J21*L21,"")</x:f>
-        <x:v>1672.943</x:v>
-      </x:c>
-      <x:c r="R21" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P21),ISNUMBER(M21)),P21*J21*M21,"")</x:f>
-        <x:v>52.6</x:v>
-      </x:c>
-      <x:c r="S21" s="10" t="str">
+      <x:c r="N21" s="10" t="str">
         <x:v>Listed</x:v>
       </x:c>
-      <x:c r="T21" s="10" t="str"/>
-      <x:c r="U21" s="10" t="str">
+      <x:c r="O21" s="10" t="str"/>
+      <x:c r="P21" s="10" t="str">
         <x:v>Record stock concentration, solvent/pH and lot per validation guide. Instrument bandwidth/calibration/probe points require confirmation. A fluorescence standard does not establish GCaMP sensitivity, gas t90 or odor recognition.</x:v>
       </x:c>
-      <x:c r="V21" s="10" t="str">
+      <x:c r="Q21" s="10" t="str">
         <x:v>DYE
+Original unit input: USD 52.6. No conversion.
 USD 52.60 per 100 g. Budget includes whole bottle, not a fictitious single-well quantity. Prefer a documented laboratory aliquot. Not an assay-specific or GCaMP-certified standard.
 https://www.sigmaaldrich.com/US/en/product/sigma/46970</x:v>
       </x:c>
-      <x:c r="W21" s="10" t="str">
-        <x:f>IF(AND(ISNUMBER(N21),ISNUMBER(Q21)),"OK","Missing")</x:f>
+      <x:c r="R21" s="10" t="str">
+        <x:f>IF(AND(ISNUMBER(K21),ISNUMBER(M21)),"OK","Missing")</x:f>
         <x:v>OK</x:v>
       </x:c>
-    </x:row>
-    <x:row r="22" ht="123" customHeight="1">
+      <x:c r="S21"/>
+      <x:c r="T21"/>
+      <x:c r="U21"/>
+      <x:c r="V21"/>
+      <x:c r="W21"/>
+    </x:row>
+    <x:row r="22" ht="138" customHeight="1">
       <x:c r="A22" s="10" t="str">
         <x:v>P02</x:v>
       </x:c>
@@ -5177,64 +5017,51 @@
       <x:c r="G22" s="10" t="str">
         <x:v>Developer</x:v>
       </x:c>
-      <x:c r="H22" s="14" t="n">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="I22" s="11" t="str">
-        <x:v>NTD</x:v>
-      </x:c>
-      <x:c r="J22" s="11" t="n">
+      <x:c r="H22" s="19" t="n">
+        <x:v>4.716239584970917</x:v>
+      </x:c>
+      <x:c r="I22" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K22" s="11" t="n">
+      <x:c r="J22" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L22" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H22),H22&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I22="NTD",I22="USD")),IF(I22="USD",H22*Summary!$F$5,H22),"")</x:f>
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="M22" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H22),H22&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I22="NTD",I22="USD")),IF(I22="USD",H22,H22/Summary!$F$5),"")</x:f>
+      <x:c r="K22" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(E22),E22&gt;=0,ISNUMBER(H22),H22&gt;=0),E22*H22,"")</x:f>
         <x:v>4.716239584970917</x:v>
       </x:c>
-      <x:c r="N22" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E22),E22&gt;=0,ISNUMBER(L22)),E22*L22,"")</x:f>
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="O22" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E22),E22&gt;=0,ISNUMBER(M22)),E22*M22,"")</x:f>
+      <x:c r="L22" s="10" t="n">
+        <x:f>IF(AND(ISNUMBER(E22),E22&gt;=0,ISNUMBER(I22),I22&gt;0,ISNUMBER(J22),J22&gt;=0),ROUNDUP(MAX(0,E22-J22)/I22,0),"")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M22" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(L22),ISNUMBER(H22),H22&gt;=0),L22*I22*H22,"")</x:f>
         <x:v>4.716239584970917</x:v>
       </x:c>
-      <x:c r="P22" s="10" t="n">
-        <x:f>IF(AND(ISNUMBER(E22),E22&gt;=0,ISNUMBER(J22),J22&gt;0,ISNUMBER(K22),K22&gt;=0),ROUNDUP(MAX(0,E22-K22)/J22,0),"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q22" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P22),ISNUMBER(L22)),P22*J22*L22,"")</x:f>
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="R22" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P22),ISNUMBER(M22)),P22*J22*M22,"")</x:f>
-        <x:v>4.716239584970917</x:v>
-      </x:c>
-      <x:c r="S22" s="10" t="str">
+      <x:c r="N22" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="T22" s="10" t="str"/>
-      <x:c r="U22" s="10" t="str">
+      <x:c r="O22" s="10" t="str"/>
+      <x:c r="P22" s="10" t="str">
         <x:v>Budget is not a confirmed compatible-part quotation. Borrow first; confirm model before purchase.</x:v>
       </x:c>
-      <x:c r="V22" s="10" t="str">
+      <x:c r="Q22" s="10" t="str">
         <x:v>TOOLS
+Original unit input: NTD 150. Converted at 31.805 NTD/USD.
 Engineering allowances only: hand tools/calipers NTD 1500; DMM 800; scope 10000; pipette/tips 4000; print/post-cure supplies 300. Borrow existing printer, wash/cure equipment, PC, phone, biosafety/cell facilities. Their capital replacement prices are outside this BOM.
 </x:v>
       </x:c>
-      <x:c r="W22" s="10" t="str">
-        <x:f>IF(AND(ISNUMBER(N22),ISNUMBER(Q22)),"OK","Missing")</x:f>
+      <x:c r="R22" s="10" t="str">
+        <x:f>IF(AND(ISNUMBER(K22),ISNUMBER(M22)),"OK","Missing")</x:f>
         <x:v>OK</x:v>
       </x:c>
-    </x:row>
-    <x:row r="23" ht="108" customHeight="1">
+      <x:c r="S22"/>
+      <x:c r="T22"/>
+      <x:c r="U22"/>
+      <x:c r="V22"/>
+      <x:c r="W22"/>
+    </x:row>
+    <x:row r="23" ht="138" customHeight="1">
       <x:c r="A23" s="10" t="str">
         <x:v>L04</x:v>
       </x:c>
@@ -5257,64 +5084,51 @@
       <x:c r="G23" s="10" t="str">
         <x:v>Developer</x:v>
       </x:c>
-      <x:c r="H23" s="14" t="n">
-        <x:v>15000</x:v>
-      </x:c>
-      <x:c r="I23" s="11" t="str">
-        <x:v>NTD</x:v>
-      </x:c>
-      <x:c r="J23" s="11" t="n">
+      <x:c r="H23" s="19" t="n">
+        <x:v>471.6239584970917</x:v>
+      </x:c>
+      <x:c r="I23" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K23" s="11" t="n">
+      <x:c r="J23" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L23" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H23),H23&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I23="NTD",I23="USD")),IF(I23="USD",H23*Summary!$F$5,H23),"")</x:f>
-        <x:v>15000</x:v>
-      </x:c>
-      <x:c r="M23" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H23),H23&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I23="NTD",I23="USD")),IF(I23="USD",H23,H23/Summary!$F$5),"")</x:f>
+      <x:c r="K23" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(E23),E23&gt;=0,ISNUMBER(H23),H23&gt;=0),E23*H23,"")</x:f>
         <x:v>471.6239584970917</x:v>
       </x:c>
-      <x:c r="N23" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E23),E23&gt;=0,ISNUMBER(L23)),E23*L23,"")</x:f>
-        <x:v>15000</x:v>
-      </x:c>
-      <x:c r="O23" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E23),E23&gt;=0,ISNUMBER(M23)),E23*M23,"")</x:f>
+      <x:c r="L23" s="10" t="n">
+        <x:f>IF(AND(ISNUMBER(E23),E23&gt;=0,ISNUMBER(I23),I23&gt;0,ISNUMBER(J23),J23&gt;=0),ROUNDUP(MAX(0,E23-J23)/I23,0),"")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M23" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(L23),ISNUMBER(H23),H23&gt;=0),L23*I23*H23,"")</x:f>
         <x:v>471.6239584970917</x:v>
       </x:c>
-      <x:c r="P23" s="10" t="n">
-        <x:f>IF(AND(ISNUMBER(E23),E23&gt;=0,ISNUMBER(J23),J23&gt;0,ISNUMBER(K23),K23&gt;=0),ROUNDUP(MAX(0,E23-K23)/J23,0),"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q23" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P23),ISNUMBER(L23)),P23*J23*L23,"")</x:f>
-        <x:v>15000</x:v>
-      </x:c>
-      <x:c r="R23" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P23),ISNUMBER(M23)),P23*J23*M23,"")</x:f>
-        <x:v>471.6239584970917</x:v>
-      </x:c>
-      <x:c r="S23" s="10" t="str">
+      <x:c r="N23" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="T23" s="10" t="str"/>
-      <x:c r="U23" s="10" t="str">
+      <x:c r="O23" s="10" t="str"/>
+      <x:c r="P23" s="10" t="str">
         <x:v>Budget is not a confirmed compatible-part quotation. Borrow first; confirm model before purchase.</x:v>
       </x:c>
-      <x:c r="V23" s="10" t="str">
+      <x:c r="Q23" s="10" t="str">
         <x:v>FLOW
+Original unit input: NTD 15000. Converted at 31.805 NTD/USD.
 FL-320 nominal air range 0.02-15 cc/min. Historical price deliberately not treated as current. NTD 15000 is a planning allowance pending current calibrated meter quote; 3 mL/min must fall within usable range.
 https://br.omega.com/omegaFiles/green/pdf/FL120.pdf</x:v>
       </x:c>
-      <x:c r="W23" s="10" t="str">
-        <x:f>IF(AND(ISNUMBER(N23),ISNUMBER(Q23)),"OK","Missing")</x:f>
+      <x:c r="R23" s="10" t="str">
+        <x:f>IF(AND(ISNUMBER(K23),ISNUMBER(M23)),"OK","Missing")</x:f>
         <x:v>OK</x:v>
       </x:c>
-    </x:row>
-    <x:row r="24" ht="123" customHeight="1">
+      <x:c r="S23"/>
+      <x:c r="T23"/>
+      <x:c r="U23"/>
+      <x:c r="V23"/>
+      <x:c r="W23"/>
+    </x:row>
+    <x:row r="24" ht="138" customHeight="1">
       <x:c r="A24" s="10" t="str">
         <x:v>L05</x:v>
       </x:c>
@@ -5337,64 +5151,51 @@
       <x:c r="G24" s="10" t="str">
         <x:v>Developer</x:v>
       </x:c>
-      <x:c r="H24" s="14" t="n">
-        <x:v>800</x:v>
-      </x:c>
-      <x:c r="I24" s="11" t="str">
-        <x:v>NTD</x:v>
-      </x:c>
-      <x:c r="J24" s="11" t="n">
+      <x:c r="H24" s="19" t="n">
+        <x:v>25.153277786511556</x:v>
+      </x:c>
+      <x:c r="I24" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K24" s="11" t="n">
+      <x:c r="J24" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L24" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H24),H24&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I24="NTD",I24="USD")),IF(I24="USD",H24*Summary!$F$5,H24),"")</x:f>
-        <x:v>800</x:v>
-      </x:c>
-      <x:c r="M24" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H24),H24&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I24="NTD",I24="USD")),IF(I24="USD",H24,H24/Summary!$F$5),"")</x:f>
+      <x:c r="K24" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(E24),E24&gt;=0,ISNUMBER(H24),H24&gt;=0),E24*H24,"")</x:f>
         <x:v>25.153277786511556</x:v>
       </x:c>
-      <x:c r="N24" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E24),E24&gt;=0,ISNUMBER(L24)),E24*L24,"")</x:f>
-        <x:v>800</x:v>
-      </x:c>
-      <x:c r="O24" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E24),E24&gt;=0,ISNUMBER(M24)),E24*M24,"")</x:f>
+      <x:c r="L24" s="10" t="n">
+        <x:f>IF(AND(ISNUMBER(E24),E24&gt;=0,ISNUMBER(I24),I24&gt;0,ISNUMBER(J24),J24&gt;=0),ROUNDUP(MAX(0,E24-J24)/I24,0),"")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M24" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(L24),ISNUMBER(H24),H24&gt;=0),L24*I24*H24,"")</x:f>
         <x:v>25.153277786511556</x:v>
       </x:c>
-      <x:c r="P24" s="10" t="n">
-        <x:f>IF(AND(ISNUMBER(E24),E24&gt;=0,ISNUMBER(J24),J24&gt;0,ISNUMBER(K24),K24&gt;=0),ROUNDUP(MAX(0,E24-K24)/J24,0),"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q24" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P24),ISNUMBER(L24)),P24*J24*L24,"")</x:f>
-        <x:v>800</x:v>
-      </x:c>
-      <x:c r="R24" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P24),ISNUMBER(M24)),P24*J24*M24,"")</x:f>
-        <x:v>25.153277786511556</x:v>
-      </x:c>
-      <x:c r="S24" s="10" t="str">
+      <x:c r="N24" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="T24" s="10" t="str"/>
-      <x:c r="U24" s="10" t="str">
+      <x:c r="O24" s="10" t="str"/>
+      <x:c r="P24" s="10" t="str">
         <x:v>Budget is not a confirmed compatible-part quotation. Borrow first; confirm model before purchase.</x:v>
       </x:c>
-      <x:c r="V24" s="10" t="str">
+      <x:c r="Q24" s="10" t="str">
         <x:v>TOOLS
+Original unit input: NTD 800. Converted at 31.805 NTD/USD.
 Engineering allowances only: hand tools/calipers NTD 1500; DMM 800; scope 10000; pipette/tips 4000; print/post-cure supplies 300. Borrow existing printer, wash/cure equipment, PC, phone, biosafety/cell facilities. Their capital replacement prices are outside this BOM.
 </x:v>
       </x:c>
-      <x:c r="W24" s="10" t="str">
-        <x:f>IF(AND(ISNUMBER(N24),ISNUMBER(Q24)),"OK","Missing")</x:f>
+      <x:c r="R24" s="10" t="str">
+        <x:f>IF(AND(ISNUMBER(K24),ISNUMBER(M24)),"OK","Missing")</x:f>
         <x:v>OK</x:v>
       </x:c>
-    </x:row>
-    <x:row r="25" ht="123" customHeight="1">
+      <x:c r="S24"/>
+      <x:c r="T24"/>
+      <x:c r="U24"/>
+      <x:c r="V24"/>
+      <x:c r="W24"/>
+    </x:row>
+    <x:row r="25" ht="153" customHeight="1">
       <x:c r="A25" s="10" t="str">
         <x:v>L06</x:v>
       </x:c>
@@ -5417,64 +5218,51 @@
       <x:c r="G25" s="10" t="str">
         <x:v>Developer</x:v>
       </x:c>
-      <x:c r="H25" s="14" t="n">
-        <x:v>10000</x:v>
-      </x:c>
-      <x:c r="I25" s="11" t="str">
-        <x:v>NTD</x:v>
-      </x:c>
-      <x:c r="J25" s="11" t="n">
+      <x:c r="H25" s="19" t="n">
+        <x:v>314.4159723313944</x:v>
+      </x:c>
+      <x:c r="I25" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K25" s="11" t="n">
+      <x:c r="J25" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L25" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H25),H25&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I25="NTD",I25="USD")),IF(I25="USD",H25*Summary!$F$5,H25),"")</x:f>
-        <x:v>10000</x:v>
-      </x:c>
-      <x:c r="M25" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H25),H25&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I25="NTD",I25="USD")),IF(I25="USD",H25,H25/Summary!$F$5),"")</x:f>
+      <x:c r="K25" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(E25),E25&gt;=0,ISNUMBER(H25),H25&gt;=0),E25*H25,"")</x:f>
         <x:v>314.4159723313944</x:v>
       </x:c>
-      <x:c r="N25" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E25),E25&gt;=0,ISNUMBER(L25)),E25*L25,"")</x:f>
-        <x:v>10000</x:v>
-      </x:c>
-      <x:c r="O25" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E25),E25&gt;=0,ISNUMBER(M25)),E25*M25,"")</x:f>
+      <x:c r="L25" s="10" t="n">
+        <x:f>IF(AND(ISNUMBER(E25),E25&gt;=0,ISNUMBER(I25),I25&gt;0,ISNUMBER(J25),J25&gt;=0),ROUNDUP(MAX(0,E25-J25)/I25,0),"")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M25" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(L25),ISNUMBER(H25),H25&gt;=0),L25*I25*H25,"")</x:f>
         <x:v>314.4159723313944</x:v>
       </x:c>
-      <x:c r="P25" s="10" t="n">
-        <x:f>IF(AND(ISNUMBER(E25),E25&gt;=0,ISNUMBER(J25),J25&gt;0,ISNUMBER(K25),K25&gt;=0),ROUNDUP(MAX(0,E25-K25)/J25,0),"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q25" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P25),ISNUMBER(L25)),P25*J25*L25,"")</x:f>
-        <x:v>10000</x:v>
-      </x:c>
-      <x:c r="R25" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P25),ISNUMBER(M25)),P25*J25*M25,"")</x:f>
-        <x:v>314.4159723313944</x:v>
-      </x:c>
-      <x:c r="S25" s="10" t="str">
+      <x:c r="N25" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="T25" s="10" t="str"/>
-      <x:c r="U25" s="10" t="str">
+      <x:c r="O25" s="10" t="str"/>
+      <x:c r="P25" s="10" t="str">
         <x:v>Budget is not a confirmed compatible-part quotation. Borrow first; confirm model before purchase.</x:v>
       </x:c>
-      <x:c r="V25" s="10" t="str">
+      <x:c r="Q25" s="10" t="str">
         <x:v>TOOLS
+Original unit input: NTD 10000. Converted at 31.805 NTD/USD.
 Engineering allowances only: hand tools/calipers NTD 1500; DMM 800; scope 10000; pipette/tips 4000; print/post-cure supplies 300. Borrow existing printer, wash/cure equipment, PC, phone, biosafety/cell facilities. Their capital replacement prices are outside this BOM.
 </x:v>
       </x:c>
-      <x:c r="W25" s="10" t="str">
-        <x:f>IF(AND(ISNUMBER(N25),ISNUMBER(Q25)),"OK","Missing")</x:f>
+      <x:c r="R25" s="10" t="str">
+        <x:f>IF(AND(ISNUMBER(K25),ISNUMBER(M25)),"OK","Missing")</x:f>
         <x:v>OK</x:v>
       </x:c>
-    </x:row>
-    <x:row r="26" ht="123" customHeight="1">
+      <x:c r="S25"/>
+      <x:c r="T25"/>
+      <x:c r="U25"/>
+      <x:c r="V25"/>
+      <x:c r="W25"/>
+    </x:row>
+    <x:row r="26" ht="153" customHeight="1">
       <x:c r="A26" s="10" t="str">
         <x:v>L07</x:v>
       </x:c>
@@ -5497,64 +5285,51 @@
       <x:c r="G26" s="10" t="str">
         <x:v>Developer</x:v>
       </x:c>
-      <x:c r="H26" s="14" t="n">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="I26" s="11" t="str">
-        <x:v>NTD</x:v>
-      </x:c>
-      <x:c r="J26" s="11" t="n">
+      <x:c r="H26" s="19" t="n">
+        <x:v>125.76638893255777</x:v>
+      </x:c>
+      <x:c r="I26" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K26" s="11" t="n">
+      <x:c r="J26" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L26" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H26),H26&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I26="NTD",I26="USD")),IF(I26="USD",H26*Summary!$F$5,H26),"")</x:f>
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="M26" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H26),H26&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I26="NTD",I26="USD")),IF(I26="USD",H26,H26/Summary!$F$5),"")</x:f>
+      <x:c r="K26" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(E26),E26&gt;=0,ISNUMBER(H26),H26&gt;=0),E26*H26,"")</x:f>
         <x:v>125.76638893255777</x:v>
       </x:c>
-      <x:c r="N26" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E26),E26&gt;=0,ISNUMBER(L26)),E26*L26,"")</x:f>
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="O26" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E26),E26&gt;=0,ISNUMBER(M26)),E26*M26,"")</x:f>
+      <x:c r="L26" s="10" t="n">
+        <x:f>IF(AND(ISNUMBER(E26),E26&gt;=0,ISNUMBER(I26),I26&gt;0,ISNUMBER(J26),J26&gt;=0),ROUNDUP(MAX(0,E26-J26)/I26,0),"")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M26" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(L26),ISNUMBER(H26),H26&gt;=0),L26*I26*H26,"")</x:f>
         <x:v>125.76638893255777</x:v>
       </x:c>
-      <x:c r="P26" s="10" t="n">
-        <x:f>IF(AND(ISNUMBER(E26),E26&gt;=0,ISNUMBER(J26),J26&gt;0,ISNUMBER(K26),K26&gt;=0),ROUNDUP(MAX(0,E26-K26)/J26,0),"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q26" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P26),ISNUMBER(L26)),P26*J26*L26,"")</x:f>
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R26" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P26),ISNUMBER(M26)),P26*J26*M26,"")</x:f>
-        <x:v>125.76638893255777</x:v>
-      </x:c>
-      <x:c r="S26" s="10" t="str">
+      <x:c r="N26" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="T26" s="10" t="str"/>
-      <x:c r="U26" s="10" t="str">
+      <x:c r="O26" s="10" t="str"/>
+      <x:c r="P26" s="10" t="str">
         <x:v>Budget is not a confirmed compatible-part quotation. Borrow first; confirm model before purchase.</x:v>
       </x:c>
-      <x:c r="V26" s="10" t="str">
+      <x:c r="Q26" s="10" t="str">
         <x:v>TOOLS
+Original unit input: NTD 4000. Converted at 31.805 NTD/USD.
 Engineering allowances only: hand tools/calipers NTD 1500; DMM 800; scope 10000; pipette/tips 4000; print/post-cure supplies 300. Borrow existing printer, wash/cure equipment, PC, phone, biosafety/cell facilities. Their capital replacement prices are outside this BOM.
 </x:v>
       </x:c>
-      <x:c r="W26" s="10" t="str">
-        <x:f>IF(AND(ISNUMBER(N26),ISNUMBER(Q26)),"OK","Missing")</x:f>
+      <x:c r="R26" s="10" t="str">
+        <x:f>IF(AND(ISNUMBER(K26),ISNUMBER(M26)),"OK","Missing")</x:f>
         <x:v>OK</x:v>
       </x:c>
-    </x:row>
-    <x:row r="27" ht="123" customHeight="1">
+      <x:c r="S26"/>
+      <x:c r="T26"/>
+      <x:c r="U26"/>
+      <x:c r="V26"/>
+      <x:c r="W26"/>
+    </x:row>
+    <x:row r="27" ht="138" customHeight="1">
       <x:c r="A27" s="10" t="str">
         <x:v>L08</x:v>
       </x:c>
@@ -5577,64 +5352,51 @@
       <x:c r="G27" s="10" t="str">
         <x:v>Developer</x:v>
       </x:c>
-      <x:c r="H27" s="14" t="n">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="I27" s="11" t="str">
-        <x:v>NTD</x:v>
-      </x:c>
-      <x:c r="J27" s="11" t="n">
+      <x:c r="H27" s="19" t="n">
+        <x:v>9.432479169941834</x:v>
+      </x:c>
+      <x:c r="I27" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K27" s="11" t="n">
+      <x:c r="J27" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L27" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H27),H27&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I27="NTD",I27="USD")),IF(I27="USD",H27*Summary!$F$5,H27),"")</x:f>
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="M27" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H27),H27&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I27="NTD",I27="USD")),IF(I27="USD",H27,H27/Summary!$F$5),"")</x:f>
+      <x:c r="K27" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(E27),E27&gt;=0,ISNUMBER(H27),H27&gt;=0),E27*H27,"")</x:f>
         <x:v>9.432479169941834</x:v>
       </x:c>
-      <x:c r="N27" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E27),E27&gt;=0,ISNUMBER(L27)),E27*L27,"")</x:f>
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="O27" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E27),E27&gt;=0,ISNUMBER(M27)),E27*M27,"")</x:f>
+      <x:c r="L27" s="10" t="n">
+        <x:f>IF(AND(ISNUMBER(E27),E27&gt;=0,ISNUMBER(I27),I27&gt;0,ISNUMBER(J27),J27&gt;=0),ROUNDUP(MAX(0,E27-J27)/I27,0),"")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M27" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(L27),ISNUMBER(H27),H27&gt;=0),L27*I27*H27,"")</x:f>
         <x:v>9.432479169941834</x:v>
       </x:c>
-      <x:c r="P27" s="10" t="n">
-        <x:f>IF(AND(ISNUMBER(E27),E27&gt;=0,ISNUMBER(J27),J27&gt;0,ISNUMBER(K27),K27&gt;=0),ROUNDUP(MAX(0,E27-K27)/J27,0),"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q27" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P27),ISNUMBER(L27)),P27*J27*L27,"")</x:f>
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="R27" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P27),ISNUMBER(M27)),P27*J27*M27,"")</x:f>
-        <x:v>9.432479169941834</x:v>
-      </x:c>
-      <x:c r="S27" s="10" t="str">
+      <x:c r="N27" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="T27" s="10" t="str"/>
-      <x:c r="U27" s="10" t="str">
+      <x:c r="O27" s="10" t="str"/>
+      <x:c r="P27" s="10" t="str">
         <x:v>Budget is not a confirmed compatible-part quotation. Borrow first; confirm model before purchase.</x:v>
       </x:c>
-      <x:c r="V27" s="10" t="str">
+      <x:c r="Q27" s="10" t="str">
         <x:v>TOOLS
+Original unit input: NTD 300. Converted at 31.805 NTD/USD.
 Engineering allowances only: hand tools/calipers NTD 1500; DMM 800; scope 10000; pipette/tips 4000; print/post-cure supplies 300. Borrow existing printer, wash/cure equipment, PC, phone, biosafety/cell facilities. Their capital replacement prices are outside this BOM.
 </x:v>
       </x:c>
-      <x:c r="W27" s="10" t="str">
-        <x:f>IF(AND(ISNUMBER(N27),ISNUMBER(Q27)),"OK","Missing")</x:f>
+      <x:c r="R27" s="10" t="str">
+        <x:f>IF(AND(ISNUMBER(K27),ISNUMBER(M27)),"OK","Missing")</x:f>
         <x:v>OK</x:v>
       </x:c>
-    </x:row>
-    <x:row r="28" ht="108" customHeight="1">
+      <x:c r="S27"/>
+      <x:c r="T27"/>
+      <x:c r="U27"/>
+      <x:c r="V27"/>
+      <x:c r="W27"/>
+    </x:row>
+    <x:row r="28" ht="138" customHeight="1">
       <x:c r="A28" s="10" t="str">
         <x:v>FUT01</x:v>
       </x:c>
@@ -5657,64 +5419,51 @@
       <x:c r="G28" s="10" t="str">
         <x:v>Future</x:v>
       </x:c>
-      <x:c r="H28" s="14" t="n">
-        <x:v>6000</x:v>
-      </x:c>
-      <x:c r="I28" s="11" t="str">
-        <x:v>NTD</x:v>
-      </x:c>
-      <x:c r="J28" s="11" t="n">
+      <x:c r="H28" s="19" t="n">
+        <x:v>188.64958339883665</x:v>
+      </x:c>
+      <x:c r="I28" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K28" s="11" t="n">
+      <x:c r="J28" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L28" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H28),H28&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I28="NTD",I28="USD")),IF(I28="USD",H28*Summary!$F$5,H28),"")</x:f>
-        <x:v>6000</x:v>
-      </x:c>
-      <x:c r="M28" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H28),H28&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I28="NTD",I28="USD")),IF(I28="USD",H28,H28/Summary!$F$5),"")</x:f>
+      <x:c r="K28" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(E28),E28&gt;=0,ISNUMBER(H28),H28&gt;=0),E28*H28,"")</x:f>
         <x:v>188.64958339883665</x:v>
       </x:c>
-      <x:c r="N28" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E28),E28&gt;=0,ISNUMBER(L28)),E28*L28,"")</x:f>
-        <x:v>6000</x:v>
-      </x:c>
-      <x:c r="O28" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E28),E28&gt;=0,ISNUMBER(M28)),E28*M28,"")</x:f>
+      <x:c r="L28" s="10" t="n">
+        <x:f>IF(AND(ISNUMBER(E28),E28&gt;=0,ISNUMBER(I28),I28&gt;0,ISNUMBER(J28),J28&gt;=0),ROUNDUP(MAX(0,E28-J28)/I28,0),"")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M28" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(L28),ISNUMBER(H28),H28&gt;=0),L28*I28*H28,"")</x:f>
         <x:v>188.64958339883665</x:v>
       </x:c>
-      <x:c r="P28" s="10" t="n">
-        <x:f>IF(AND(ISNUMBER(E28),E28&gt;=0,ISNUMBER(J28),J28&gt;0,ISNUMBER(K28),K28&gt;=0),ROUNDUP(MAX(0,E28-K28)/J28,0),"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q28" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P28),ISNUMBER(L28)),P28*J28*L28,"")</x:f>
-        <x:v>6000</x:v>
-      </x:c>
-      <x:c r="R28" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P28),ISNUMBER(M28)),P28*J28*M28,"")</x:f>
-        <x:v>188.64958339883665</x:v>
-      </x:c>
-      <x:c r="S28" s="10" t="str">
+      <x:c r="N28" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="T28" s="10" t="str"/>
-      <x:c r="U28" s="10" t="str">
+      <x:c r="O28" s="10" t="str"/>
+      <x:c r="P28" s="10" t="str">
         <x:v>Budget is not a confirmed compatible-part quotation. Borrow first; confirm model before purchase.</x:v>
       </x:c>
-      <x:c r="V28" s="10" t="str">
+      <x:c r="Q28" s="10" t="str">
         <x:v>PDMS
+Original unit input: NTD 6000. Converted at 31.805 NTD/USD.
 Kit identity found; current public price not verified. NTD 6000 planning allowance for kit and basic casting consumables. No claim that PDMS removes water selectively.
 https://labproinc.com/products/dow-sylgard-184-silicone-encapsulant-clear-0-5-kg-kit-184-sil-elast-kit-0-5kg</x:v>
       </x:c>
-      <x:c r="W28" s="10" t="str">
-        <x:f>IF(AND(ISNUMBER(N28),ISNUMBER(Q28)),"OK","Missing")</x:f>
+      <x:c r="R28" s="10" t="str">
+        <x:f>IF(AND(ISNUMBER(K28),ISNUMBER(M28)),"OK","Missing")</x:f>
         <x:v>OK</x:v>
       </x:c>
-    </x:row>
-    <x:row r="29" ht="108" customHeight="1">
+      <x:c r="S28"/>
+      <x:c r="T28"/>
+      <x:c r="U28"/>
+      <x:c r="V28"/>
+      <x:c r="W28"/>
+    </x:row>
+    <x:row r="29" ht="123" customHeight="1">
       <x:c r="A29" s="10" t="str">
         <x:v>FUT02</x:v>
       </x:c>
@@ -5737,64 +5486,51 @@
       <x:c r="G29" s="10" t="str">
         <x:v>Future</x:v>
       </x:c>
-      <x:c r="H29" s="14" t="n">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="I29" s="11" t="str">
-        <x:v>NTD</x:v>
-      </x:c>
-      <x:c r="J29" s="11" t="n">
+      <x:c r="H29" s="19" t="n">
+        <x:v>15.720798616569722</x:v>
+      </x:c>
+      <x:c r="I29" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K29" s="11" t="n">
+      <x:c r="J29" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L29" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H29),H29&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I29="NTD",I29="USD")),IF(I29="USD",H29*Summary!$F$5,H29),"")</x:f>
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="M29" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H29),H29&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I29="NTD",I29="USD")),IF(I29="USD",H29,H29/Summary!$F$5),"")</x:f>
+      <x:c r="K29" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(E29),E29&gt;=0,ISNUMBER(H29),H29&gt;=0),E29*H29,"")</x:f>
         <x:v>15.720798616569722</x:v>
       </x:c>
-      <x:c r="N29" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E29),E29&gt;=0,ISNUMBER(L29)),E29*L29,"")</x:f>
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="O29" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E29),E29&gt;=0,ISNUMBER(M29)),E29*M29,"")</x:f>
+      <x:c r="L29" s="10" t="n">
+        <x:f>IF(AND(ISNUMBER(E29),E29&gt;=0,ISNUMBER(I29),I29&gt;0,ISNUMBER(J29),J29&gt;=0),ROUNDUP(MAX(0,E29-J29)/I29,0),"")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M29" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(L29),ISNUMBER(H29),H29&gt;=0),L29*I29*H29,"")</x:f>
         <x:v>15.720798616569722</x:v>
       </x:c>
-      <x:c r="P29" s="10" t="n">
-        <x:f>IF(AND(ISNUMBER(E29),E29&gt;=0,ISNUMBER(J29),J29&gt;0,ISNUMBER(K29),K29&gt;=0),ROUNDUP(MAX(0,E29-K29)/J29,0),"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q29" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P29),ISNUMBER(L29)),P29*J29*L29,"")</x:f>
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="R29" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P29),ISNUMBER(M29)),P29*J29*M29,"")</x:f>
-        <x:v>15.720798616569722</x:v>
-      </x:c>
-      <x:c r="S29" s="10" t="str">
+      <x:c r="N29" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="T29" s="10" t="str"/>
-      <x:c r="U29" s="10" t="str">
+      <x:c r="O29" s="10" t="str"/>
+      <x:c r="P29" s="10" t="str">
         <x:v>Budget is not a confirmed compatible-part quotation. Borrow first; confirm model before purchase.</x:v>
       </x:c>
-      <x:c r="V29" s="10" t="str">
+      <x:c r="Q29" s="10" t="str">
         <x:v>VALVE
+Original unit input: NTD 500. Converted at 31.805 NTD/USD.
 USD 2.95 for 6 V valve alone. NTD 500 system allowance includes driver, flyback diode, supply and fittings. Future only; VOC wetted-material suitability and firmware support unverified.
 https://www.adafruit.com/product/4663</x:v>
       </x:c>
-      <x:c r="W29" s="10" t="str">
-        <x:f>IF(AND(ISNUMBER(N29),ISNUMBER(Q29)),"OK","Missing")</x:f>
+      <x:c r="R29" s="10" t="str">
+        <x:f>IF(AND(ISNUMBER(K29),ISNUMBER(M29)),"OK","Missing")</x:f>
         <x:v>OK</x:v>
       </x:c>
-    </x:row>
-    <x:row r="30" ht="123" customHeight="1">
+      <x:c r="S29"/>
+      <x:c r="T29"/>
+      <x:c r="U29"/>
+      <x:c r="V29"/>
+      <x:c r="W29"/>
+    </x:row>
+    <x:row r="30" ht="153" customHeight="1">
       <x:c r="A30" s="10" t="str">
         <x:v>FUT03</x:v>
       </x:c>
@@ -5817,187 +5553,174 @@
       <x:c r="G30" s="10" t="str">
         <x:v>Future</x:v>
       </x:c>
-      <x:c r="H30" s="14" t="n">
-        <x:v>1000</x:v>
-      </x:c>
-      <x:c r="I30" s="11" t="str">
-        <x:v>NTD</x:v>
-      </x:c>
-      <x:c r="J30" s="11" t="n">
+      <x:c r="H30" s="19" t="n">
+        <x:v>31.441597233139444</x:v>
+      </x:c>
+      <x:c r="I30" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K30" s="11" t="n">
+      <x:c r="J30" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L30" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H30),H30&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I30="NTD",I30="USD")),IF(I30="USD",H30*Summary!$F$5,H30),"")</x:f>
-        <x:v>1000</x:v>
-      </x:c>
-      <x:c r="M30" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(H30),H30&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0,OR(I30="NTD",I30="USD")),IF(I30="USD",H30,H30/Summary!$F$5),"")</x:f>
+      <x:c r="K30" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(E30),E30&gt;=0,ISNUMBER(H30),H30&gt;=0),E30*H30,"")</x:f>
         <x:v>31.441597233139444</x:v>
       </x:c>
-      <x:c r="N30" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E30),E30&gt;=0,ISNUMBER(L30)),E30*L30,"")</x:f>
-        <x:v>1000</x:v>
-      </x:c>
-      <x:c r="O30" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(E30),E30&gt;=0,ISNUMBER(M30)),E30*M30,"")</x:f>
+      <x:c r="L30" s="10" t="n">
+        <x:f>IF(AND(ISNUMBER(E30),E30&gt;=0,ISNUMBER(I30),I30&gt;0,ISNUMBER(J30),J30&gt;=0),ROUNDUP(MAX(0,E30-J30)/I30,0),"")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M30" s="24" t="n">
+        <x:f>IF(AND(ISNUMBER(L30),ISNUMBER(H30),H30&gt;=0),L30*I30*H30,"")</x:f>
         <x:v>31.441597233139444</x:v>
       </x:c>
-      <x:c r="P30" s="10" t="n">
-        <x:f>IF(AND(ISNUMBER(E30),E30&gt;=0,ISNUMBER(J30),J30&gt;0,ISNUMBER(K30),K30&gt;=0),ROUNDUP(MAX(0,E30-K30)/J30,0),"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q30" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P30),ISNUMBER(L30)),P30*J30*L30,"")</x:f>
-        <x:v>1000</x:v>
-      </x:c>
-      <x:c r="R30" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(P30),ISNUMBER(M30)),P30*J30*M30,"")</x:f>
-        <x:v>31.441597233139444</x:v>
-      </x:c>
-      <x:c r="S30" s="10" t="str">
+      <x:c r="N30" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="T30" s="10" t="str"/>
-      <x:c r="U30" s="10" t="str">
+      <x:c r="O30" s="10" t="str"/>
+      <x:c r="P30" s="10" t="str">
         <x:v>Budget is not a confirmed compatible-part quotation. Borrow first; confirm model before purchase.</x:v>
       </x:c>
-      <x:c r="V30" s="10" t="str">
+      <x:c r="Q30" s="10" t="str">
         <x:v>TOOLS
+Original unit input: NTD 1000. Converted at 31.805 NTD/USD.
 Engineering allowances only: hand tools/calipers NTD 1500; DMM 800; scope 10000; pipette/tips 4000; print/post-cure supplies 300. Borrow existing printer, wash/cure equipment, PC, phone, biosafety/cell facilities. Their capital replacement prices are outside this BOM.
 </x:v>
       </x:c>
-      <x:c r="W30" s="10" t="str">
-        <x:f>IF(AND(ISNUMBER(N30),ISNUMBER(Q30)),"OK","Missing")</x:f>
+      <x:c r="R30" s="10" t="str">
+        <x:f>IF(AND(ISNUMBER(K30),ISNUMBER(M30)),"OK","Missing")</x:f>
         <x:v>OK</x:v>
       </x:c>
-    </x:row>
-    <x:row r="31" ht="28" customHeight="1">
-      <x:c r="A31" s="2"/>
-      <x:c r="B31" s="2"/>
-      <x:c r="C31" s="2"/>
-      <x:c r="D31" s="2"/>
-      <x:c r="E31" s="2"/>
-      <x:c r="F31" s="2"/>
-      <x:c r="G31" s="2"/>
-      <x:c r="H31" s="2"/>
-      <x:c r="I31" s="2"/>
-      <x:c r="J31" s="2"/>
-      <x:c r="K31" s="2"/>
-      <x:c r="L31" s="2"/>
-      <x:c r="M31" s="2"/>
-      <x:c r="N31" s="2"/>
-      <x:c r="O31" s="2"/>
-      <x:c r="P31" s="2"/>
-      <x:c r="Q31" s="2"/>
-      <x:c r="R31" s="2"/>
-      <x:c r="S31" s="2"/>
-      <x:c r="T31" s="2"/>
-      <x:c r="U31" s="2"/>
-      <x:c r="V31" s="2"/>
-      <x:c r="W31" s="2"/>
-    </x:row>
-    <x:row r="32" ht="28" customHeight="1">
-      <x:c r="A32" s="2"/>
-      <x:c r="B32" s="2"/>
-      <x:c r="C32" s="2"/>
-      <x:c r="D32" s="2"/>
-      <x:c r="E32" s="2"/>
-      <x:c r="F32" s="2"/>
-      <x:c r="G32" s="2"/>
-      <x:c r="H32" s="2"/>
-      <x:c r="I32" s="2"/>
-      <x:c r="J32" s="2"/>
-      <x:c r="K32" s="2"/>
-      <x:c r="L32" s="2"/>
-      <x:c r="M32" s="2"/>
-      <x:c r="N32" s="2"/>
-      <x:c r="O32" s="2"/>
-      <x:c r="P32" s="2"/>
-      <x:c r="Q32" s="2"/>
-      <x:c r="R32" s="2"/>
-      <x:c r="S32" s="2"/>
-      <x:c r="T32" s="2"/>
-      <x:c r="U32" s="2"/>
-      <x:c r="V32" s="2"/>
-      <x:c r="W32" s="2"/>
-    </x:row>
-    <x:row r="33" ht="28" customHeight="1">
-      <x:c r="A33" s="2"/>
-      <x:c r="B33" s="2"/>
-      <x:c r="C33" s="2"/>
-      <x:c r="D33" s="2"/>
-      <x:c r="E33" s="2"/>
-      <x:c r="F33" s="2"/>
-      <x:c r="G33" s="2"/>
-      <x:c r="H33" s="2"/>
-      <x:c r="I33" s="2"/>
-      <x:c r="J33" s="2"/>
-      <x:c r="K33" s="2"/>
-      <x:c r="L33" s="2"/>
-      <x:c r="M33" s="2"/>
-      <x:c r="N33" s="2"/>
-      <x:c r="O33" s="2"/>
-      <x:c r="P33" s="2"/>
-      <x:c r="Q33" s="2"/>
-      <x:c r="R33" s="2"/>
-      <x:c r="S33" s="2"/>
-      <x:c r="T33" s="2"/>
-      <x:c r="U33" s="2"/>
-      <x:c r="V33" s="2"/>
-      <x:c r="W33" s="2"/>
-    </x:row>
-    <x:row r="34" ht="28" customHeight="1">
-      <x:c r="A34" s="2"/>
-      <x:c r="B34" s="2"/>
-      <x:c r="C34" s="2"/>
-      <x:c r="D34" s="2"/>
-      <x:c r="E34" s="2"/>
-      <x:c r="F34" s="2"/>
-      <x:c r="G34" s="2"/>
-      <x:c r="H34" s="2"/>
-      <x:c r="I34" s="2"/>
-      <x:c r="J34" s="2"/>
-      <x:c r="K34" s="2"/>
-      <x:c r="L34" s="2"/>
-      <x:c r="M34" s="2"/>
-      <x:c r="N34" s="2"/>
-      <x:c r="O34" s="2"/>
-      <x:c r="P34" s="2"/>
-      <x:c r="Q34" s="2"/>
-      <x:c r="R34" s="2"/>
-      <x:c r="S34" s="2"/>
-      <x:c r="T34" s="2"/>
-      <x:c r="U34" s="2"/>
-      <x:c r="V34" s="2"/>
-      <x:c r="W34" s="2"/>
-    </x:row>
-    <x:row r="35" ht="28" customHeight="1">
-      <x:c r="A35" s="2"/>
-      <x:c r="B35" s="2"/>
-      <x:c r="C35" s="2"/>
-      <x:c r="D35" s="2"/>
-      <x:c r="E35" s="2"/>
-      <x:c r="F35" s="2"/>
-      <x:c r="G35" s="2"/>
-      <x:c r="H35" s="2"/>
-      <x:c r="I35" s="2"/>
-      <x:c r="J35" s="2"/>
-      <x:c r="K35" s="2"/>
-      <x:c r="L35" s="2"/>
-      <x:c r="M35" s="2"/>
-      <x:c r="N35" s="2"/>
-      <x:c r="O35" s="2"/>
-      <x:c r="P35" s="2"/>
-      <x:c r="Q35" s="2"/>
-      <x:c r="R35" s="2"/>
-      <x:c r="S35" s="2"/>
-      <x:c r="T35" s="2"/>
-      <x:c r="U35" s="2"/>
-      <x:c r="V35" s="2"/>
-      <x:c r="W35" s="2"/>
+      <x:c r="S30"/>
+      <x:c r="T30"/>
+      <x:c r="U30"/>
+      <x:c r="V30"/>
+      <x:c r="W30"/>
+    </x:row>
+    <x:row r="31" ht="54" customHeight="1">
+      <x:c r="A31" s="10"/>
+      <x:c r="B31" s="10"/>
+      <x:c r="C31" s="10"/>
+      <x:c r="D31" s="10"/>
+      <x:c r="E31" s="10"/>
+      <x:c r="F31" s="10"/>
+      <x:c r="G31" s="10"/>
+      <x:c r="H31" s="10"/>
+      <x:c r="I31" s="10"/>
+      <x:c r="J31" s="10"/>
+      <x:c r="K31" s="10"/>
+      <x:c r="L31" s="10"/>
+      <x:c r="M31" s="10"/>
+      <x:c r="N31" s="10"/>
+      <x:c r="O31" s="10"/>
+      <x:c r="P31" s="10"/>
+      <x:c r="Q31" s="10"/>
+      <x:c r="R31" s="10"/>
+      <x:c r="S31"/>
+      <x:c r="T31"/>
+      <x:c r="U31"/>
+      <x:c r="V31"/>
+      <x:c r="W31"/>
+    </x:row>
+    <x:row r="32" ht="54" customHeight="1">
+      <x:c r="A32" s="10"/>
+      <x:c r="B32" s="10"/>
+      <x:c r="C32" s="10"/>
+      <x:c r="D32" s="10"/>
+      <x:c r="E32" s="10"/>
+      <x:c r="F32" s="10"/>
+      <x:c r="G32" s="10"/>
+      <x:c r="H32" s="10"/>
+      <x:c r="I32" s="10"/>
+      <x:c r="J32" s="10"/>
+      <x:c r="K32" s="10"/>
+      <x:c r="L32" s="10"/>
+      <x:c r="M32" s="10"/>
+      <x:c r="N32" s="10"/>
+      <x:c r="O32" s="10"/>
+      <x:c r="P32" s="10"/>
+      <x:c r="Q32" s="10"/>
+      <x:c r="R32" s="10"/>
+      <x:c r="S32"/>
+      <x:c r="T32"/>
+      <x:c r="U32"/>
+      <x:c r="V32"/>
+      <x:c r="W32"/>
+    </x:row>
+    <x:row r="33" ht="54" customHeight="1">
+      <x:c r="A33" s="10"/>
+      <x:c r="B33" s="10"/>
+      <x:c r="C33" s="10"/>
+      <x:c r="D33" s="10"/>
+      <x:c r="E33" s="10"/>
+      <x:c r="F33" s="10"/>
+      <x:c r="G33" s="10"/>
+      <x:c r="H33" s="10"/>
+      <x:c r="I33" s="10"/>
+      <x:c r="J33" s="10"/>
+      <x:c r="K33" s="10"/>
+      <x:c r="L33" s="10"/>
+      <x:c r="M33" s="10"/>
+      <x:c r="N33" s="10"/>
+      <x:c r="O33" s="10"/>
+      <x:c r="P33" s="10"/>
+      <x:c r="Q33" s="10"/>
+      <x:c r="R33" s="10"/>
+      <x:c r="S33"/>
+      <x:c r="T33"/>
+      <x:c r="U33"/>
+      <x:c r="V33"/>
+      <x:c r="W33"/>
+    </x:row>
+    <x:row r="34" ht="54" customHeight="1">
+      <x:c r="A34" s="10"/>
+      <x:c r="B34" s="10"/>
+      <x:c r="C34" s="10"/>
+      <x:c r="D34" s="10"/>
+      <x:c r="E34" s="10"/>
+      <x:c r="F34" s="10"/>
+      <x:c r="G34" s="10"/>
+      <x:c r="H34" s="10"/>
+      <x:c r="I34" s="10"/>
+      <x:c r="J34" s="10"/>
+      <x:c r="K34" s="10"/>
+      <x:c r="L34" s="10"/>
+      <x:c r="M34" s="10"/>
+      <x:c r="N34" s="10"/>
+      <x:c r="O34" s="10"/>
+      <x:c r="P34" s="10"/>
+      <x:c r="Q34" s="10"/>
+      <x:c r="R34" s="10"/>
+      <x:c r="S34"/>
+      <x:c r="T34"/>
+      <x:c r="U34"/>
+      <x:c r="V34"/>
+      <x:c r="W34"/>
+    </x:row>
+    <x:row r="35" ht="54" customHeight="1">
+      <x:c r="A35" s="10"/>
+      <x:c r="B35" s="10"/>
+      <x:c r="C35" s="10"/>
+      <x:c r="D35" s="10"/>
+      <x:c r="E35" s="10"/>
+      <x:c r="F35" s="10"/>
+      <x:c r="G35" s="10"/>
+      <x:c r="H35" s="10"/>
+      <x:c r="I35" s="10"/>
+      <x:c r="J35" s="10"/>
+      <x:c r="K35" s="10"/>
+      <x:c r="L35" s="10"/>
+      <x:c r="M35" s="10"/>
+      <x:c r="N35" s="10"/>
+      <x:c r="O35" s="10"/>
+      <x:c r="P35" s="10"/>
+      <x:c r="Q35" s="10"/>
+      <x:c r="R35" s="10"/>
+      <x:c r="S35"/>
+      <x:c r="T35"/>
+      <x:c r="U35"/>
+      <x:c r="V35"/>
+      <x:c r="W35"/>
     </x:row>
     <x:row r="36" ht="28" customHeight="1">
       <x:c r="A36" s="2"/>
@@ -8143,9 +7866,9 @@
     <x:col min="8" max="8" width="36" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="4" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="15" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="16" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="16" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="20" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="62" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="20" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="58" hidden="0" customWidth="1"/>
   </x:cols>
@@ -8206,51 +7929,47 @@
       <x:c r="O3" s="2"/>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
-      <x:c r="A4" s="8" t="str">
+      <x:c r="A4" s="23" t="str">
         <x:v>Row</x:v>
       </x:c>
-      <x:c r="B4" s="8" t="str">
+      <x:c r="B4" s="23" t="str">
         <x:v>Reference</x:v>
       </x:c>
-      <x:c r="C4" s="8" t="str">
+      <x:c r="C4" s="23" t="str">
         <x:v>Name</x:v>
       </x:c>
-      <x:c r="D4" s="8" t="str">
+      <x:c r="D4" s="23" t="str">
         <x:v>Qty</x:v>
       </x:c>
-      <x:c r="E4" s="8" t="str">
+      <x:c r="E4" s="23" t="str">
         <x:v>Vendor value</x:v>
       </x:c>
-      <x:c r="F4" s="8" t="str">
+      <x:c r="F4" s="23" t="str">
         <x:v>Specification</x:v>
       </x:c>
-      <x:c r="G4" s="8" t="str">
+      <x:c r="G4" s="23" t="str">
         <x:v>Purpose and location</x:v>
       </x:c>
-      <x:c r="H4" s="8" t="str">
+      <x:c r="H4" s="23" t="str">
         <x:v>Missing details</x:v>
       </x:c>
-      <x:c r="I4" s="8" t="str"/>
-      <x:c r="J4" s="8" t="str">
-        <x:v>Unit NTD</x:v>
-      </x:c>
-      <x:c r="K4" s="8" t="str">
+      <x:c r="I4" s="23" t="str"/>
+      <x:c r="J4" s="23" t="str">
         <x:v>Unit USD</x:v>
       </x:c>
-      <x:c r="L4" s="8" t="str">
-        <x:v>Material NTD</x:v>
-      </x:c>
-      <x:c r="M4" s="8" t="str">
+      <x:c r="K4" s="23" t="str">
         <x:v>Material USD</x:v>
       </x:c>
-      <x:c r="N4" s="8" t="str">
+      <x:c r="L4" s="23" t="str">
         <x:v>Price type</x:v>
       </x:c>
-      <x:c r="O4" s="8" t="str">
-        <x:v>Sources and price limits</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="138" customHeight="1">
+      <x:c r="M4" s="23" t="str">
+        <x:v>Sources / original quotations</x:v>
+      </x:c>
+      <x:c r="N4"/>
+      <x:c r="O4"/>
+    </x:row>
+    <x:row r="5" ht="153" customHeight="1">
       <x:c r="A5" s="10" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -8275,31 +7994,26 @@
         <x:v>Confirm MPN,case/height,voltage,tolerance,dielectric and ESR</x:v>
       </x:c>
       <x:c r="I5" s="10" t="str"/>
-      <x:c r="J5" s="14" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K5" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J5),J5&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J5/Summary!$F$5,"")</x:f>
+      <x:c r="J5" s="19" t="n">
         <x:v>0.0628831944662789</x:v>
       </x:c>
-      <x:c r="L5" s="12" t="n">
+      <x:c r="K5" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J5),J5&gt;=0,ISNUMBER(D5),D5&gt;=0),J5*D5,"")</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M5" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K5),ISNUMBER(D5),D5&gt;=0),K5*D5,"")</x:f>
         <x:v>0.0628831944662789</x:v>
       </x:c>
-      <x:c r="N5" s="10" t="str">
+      <x:c r="L5" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O5" s="10" t="str">
+      <x:c r="M5" s="10" t="str">
         <x:v>vendor_BOM row 1; schematic
+Original unit input: NTD 2. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="6" ht="138" customHeight="1">
+      <x:c r="N5"/>
+      <x:c r="O5"/>
+    </x:row>
+    <x:row r="6" ht="153" customHeight="1">
       <x:c r="A6" s="10" t="n">
         <x:v>2</x:v>
       </x:c>
@@ -8324,31 +8038,26 @@
         <x:v>Confirm MPN,case/height,voltage,tolerance,dielectric and ESR</x:v>
       </x:c>
       <x:c r="I6" s="10" t="str"/>
-      <x:c r="J6" s="14" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K6" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J6),J6&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J6/Summary!$F$5,"")</x:f>
+      <x:c r="J6" s="19" t="n">
         <x:v>0.0628831944662789</x:v>
       </x:c>
-      <x:c r="L6" s="12" t="n">
+      <x:c r="K6" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J6),J6&gt;=0,ISNUMBER(D6),D6&gt;=0),J6*D6,"")</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M6" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K6),ISNUMBER(D6),D6&gt;=0),K6*D6,"")</x:f>
         <x:v>0.0628831944662789</x:v>
       </x:c>
-      <x:c r="N6" s="10" t="str">
+      <x:c r="L6" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O6" s="10" t="str">
+      <x:c r="M6" s="10" t="str">
         <x:v>vendor_BOM row 2; schematic
+Original unit input: NTD 2. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="7" ht="138" customHeight="1">
+      <x:c r="N6"/>
+      <x:c r="O6"/>
+    </x:row>
+    <x:row r="7" ht="153" customHeight="1">
       <x:c r="A7" s="10" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -8373,31 +8082,26 @@
         <x:v>Confirm MPN,case/height,voltage,tolerance,dielectric and ESR</x:v>
       </x:c>
       <x:c r="I7" s="10" t="str"/>
-      <x:c r="J7" s="14" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K7" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J7),J7&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J7/Summary!$F$5,"")</x:f>
+      <x:c r="J7" s="19" t="n">
         <x:v>0.0628831944662789</x:v>
       </x:c>
-      <x:c r="L7" s="12" t="n">
+      <x:c r="K7" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J7),J7&gt;=0,ISNUMBER(D7),D7&gt;=0),J7*D7,"")</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M7" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K7),ISNUMBER(D7),D7&gt;=0),K7*D7,"")</x:f>
         <x:v>0.0628831944662789</x:v>
       </x:c>
-      <x:c r="N7" s="10" t="str">
+      <x:c r="L7" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O7" s="10" t="str">
+      <x:c r="M7" s="10" t="str">
         <x:v>vendor_BOM row 3; schematic
+Original unit input: NTD 2. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="8" ht="138" customHeight="1">
+      <x:c r="N7"/>
+      <x:c r="O7"/>
+    </x:row>
+    <x:row r="8" ht="153" customHeight="1">
       <x:c r="A8" s="10" t="n">
         <x:v>4</x:v>
       </x:c>
@@ -8422,31 +8126,26 @@
         <x:v>Confirm MPN,case/height,voltage,tolerance,dielectric and ESR</x:v>
       </x:c>
       <x:c r="I8" s="10" t="str"/>
-      <x:c r="J8" s="14" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K8" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J8),J8&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J8/Summary!$F$5,"")</x:f>
+      <x:c r="J8" s="19" t="n">
         <x:v>0.0628831944662789</x:v>
       </x:c>
-      <x:c r="L8" s="12" t="n">
+      <x:c r="K8" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J8),J8&gt;=0,ISNUMBER(D8),D8&gt;=0),J8*D8,"")</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M8" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K8),ISNUMBER(D8),D8&gt;=0),K8*D8,"")</x:f>
         <x:v>0.0628831944662789</x:v>
       </x:c>
-      <x:c r="N8" s="10" t="str">
+      <x:c r="L8" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O8" s="10" t="str">
+      <x:c r="M8" s="10" t="str">
         <x:v>vendor_BOM row 4; schematic
+Original unit input: NTD 2. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="9" ht="138" customHeight="1">
+      <x:c r="N8"/>
+      <x:c r="O8"/>
+    </x:row>
+    <x:row r="9" ht="153" customHeight="1">
       <x:c r="A9" s="10" t="n">
         <x:v>5</x:v>
       </x:c>
@@ -8471,31 +8170,26 @@
         <x:v>Confirm MPN,case/height,voltage,tolerance,dielectric and ESR</x:v>
       </x:c>
       <x:c r="I9" s="10" t="str"/>
-      <x:c r="J9" s="14" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K9" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J9),J9&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J9/Summary!$F$5,"")</x:f>
+      <x:c r="J9" s="19" t="n">
         <x:v>0.0628831944662789</x:v>
       </x:c>
-      <x:c r="L9" s="12" t="n">
+      <x:c r="K9" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J9),J9&gt;=0,ISNUMBER(D9),D9&gt;=0),J9*D9,"")</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M9" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K9),ISNUMBER(D9),D9&gt;=0),K9*D9,"")</x:f>
         <x:v>0.0628831944662789</x:v>
       </x:c>
-      <x:c r="N9" s="10" t="str">
+      <x:c r="L9" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O9" s="10" t="str">
+      <x:c r="M9" s="10" t="str">
         <x:v>vendor_BOM row 5; schematic
+Original unit input: NTD 2. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="10" ht="138" customHeight="1">
+      <x:c r="N9"/>
+      <x:c r="O9"/>
+    </x:row>
+    <x:row r="10" ht="153" customHeight="1">
       <x:c r="A10" s="10" t="n">
         <x:v>6</x:v>
       </x:c>
@@ -8520,31 +8214,26 @@
         <x:v>Confirm MPN,case/height,voltage,tolerance,dielectric and ESR</x:v>
       </x:c>
       <x:c r="I10" s="10" t="str"/>
-      <x:c r="J10" s="14" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K10" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J10),J10&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J10/Summary!$F$5,"")</x:f>
+      <x:c r="J10" s="19" t="n">
         <x:v>0.0628831944662789</x:v>
       </x:c>
-      <x:c r="L10" s="12" t="n">
+      <x:c r="K10" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J10),J10&gt;=0,ISNUMBER(D10),D10&gt;=0),J10*D10,"")</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M10" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K10),ISNUMBER(D10),D10&gt;=0),K10*D10,"")</x:f>
         <x:v>0.0628831944662789</x:v>
       </x:c>
-      <x:c r="N10" s="10" t="str">
+      <x:c r="L10" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O10" s="10" t="str">
+      <x:c r="M10" s="10" t="str">
         <x:v>vendor_BOM row 6; schematic
+Original unit input: NTD 2. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="11" ht="138" customHeight="1">
+      <x:c r="N10"/>
+      <x:c r="O10"/>
+    </x:row>
+    <x:row r="11" ht="153" customHeight="1">
       <x:c r="A11" s="10" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -8569,31 +8258,26 @@
         <x:v>Confirm MPN,case/height,voltage,tolerance,dielectric and ESR</x:v>
       </x:c>
       <x:c r="I11" s="10" t="str"/>
-      <x:c r="J11" s="14" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K11" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J11),J11&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J11/Summary!$F$5,"")</x:f>
+      <x:c r="J11" s="19" t="n">
         <x:v>0.0628831944662789</x:v>
       </x:c>
-      <x:c r="L11" s="12" t="n">
+      <x:c r="K11" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J11),J11&gt;=0,ISNUMBER(D11),D11&gt;=0),J11*D11,"")</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M11" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K11),ISNUMBER(D11),D11&gt;=0),K11*D11,"")</x:f>
         <x:v>0.0628831944662789</x:v>
       </x:c>
-      <x:c r="N11" s="10" t="str">
+      <x:c r="L11" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O11" s="10" t="str">
+      <x:c r="M11" s="10" t="str">
         <x:v>vendor_BOM row 7; schematic
+Original unit input: NTD 2. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="12" ht="138" customHeight="1">
+      <x:c r="N11"/>
+      <x:c r="O11"/>
+    </x:row>
+    <x:row r="12" ht="153" customHeight="1">
       <x:c r="A12" s="10" t="n">
         <x:v>8</x:v>
       </x:c>
@@ -8618,31 +8302,26 @@
         <x:v>Confirm MPN,case/height,voltage,tolerance,dielectric and ESR</x:v>
       </x:c>
       <x:c r="I12" s="10" t="str"/>
-      <x:c r="J12" s="14" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K12" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J12),J12&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J12/Summary!$F$5,"")</x:f>
+      <x:c r="J12" s="19" t="n">
         <x:v>0.0628831944662789</x:v>
       </x:c>
-      <x:c r="L12" s="12" t="n">
+      <x:c r="K12" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J12),J12&gt;=0,ISNUMBER(D12),D12&gt;=0),J12*D12,"")</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M12" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K12),ISNUMBER(D12),D12&gt;=0),K12*D12,"")</x:f>
         <x:v>0.0628831944662789</x:v>
       </x:c>
-      <x:c r="N12" s="10" t="str">
+      <x:c r="L12" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O12" s="10" t="str">
+      <x:c r="M12" s="10" t="str">
         <x:v>vendor_BOM row 8; schematic
+Original unit input: NTD 2. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="13" ht="138" customHeight="1">
+      <x:c r="N12"/>
+      <x:c r="O12"/>
+    </x:row>
+    <x:row r="13" ht="153" customHeight="1">
       <x:c r="A13" s="10" t="n">
         <x:v>9</x:v>
       </x:c>
@@ -8667,31 +8346,26 @@
         <x:v>Confirm MPN,case/height,voltage,tolerance,dielectric and ESR</x:v>
       </x:c>
       <x:c r="I13" s="10" t="str"/>
-      <x:c r="J13" s="14" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K13" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J13),J13&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J13/Summary!$F$5,"")</x:f>
+      <x:c r="J13" s="19" t="n">
         <x:v>0.0628831944662789</x:v>
       </x:c>
-      <x:c r="L13" s="12" t="n">
+      <x:c r="K13" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J13),J13&gt;=0,ISNUMBER(D13),D13&gt;=0),J13*D13,"")</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M13" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K13),ISNUMBER(D13),D13&gt;=0),K13*D13,"")</x:f>
         <x:v>0.0628831944662789</x:v>
       </x:c>
-      <x:c r="N13" s="10" t="str">
+      <x:c r="L13" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O13" s="10" t="str">
+      <x:c r="M13" s="10" t="str">
         <x:v>vendor_BOM row 9; schematic
+Original unit input: NTD 2. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="14" ht="138" customHeight="1">
+      <x:c r="N13"/>
+      <x:c r="O13"/>
+    </x:row>
+    <x:row r="14" ht="153" customHeight="1">
       <x:c r="A14" s="10" t="n">
         <x:v>10</x:v>
       </x:c>
@@ -8716,31 +8390,26 @@
         <x:v>Confirm MPN,case/height,voltage,tolerance,dielectric and ESR</x:v>
       </x:c>
       <x:c r="I14" s="10" t="str"/>
-      <x:c r="J14" s="14" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K14" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J14),J14&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J14/Summary!$F$5,"")</x:f>
+      <x:c r="J14" s="19" t="n">
         <x:v>0.0628831944662789</x:v>
       </x:c>
-      <x:c r="L14" s="12" t="n">
+      <x:c r="K14" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J14),J14&gt;=0,ISNUMBER(D14),D14&gt;=0),J14*D14,"")</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M14" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K14),ISNUMBER(D14),D14&gt;=0),K14*D14,"")</x:f>
         <x:v>0.0628831944662789</x:v>
       </x:c>
-      <x:c r="N14" s="10" t="str">
+      <x:c r="L14" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O14" s="10" t="str">
+      <x:c r="M14" s="10" t="str">
         <x:v>vendor_BOM row 10; schematic
+Original unit input: NTD 2. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="15" ht="138" customHeight="1">
+      <x:c r="N14"/>
+      <x:c r="O14"/>
+    </x:row>
+    <x:row r="15" ht="153" customHeight="1">
       <x:c r="A15" s="10" t="n">
         <x:v>11</x:v>
       </x:c>
@@ -8765,31 +8434,26 @@
         <x:v>Confirm MPN,case/height,voltage,tolerance,dielectric and ESR</x:v>
       </x:c>
       <x:c r="I15" s="10" t="str"/>
-      <x:c r="J15" s="14" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K15" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J15),J15&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J15/Summary!$F$5,"")</x:f>
+      <x:c r="J15" s="19" t="n">
         <x:v>0.0628831944662789</x:v>
       </x:c>
-      <x:c r="L15" s="12" t="n">
+      <x:c r="K15" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J15),J15&gt;=0,ISNUMBER(D15),D15&gt;=0),J15*D15,"")</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M15" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K15),ISNUMBER(D15),D15&gt;=0),K15*D15,"")</x:f>
         <x:v>0.0628831944662789</x:v>
       </x:c>
-      <x:c r="N15" s="10" t="str">
+      <x:c r="L15" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O15" s="10" t="str">
+      <x:c r="M15" s="10" t="str">
         <x:v>vendor_BOM row 11; schematic
+Original unit input: NTD 2. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="16" ht="138" customHeight="1">
+      <x:c r="N15"/>
+      <x:c r="O15"/>
+    </x:row>
+    <x:row r="16" ht="153" customHeight="1">
       <x:c r="A16" s="10" t="n">
         <x:v>12</x:v>
       </x:c>
@@ -8816,31 +8480,26 @@
         <x:v>Confirm MPN,case/height,voltage,tolerance,dielectric and ESR</x:v>
       </x:c>
       <x:c r="I16" s="10" t="str"/>
-      <x:c r="J16" s="14" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="K16" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J16),J16&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J16/Summary!$F$5,"")</x:f>
+      <x:c r="J16" s="19" t="n">
         <x:v>0.47162395849709166</x:v>
       </x:c>
-      <x:c r="L16" s="12" t="n">
+      <x:c r="K16" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J16),J16&gt;=0,ISNUMBER(D16),D16&gt;=0),J16*D16,"")</x:f>
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="M16" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K16),ISNUMBER(D16),D16&gt;=0),K16*D16,"")</x:f>
         <x:v>0.47162395849709166</x:v>
       </x:c>
-      <x:c r="N16" s="10" t="str">
+      <x:c r="L16" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O16" s="10" t="str">
+      <x:c r="M16" s="10" t="str">
         <x:v>vendor_BOM row 12; schematic
+Original unit input: NTD 15. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="17" ht="138" customHeight="1">
+      <x:c r="N16"/>
+      <x:c r="O16"/>
+    </x:row>
+    <x:row r="17" ht="153" customHeight="1">
       <x:c r="A17" s="10" t="n">
         <x:v>13</x:v>
       </x:c>
@@ -8867,31 +8526,26 @@
         <x:v>Confirm MPN,case/height,voltage,tolerance,dielectric and ESR</x:v>
       </x:c>
       <x:c r="I17" s="10" t="str"/>
-      <x:c r="J17" s="14" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="K17" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J17),J17&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J17/Summary!$F$5,"")</x:f>
+      <x:c r="J17" s="19" t="n">
         <x:v>0.2515327778651156</x:v>
       </x:c>
-      <x:c r="L17" s="12" t="n">
+      <x:c r="K17" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J17),J17&gt;=0,ISNUMBER(D17),D17&gt;=0),J17*D17,"")</x:f>
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="M17" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K17),ISNUMBER(D17),D17&gt;=0),K17*D17,"")</x:f>
         <x:v>0.5030655557302312</x:v>
       </x:c>
-      <x:c r="N17" s="10" t="str">
+      <x:c r="L17" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O17" s="10" t="str">
+      <x:c r="M17" s="10" t="str">
         <x:v>vendor_BOM row 13; schematic
+Original unit input: NTD 8. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="18" ht="138" customHeight="1">
+      <x:c r="N17"/>
+      <x:c r="O17"/>
+    </x:row>
+    <x:row r="18" ht="153" customHeight="1">
       <x:c r="A18" s="10" t="n">
         <x:v>14</x:v>
       </x:c>
@@ -8918,31 +8572,26 @@
         <x:v>Confirm MPN,case/height,voltage,tolerance,dielectric and ESR</x:v>
       </x:c>
       <x:c r="I18" s="10" t="str"/>
-      <x:c r="J18" s="14" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K18" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J18),J18&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J18/Summary!$F$5,"")</x:f>
+      <x:c r="J18" s="19" t="n">
         <x:v>0.0628831944662789</x:v>
       </x:c>
-      <x:c r="L18" s="12" t="n">
+      <x:c r="K18" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J18),J18&gt;=0,ISNUMBER(D18),D18&gt;=0),J18*D18,"")</x:f>
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="M18" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K18),ISNUMBER(D18),D18&gt;=0),K18*D18,"")</x:f>
         <x:v>0.2515327778651156</x:v>
       </x:c>
-      <x:c r="N18" s="10" t="str">
+      <x:c r="L18" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O18" s="10" t="str">
+      <x:c r="M18" s="10" t="str">
         <x:v>vendor_BOM row 14; schematic
+Original unit input: NTD 2. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="19" ht="138" customHeight="1">
+      <x:c r="N18"/>
+      <x:c r="O18"/>
+    </x:row>
+    <x:row r="19" ht="153" customHeight="1">
       <x:c r="A19" s="10" t="n">
         <x:v>15</x:v>
       </x:c>
@@ -8969,31 +8618,26 @@
         <x:v>Confirm MPN,case/height,voltage,tolerance,dielectric and ESR</x:v>
       </x:c>
       <x:c r="I19" s="10" t="str"/>
-      <x:c r="J19" s="14" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="K19" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J19),J19&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J19/Summary!$F$5,"")</x:f>
+      <x:c r="J19" s="19" t="n">
         <x:v>0.2515327778651156</x:v>
       </x:c>
-      <x:c r="L19" s="12" t="n">
+      <x:c r="K19" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J19),J19&gt;=0,ISNUMBER(D19),D19&gt;=0),J19*D19,"")</x:f>
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="M19" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K19),ISNUMBER(D19),D19&gt;=0),K19*D19,"")</x:f>
         <x:v>1.0061311114604623</x:v>
       </x:c>
-      <x:c r="N19" s="10" t="str">
+      <x:c r="L19" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O19" s="10" t="str">
+      <x:c r="M19" s="10" t="str">
         <x:v>vendor_BOM row 15; schematic
+Original unit input: NTD 8. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="20" ht="138" customHeight="1">
+      <x:c r="N19"/>
+      <x:c r="O19"/>
+    </x:row>
+    <x:row r="20" ht="153" customHeight="1">
       <x:c r="A20" s="10" t="n">
         <x:v>16</x:v>
       </x:c>
@@ -9020,31 +8664,26 @@
         <x:v>Confirm MPN,case/height,voltage,tolerance,dielectric and ESR</x:v>
       </x:c>
       <x:c r="I20" s="10" t="str"/>
-      <x:c r="J20" s="14" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K20" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J20),J20&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J20/Summary!$F$5,"")</x:f>
+      <x:c r="J20" s="19" t="n">
         <x:v>0.0628831944662789</x:v>
       </x:c>
-      <x:c r="L20" s="12" t="n">
+      <x:c r="K20" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J20),J20&gt;=0,ISNUMBER(D20),D20&gt;=0),J20*D20,"")</x:f>
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="M20" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K20),ISNUMBER(D20),D20&gt;=0),K20*D20,"")</x:f>
         <x:v>0.2515327778651156</x:v>
       </x:c>
-      <x:c r="N20" s="10" t="str">
+      <x:c r="L20" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O20" s="10" t="str">
+      <x:c r="M20" s="10" t="str">
         <x:v>vendor_BOM row 16; schematic
+Original unit input: NTD 2. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="21" ht="138" customHeight="1">
+      <x:c r="N20"/>
+      <x:c r="O20"/>
+    </x:row>
+    <x:row r="21" ht="153" customHeight="1">
       <x:c r="A21" s="10" t="n">
         <x:v>17</x:v>
       </x:c>
@@ -9071,31 +8710,26 @@
         <x:v>Confirm MPN/package,dielectric/leakage and parasitic capacitance</x:v>
       </x:c>
       <x:c r="I21" s="10" t="str"/>
-      <x:c r="J21" s="14" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K21" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J21),J21&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J21/Summary!$F$5,"")</x:f>
+      <x:c r="J21" s="19" t="n">
         <x:v>0.0628831944662789</x:v>
       </x:c>
-      <x:c r="L21" s="12" t="n">
+      <x:c r="K21" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J21),J21&gt;=0,ISNUMBER(D21),D21&gt;=0),J21*D21,"")</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M21" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K21),ISNUMBER(D21),D21&gt;=0),K21*D21,"")</x:f>
         <x:v>0.0628831944662789</x:v>
       </x:c>
-      <x:c r="N21" s="10" t="str">
+      <x:c r="L21" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O21" s="10" t="str">
+      <x:c r="M21" s="10" t="str">
         <x:v>vendor_BOM row 17; schematic
+Original unit input: NTD 2. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="22" ht="138" customHeight="1">
+      <x:c r="N21"/>
+      <x:c r="O21"/>
+    </x:row>
+    <x:row r="22" ht="153" customHeight="1">
       <x:c r="A22" s="10" t="n">
         <x:v>18</x:v>
       </x:c>
@@ -9122,31 +8756,26 @@
         <x:v>Confirm MPN,case/height,voltage,tolerance,dielectric and ESR</x:v>
       </x:c>
       <x:c r="I22" s="10" t="str"/>
-      <x:c r="J22" s="14" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K22" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J22),J22&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J22/Summary!$F$5,"")</x:f>
+      <x:c r="J22" s="19" t="n">
         <x:v>0.0628831944662789</x:v>
       </x:c>
-      <x:c r="L22" s="12" t="n">
+      <x:c r="K22" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J22),J22&gt;=0,ISNUMBER(D22),D22&gt;=0),J22*D22,"")</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M22" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K22),ISNUMBER(D22),D22&gt;=0),K22*D22,"")</x:f>
         <x:v>0.0628831944662789</x:v>
       </x:c>
-      <x:c r="N22" s="10" t="str">
+      <x:c r="L22" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O22" s="10" t="str">
+      <x:c r="M22" s="10" t="str">
         <x:v>vendor_BOM row 18; schematic
+Original unit input: NTD 2. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="23" ht="138" customHeight="1">
+      <x:c r="N22"/>
+      <x:c r="O22"/>
+    </x:row>
+    <x:row r="23" ht="153" customHeight="1">
       <x:c r="A23" s="10" t="n">
         <x:v>19</x:v>
       </x:c>
@@ -9173,31 +8802,26 @@
         <x:v>Confirm MPN,case/height,voltage,tolerance,dielectric and ESR</x:v>
       </x:c>
       <x:c r="I23" s="10" t="str"/>
-      <x:c r="J23" s="14" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="K23" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J23),J23&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J23/Summary!$F$5,"")</x:f>
+      <x:c r="J23" s="19" t="n">
         <x:v>0.47162395849709166</x:v>
       </x:c>
-      <x:c r="L23" s="12" t="n">
+      <x:c r="K23" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J23),J23&gt;=0,ISNUMBER(D23),D23&gt;=0),J23*D23,"")</x:f>
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="M23" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K23),ISNUMBER(D23),D23&gt;=0),K23*D23,"")</x:f>
         <x:v>0.47162395849709166</x:v>
       </x:c>
-      <x:c r="N23" s="10" t="str">
+      <x:c r="L23" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O23" s="10" t="str">
+      <x:c r="M23" s="10" t="str">
         <x:v>vendor_BOM row 19; schematic
+Original unit input: NTD 15. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="24" ht="138" customHeight="1">
+      <x:c r="N23"/>
+      <x:c r="O23"/>
+    </x:row>
+    <x:row r="24" ht="153" customHeight="1">
       <x:c r="A24" s="10" t="n">
         <x:v>20</x:v>
       </x:c>
@@ -9224,31 +8848,26 @@
         <x:v>Confirm MPN,color,package/height,current and brightness</x:v>
       </x:c>
       <x:c r="I24" s="10" t="str"/>
-      <x:c r="J24" s="14" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K24" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J24),J24&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J24/Summary!$F$5,"")</x:f>
+      <x:c r="J24" s="19" t="n">
         <x:v>0.0628831944662789</x:v>
       </x:c>
-      <x:c r="L24" s="12" t="n">
+      <x:c r="K24" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J24),J24&gt;=0,ISNUMBER(D24),D24&gt;=0),J24*D24,"")</x:f>
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="M24" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K24),ISNUMBER(D24),D24&gt;=0),K24*D24,"")</x:f>
         <x:v>0.1257663889325578</x:v>
       </x:c>
-      <x:c r="N24" s="10" t="str">
+      <x:c r="L24" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O24" s="10" t="str">
+      <x:c r="M24" s="10" t="str">
         <x:v>vendor_BOM row 20; schematic
+Original unit input: NTD 2. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="25" ht="78" customHeight="1">
+      <x:c r="N24"/>
+      <x:c r="O24"/>
+    </x:row>
+    <x:row r="25" ht="93" customHeight="1">
       <x:c r="A25" s="10" t="n">
         <x:v>21</x:v>
       </x:c>
@@ -9275,31 +8894,26 @@
         <x:v>Verify orientation/height,optical axis,actual current and optical power</x:v>
       </x:c>
       <x:c r="I25" s="10" t="str"/>
-      <x:c r="J25" s="14" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K25" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J25),J25&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J25/Summary!$F$5,"")</x:f>
+      <x:c r="J25" s="19" t="n">
         <x:v>0.5345071529633706</x:v>
       </x:c>
-      <x:c r="L25" s="12" t="n">
+      <x:c r="K25" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J25),J25&gt;=0,ISNUMBER(D25),D25&gt;=0),J25*D25,"")</x:f>
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="M25" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K25),ISNUMBER(D25),D25&gt;=0),K25*D25,"")</x:f>
         <x:v>2.1380286118534824</x:v>
       </x:c>
-      <x:c r="N25" s="10" t="str">
+      <x:c r="L25" s="10" t="str">
         <x:v>Listed</x:v>
       </x:c>
-      <x:c r="O25" s="10" t="str">
+      <x:c r="M25" s="10" t="str">
         <x:v>vendor_BOM row 21; schematic; WURTH_LED
+Original unit input: NTD 17. Converted at 31.805 NTD/USD.
 NTD 17 each at quantity 1.
 https://www.digikey.tw/en/products/detail/w%C3%BCrth-elektronik/155124BS73200/4490035</x:v>
       </x:c>
-    </x:row>
-    <x:row r="26" ht="78" customHeight="1">
+      <x:c r="N25"/>
+      <x:c r="O25"/>
+    </x:row>
+    <x:row r="26" ht="93" customHeight="1">
       <x:c r="A26" s="10" t="n">
         <x:v>22</x:v>
       </x:c>
@@ -9326,31 +8940,26 @@
         <x:v>Verify offset active area,assembled height and filter obscuration</x:v>
       </x:c>
       <x:c r="I26" s="10" t="str"/>
-      <x:c r="J26" s="14" t="n">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="K26" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J26),J26&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J26/Summary!$F$5,"")</x:f>
+      <x:c r="J26" s="19" t="n">
         <x:v>2.1380286118534824</x:v>
       </x:c>
-      <x:c r="L26" s="12" t="n">
+      <x:c r="K26" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J26),J26&gt;=0,ISNUMBER(D26),D26&gt;=0),J26*D26,"")</x:f>
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="M26" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K26),ISNUMBER(D26),D26&gt;=0),K26*D26,"")</x:f>
         <x:v>2.1380286118534824</x:v>
       </x:c>
-      <x:c r="N26" s="10" t="str">
+      <x:c r="L26" s="10" t="str">
         <x:v>Listed</x:v>
       </x:c>
-      <x:c r="O26" s="10" t="str">
+      <x:c r="M26" s="10" t="str">
         <x:v>vendor_BOM row 22; schematic; VISHAY_PD
+Original unit input: NTD 68. Converted at 31.805 NTD/USD.
 NTD 68 each at quantity 1.
 https://www.digikey.tw/en/products/detail/vishay-semiconductor-opto-division/VEMD5060X01/5879084</x:v>
       </x:c>
-    </x:row>
-    <x:row r="27" ht="138" customHeight="1">
+      <x:c r="N26"/>
+      <x:c r="O26"/>
+    </x:row>
+    <x:row r="27" ht="153" customHeight="1">
       <x:c r="A27" s="10" t="n">
         <x:v>23</x:v>
       </x:c>
@@ -9377,31 +8986,26 @@
         <x:v>Geometry/mask opening from fabrication data;not separately purchased</x:v>
       </x:c>
       <x:c r="I27" s="10" t="str"/>
-      <x:c r="J27" s="14" t="n">
+      <x:c r="J27" s="19" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K27" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J27),J27&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J27/Summary!$F$5,"")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L27" s="12" t="n">
+      <x:c r="K27" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J27),J27&gt;=0,ISNUMBER(D27),D27&gt;=0),J27*D27,"")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M27" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K27),ISNUMBER(D27),D27&gt;=0),K27*D27,"")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N27" s="10" t="str">
+      <x:c r="L27" s="10" t="str">
         <x:v>Fabrication feature</x:v>
       </x:c>
-      <x:c r="O27" s="10" t="str">
+      <x:c r="M27" s="10" t="str">
         <x:v>vendor_BOM row 23; schematic
+Original unit input: NTD 0. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="28" ht="138" customHeight="1">
+      <x:c r="N27"/>
+      <x:c r="O27"/>
+    </x:row>
+    <x:row r="28" ht="153" customHeight="1">
       <x:c r="A28" s="10" t="n">
         <x:v>24</x:v>
       </x:c>
@@ -9428,31 +9032,26 @@
         <x:v>Confirm hole/plating/copper keepout;do not double-count screws</x:v>
       </x:c>
       <x:c r="I28" s="10" t="str"/>
-      <x:c r="J28" s="14" t="n">
+      <x:c r="J28" s="19" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K28" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J28),J28&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J28/Summary!$F$5,"")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L28" s="12" t="n">
+      <x:c r="K28" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J28),J28&gt;=0,ISNUMBER(D28),D28&gt;=0),J28*D28,"")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M28" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K28),ISNUMBER(D28),D28&gt;=0),K28*D28,"")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N28" s="10" t="str">
+      <x:c r="L28" s="10" t="str">
         <x:v>Fabrication feature</x:v>
       </x:c>
-      <x:c r="O28" s="10" t="str">
+      <x:c r="M28" s="10" t="str">
         <x:v>vendor_BOM row 24; schematic
+Original unit input: NTD 0. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="29" ht="138" customHeight="1">
+      <x:c r="N28"/>
+      <x:c r="O28"/>
+    </x:row>
+    <x:row r="29" ht="153" customHeight="1">
       <x:c r="A29" s="10" t="n">
         <x:v>25</x:v>
       </x:c>
@@ -9479,31 +9078,26 @@
         <x:v>Confirm MPN,cell size/protection,polarity/height and charger settings</x:v>
       </x:c>
       <x:c r="I29" s="10" t="str"/>
-      <x:c r="J29" s="14" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="K29" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J29),J29&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J29/Summary!$F$5,"")</x:f>
+      <x:c r="J29" s="19" t="n">
         <x:v>0.9432479169941833</x:v>
       </x:c>
-      <x:c r="L29" s="12" t="n">
+      <x:c r="K29" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J29),J29&gt;=0,ISNUMBER(D29),D29&gt;=0),J29*D29,"")</x:f>
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="M29" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K29),ISNUMBER(D29),D29&gt;=0),K29*D29,"")</x:f>
         <x:v>0.9432479169941833</x:v>
       </x:c>
-      <x:c r="N29" s="10" t="str">
+      <x:c r="L29" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O29" s="10" t="str">
+      <x:c r="M29" s="10" t="str">
         <x:v>vendor_BOM row 25; schematic; TI_BQ24074
+Original unit input: NTD 30. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="30" ht="138" customHeight="1">
+      <x:c r="N29"/>
+      <x:c r="O29"/>
+    </x:row>
+    <x:row r="30" ht="153" customHeight="1">
       <x:c r="A30" s="10" t="n">
         <x:v>26</x:v>
       </x:c>
@@ -9530,31 +9124,26 @@
         <x:v>Confirm MPN,opening/height/ratings and CC resistors</x:v>
       </x:c>
       <x:c r="I30" s="10" t="str"/>
-      <x:c r="J30" s="14" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="K30" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J30),J30&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J30/Summary!$F$5,"")</x:f>
+      <x:c r="J30" s="19" t="n">
         <x:v>0.6288319446627889</x:v>
       </x:c>
-      <x:c r="L30" s="12" t="n">
+      <x:c r="K30" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J30),J30&gt;=0,ISNUMBER(D30),D30&gt;=0),J30*D30,"")</x:f>
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="M30" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K30),ISNUMBER(D30),D30&gt;=0),K30*D30,"")</x:f>
         <x:v>0.6288319446627889</x:v>
       </x:c>
-      <x:c r="N30" s="10" t="str">
+      <x:c r="L30" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O30" s="10" t="str">
+      <x:c r="M30" s="10" t="str">
         <x:v>vendor_BOM row 26; schematic
+Original unit input: NTD 20. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="31" ht="138" customHeight="1">
+      <x:c r="N30"/>
+      <x:c r="O30"/>
+    </x:row>
+    <x:row r="31" ht="153" customHeight="1">
       <x:c r="A31" s="10" t="n">
         <x:v>27</x:v>
       </x:c>
@@ -9581,31 +9170,26 @@
         <x:v>Confirm MPN,pitch/height/orientation and mating cable</x:v>
       </x:c>
       <x:c r="I31" s="10" t="str"/>
-      <x:c r="J31" s="14" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="K31" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J31),J31&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J31/Summary!$F$5,"")</x:f>
+      <x:c r="J31" s="19" t="n">
         <x:v>0.15720798616569723</x:v>
       </x:c>
-      <x:c r="L31" s="12" t="n">
+      <x:c r="K31" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J31),J31&gt;=0,ISNUMBER(D31),D31&gt;=0),J31*D31,"")</x:f>
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="M31" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K31),ISNUMBER(D31),D31&gt;=0),K31*D31,"")</x:f>
         <x:v>0.15720798616569723</x:v>
       </x:c>
-      <x:c r="N31" s="10" t="str">
+      <x:c r="L31" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O31" s="10" t="str">
+      <x:c r="M31" s="10" t="str">
         <x:v>vendor_BOM row 27; schematic
+Original unit input: NTD 5. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="32" ht="138" customHeight="1">
+      <x:c r="N31"/>
+      <x:c r="O31"/>
+    </x:row>
+    <x:row r="32" ht="153" customHeight="1">
       <x:c r="A32" s="10" t="n">
         <x:v>28</x:v>
       </x:c>
@@ -9630,31 +9214,26 @@
         <x:v>Confirm inductance,current,DCR,package/height and MPN</x:v>
       </x:c>
       <x:c r="I32" s="10" t="str"/>
-      <x:c r="J32" s="14" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="K32" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J32),J32&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J32/Summary!$F$5,"")</x:f>
+      <x:c r="J32" s="19" t="n">
         <x:v>0.31441597233139446</x:v>
       </x:c>
-      <x:c r="L32" s="12" t="n">
+      <x:c r="K32" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J32),J32&gt;=0,ISNUMBER(D32),D32&gt;=0),J32*D32,"")</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="M32" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K32),ISNUMBER(D32),D32&gt;=0),K32*D32,"")</x:f>
         <x:v>0.31441597233139446</x:v>
       </x:c>
-      <x:c r="N32" s="10" t="str">
+      <x:c r="L32" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O32" s="10" t="str">
+      <x:c r="M32" s="10" t="str">
         <x:v>vendor_BOM row 28; schematic; TI_TPS61023
+Original unit input: NTD 10. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="33" ht="138" customHeight="1">
+      <x:c r="N32"/>
+      <x:c r="O32"/>
+    </x:row>
+    <x:row r="33" ht="153" customHeight="1">
       <x:c r="A33" s="10" t="n">
         <x:v>29</x:v>
       </x:c>
@@ -9681,31 +9260,26 @@
         <x:v>Verify package pinout,actual current and temperature rise</x:v>
       </x:c>
       <x:c r="I33" s="10" t="str"/>
-      <x:c r="J33" s="14" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="K33" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J33),J33&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J33/Summary!$F$5,"")</x:f>
+      <x:c r="J33" s="19" t="n">
         <x:v>0.15720798616569723</x:v>
       </x:c>
-      <x:c r="L33" s="12" t="n">
+      <x:c r="K33" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J33),J33&gt;=0,ISNUMBER(D33),D33&gt;=0),J33*D33,"")</x:f>
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="M33" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K33),ISNUMBER(D33),D33&gt;=0),K33*D33,"")</x:f>
         <x:v>0.6288319446627889</x:v>
       </x:c>
-      <x:c r="N33" s="10" t="str">
+      <x:c r="L33" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O33" s="10" t="str">
+      <x:c r="M33" s="10" t="str">
         <x:v>vendor_BOM row 29; schematic; AOS_AO3400A
+Original unit input: NTD 5. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="34" ht="138" customHeight="1">
+      <x:c r="N33"/>
+      <x:c r="O33"/>
+    </x:row>
+    <x:row r="34" ht="153" customHeight="1">
       <x:c r="A34" s="10" t="n">
         <x:v>30</x:v>
       </x:c>
@@ -9730,31 +9304,26 @@
         <x:v>Confirm MPN,case/height,power,tolerance,TCR and voltage rating</x:v>
       </x:c>
       <x:c r="I34" s="10" t="str"/>
-      <x:c r="J34" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K34" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J34),J34&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J34/Summary!$F$5,"")</x:f>
+      <x:c r="J34" s="19" t="n">
         <x:v>0.03144159723313945</x:v>
       </x:c>
-      <x:c r="L34" s="12" t="n">
+      <x:c r="K34" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J34),J34&gt;=0,ISNUMBER(D34),D34&gt;=0),J34*D34,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M34" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K34),ISNUMBER(D34),D34&gt;=0),K34*D34,"")</x:f>
         <x:v>0.03144159723313945</x:v>
       </x:c>
-      <x:c r="N34" s="10" t="str">
+      <x:c r="L34" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O34" s="10" t="str">
+      <x:c r="M34" s="10" t="str">
         <x:v>vendor_BOM row 30; schematic
+Original unit input: NTD 1. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="35" ht="138" customHeight="1">
+      <x:c r="N34"/>
+      <x:c r="O34"/>
+    </x:row>
+    <x:row r="35" ht="153" customHeight="1">
       <x:c r="A35" s="10" t="n">
         <x:v>31</x:v>
       </x:c>
@@ -9779,31 +9348,26 @@
         <x:v>Confirm MPN,case/height,power,tolerance,TCR and voltage rating</x:v>
       </x:c>
       <x:c r="I35" s="10" t="str"/>
-      <x:c r="J35" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K35" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J35),J35&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J35/Summary!$F$5,"")</x:f>
+      <x:c r="J35" s="19" t="n">
         <x:v>0.03144159723313945</x:v>
       </x:c>
-      <x:c r="L35" s="12" t="n">
+      <x:c r="K35" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J35),J35&gt;=0,ISNUMBER(D35),D35&gt;=0),J35*D35,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M35" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K35),ISNUMBER(D35),D35&gt;=0),K35*D35,"")</x:f>
         <x:v>0.03144159723313945</x:v>
       </x:c>
-      <x:c r="N35" s="10" t="str">
+      <x:c r="L35" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O35" s="10" t="str">
+      <x:c r="M35" s="10" t="str">
         <x:v>vendor_BOM row 31; schematic
+Original unit input: NTD 1. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="36" ht="138" customHeight="1">
+      <x:c r="N35"/>
+      <x:c r="O35"/>
+    </x:row>
+    <x:row r="36" ht="153" customHeight="1">
       <x:c r="A36" s="10" t="n">
         <x:v>32</x:v>
       </x:c>
@@ -9828,31 +9392,26 @@
         <x:v>Confirm MPN,case/height,power,tolerance,TCR and voltage rating</x:v>
       </x:c>
       <x:c r="I36" s="10" t="str"/>
-      <x:c r="J36" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K36" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J36),J36&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J36/Summary!$F$5,"")</x:f>
+      <x:c r="J36" s="19" t="n">
         <x:v>0.03144159723313945</x:v>
       </x:c>
-      <x:c r="L36" s="12" t="n">
+      <x:c r="K36" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J36),J36&gt;=0,ISNUMBER(D36),D36&gt;=0),J36*D36,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M36" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K36),ISNUMBER(D36),D36&gt;=0),K36*D36,"")</x:f>
         <x:v>0.03144159723313945</x:v>
       </x:c>
-      <x:c r="N36" s="10" t="str">
+      <x:c r="L36" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O36" s="10" t="str">
+      <x:c r="M36" s="10" t="str">
         <x:v>vendor_BOM row 32; schematic
+Original unit input: NTD 1. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="37" ht="138" customHeight="1">
+      <x:c r="N36"/>
+      <x:c r="O36"/>
+    </x:row>
+    <x:row r="37" ht="153" customHeight="1">
       <x:c r="A37" s="10" t="n">
         <x:v>33</x:v>
       </x:c>
@@ -9877,31 +9436,26 @@
         <x:v>Confirm MPN,case/height,power,tolerance,TCR and voltage rating</x:v>
       </x:c>
       <x:c r="I37" s="10" t="str"/>
-      <x:c r="J37" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K37" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J37),J37&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J37/Summary!$F$5,"")</x:f>
+      <x:c r="J37" s="19" t="n">
         <x:v>0.03144159723313945</x:v>
       </x:c>
-      <x:c r="L37" s="12" t="n">
+      <x:c r="K37" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J37),J37&gt;=0,ISNUMBER(D37),D37&gt;=0),J37*D37,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M37" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K37),ISNUMBER(D37),D37&gt;=0),K37*D37,"")</x:f>
         <x:v>0.03144159723313945</x:v>
       </x:c>
-      <x:c r="N37" s="10" t="str">
+      <x:c r="L37" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O37" s="10" t="str">
+      <x:c r="M37" s="10" t="str">
         <x:v>vendor_BOM row 33; schematic
+Original unit input: NTD 1. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="38" ht="138" customHeight="1">
+      <x:c r="N37"/>
+      <x:c r="O37"/>
+    </x:row>
+    <x:row r="38" ht="153" customHeight="1">
       <x:c r="A38" s="10" t="n">
         <x:v>34</x:v>
       </x:c>
@@ -9926,31 +9480,26 @@
         <x:v>Confirm MPN,case/height,power,tolerance,TCR and voltage rating</x:v>
       </x:c>
       <x:c r="I38" s="10" t="str"/>
-      <x:c r="J38" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K38" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J38),J38&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J38/Summary!$F$5,"")</x:f>
+      <x:c r="J38" s="19" t="n">
         <x:v>0.03144159723313945</x:v>
       </x:c>
-      <x:c r="L38" s="12" t="n">
+      <x:c r="K38" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J38),J38&gt;=0,ISNUMBER(D38),D38&gt;=0),J38*D38,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M38" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K38),ISNUMBER(D38),D38&gt;=0),K38*D38,"")</x:f>
         <x:v>0.03144159723313945</x:v>
       </x:c>
-      <x:c r="N38" s="10" t="str">
+      <x:c r="L38" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O38" s="10" t="str">
+      <x:c r="M38" s="10" t="str">
         <x:v>vendor_BOM row 34; schematic
+Original unit input: NTD 1. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="39" ht="138" customHeight="1">
+      <x:c r="N38"/>
+      <x:c r="O38"/>
+    </x:row>
+    <x:row r="39" ht="153" customHeight="1">
       <x:c r="A39" s="10" t="n">
         <x:v>35</x:v>
       </x:c>
@@ -9975,31 +9524,26 @@
         <x:v>Confirm MPN,case/height,power,tolerance,TCR and voltage rating</x:v>
       </x:c>
       <x:c r="I39" s="10" t="str"/>
-      <x:c r="J39" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K39" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J39),J39&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J39/Summary!$F$5,"")</x:f>
+      <x:c r="J39" s="19" t="n">
         <x:v>0.03144159723313945</x:v>
       </x:c>
-      <x:c r="L39" s="12" t="n">
+      <x:c r="K39" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J39),J39&gt;=0,ISNUMBER(D39),D39&gt;=0),J39*D39,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M39" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K39),ISNUMBER(D39),D39&gt;=0),K39*D39,"")</x:f>
         <x:v>0.03144159723313945</x:v>
       </x:c>
-      <x:c r="N39" s="10" t="str">
+      <x:c r="L39" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O39" s="10" t="str">
+      <x:c r="M39" s="10" t="str">
         <x:v>vendor_BOM row 35; schematic
+Original unit input: NTD 1. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="40" ht="138" customHeight="1">
+      <x:c r="N39"/>
+      <x:c r="O39"/>
+    </x:row>
+    <x:row r="40" ht="153" customHeight="1">
       <x:c r="A40" s="10" t="n">
         <x:v>36</x:v>
       </x:c>
@@ -10024,31 +9568,26 @@
         <x:v>Confirm MPN,case/height,power,tolerance,TCR and voltage rating</x:v>
       </x:c>
       <x:c r="I40" s="10" t="str"/>
-      <x:c r="J40" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K40" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J40),J40&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J40/Summary!$F$5,"")</x:f>
+      <x:c r="J40" s="19" t="n">
         <x:v>0.03144159723313945</x:v>
       </x:c>
-      <x:c r="L40" s="12" t="n">
+      <x:c r="K40" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J40),J40&gt;=0,ISNUMBER(D40),D40&gt;=0),J40*D40,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M40" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K40),ISNUMBER(D40),D40&gt;=0),K40*D40,"")</x:f>
         <x:v>0.03144159723313945</x:v>
       </x:c>
-      <x:c r="N40" s="10" t="str">
+      <x:c r="L40" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O40" s="10" t="str">
+      <x:c r="M40" s="10" t="str">
         <x:v>vendor_BOM row 36; schematic
+Original unit input: NTD 1. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="41" ht="138" customHeight="1">
+      <x:c r="N40"/>
+      <x:c r="O40"/>
+    </x:row>
+    <x:row r="41" ht="153" customHeight="1">
       <x:c r="A41" s="10" t="n">
         <x:v>37</x:v>
       </x:c>
@@ -10073,31 +9612,26 @@
         <x:v>Confirm MPN,case/height,power,tolerance,TCR and voltage rating</x:v>
       </x:c>
       <x:c r="I41" s="10" t="str"/>
-      <x:c r="J41" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K41" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J41),J41&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J41/Summary!$F$5,"")</x:f>
+      <x:c r="J41" s="19" t="n">
         <x:v>0.03144159723313945</x:v>
       </x:c>
-      <x:c r="L41" s="12" t="n">
+      <x:c r="K41" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J41),J41&gt;=0,ISNUMBER(D41),D41&gt;=0),J41*D41,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M41" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K41),ISNUMBER(D41),D41&gt;=0),K41*D41,"")</x:f>
         <x:v>0.03144159723313945</x:v>
       </x:c>
-      <x:c r="N41" s="10" t="str">
+      <x:c r="L41" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O41" s="10" t="str">
+      <x:c r="M41" s="10" t="str">
         <x:v>vendor_BOM row 37; schematic
+Original unit input: NTD 1. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="42" ht="138" customHeight="1">
+      <x:c r="N41"/>
+      <x:c r="O41"/>
+    </x:row>
+    <x:row r="42" ht="153" customHeight="1">
       <x:c r="A42" s="10" t="n">
         <x:v>38</x:v>
       </x:c>
@@ -10122,31 +9656,26 @@
         <x:v>Confirm MPN,case/height,power,tolerance,TCR and voltage rating</x:v>
       </x:c>
       <x:c r="I42" s="10" t="str"/>
-      <x:c r="J42" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K42" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J42),J42&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J42/Summary!$F$5,"")</x:f>
+      <x:c r="J42" s="19" t="n">
         <x:v>0.03144159723313945</x:v>
       </x:c>
-      <x:c r="L42" s="12" t="n">
+      <x:c r="K42" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J42),J42&gt;=0,ISNUMBER(D42),D42&gt;=0),J42*D42,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M42" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K42),ISNUMBER(D42),D42&gt;=0),K42*D42,"")</x:f>
         <x:v>0.03144159723313945</x:v>
       </x:c>
-      <x:c r="N42" s="10" t="str">
+      <x:c r="L42" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O42" s="10" t="str">
+      <x:c r="M42" s="10" t="str">
         <x:v>vendor_BOM row 38; schematic
+Original unit input: NTD 1. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="43" ht="138" customHeight="1">
+      <x:c r="N42"/>
+      <x:c r="O42"/>
+    </x:row>
+    <x:row r="43" ht="153" customHeight="1">
       <x:c r="A43" s="10" t="n">
         <x:v>39</x:v>
       </x:c>
@@ -10171,31 +9700,26 @@
         <x:v>Confirm MPN,case/height,power,tolerance,TCR and voltage rating</x:v>
       </x:c>
       <x:c r="I43" s="10" t="str"/>
-      <x:c r="J43" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K43" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J43),J43&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J43/Summary!$F$5,"")</x:f>
+      <x:c r="J43" s="19" t="n">
         <x:v>0.03144159723313945</x:v>
       </x:c>
-      <x:c r="L43" s="12" t="n">
+      <x:c r="K43" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J43),J43&gt;=0,ISNUMBER(D43),D43&gt;=0),J43*D43,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M43" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K43),ISNUMBER(D43),D43&gt;=0),K43*D43,"")</x:f>
         <x:v>0.03144159723313945</x:v>
       </x:c>
-      <x:c r="N43" s="10" t="str">
+      <x:c r="L43" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O43" s="10" t="str">
+      <x:c r="M43" s="10" t="str">
         <x:v>vendor_BOM row 39; schematic
+Original unit input: NTD 1. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="44" ht="138" customHeight="1">
+      <x:c r="N43"/>
+      <x:c r="O43"/>
+    </x:row>
+    <x:row r="44" ht="153" customHeight="1">
       <x:c r="A44" s="10" t="n">
         <x:v>40</x:v>
       </x:c>
@@ -10220,31 +9744,26 @@
         <x:v>Confirm MPN,case/height,power,tolerance,TCR and voltage rating</x:v>
       </x:c>
       <x:c r="I44" s="10" t="str"/>
-      <x:c r="J44" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K44" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J44),J44&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J44/Summary!$F$5,"")</x:f>
+      <x:c r="J44" s="19" t="n">
         <x:v>0.03144159723313945</x:v>
       </x:c>
-      <x:c r="L44" s="12" t="n">
+      <x:c r="K44" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J44),J44&gt;=0,ISNUMBER(D44),D44&gt;=0),J44*D44,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M44" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K44),ISNUMBER(D44),D44&gt;=0),K44*D44,"")</x:f>
         <x:v>0.03144159723313945</x:v>
       </x:c>
-      <x:c r="N44" s="10" t="str">
+      <x:c r="L44" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O44" s="10" t="str">
+      <x:c r="M44" s="10" t="str">
         <x:v>vendor_BOM row 40; schematic
+Original unit input: NTD 1. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="45" ht="138" customHeight="1">
+      <x:c r="N44"/>
+      <x:c r="O44"/>
+    </x:row>
+    <x:row r="45" ht="153" customHeight="1">
       <x:c r="A45" s="10" t="n">
         <x:v>41</x:v>
       </x:c>
@@ -10269,31 +9788,26 @@
         <x:v>Confirm MPN,case/height,power,tolerance,TCR and voltage rating</x:v>
       </x:c>
       <x:c r="I45" s="10" t="str"/>
-      <x:c r="J45" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K45" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J45),J45&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J45/Summary!$F$5,"")</x:f>
+      <x:c r="J45" s="19" t="n">
         <x:v>0.03144159723313945</x:v>
       </x:c>
-      <x:c r="L45" s="12" t="n">
+      <x:c r="K45" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J45),J45&gt;=0,ISNUMBER(D45),D45&gt;=0),J45*D45,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M45" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K45),ISNUMBER(D45),D45&gt;=0),K45*D45,"")</x:f>
         <x:v>0.03144159723313945</x:v>
       </x:c>
-      <x:c r="N45" s="10" t="str">
+      <x:c r="L45" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O45" s="10" t="str">
+      <x:c r="M45" s="10" t="str">
         <x:v>vendor_BOM row 41; schematic
+Original unit input: NTD 1. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="46" ht="138" customHeight="1">
+      <x:c r="N45"/>
+      <x:c r="O45"/>
+    </x:row>
+    <x:row r="46" ht="153" customHeight="1">
       <x:c r="A46" s="10" t="n">
         <x:v>42</x:v>
       </x:c>
@@ -10318,31 +9832,26 @@
         <x:v>Confirm MPN,case/height,power,tolerance,TCR and voltage rating</x:v>
       </x:c>
       <x:c r="I46" s="10" t="str"/>
-      <x:c r="J46" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K46" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J46),J46&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J46/Summary!$F$5,"")</x:f>
+      <x:c r="J46" s="19" t="n">
         <x:v>0.03144159723313945</x:v>
       </x:c>
-      <x:c r="L46" s="12" t="n">
+      <x:c r="K46" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J46),J46&gt;=0,ISNUMBER(D46),D46&gt;=0),J46*D46,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M46" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K46),ISNUMBER(D46),D46&gt;=0),K46*D46,"")</x:f>
         <x:v>0.03144159723313945</x:v>
       </x:c>
-      <x:c r="N46" s="10" t="str">
+      <x:c r="L46" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O46" s="10" t="str">
+      <x:c r="M46" s="10" t="str">
         <x:v>vendor_BOM row 42; schematic
+Original unit input: NTD 1. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="47" ht="138" customHeight="1">
+      <x:c r="N46"/>
+      <x:c r="O46"/>
+    </x:row>
+    <x:row r="47" ht="153" customHeight="1">
       <x:c r="A47" s="10" t="n">
         <x:v>43</x:v>
       </x:c>
@@ -10367,31 +9876,26 @@
         <x:v>Confirm MPN,case/height,power,tolerance,TCR and voltage rating</x:v>
       </x:c>
       <x:c r="I47" s="10" t="str"/>
-      <x:c r="J47" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K47" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J47),J47&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J47/Summary!$F$5,"")</x:f>
+      <x:c r="J47" s="19" t="n">
         <x:v>0.03144159723313945</x:v>
       </x:c>
-      <x:c r="L47" s="12" t="n">
+      <x:c r="K47" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J47),J47&gt;=0,ISNUMBER(D47),D47&gt;=0),J47*D47,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M47" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K47),ISNUMBER(D47),D47&gt;=0),K47*D47,"")</x:f>
         <x:v>0.03144159723313945</x:v>
       </x:c>
-      <x:c r="N47" s="10" t="str">
+      <x:c r="L47" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O47" s="10" t="str">
+      <x:c r="M47" s="10" t="str">
         <x:v>vendor_BOM row 43; schematic
+Original unit input: NTD 1. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="48" ht="138" customHeight="1">
+      <x:c r="N47"/>
+      <x:c r="O47"/>
+    </x:row>
+    <x:row r="48" ht="153" customHeight="1">
       <x:c r="A48" s="10" t="n">
         <x:v>44</x:v>
       </x:c>
@@ -10418,31 +9922,26 @@
         <x:v>Confirm MPN,case/height,power,tolerance,TCR and voltage rating</x:v>
       </x:c>
       <x:c r="I48" s="10" t="str"/>
-      <x:c r="J48" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K48" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J48),J48&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J48/Summary!$F$5,"")</x:f>
+      <x:c r="J48" s="19" t="n">
         <x:v>0.03144159723313945</x:v>
       </x:c>
-      <x:c r="L48" s="12" t="n">
+      <x:c r="K48" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J48),J48&gt;=0,ISNUMBER(D48),D48&gt;=0),J48*D48,"")</x:f>
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="M48" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K48),ISNUMBER(D48),D48&gt;=0),K48*D48,"")</x:f>
         <x:v>0.09432479169941835</x:v>
       </x:c>
-      <x:c r="N48" s="10" t="str">
+      <x:c r="L48" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O48" s="10" t="str">
+      <x:c r="M48" s="10" t="str">
         <x:v>vendor_BOM row 44; schematic
+Original unit input: NTD 1. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="49" ht="138" customHeight="1">
+      <x:c r="N48"/>
+      <x:c r="O48"/>
+    </x:row>
+    <x:row r="49" ht="153" customHeight="1">
       <x:c r="A49" s="10" t="n">
         <x:v>45</x:v>
       </x:c>
@@ -10469,31 +9968,26 @@
         <x:v>Confirm MPN,case/height,power,tolerance,TCR and voltage rating</x:v>
       </x:c>
       <x:c r="I49" s="10" t="str"/>
-      <x:c r="J49" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K49" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J49),J49&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J49/Summary!$F$5,"")</x:f>
+      <x:c r="J49" s="19" t="n">
         <x:v>0.03144159723313945</x:v>
       </x:c>
-      <x:c r="L49" s="12" t="n">
+      <x:c r="K49" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J49),J49&gt;=0,ISNUMBER(D49),D49&gt;=0),J49*D49,"")</x:f>
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="M49" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K49),ISNUMBER(D49),D49&gt;=0),K49*D49,"")</x:f>
         <x:v>0.22009118063197614</x:v>
       </x:c>
-      <x:c r="N49" s="10" t="str">
+      <x:c r="L49" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O49" s="10" t="str">
+      <x:c r="M49" s="10" t="str">
         <x:v>vendor_BOM row 45; schematic
+Original unit input: NTD 1. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="50" ht="138" customHeight="1">
+      <x:c r="N49"/>
+      <x:c r="O49"/>
+    </x:row>
+    <x:row r="50" ht="153" customHeight="1">
       <x:c r="A50" s="10" t="n">
         <x:v>46</x:v>
       </x:c>
@@ -10520,31 +10014,26 @@
         <x:v>Confirm MPN,case/height,power,tolerance,TCR and voltage rating</x:v>
       </x:c>
       <x:c r="I50" s="10" t="str"/>
-      <x:c r="J50" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K50" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J50),J50&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J50/Summary!$F$5,"")</x:f>
+      <x:c r="J50" s="19" t="n">
         <x:v>0.03144159723313945</x:v>
       </x:c>
-      <x:c r="L50" s="12" t="n">
+      <x:c r="K50" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J50),J50&gt;=0,ISNUMBER(D50),D50&gt;=0),J50*D50,"")</x:f>
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="M50" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K50),ISNUMBER(D50),D50&gt;=0),K50*D50,"")</x:f>
         <x:v>0.1257663889325578</x:v>
       </x:c>
-      <x:c r="N50" s="10" t="str">
+      <x:c r="L50" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O50" s="10" t="str">
+      <x:c r="M50" s="10" t="str">
         <x:v>vendor_BOM row 46; schematic
+Original unit input: NTD 1. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="51" ht="138" customHeight="1">
+      <x:c r="N50"/>
+      <x:c r="O50"/>
+    </x:row>
+    <x:row r="51" ht="153" customHeight="1">
       <x:c r="A51" s="10" t="n">
         <x:v>47</x:v>
       </x:c>
@@ -10571,31 +10060,26 @@
         <x:v>Confirm MPN,case/height,power,tolerance,TCR and voltage rating</x:v>
       </x:c>
       <x:c r="I51" s="10" t="str"/>
-      <x:c r="J51" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K51" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J51),J51&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J51/Summary!$F$5,"")</x:f>
+      <x:c r="J51" s="19" t="n">
         <x:v>0.03144159723313945</x:v>
       </x:c>
-      <x:c r="L51" s="12" t="n">
+      <x:c r="K51" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J51),J51&gt;=0,ISNUMBER(D51),D51&gt;=0),J51*D51,"")</x:f>
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="M51" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K51),ISNUMBER(D51),D51&gt;=0),K51*D51,"")</x:f>
         <x:v>0.1257663889325578</x:v>
       </x:c>
-      <x:c r="N51" s="10" t="str">
+      <x:c r="L51" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O51" s="10" t="str">
+      <x:c r="M51" s="10" t="str">
         <x:v>vendor_BOM row 47; schematic
+Original unit input: NTD 1. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="52" ht="138" customHeight="1">
+      <x:c r="N51"/>
+      <x:c r="O51"/>
+    </x:row>
+    <x:row r="52" ht="153" customHeight="1">
       <x:c r="A52" s="10" t="n">
         <x:v>48</x:v>
       </x:c>
@@ -10622,31 +10106,26 @@
         <x:v>Confirm MPN/package,ratings/tolerance,leakage and noise</x:v>
       </x:c>
       <x:c r="I52" s="10" t="str"/>
-      <x:c r="J52" s="14" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="K52" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J52),J52&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J52/Summary!$F$5,"")</x:f>
+      <x:c r="J52" s="19" t="n">
         <x:v>0.9432479169941833</x:v>
       </x:c>
-      <x:c r="L52" s="12" t="n">
+      <x:c r="K52" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J52),J52&gt;=0,ISNUMBER(D52),D52&gt;=0),J52*D52,"")</x:f>
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="M52" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K52),ISNUMBER(D52),D52&gt;=0),K52*D52,"")</x:f>
         <x:v>0.9432479169941833</x:v>
       </x:c>
-      <x:c r="N52" s="10" t="str">
+      <x:c r="L52" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O52" s="10" t="str">
+      <x:c r="M52" s="10" t="str">
         <x:v>vendor_BOM row 48; schematic
+Original unit input: NTD 30. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="53" ht="138" customHeight="1">
+      <x:c r="N52"/>
+      <x:c r="O52"/>
+    </x:row>
+    <x:row r="53" ht="153" customHeight="1">
       <x:c r="A53" s="10" t="n">
         <x:v>49</x:v>
       </x:c>
@@ -10673,31 +10152,26 @@
         <x:v>Confirm MPN,case/height,power,tolerance,TCR and voltage rating</x:v>
       </x:c>
       <x:c r="I53" s="10" t="str"/>
-      <x:c r="J53" s="14" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="K53" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J53),J53&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J53/Summary!$F$5,"")</x:f>
+      <x:c r="J53" s="19" t="n">
         <x:v>0.15720798616569723</x:v>
       </x:c>
-      <x:c r="L53" s="12" t="n">
+      <x:c r="K53" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J53),J53&gt;=0,ISNUMBER(D53),D53&gt;=0),J53*D53,"")</x:f>
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="M53" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K53),ISNUMBER(D53),D53&gt;=0),K53*D53,"")</x:f>
         <x:v>0.15720798616569723</x:v>
       </x:c>
-      <x:c r="N53" s="10" t="str">
+      <x:c r="L53" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O53" s="10" t="str">
+      <x:c r="M53" s="10" t="str">
         <x:v>vendor_BOM row 49; schematic
+Original unit input: NTD 5. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="54" ht="138" customHeight="1">
+      <x:c r="N53"/>
+      <x:c r="O53"/>
+    </x:row>
+    <x:row r="54" ht="153" customHeight="1">
       <x:c r="A54" s="10" t="n">
         <x:v>50</x:v>
       </x:c>
@@ -10724,31 +10198,26 @@
         <x:v>Confirm MPN,case/height,power,tolerance,TCR and voltage rating</x:v>
       </x:c>
       <x:c r="I54" s="10" t="str"/>
-      <x:c r="J54" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K54" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J54),J54&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J54/Summary!$F$5,"")</x:f>
+      <x:c r="J54" s="19" t="n">
         <x:v>0.03144159723313945</x:v>
       </x:c>
-      <x:c r="L54" s="12" t="n">
+      <x:c r="K54" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J54),J54&gt;=0,ISNUMBER(D54),D54&gt;=0),J54*D54,"")</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M54" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K54),ISNUMBER(D54),D54&gt;=0),K54*D54,"")</x:f>
         <x:v>0.0628831944662789</x:v>
       </x:c>
-      <x:c r="N54" s="10" t="str">
+      <x:c r="L54" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O54" s="10" t="str">
+      <x:c r="M54" s="10" t="str">
         <x:v>vendor_BOM row 50; schematic
+Original unit input: NTD 1. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="55" ht="138" customHeight="1">
+      <x:c r="N54"/>
+      <x:c r="O54"/>
+    </x:row>
+    <x:row r="55" ht="153" customHeight="1">
       <x:c r="A55" s="10" t="n">
         <x:v>51</x:v>
       </x:c>
@@ -10775,31 +10244,26 @@
         <x:v>Confirm MPN,type,actuator/travel,ratings and opening</x:v>
       </x:c>
       <x:c r="I55" s="10" t="str"/>
-      <x:c r="J55" s="14" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="K55" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J55),J55&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J55/Summary!$F$5,"")</x:f>
+      <x:c r="J55" s="19" t="n">
         <x:v>0.47162395849709166</x:v>
       </x:c>
-      <x:c r="L55" s="12" t="n">
+      <x:c r="K55" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J55),J55&gt;=0,ISNUMBER(D55),D55&gt;=0),J55*D55,"")</x:f>
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="M55" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K55),ISNUMBER(D55),D55&gt;=0),K55*D55,"")</x:f>
         <x:v>0.47162395849709166</x:v>
       </x:c>
-      <x:c r="N55" s="10" t="str">
+      <x:c r="L55" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O55" s="10" t="str">
+      <x:c r="M55" s="10" t="str">
         <x:v>vendor_BOM row 51; schematic
+Original unit input: NTD 15. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="56" ht="138" customHeight="1">
+      <x:c r="N55"/>
+      <x:c r="O55"/>
+    </x:row>
+    <x:row r="56" ht="153" customHeight="1">
       <x:c r="A56" s="10" t="n">
         <x:v>52</x:v>
       </x:c>
@@ -10826,31 +10290,26 @@
         <x:v>Confirm MPN,package/height,actuation force and contact ratings</x:v>
       </x:c>
       <x:c r="I56" s="10" t="str"/>
-      <x:c r="J56" s="14" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="K56" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J56),J56&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J56/Summary!$F$5,"")</x:f>
+      <x:c r="J56" s="19" t="n">
         <x:v>0.15720798616569723</x:v>
       </x:c>
-      <x:c r="L56" s="12" t="n">
+      <x:c r="K56" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J56),J56&gt;=0,ISNUMBER(D56),D56&gt;=0),J56*D56,"")</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="M56" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K56),ISNUMBER(D56),D56&gt;=0),K56*D56,"")</x:f>
         <x:v>0.31441597233139446</x:v>
       </x:c>
-      <x:c r="N56" s="10" t="str">
+      <x:c r="L56" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O56" s="10" t="str">
+      <x:c r="M56" s="10" t="str">
         <x:v>vendor_BOM row 52; schematic
+Original unit input: NTD 5. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="57" ht="108" customHeight="1">
+      <x:c r="N56"/>
+      <x:c r="O56"/>
+    </x:row>
+    <x:row r="57" ht="123" customHeight="1">
       <x:c r="A57" s="10" t="n">
         <x:v>53</x:v>
       </x:c>
@@ -10877,31 +10336,26 @@
         <x:v>Confirm ordering suffix/external values;5V/fan margin unverified</x:v>
       </x:c>
       <x:c r="I57" s="10" t="str"/>
-      <x:c r="J57" s="14" t="n">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="K57" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J57),J57&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J57/Summary!$F$5,"")</x:f>
+      <x:c r="J57" s="19" t="n">
         <x:v>1.634963056123251</x:v>
       </x:c>
-      <x:c r="L57" s="12" t="n">
+      <x:c r="K57" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J57),J57&gt;=0,ISNUMBER(D57),D57&gt;=0),J57*D57,"")</x:f>
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="M57" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K57),ISNUMBER(D57),D57&gt;=0),K57*D57,"")</x:f>
         <x:v>1.634963056123251</x:v>
       </x:c>
-      <x:c r="N57" s="10" t="str">
+      <x:c r="L57" s="10" t="str">
         <x:v>Proxy</x:v>
       </x:c>
-      <x:c r="O57" s="10" t="str">
+      <x:c r="M57" s="10" t="str">
         <x:v>vendor_BOM row 53; schematic; TI_TPS61023
+Original unit input: NTD 52. Converted at 31.805 NTD/USD.
 Search results list TPS61023DRLT cut tape NTD 52. Packaging-suffix proxy for vendor TPS61023; exact order code requires confirmation.
 https://www.digikey.tw/en/products/detail/texas-instruments/TPS61023DRLR/11310629</x:v>
       </x:c>
-    </x:row>
-    <x:row r="58" ht="93" customHeight="1">
+      <x:c r="N57"/>
+      <x:c r="O57"/>
+    </x:row>
+    <x:row r="58" ht="108" customHeight="1">
       <x:c r="A58" s="10" t="n">
         <x:v>54</x:v>
       </x:c>
@@ -10928,31 +10382,26 @@
         <x:v>Confirm suffix,R1–R3/R9 and battery/thermal configuration</x:v>
       </x:c>
       <x:c r="I58" s="10" t="str"/>
-      <x:c r="J58" s="14" t="n">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="K58" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J58),J58&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J58/Summary!$F$5,"")</x:f>
+      <x:c r="J58" s="19" t="n">
         <x:v>2.766860556516271</x:v>
       </x:c>
-      <x:c r="L58" s="12" t="n">
+      <x:c r="K58" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J58),J58&gt;=0,ISNUMBER(D58),D58&gt;=0),J58*D58,"")</x:f>
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="M58" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K58),ISNUMBER(D58),D58&gt;=0),K58*D58,"")</x:f>
         <x:v>2.766860556516271</x:v>
       </x:c>
-      <x:c r="N58" s="10" t="str">
+      <x:c r="L58" s="10" t="str">
         <x:v>Proxy</x:v>
       </x:c>
-      <x:c r="O58" s="10" t="str">
+      <x:c r="M58" s="10" t="str">
         <x:v>vendor_BOM row 54; schematic; TI_BQ24074
+Original unit input: NTD 88. Converted at 31.805 NTD/USD.
 NTD 88 each at quantity 1; RGT package assumed from schematic.
 https://www.digikey.tw/en/products/detail/texas-instruments/BQ24074RGTR/2047269</x:v>
       </x:c>
-    </x:row>
-    <x:row r="59" ht="138" customHeight="1">
+      <x:c r="N58"/>
+      <x:c r="O58"/>
+    </x:row>
+    <x:row r="59" ht="153" customHeight="1">
       <x:c r="A59" s="10" t="n">
         <x:v>55</x:v>
       </x:c>
@@ -10977,26 +10426,23 @@
         <x:v>Vendor must identify model,function,package and external values</x:v>
       </x:c>
       <x:c r="I59" s="10" t="str"/>
-      <x:c r="J59" s="14"/>
-      <x:c r="K59" s="12" t="str">
-        <x:f>IF(AND(ISNUMBER(J59),J59&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J59/Summary!$F$5,"")</x:f>
-      </x:c>
-      <x:c r="L59" s="12" t="str">
+      <x:c r="J59" s="19"/>
+      <x:c r="K59" s="24" t="str">
         <x:f>IF(AND(ISNUMBER(J59),J59&gt;=0,ISNUMBER(D59),D59&gt;=0),J59*D59,"")</x:f>
       </x:c>
-      <x:c r="M59" s="12" t="str">
-        <x:f>IF(AND(ISNUMBER(K59),ISNUMBER(D59),D59&gt;=0),K59*D59,"")</x:f>
-      </x:c>
-      <x:c r="N59" s="10" t="str">
+      <x:c r="L59" s="10" t="str">
         <x:v>Unidentified part</x:v>
       </x:c>
-      <x:c r="O59" s="10" t="str">
+      <x:c r="M59" s="10" t="str">
         <x:v>vendor_BOM row 55; schematic
+Original unit input: unpriced. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="60" ht="93" customHeight="1">
+      <x:c r="N59"/>
+      <x:c r="O59"/>
+    </x:row>
+    <x:row r="60" ht="108" customHeight="1">
       <x:c r="A60" s="10" t="n">
         <x:v>56</x:v>
       </x:c>
@@ -11023,31 +10469,26 @@
         <x:v>Confirm memory variant,antenna keepout and assembled height</x:v>
       </x:c>
       <x:c r="I60" s="10" t="str"/>
-      <x:c r="J60" s="14" t="n">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="K60" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J60),J60&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J60/Summary!$F$5,"")</x:f>
+      <x:c r="J60" s="19" t="n">
         <x:v>5.6909290991982395</x:v>
       </x:c>
-      <x:c r="L60" s="12" t="n">
+      <x:c r="K60" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J60),J60&gt;=0,ISNUMBER(D60),D60&gt;=0),J60*D60,"")</x:f>
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="M60" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K60),ISNUMBER(D60),D60&gt;=0),K60*D60,"")</x:f>
         <x:v>5.6909290991982395</x:v>
       </x:c>
-      <x:c r="N60" s="10" t="str">
+      <x:c r="L60" s="10" t="str">
         <x:v>Proxy</x:v>
       </x:c>
-      <x:c r="O60" s="10" t="str">
+      <x:c r="M60" s="10" t="str">
         <x:v>vendor_BOM row 56; schematic; ESPRESSIF_32E
+Original unit input: NTD 181. Converted at 31.805 NTD/USD.
 NTD 181 each. N4 is a price proxy; vendor flash suffix missing.
 https://www.digikey.tw/en/products/detail/espressif-systems/ESP32-WROOM-32E-N4/11613125</x:v>
       </x:c>
-    </x:row>
-    <x:row r="61" ht="138" customHeight="1">
+      <x:c r="N60"/>
+      <x:c r="O60"/>
+    </x:row>
+    <x:row r="61" ht="153" customHeight="1">
       <x:c r="A61" s="10" t="n">
         <x:v>57</x:v>
       </x:c>
@@ -11074,31 +10515,26 @@
         <x:v>Verify C17/C18,thermal design and available current</x:v>
       </x:c>
       <x:c r="I61" s="10" t="str"/>
-      <x:c r="J61" s="14" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="K61" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J61),J61&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J61/Summary!$F$5,"")</x:f>
+      <x:c r="J61" s="19" t="n">
         <x:v>0.31441597233139446</x:v>
       </x:c>
-      <x:c r="L61" s="12" t="n">
+      <x:c r="K61" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J61),J61&gt;=0,ISNUMBER(D61),D61&gt;=0),J61*D61,"")</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="M61" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K61),ISNUMBER(D61),D61&gt;=0),K61*D61,"")</x:f>
         <x:v>0.31441597233139446</x:v>
       </x:c>
-      <x:c r="N61" s="10" t="str">
+      <x:c r="L61" s="10" t="str">
         <x:v>Allowance</x:v>
       </x:c>
-      <x:c r="O61" s="10" t="str">
+      <x:c r="M61" s="10" t="str">
         <x:v>vendor_BOM row 57; schematic; ECMOS_EC50117
+Original unit input: NTD 10. Converted at 31.805 NTD/USD.
 Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.
 </x:v>
       </x:c>
-    </x:row>
-    <x:row r="62" ht="78" customHeight="1">
+      <x:c r="N61"/>
+      <x:c r="O61"/>
+    </x:row>
+    <x:row r="62" ht="93" customHeight="1">
       <x:c r="A62" s="10" t="n">
         <x:v>58</x:v>
       </x:c>
@@ -11125,31 +10561,26 @@
         <x:v>Verify C19/C20 effective capacitance,stability and thermal load</x:v>
       </x:c>
       <x:c r="I62" s="10" t="str"/>
-      <x:c r="J62" s="14" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K62" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J62),J62&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J62/Summary!$F$5,"")</x:f>
+      <x:c r="J62" s="19" t="n">
         <x:v>0.7545983335953467</x:v>
       </x:c>
-      <x:c r="L62" s="12" t="n">
+      <x:c r="K62" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J62),J62&gt;=0,ISNUMBER(D62),D62&gt;=0),J62*D62,"")</x:f>
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="M62" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K62),ISNUMBER(D62),D62&gt;=0),K62*D62,"")</x:f>
         <x:v>0.7545983335953467</x:v>
       </x:c>
-      <x:c r="N62" s="10" t="str">
+      <x:c r="L62" s="10" t="str">
         <x:v>Listed</x:v>
       </x:c>
-      <x:c r="O62" s="10" t="str">
+      <x:c r="M62" s="10" t="str">
         <x:v>vendor_BOM row 58; schematic; TI_LP5907
+Original unit input: NTD 24. Converted at 31.805 NTD/USD.
 NTD 24 each at quantity 1.
 https://www.digikey.tw/en/products/detail/texas-instruments/LP5907MFX-3-3-NOPB/3906441</x:v>
       </x:c>
-    </x:row>
-    <x:row r="63" ht="93" customHeight="1">
+      <x:c r="N62"/>
+      <x:c r="O62"/>
+    </x:row>
+    <x:row r="63" ht="108" customHeight="1">
       <x:c r="A63" s="10" t="n">
         <x:v>59</x:v>
       </x:c>
@@ -11176,31 +10607,26 @@
         <x:v>Verify C22/C23,layout and measured reference voltage</x:v>
       </x:c>
       <x:c r="I63" s="10" t="str"/>
-      <x:c r="J63" s="14" t="n">
-        <x:v>628</x:v>
-      </x:c>
-      <x:c r="K63" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J63),J63&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J63/Summary!$F$5,"")</x:f>
+      <x:c r="J63" s="19" t="n">
         <x:v>19.745323062411572</x:v>
       </x:c>
-      <x:c r="L63" s="12" t="n">
+      <x:c r="K63" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J63),J63&gt;=0,ISNUMBER(D63),D63&gt;=0),J63*D63,"")</x:f>
-        <x:v>628</x:v>
-      </x:c>
-      <x:c r="M63" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K63),ISNUMBER(D63),D63&gt;=0),K63*D63,"")</x:f>
         <x:v>19.745323062411572</x:v>
       </x:c>
-      <x:c r="N63" s="10" t="str">
+      <x:c r="L63" s="10" t="str">
         <x:v>Proxy</x:v>
       </x:c>
-      <x:c r="O63" s="10" t="str">
+      <x:c r="M63" s="10" t="str">
         <x:v>vendor_BOM row 59; schematic; ADI_LTC6655
+Original unit input: NTD 628. Converted at 31.805 NTD/USD.
 NTD 628 for cut tape. Packaging proxy for #PBF; listed no stock.
 https://www.digikey.tw/en/products/detail/analog-devices-inc/LTC6655BHMS8-2-5-TRPBF/2181717</x:v>
       </x:c>
-    </x:row>
-    <x:row r="64" ht="93" customHeight="1">
+      <x:c r="N63"/>
+      <x:c r="O63"/>
+    </x:row>
+    <x:row r="64" ht="108" customHeight="1">
       <x:c r="A64" s="10" t="n">
         <x:v>60</x:v>
       </x:c>
@@ -11227,31 +10653,26 @@
         <x:v>Confirm suffix,leakage/stability and output range</x:v>
       </x:c>
       <x:c r="I64" s="10" t="str"/>
-      <x:c r="J64" s="14" t="n">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="K64" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J64),J64&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J64/Summary!$F$5,"")</x:f>
+      <x:c r="J64" s="19" t="n">
         <x:v>7.105800974689514</x:v>
       </x:c>
-      <x:c r="L64" s="12" t="n">
+      <x:c r="K64" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J64),J64&gt;=0,ISNUMBER(D64),D64&gt;=0),J64*D64,"")</x:f>
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="M64" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K64),ISNUMBER(D64),D64&gt;=0),K64*D64,"")</x:f>
         <x:v>7.105800974689514</x:v>
       </x:c>
-      <x:c r="N64" s="10" t="str">
+      <x:c r="L64" s="10" t="str">
         <x:v>Proxy</x:v>
       </x:c>
-      <x:c r="O64" s="10" t="str">
+      <x:c r="M64" s="10" t="str">
         <x:v>vendor_BOM row 60; schematic; TI_LMP7721
+Original unit input: NTD 226. Converted at 31.805 NTD/USD.
 Search listing NTD 226 for MAX/NOPB. Vendor LMP7721 suffix missing; package proxy.
 https://www.digikey.tw/en/products/filter/linear/amplifiers/instrumentation-op-amps-buffer-amps/687</x:v>
       </x:c>
-    </x:row>
-    <x:row r="65" ht="78" customHeight="1">
+      <x:c r="N64"/>
+      <x:c r="O64"/>
+    </x:row>
+    <x:row r="65" ht="93" customHeight="1">
       <x:c r="A65" s="10" t="n">
         <x:v>61</x:v>
       </x:c>
@@ -11278,88 +10699,80 @@
         <x:v>Verify sampling timing,input settling,decoupling and measured noise</x:v>
       </x:c>
       <x:c r="I65" s="10" t="str"/>
-      <x:c r="J65" s="14" t="n">
-        <x:v>306</x:v>
-      </x:c>
-      <x:c r="K65" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(J65),J65&gt;=0,ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),J65/Summary!$F$5,"")</x:f>
+      <x:c r="J65" s="19" t="n">
         <x:v>9.62112875334067</x:v>
       </x:c>
-      <x:c r="L65" s="12" t="n">
+      <x:c r="K65" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(J65),J65&gt;=0,ISNUMBER(D65),D65&gt;=0),J65*D65,"")</x:f>
-        <x:v>306</x:v>
-      </x:c>
-      <x:c r="M65" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K65),ISNUMBER(D65),D65&gt;=0),K65*D65,"")</x:f>
         <x:v>9.62112875334067</x:v>
       </x:c>
-      <x:c r="N65" s="10" t="str">
+      <x:c r="L65" s="10" t="str">
         <x:v>Listed</x:v>
       </x:c>
-      <x:c r="O65" s="10" t="str">
+      <x:c r="M65" s="10" t="str">
         <x:v>vendor_BOM row 61; schematic; TI_ADS8866
+Original unit input: NTD 306. Converted at 31.805 NTD/USD.
 NTD 306 each at quantity 1.
 https://www.digikey.tw/zh/products/detail/texas-instruments/ADS8866IDGS/5176196</x:v>
       </x:c>
-    </x:row>
-    <x:row r="66" ht="28" customHeight="1">
-      <x:c r="A66" s="2"/>
-      <x:c r="B66" s="2"/>
-      <x:c r="C66" s="2"/>
-      <x:c r="D66" s="2"/>
-      <x:c r="E66" s="2"/>
-      <x:c r="F66" s="2"/>
-      <x:c r="G66" s="2"/>
-      <x:c r="H66" s="2"/>
-      <x:c r="I66" s="2"/>
-      <x:c r="J66" s="2"/>
-      <x:c r="K66" s="2"/>
-      <x:c r="L66" s="2"/>
-      <x:c r="M66" s="2"/>
-      <x:c r="N66" s="2"/>
-      <x:c r="O66" s="2"/>
-    </x:row>
-    <x:row r="67" ht="28" customHeight="1">
-      <x:c r="A67" s="2"/>
-      <x:c r="B67" s="2"/>
-      <x:c r="C67" s="2"/>
-      <x:c r="D67" s="2"/>
-      <x:c r="E67" s="2"/>
-      <x:c r="F67" s="2"/>
-      <x:c r="G67" s="2"/>
-      <x:c r="H67" s="2"/>
-      <x:c r="I67" s="2"/>
-      <x:c r="J67" s="2"/>
-      <x:c r="K67" s="2"/>
-      <x:c r="L67" s="2"/>
-      <x:c r="M67" s="2"/>
-      <x:c r="N67" s="2"/>
-      <x:c r="O67" s="2"/>
-    </x:row>
-    <x:row r="68" ht="28" customHeight="1">
-      <x:c r="A68" s="2"/>
-      <x:c r="B68" s="2"/>
-      <x:c r="C68" s="2"/>
-      <x:c r="D68" s="2"/>
-      <x:c r="E68" s="2"/>
-      <x:c r="F68" s="2"/>
-      <x:c r="G68" s="2" t="str">
+      <x:c r="N65"/>
+      <x:c r="O65"/>
+    </x:row>
+    <x:row r="66" ht="54" customHeight="1">
+      <x:c r="A66" s="10"/>
+      <x:c r="B66" s="10"/>
+      <x:c r="C66" s="10"/>
+      <x:c r="D66" s="10"/>
+      <x:c r="E66" s="10"/>
+      <x:c r="F66" s="10"/>
+      <x:c r="G66" s="10"/>
+      <x:c r="H66" s="10"/>
+      <x:c r="I66" s="10"/>
+      <x:c r="J66" s="10"/>
+      <x:c r="K66" s="10"/>
+      <x:c r="L66" s="10"/>
+      <x:c r="M66" s="10"/>
+      <x:c r="N66"/>
+      <x:c r="O66"/>
+    </x:row>
+    <x:row r="67" ht="54" customHeight="1">
+      <x:c r="A67" s="10"/>
+      <x:c r="B67" s="10"/>
+      <x:c r="C67" s="10"/>
+      <x:c r="D67" s="10"/>
+      <x:c r="E67" s="10"/>
+      <x:c r="F67" s="10"/>
+      <x:c r="G67" s="10"/>
+      <x:c r="H67" s="10"/>
+      <x:c r="I67" s="10"/>
+      <x:c r="J67" s="10"/>
+      <x:c r="K67" s="10"/>
+      <x:c r="L67" s="10"/>
+      <x:c r="M67" s="10"/>
+      <x:c r="N67"/>
+      <x:c r="O67"/>
+    </x:row>
+    <x:row r="68" ht="54" customHeight="1">
+      <x:c r="A68" s="10"/>
+      <x:c r="B68" s="10"/>
+      <x:c r="C68" s="10"/>
+      <x:c r="D68" s="10"/>
+      <x:c r="E68" s="10"/>
+      <x:c r="F68" s="10"/>
+      <x:c r="G68" s="10" t="str">
         <x:v>Priced materials only; U3, fabrication and assembly excluded.</x:v>
       </x:c>
-      <x:c r="H68" s="2"/>
-      <x:c r="I68" s="2"/>
-      <x:c r="J68" s="2"/>
-      <x:c r="K68" s="2"/>
-      <x:c r="L68" s="13" t="n">
-        <x:f>SUM(L5:L65)</x:f>
-        <x:v>1954</x:v>
-      </x:c>
-      <x:c r="M68" s="13" t="n">
-        <x:f>SUM(M5:M65)</x:f>
+      <x:c r="H68" s="10"/>
+      <x:c r="I68" s="10"/>
+      <x:c r="J68" s="10"/>
+      <x:c r="K68" s="24" t="n">
+        <x:f>SUM(K5:K65)</x:f>
         <x:v>61.436880993554496</x:v>
       </x:c>
-      <x:c r="N68" s="2"/>
-      <x:c r="O68" s="2"/>
+      <x:c r="L68" s="10"/>
+      <x:c r="M68" s="10"/>
+      <x:c r="N68"/>
+      <x:c r="O68"/>
     </x:row>
     <x:row r="69" ht="28" customHeight="1">
       <x:c r="A69" s="2"/>
@@ -12254,7 +11667,7 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="15" hidden="0" customWidth="1"/>
@@ -12300,7 +11713,7 @@
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
       <x:c r="A3" s="4" t="str">
-        <x:v>Recalculated from cost.md. No duplicate resin charge.</x:v>
+        <x:v>All monetary terms converted to USD; the original printing formula and three batches are preserved.</x:v>
       </x:c>
       <x:c r="B3" s="2"/>
       <x:c r="C3" s="2"/>
@@ -12315,44 +11728,42 @@
       <x:c r="L3" s="2"/>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
-      <x:c r="A4" s="8" t="str">
+      <x:c r="A4" s="23" t="str">
         <x:v>Batch</x:v>
       </x:c>
-      <x:c r="B4" s="8" t="str">
+      <x:c r="B4" s="23" t="str">
         <x:v>Included IDs</x:v>
       </x:c>
-      <x:c r="C4" s="8" t="str">
+      <x:c r="C4" s="23" t="str">
         <x:v>min</x:v>
       </x:c>
-      <x:c r="D4" s="8" t="str">
+      <x:c r="D4" s="23" t="str">
         <x:v>h</x:v>
       </x:c>
-      <x:c r="E4" s="8" t="str">
+      <x:c r="E4" s="23" t="str">
         <x:v>mL</x:v>
       </x:c>
-      <x:c r="F4" s="8" t="str">
+      <x:c r="F4" s="23" t="str">
         <x:v>g</x:v>
       </x:c>
-      <x:c r="G4" s="8" t="str">
-        <x:v>Source resin NTD</x:v>
-      </x:c>
-      <x:c r="H4" s="8" t="str">
-        <x:v>Resin term NTD</x:v>
-      </x:c>
-      <x:c r="I4" s="8" t="str">
-        <x:v>Time term NTD</x:v>
-      </x:c>
-      <x:c r="J4" s="8" t="str">
-        <x:v>Fixed term NTD</x:v>
-      </x:c>
-      <x:c r="K4" s="8" t="str">
-        <x:v>Total NTD</x:v>
-      </x:c>
-      <x:c r="L4" s="8" t="str">
+      <x:c r="G4" s="23" t="str">
+        <x:v>Source resin USD</x:v>
+      </x:c>
+      <x:c r="H4" s="23" t="str">
+        <x:v>Resin term USD</x:v>
+      </x:c>
+      <x:c r="I4" s="23" t="str">
+        <x:v>Time term USD</x:v>
+      </x:c>
+      <x:c r="J4" s="23" t="str">
+        <x:v>Fixed term USD</x:v>
+      </x:c>
+      <x:c r="K4" s="23" t="str">
         <x:v>Total USD</x:v>
       </x:c>
-    </x:row>
-    <x:row r="5" ht="42" customHeight="1">
+      <x:c r="L4"/>
+    </x:row>
+    <x:row r="5" ht="48" customHeight="1">
       <x:c r="A5" s="10" t="str">
         <x:v>P1</x:v>
       </x:c>
@@ -12372,31 +11783,28 @@
       <x:c r="F5" s="10" t="n">
         <x:v>118.285</x:v>
       </x:c>
-      <x:c r="G5" s="12" t="n">
-        <x:v>260.226</x:v>
-      </x:c>
-      <x:c r="H5" s="12" t="n">
+      <x:c r="G5" s="24" t="n">
+        <x:v>8.181921081590945</x:v>
+      </x:c>
+      <x:c r="H5" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(G5),G5&gt;=0,ISNUMBER($B$14),$B$14&gt;=0),G5*$B$14,"")</x:f>
-        <x:v>286.2486</x:v>
-      </x:c>
-      <x:c r="I5" s="12" t="n">
+        <x:v>9.00011318975004</x:v>
+      </x:c>
+      <x:c r="I5" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(D5),ISNUMBER($B$15),$B$15&gt;=0),D5*$B$15,"")</x:f>
-        <x:v>126.51208333333334</x:v>
-      </x:c>
-      <x:c r="J5" s="12" t="n">
+        <x:v>3.97774196929204</x:v>
+      </x:c>
+      <x:c r="J5" s="24" t="n">
         <x:f>IF(AND(ISNUMBER($B$13),$B$13&gt;=0),$B$13,"")</x:f>
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="K5" s="12" t="n">
+        <x:v>0.7860399308284861</x:v>
+      </x:c>
+      <x:c r="K5" s="24" t="n">
         <x:f>IF(AND(COUNT(H5:J5)=3,ISNUMBER($B$12),$B$12&gt;=0),$B$12*SUM(H5:J5),"")</x:f>
-        <x:v>525.31282</x:v>
-      </x:c>
-      <x:c r="L5" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K5),ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),K5/Summary!$F$5,"")</x:f>
         <x:v>16.51667410784468</x:v>
       </x:c>
-    </x:row>
-    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="L5"/>
+    </x:row>
+    <x:row r="6" ht="48" customHeight="1">
       <x:c r="A6" s="10" t="str">
         <x:v>P2</x:v>
       </x:c>
@@ -12416,31 +11824,28 @@
       <x:c r="F6" s="10" t="n">
         <x:v>125.43</x:v>
       </x:c>
-      <x:c r="G6" s="12" t="n">
-        <x:v>275.945</x:v>
-      </x:c>
-      <x:c r="H6" s="12" t="n">
+      <x:c r="G6" s="24" t="n">
+        <x:v>8.676151548498664</x:v>
+      </x:c>
+      <x:c r="H6" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(G6),G6&gt;=0,ISNUMBER($B$14),$B$14&gt;=0),G6*$B$14,"")</x:f>
-        <x:v>303.53950000000003</x:v>
-      </x:c>
-      <x:c r="I6" s="12" t="n">
+        <x:v>9.543766703348531</x:v>
+      </x:c>
+      <x:c r="I6" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(D6),ISNUMBER($B$15),$B$15&gt;=0),D6*$B$15,"")</x:f>
-        <x:v>117.39841666666668</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
+        <x:v>3.691193732641618</x:v>
+      </x:c>
+      <x:c r="J6" s="24" t="n">
         <x:f>IF(AND(ISNUMBER($B$13),$B$13&gt;=0),$B$13,"")</x:f>
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="K6" s="12" t="n">
+        <x:v>0.7860399308284861</x:v>
+      </x:c>
+      <x:c r="K6" s="24" t="n">
         <x:f>IF(AND(COUNT(H6:J6)=3,ISNUMBER($B$12),$B$12&gt;=0),$B$12*SUM(H6:J6),"")</x:f>
-        <x:v>535.1255</x:v>
-      </x:c>
-      <x:c r="L6" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K6),ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),K6/Summary!$F$5,"")</x:f>
-        <x:v>16.82520044018236</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="42" customHeight="1">
+        <x:v>16.825200440182364</x:v>
+      </x:c>
+      <x:c r="L6"/>
+    </x:row>
+    <x:row r="7" ht="48" customHeight="1">
       <x:c r="A7" s="10" t="str">
         <x:v>P3</x:v>
       </x:c>
@@ -12460,239 +11865,235 @@
       <x:c r="F7" s="10" t="n">
         <x:v>1.318</x:v>
       </x:c>
-      <x:c r="G7" s="12" t="n">
-        <x:v>1.239</x:v>
-      </x:c>
-      <x:c r="H7" s="12" t="n">
+      <x:c r="G7" s="24" t="n">
+        <x:v>0.038956138971859774</x:v>
+      </x:c>
+      <x:c r="H7" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(G7),G7&gt;=0,ISNUMBER($B$14),$B$14&gt;=0),G7*$B$14,"")</x:f>
-        <x:v>1.3629000000000002</x:v>
-      </x:c>
-      <x:c r="I7" s="12" t="n">
+        <x:v>0.04285175286904575</x:v>
+      </x:c>
+      <x:c r="I7" s="24" t="n">
         <x:f>IF(AND(ISNUMBER(D7),ISNUMBER($B$15),$B$15&gt;=0),D7*$B$15,"")</x:f>
-        <x:v>19.4265</x:v>
-      </x:c>
-      <x:c r="J7" s="12" t="n">
+        <x:v>0.6108001886495834</x:v>
+      </x:c>
+      <x:c r="J7" s="24" t="n">
         <x:f>IF(AND(ISNUMBER($B$13),$B$13&gt;=0),$B$13,"")</x:f>
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="K7" s="12" t="n">
+        <x:v>0.7860399308284861</x:v>
+      </x:c>
+      <x:c r="K7" s="24" t="n">
         <x:f>IF(AND(COUNT(H7:J7)=3,ISNUMBER($B$12),$B$12&gt;=0),$B$12*SUM(H7:J7),"")</x:f>
-        <x:v>54.94728</x:v>
-      </x:c>
-      <x:c r="L7" s="12" t="n">
-        <x:f>IF(AND(ISNUMBER(K7),ISNUMBER(Summary!$F$5),Summary!$F$5&gt;0),K7/Summary!$F$5,"")</x:f>
         <x:v>1.7276302468165383</x:v>
       </x:c>
-    </x:row>
-    <x:row r="8" ht="28" customHeight="1">
-      <x:c r="A8" s="2" t="str">
+      <x:c r="L7"/>
+    </x:row>
+    <x:row r="8" ht="54" customHeight="1">
+      <x:c r="A8" s="10" t="str">
         <x:v>Total</x:v>
       </x:c>
-      <x:c r="B8" s="2"/>
-      <x:c r="C8" s="2" t="n">
+      <x:c r="B8" s="10"/>
+      <x:c r="C8" s="10" t="n">
         <x:f>IF(COUNT(C5:C7)=3,SUM(C5:C7),"")</x:f>
         <x:v>2196</x:v>
       </x:c>
-      <x:c r="D8" s="2" t="n">
+      <x:c r="D8" s="10" t="n">
         <x:f>IF(COUNT(D5:D7)=3,SUM(D5:D7),"")</x:f>
         <x:v>36.6</x:v>
       </x:c>
-      <x:c r="E8" s="2" t="n">
+      <x:c r="E8" s="10" t="n">
         <x:f>IF(COUNT(E5:E7)=3,SUM(E5:E7),"")</x:f>
         <x:v>222.756</x:v>
       </x:c>
-      <x:c r="F8" s="2" t="n">
+      <x:c r="F8" s="10" t="n">
         <x:f>IF(COUNT(F5:F7)=3,SUM(F5:F7),"")</x:f>
         <x:v>245.03300000000002</x:v>
       </x:c>
-      <x:c r="G8" s="13" t="n">
+      <x:c r="G8" s="24" t="n">
         <x:f>IF(COUNT(G5:G7)=3,SUM(G5:G7),"")</x:f>
-        <x:v>537.4100000000001</x:v>
-      </x:c>
-      <x:c r="H8" s="13" t="n">
+        <x:v>16.897028769061468</x:v>
+      </x:c>
+      <x:c r="H8" s="24" t="n">
         <x:f>IF(COUNT(H5:H7)=3,SUM(H5:H7),"")</x:f>
-        <x:v>591.151</x:v>
-      </x:c>
-      <x:c r="I8" s="13" t="n">
+        <x:v>18.586731645967614</x:v>
+      </x:c>
+      <x:c r="I8" s="24" t="n">
         <x:f>IF(COUNT(I5:I7)=3,SUM(I5:I7),"")</x:f>
-        <x:v>263.337</x:v>
-      </x:c>
-      <x:c r="J8" s="13" t="n">
+        <x:v>8.279735890583241</x:v>
+      </x:c>
+      <x:c r="J8" s="24" t="n">
         <x:f>IF(COUNT(J5:J7)=3,SUM(J5:J7),"")</x:f>
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="K8" s="13" t="n">
+        <x:v>2.3581197924854584</x:v>
+      </x:c>
+      <x:c r="K8" s="24" t="n">
         <x:f>IF(COUNT(K5:K7)=3,SUM(K5:K7),"")</x:f>
-        <x:v>1115.3856</x:v>
-      </x:c>
-      <x:c r="L8" s="13" t="n">
-        <x:f>IF(COUNT(L5:L7)=3,SUM(L5:L7),"")</x:f>
-        <x:v>35.069504794843574</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="28" customHeight="1">
-      <x:c r="A9" s="2"/>
-      <x:c r="B9" s="2"/>
-      <x:c r="C9" s="2"/>
-      <x:c r="D9" s="2"/>
-      <x:c r="E9" s="2"/>
-      <x:c r="F9" s="2"/>
-      <x:c r="G9" s="2"/>
-      <x:c r="H9" s="2"/>
-      <x:c r="I9" s="2"/>
-      <x:c r="J9" s="2"/>
-      <x:c r="K9" s="2"/>
-      <x:c r="L9" s="2"/>
-    </x:row>
-    <x:row r="10" ht="28" customHeight="1">
-      <x:c r="A10" s="2"/>
-      <x:c r="B10" s="2"/>
-      <x:c r="C10" s="2"/>
-      <x:c r="D10" s="2"/>
-      <x:c r="E10" s="2"/>
-      <x:c r="F10" s="2"/>
-      <x:c r="G10" s="2"/>
-      <x:c r="H10" s="2"/>
-      <x:c r="I10" s="2"/>
-      <x:c r="J10" s="2"/>
-      <x:c r="K10" s="2"/>
-      <x:c r="L10" s="2"/>
-    </x:row>
-    <x:row r="11" ht="28" customHeight="1">
-      <x:c r="A11" s="2" t="str">
+        <x:v>35.06950479484358</x:v>
+      </x:c>
+      <x:c r="L8"/>
+    </x:row>
+    <x:row r="9" ht="54" customHeight="1">
+      <x:c r="A9" s="10"/>
+      <x:c r="B9" s="10"/>
+      <x:c r="C9" s="10"/>
+      <x:c r="D9" s="10"/>
+      <x:c r="E9" s="10"/>
+      <x:c r="F9" s="10"/>
+      <x:c r="G9" s="10"/>
+      <x:c r="H9" s="10"/>
+      <x:c r="I9" s="10"/>
+      <x:c r="J9" s="10"/>
+      <x:c r="K9" s="10"/>
+      <x:c r="L9"/>
+    </x:row>
+    <x:row r="10" ht="54" customHeight="1">
+      <x:c r="A10" s="10"/>
+      <x:c r="B10" s="10"/>
+      <x:c r="C10" s="10"/>
+      <x:c r="D10" s="10"/>
+      <x:c r="E10" s="10"/>
+      <x:c r="F10" s="10"/>
+      <x:c r="G10" s="10"/>
+      <x:c r="H10" s="10"/>
+      <x:c r="I10" s="10"/>
+      <x:c r="J10" s="10"/>
+      <x:c r="K10" s="10"/>
+      <x:c r="L10"/>
+    </x:row>
+    <x:row r="11" ht="54" customHeight="1">
+      <x:c r="A11" s="10" t="str">
         <x:v>Coefficient</x:v>
       </x:c>
-      <x:c r="B11" s="2" t="str">
+      <x:c r="B11" s="10" t="str">
         <x:v>Value</x:v>
       </x:c>
-      <x:c r="C11" s="2"/>
-      <x:c r="D11" s="2"/>
-      <x:c r="E11" s="2"/>
-      <x:c r="F11" s="2"/>
-      <x:c r="G11" s="2"/>
-      <x:c r="H11" s="2"/>
-      <x:c r="I11" s="2"/>
-      <x:c r="J11" s="2"/>
-      <x:c r="K11" s="2"/>
-      <x:c r="L11" s="2"/>
-    </x:row>
-    <x:row r="12" ht="28" customHeight="1">
-      <x:c r="A12" s="2" t="str">
+      <x:c r="C11" s="10"/>
+      <x:c r="D11" s="10"/>
+      <x:c r="E11" s="10"/>
+      <x:c r="F11" s="10"/>
+      <x:c r="G11" s="10"/>
+      <x:c r="H11" s="10"/>
+      <x:c r="I11" s="10"/>
+      <x:c r="J11" s="10"/>
+      <x:c r="K11" s="10"/>
+      <x:c r="L11"/>
+    </x:row>
+    <x:row r="12" ht="54" customHeight="1">
+      <x:c r="A12" s="10" t="str">
         <x:v>Outer</x:v>
       </x:c>
-      <x:c r="B12" s="9" t="n">
+      <x:c r="B12" s="18" t="n">
         <x:v>1.2</x:v>
       </x:c>
-      <x:c r="C12" s="2"/>
-      <x:c r="D12" s="2" t="str">
-        <x:v>1.2 × (25 + source resin × 1.1 + minutes/60 × 7.195)</x:v>
-      </x:c>
-      <x:c r="E12" s="2"/>
-      <x:c r="F12" s="2"/>
-      <x:c r="G12" s="2"/>
-      <x:c r="H12" s="2"/>
-      <x:c r="I12" s="2"/>
-      <x:c r="J12" s="2"/>
-      <x:c r="K12" s="2"/>
-      <x:c r="L12" s="2"/>
-    </x:row>
-    <x:row r="13" ht="28" customHeight="1">
-      <x:c r="A13" s="2" t="str">
-        <x:v>Fixed NTD</x:v>
-      </x:c>
-      <x:c r="B13" s="9" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C13" s="2"/>
-      <x:c r="D13" s="2"/>
-      <x:c r="E13" s="2"/>
-      <x:c r="F13" s="2"/>
-      <x:c r="G13" s="2"/>
-      <x:c r="H13" s="2"/>
-      <x:c r="I13" s="2"/>
-      <x:c r="J13" s="2"/>
-      <x:c r="K13" s="2"/>
-      <x:c r="L13" s="2"/>
-    </x:row>
-    <x:row r="14" ht="28" customHeight="1">
-      <x:c r="A14" s="2" t="str">
+      <x:c r="C12" s="10"/>
+      <x:c r="D12" s="10" t="str">
+        <x:v>USD total = outer × (fixed USD + resin USD × multiplier + hours × USD/hour)</x:v>
+      </x:c>
+      <x:c r="E12" s="10"/>
+      <x:c r="F12" s="10"/>
+      <x:c r="G12" s="10"/>
+      <x:c r="H12" s="10"/>
+      <x:c r="I12" s="10"/>
+      <x:c r="J12" s="10"/>
+      <x:c r="K12" s="10"/>
+      <x:c r="L12"/>
+    </x:row>
+    <x:row r="13" ht="54" customHeight="1">
+      <x:c r="A13" s="10" t="str">
+        <x:v>Fixed USD</x:v>
+      </x:c>
+      <x:c r="B13" s="19" t="n">
+        <x:v>0.7860399308284861</x:v>
+      </x:c>
+      <x:c r="C13" s="10"/>
+      <x:c r="D13" s="10"/>
+      <x:c r="E13" s="10"/>
+      <x:c r="F13" s="10"/>
+      <x:c r="G13" s="10"/>
+      <x:c r="H13" s="10"/>
+      <x:c r="I13" s="10"/>
+      <x:c r="J13" s="10"/>
+      <x:c r="K13" s="10"/>
+      <x:c r="L13"/>
+    </x:row>
+    <x:row r="14" ht="54" customHeight="1">
+      <x:c r="A14" s="10" t="str">
         <x:v>Resin multiplier</x:v>
       </x:c>
-      <x:c r="B14" s="9" t="n">
+      <x:c r="B14" s="18" t="n">
         <x:v>1.1</x:v>
       </x:c>
-      <x:c r="C14" s="2"/>
-      <x:c r="D14" s="2" t="str">
-        <x:v>P2 and P3 are combined batches. No invented per-part prices. cost.md is unchanged.</x:v>
-      </x:c>
-      <x:c r="E14" s="2"/>
-      <x:c r="F14" s="2"/>
-      <x:c r="G14" s="2"/>
-      <x:c r="H14" s="2"/>
-      <x:c r="I14" s="2"/>
-      <x:c r="J14" s="2"/>
-      <x:c r="K14" s="2"/>
-      <x:c r="L14" s="2"/>
-    </x:row>
-    <x:row r="15" ht="28" customHeight="1">
-      <x:c r="A15" s="2" t="str">
-        <x:v>Time NTD/h</x:v>
-      </x:c>
-      <x:c r="B15" s="9" t="n">
-        <x:v>7.195</x:v>
-      </x:c>
-      <x:c r="C15" s="2"/>
-      <x:c r="D15" s="2"/>
-      <x:c r="E15" s="2"/>
-      <x:c r="F15" s="2"/>
-      <x:c r="G15" s="2"/>
-      <x:c r="H15" s="2"/>
-      <x:c r="I15" s="2"/>
-      <x:c r="J15" s="2"/>
-      <x:c r="K15" s="2"/>
-      <x:c r="L15" s="2"/>
-    </x:row>
-    <x:row r="16" ht="28" customHeight="1">
-      <x:c r="A16" s="2"/>
-      <x:c r="B16" s="2"/>
-      <x:c r="C16" s="2"/>
-      <x:c r="D16" s="2"/>
-      <x:c r="E16" s="2"/>
-      <x:c r="F16" s="2"/>
-      <x:c r="G16" s="2"/>
-      <x:c r="H16" s="2"/>
-      <x:c r="I16" s="2"/>
-      <x:c r="J16" s="2"/>
-      <x:c r="K16" s="2"/>
-      <x:c r="L16" s="2"/>
-    </x:row>
-    <x:row r="17" ht="28" customHeight="1">
-      <x:c r="A17" s="2"/>
-      <x:c r="B17" s="2"/>
-      <x:c r="C17" s="2"/>
-      <x:c r="D17" s="2"/>
-      <x:c r="E17" s="2"/>
-      <x:c r="F17" s="2"/>
-      <x:c r="G17" s="2"/>
-      <x:c r="H17" s="2"/>
-      <x:c r="I17" s="2"/>
-      <x:c r="J17" s="2"/>
-      <x:c r="K17" s="2"/>
-      <x:c r="L17" s="2"/>
-    </x:row>
-    <x:row r="18" ht="28" customHeight="1">
-      <x:c r="A18" s="2"/>
-      <x:c r="B18" s="2"/>
-      <x:c r="C18" s="2"/>
-      <x:c r="D18" s="2"/>
-      <x:c r="E18" s="2"/>
-      <x:c r="F18" s="2"/>
-      <x:c r="G18" s="2"/>
-      <x:c r="H18" s="2"/>
-      <x:c r="I18" s="2"/>
-      <x:c r="J18" s="2"/>
-      <x:c r="K18" s="2"/>
-      <x:c r="L18" s="2"/>
+      <x:c r="C14" s="10"/>
+      <x:c r="D14" s="10" t="str">
+        <x:v>Combined batches keep one batch cost. No invented per-part prices.</x:v>
+      </x:c>
+      <x:c r="E14" s="10"/>
+      <x:c r="F14" s="10"/>
+      <x:c r="G14" s="10"/>
+      <x:c r="H14" s="10"/>
+      <x:c r="I14" s="10"/>
+      <x:c r="J14" s="10"/>
+      <x:c r="K14" s="10"/>
+      <x:c r="L14"/>
+    </x:row>
+    <x:row r="15" ht="54" customHeight="1">
+      <x:c r="A15" s="10" t="str">
+        <x:v>Time USD/h</x:v>
+      </x:c>
+      <x:c r="B15" s="25" t="n">
+        <x:v>0.2262222920924383</x:v>
+      </x:c>
+      <x:c r="C15" s="10"/>
+      <x:c r="D15" s="10"/>
+      <x:c r="E15" s="10"/>
+      <x:c r="F15" s="10"/>
+      <x:c r="G15" s="10"/>
+      <x:c r="H15" s="10"/>
+      <x:c r="I15" s="10"/>
+      <x:c r="J15" s="10"/>
+      <x:c r="K15" s="10"/>
+      <x:c r="L15"/>
+    </x:row>
+    <x:row r="16" ht="54" customHeight="1">
+      <x:c r="A16" s="10"/>
+      <x:c r="B16" s="10"/>
+      <x:c r="C16" s="10"/>
+      <x:c r="D16" s="10" t="str">
+        <x:v>Print source archived in Notes: fixed NTD 25; time NTD 7.195/h; resin NTD 260.226, 275.945, 1.239. Conversion 31.805 NTD/USD.</x:v>
+      </x:c>
+      <x:c r="E16" s="10"/>
+      <x:c r="F16" s="10"/>
+      <x:c r="G16" s="10"/>
+      <x:c r="H16" s="10"/>
+      <x:c r="I16" s="10"/>
+      <x:c r="J16" s="10"/>
+      <x:c r="K16" s="10"/>
+      <x:c r="L16"/>
+    </x:row>
+    <x:row r="17" ht="54" customHeight="1">
+      <x:c r="A17" s="10"/>
+      <x:c r="B17" s="10"/>
+      <x:c r="C17" s="10"/>
+      <x:c r="D17" s="10"/>
+      <x:c r="E17" s="10"/>
+      <x:c r="F17" s="10"/>
+      <x:c r="G17" s="10"/>
+      <x:c r="H17" s="10"/>
+      <x:c r="I17" s="10"/>
+      <x:c r="J17" s="10"/>
+      <x:c r="K17" s="10"/>
+      <x:c r="L17"/>
+    </x:row>
+    <x:row r="18" ht="54" customHeight="1">
+      <x:c r="A18" s="10"/>
+      <x:c r="B18" s="10"/>
+      <x:c r="C18" s="10"/>
+      <x:c r="D18" s="10"/>
+      <x:c r="E18" s="10"/>
+      <x:c r="F18" s="10"/>
+      <x:c r="G18" s="10"/>
+      <x:c r="H18" s="10"/>
+      <x:c r="I18" s="10"/>
+      <x:c r="J18" s="10"/>
+      <x:c r="K18" s="10"/>
+      <x:c r="L18"/>
     </x:row>
     <x:row r="19" ht="28" customHeight="1">
       <x:c r="A19" s="2"/>
@@ -14123,6 +13524,3239 @@
       <x:c r="L120" s="2"/>
     </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="D12:K12"/>
+    <x:mergeCell ref="D14:K14"/>
+    <x:mergeCell ref="D16:K17"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF7B8991"/>
+  </x:sheetPr>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="31" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="105" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="90" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="29"/>
+      <x:c r="B1" s="29"/>
+      <x:c r="C1" s="29"/>
+    </x:row>
+    <x:row r="2" ht="34" customHeight="1">
+      <x:c r="A2" s="30" t="str">
+        <x:v>Notes and sources</x:v>
+      </x:c>
+      <x:c r="B2" s="29" t="str">
+        <x:v>Consolidated 2026-10-11. Original budget inputs and formulas are retained.</x:v>
+      </x:c>
+      <x:c r="C2" s="29"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="29"/>
+      <x:c r="B3" s="29"/>
+      <x:c r="C3" s="29"/>
+    </x:row>
+    <x:row r="4" ht="30" customHeight="1">
+      <x:c r="A4" s="33" t="str">
+        <x:v>Topic / identifier</x:v>
+      </x:c>
+      <x:c r="B4" s="33" t="str">
+        <x:v>Explanation / retained source detail</x:v>
+      </x:c>
+      <x:c r="C4" s="33" t="str">
+        <x:v>Source / provenance</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5" s="36" t="str">
+        <x:v>Use this workbook</x:v>
+      </x:c>
+      <x:c r="B5" s="36" t="str"/>
+      <x:c r="C5" s="36" t="str"/>
+    </x:row>
+    <x:row r="6" ht="40" customHeight="1">
+      <x:c r="A6" s="29" t="str">
+        <x:v>Complete BOM</x:v>
+      </x:c>
+      <x:c r="B6" s="29" t="str">
+        <x:v>The five original worksheets contain 8 printed parts, 26 purchase rows, 61 PCB rows and 3 print batches. Summary retains the live budget formulas.</x:v>
+      </x:c>
+      <x:c r="C6" s="29" t="str"/>
+    </x:row>
+    <x:row r="7" ht="40" customHeight="1">
+      <x:c r="A7" s="29" t="str">
+        <x:v>Currency and updates</x:v>
+      </x:c>
+      <x:c r="B7" s="29" t="str">
+        <x:v>All active English cost inputs and totals are USD. Original currency amounts below are historical source records only. The FX label is not a live repricing control.</x:v>
+      </x:c>
+      <x:c r="C7" s="29" t="str"/>
+    </x:row>
+    <x:row r="8" ht="40" customHeight="1">
+      <x:c r="A8" s="29" t="str">
+        <x:v>Change the FX basis</x:v>
+      </x:c>
+      <x:c r="B8" s="29" t="str">
+        <x:v>Reprice Purchase column H, PCB column J, Summary F6, and the monetary inputs in Print_batches (G5:G7, B13 and B15). Update the snapshot description. Quantities and ownership continue to recalculate.</x:v>
+      </x:c>
+      <x:c r="C8" s="29" t="str">
+        <x:v>Do not change only the FX label and assume that fixed USD inputs were converted.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="68" customHeight="1">
+      <x:c r="A9" s="29" t="str">
+        <x:v>Budget note 1</x:v>
+      </x:c>
+      <x:c r="B9" s="29" t="str">
+        <x:v>2026-10-11. The English workbook and CSV cost columns use USD throughout. The Chinese workbook retains its existing NTD/USD views. Required, Developer and Future are the primary classes. Printed parts, PCB records and purchases retain separate detail. Specifications, purpose, price source and unresolved compatibility are distinguished.</x:v>
+      </x:c>
+      <x:c r="C9" s="29" t="str">
+        <x:v>Retained budget reading notes; source prices dated 2026-10-08.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="68" customHeight="1">
+      <x:c r="A10" s="29" t="str">
+        <x:v>Budget note 2</x:v>
+      </x:c>
+      <x:c r="B10" s="29" t="str">
+        <x:v>Required includes eight prints, the PCB and 13 purchased assembly lines. Developer includes 10 external programming, measurement, gas-delivery and tool lines. Borrowing is acceptable; gas delivery and flow verification remain necessary for gas experiments. Future contains PDMS, valve development and environment sensing. These three lines are excluded from current device budgets.</x:v>
+      </x:c>
+      <x:c r="C10" s="29" t="str">
+        <x:v>Retained budget reading notes; source prices dated 2026-10-08.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="96" customHeight="1">
+      <x:c r="A11" s="29" t="str">
+        <x:v>Budget note 3</x:v>
+      </x:c>
+      <x:c r="B11" s="29" t="str">
+        <x:v> These are budgets, not an order-ready total. The device includes USD 377.30 for a custom thin emission filter. Edmund 67-016 lists at USD 284, but its 12.5 mm diameter and approximately 2 mm thickness do not fit the 5.2 × 4.2 × 1.0 mm seat. Cutting the outline alone does not fix thickness. Obtain a dimensional, angular-spectrum and fabrication quotation. LEE 101 stacks are an experimental candidate in the optical comparison; their price and installed compatibility are not yet substituted for this allowance.</x:v>
+      </x:c>
+      <x:c r="C11" s="29" t="str">
+        <x:v>Retained budget reading notes; source prices dated 2026-10-08.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="68" customHeight="1">
+      <x:c r="A12" s="29" t="str">
+        <x:v>Budget note 4</x:v>
+      </x:c>
+      <x:c r="B12" s="29" t="str">
+        <x:v>The four-case optical report also evaluates Edmund #29-190, the 500 nm ultra-thin OD4 candidate. It differs from the older #67-016 budget reference. Neither its simulated curve nor its 12.45 mm disc establishes installed compatibility. The custom-filter allowance remains until the chosen filter and holder have a verified quote.</x:v>
+      </x:c>
+      <x:c r="C12" s="29" t="str">
+        <x:v>Retained budget reading notes; source prices dated 2026-10-08.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="54" customHeight="1">
+      <x:c r="A13" s="29" t="str">
+        <x:v>Budget note 5</x:v>
+      </x:c>
+      <x:c r="B13" s="29" t="str">
+        <x:v>Listed identifies a public price. Proxy identifies a comparable part or package. Allowance and Custom allowance are planning values, not verified market quotations. A reference price does not change the specified cap screws, regular M3 nuts or washers.</x:v>
+      </x:c>
+      <x:c r="C13" s="29" t="str">
+        <x:v>Retained budget reading notes; source prices dated 2026-10-08.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="68" customHeight="1">
+      <x:c r="A14" s="29" t="str">
+        <x:v>Budget note 6</x:v>
+      </x:c>
+      <x:c r="B14" s="29" t="str">
+        <x:v>The gas-filter proxy is Gilson ANP1322 at USD 95 per 100. Two used filters cost USD 1.90, while one box costs USD 95.00. This 0.22 µm nonsterile hydrophobic PTFE product is not a qualified replacement for the specified 0.2 µm gas filter. Cell use, fittings, pressure drop and VOC recovery need confirmation.</x:v>
+      </x:c>
+      <x:c r="C14" s="29" t="str">
+        <x:v>Retained budget reading notes; source prices dated 2026-10-08.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="54" customHeight="1">
+      <x:c r="A15" s="29" t="str">
+        <x:v>Budget note 7</x:v>
+      </x:c>
+      <x:c r="B15" s="29" t="str">
+        <x:v>On Purchase, unit prices in H are USD, pack sizes are in I, and owned quantity in J defaults to 0. Enter available or borrowed quantities. Pack count L and new-purchase cost M recalculate; used cost K remains. Allowances are not purchasing authorization or a requirement to buy new laboratory instruments.</x:v>
+      </x:c>
+      <x:c r="C15" s="29" t="str">
+        <x:v>Retained budget reading notes; source prices dated 2026-10-08.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="82" customHeight="1">
+      <x:c r="A16" s="29" t="str">
+        <x:v>Budget note 8</x:v>
+      </x:c>
+      <x:c r="B16" s="29" t="str">
+        <x:v>PCB preserves all 61 vendor references, quantities and values. Priced component estimates sum to USD 61.44. Unidentified U3 remains blank. Many passive values or packages remain unknown; generic budgets are not purchasing specifications. FD fiducials and H mounting holes are fabrication features with zero separate component cost. Do not add component estimates to the USD 4,126.71 two-board design/setup quotation.</x:v>
+      </x:c>
+      <x:c r="C16" s="29" t="str">
+        <x:v>Retained budget reading notes; source prices dated 2026-10-08.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="96" customHeight="1">
+      <x:c r="A17" s="29" t="str">
+        <x:v>Budget note 9</x:v>
+      </x:c>
+      <x:c r="B17" s="29" t="str">
+        <x:v>Printing uses the same three batches and formula, with each monetary input converted once: 1.2 × (fixed USD + source resin USD × 1.1 + minutes/60 × time USD/hour). The fixed input is 25/31.805 USD, and the time input is 7.195/31.805 USD/hour. Displayed batch totals are USD 16.52, 16.83 and 1.73. The full-precision total is USD 35.0695047948, displayed as USD 35.07. Sum full-precision values before rounding; displayed batch cents can differ from the rounded grand total. Combined batches are not split into invented unit prices. Original printing notes are preserved below.</x:v>
+      </x:c>
+      <x:c r="C17" s="29" t="str">
+        <x:v>Retained budget reading notes; source prices dated 2026-10-08.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="96" customHeight="1">
+      <x:c r="A18" s="29" t="str">
+        <x:v>Budget note 10</x:v>
+      </x:c>
+      <x:c r="B18" s="29" t="str">
+        <x:v>Currency conversion retains the project's recorded Bank of Taiwan USD spot-selling snapshot of 31.805 NTD per USD, dated 2026-10-05 15:13 and recorded on 2026-10-08. This revision does not claim a refreshed market or execution quote. USD inputs retain full precision, with two decimals displayed. Original NTD quotations remain only in source notes. English input prices are now fixed converted USD amounts; quantities, ownership and totals still recalculate. The displayed FX snapshot is provenance, not a live repricing control. To adopt a new exchange basis, reprice the USD input cells listed above.</x:v>
+      </x:c>
+      <x:c r="C18" s="29" t="str">
+        <x:v>Retained budget reading notes; source prices dated 2026-10-08.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="40" customHeight="1">
+      <x:c r="A19" s="29" t="str">
+        <x:v>Budget note 11</x:v>
+      </x:c>
+      <x:c r="B19" s="29" t="str">
+        <x:v>Shipping, extra taxes, unlisted labor, reprints, cell-culture consumables and replacement of existing printers, curing equipment, phones, computers and culture facilities are excluded.</x:v>
+      </x:c>
+      <x:c r="C19" s="29" t="str">
+        <x:v>Retained budget reading notes; source prices dated 2026-10-08.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="54" customHeight="1">
+      <x:c r="A20" s="29" t="str">
+        <x:v>Budget note 12</x:v>
+      </x:c>
+      <x:c r="B20" s="29" t="str">
+        <x:v>The entries below preserve the original observed or assumed quotation currency for audit. All English workbook cost columns and budget totals above are USD. Source prices are the existing 2026-10-08 research record and have not been refreshed in this currency-format revision.</x:v>
+      </x:c>
+      <x:c r="C20" s="29" t="str">
+        <x:v>Retained budget reading notes; source prices dated 2026-10-08.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="30" customHeight="1">
+      <x:c r="A21" s="36" t="str">
+        <x:v>Original print-cost record</x:v>
+      </x:c>
+      <x:c r="B21" s="36" t="str"/>
+      <x:c r="C21" s="36" t="str"/>
+    </x:row>
+    <x:row r="22" ht="28" customHeight="1">
+      <x:c r="A22" s="29" t="str">
+        <x:v>Printer and sliced batches</x:v>
+      </x:c>
+      <x:c r="B22" s="29" t="str">
+        <x:v>Phrozen Sonic Mighty Revo 16K. P1: 01_base_BLACK.ctb; P2: 020308_parts.ctb; P3: 0407_wells.ctb.</x:v>
+      </x:c>
+      <x:c r="C22" s="29" t="str">
+        <x:v>Historical slicer/cost inputs. CTB files are retained unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="40" customHeight="1">
+      <x:c r="A23" s="29" t="str">
+        <x:v>Original formula</x:v>
+      </x:c>
+      <x:c r="B23" s="29" t="str">
+        <x:v>NTD = 1.2 × (25 + original resin subtotal × 1.1 + estimated printing hours × 7.195).</x:v>
+      </x:c>
+      <x:c r="C23" s="29" t="str">
+        <x:v>NTD source formula only. Print_batches uses equivalent USD terms in the English workbook. No additional machine or resin-bottle cost is added.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="96" customHeight="1">
+      <x:c r="A24" s="29" t="str">
+        <x:v>P1: 01</x:v>
+      </x:c>
+      <x:c r="B24" s="29" t="str">
+        <x:v>Material: PC/GF-like Black
+Time: 17 h 35 min (1055 min)
+Resin volume: 107.531 mL; mass: 118.285 g
+Original resin quotation: NTD 260.226
+Original reported total: NTD 525.313
+Recomputed source-formula total: NTD 525.31282</x:v>
+      </x:c>
+      <x:c r="C24" s="29" t="str">
+        <x:v>Original-quotation provenance. Active English totals are in USD on Print_batches.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="96" customHeight="1">
+      <x:c r="A25" s="29" t="str">
+        <x:v>P2: 02 + 03 + 08</x:v>
+      </x:c>
+      <x:c r="B25" s="29" t="str">
+        <x:v>Material: PC/GF-like Black
+Time: 16 h 19 min (979 min)
+Resin volume: 114.027 mL; mass: 125.43 g
+Original resin quotation: NTD 275.945
+Original reported total: NTD 535.126
+Recomputed source-formula total: NTD 535.1255</x:v>
+      </x:c>
+      <x:c r="C25" s="29" t="str">
+        <x:v>Original-quotation provenance. Active English totals are in USD on Print_batches.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="96" customHeight="1">
+      <x:c r="A26" s="29" t="str">
+        <x:v>P3: 04 + 05 + 06 + 07</x:v>
+      </x:c>
+      <x:c r="B26" s="29" t="str">
+        <x:v>Material: Aqua Clear Plus
+Time: 2 h 42 min (162 min)
+Resin volume: 1.198 mL; mass: 1.318 g
+Original resin quotation: NTD 1.239
+Original reported total: NTD 52.215
+Recomputed source-formula total: NTD 54.94728</x:v>
+      </x:c>
+      <x:c r="C26" s="29" t="str">
+        <x:v>Original-quotation provenance. Active English totals are in USD on Print_batches.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="40" customHeight="1">
+      <x:c r="A27" s="29" t="str">
+        <x:v>P3 discrepancy</x:v>
+      </x:c>
+      <x:c r="B27" s="29" t="str">
+        <x:v>The original clear-well batch reports NTD 52.215. Its stated inputs and formula give NTD 54.94728. The budget uses the formula result. P1/P2 differences are source rounding.</x:v>
+      </x:c>
+      <x:c r="C27" s="29" t="str"/>
+    </x:row>
+    <x:row r="28" ht="40" customHeight="1">
+      <x:c r="A28" s="29" t="str">
+        <x:v>Rounding and source identity</x:v>
+      </x:c>
+      <x:c r="B28" s="29" t="str">
+        <x:v>Sum the three full-precision batch results before displaying two decimals. Combined batches do not establish per-part prices.</x:v>
+      </x:c>
+      <x:c r="C28" s="29" t="str">
+        <x:v>Original print-cost record SHA256: 174599bf359f0186bfe581aab6033953525edf30911b7083e27cb033251b24dd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="30" customHeight="1">
+      <x:c r="A29" s="36" t="str">
+        <x:v>Price-source register</x:v>
+      </x:c>
+      <x:c r="B29" s="36" t="str"/>
+      <x:c r="C29" s="36" t="str"/>
+    </x:row>
+    <x:row r="30" ht="54" customHeight="1">
+      <x:c r="A30" s="29" t="str">
+        <x:v>FX</x:v>
+      </x:c>
+      <x:c r="B30" s="29" t="str">
+        <x:v>Bank of Taiwan USD spot selling
+2026-10-05 15:13 displayed snapshot: USD spot buy 31.705, sell 31.805. Budget conversion uses sell 31.805, not an October 8 live execution quote.</x:v>
+      </x:c>
+      <x:c r="C30" s="29" t="str">
+        <x:v>https://www.bot.com.tw/tw/personal-banking/foreign-exchange</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="40" customHeight="1">
+      <x:c r="A31" s="29" t="str">
+        <x:v>FAN</x:v>
+      </x:c>
+      <x:c r="B31" s="29" t="str">
+        <x:v>DigiKey MF40100V1-1000U-A99
+NTD 161 at quantity 1. Listed out of stock. Shipping and local tax not added.</x:v>
+      </x:c>
+      <x:c r="C31" s="29" t="str">
+        <x:v>https://www.digikey.tw/en/products/detail/sunon-fans/MF40100V1-1000U-A99/6198732</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="68" customHeight="1">
+      <x:c r="A32" s="29" t="str">
+        <x:v>FASTENER</x:v>
+      </x:c>
+      <x:c r="B32" s="29" t="str">
+        <x:v>Local small-fastener retail benchmark
+Listing shows small M3 fasteners around NTD 3 individually. Listed flat-head type is NOT the specified socket cap. Budget allowances 3/4/6 NTD for M3x8/16/35 cap screws, 2 for nuts and 1 for washers; local exact-type prices unverified.</x:v>
+      </x:c>
+      <x:c r="C32" s="29" t="str">
+        <x:v>https://www.ruten.com.tw/item/21306183365097/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="54" customHeight="1">
+      <x:c r="A33" s="29" t="str">
+        <x:v>SEAL</x:v>
+      </x:c>
+      <x:c r="B33" s="29" t="str">
+        <x:v>Black silicone sheet size reference
+0.8 mm selectable stock; exact price unavailable. NTD 150 per small sheet is an engineering allowance, not a verified selling price. Hardness and VOC compatibility unqualified.</x:v>
+      </x:c>
+      <x:c r="C33" s="29" t="str">
+        <x:v>https://www.ruten.com.tw/item/22517308416481/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="54" customHeight="1">
+      <x:c r="A34" s="29" t="str">
+        <x:v>POWER</x:v>
+      </x:c>
+      <x:c r="B34" s="29" t="str">
+        <x:v>Adafruit 4298 USB-C supply
+USD 8.74, 5.1 V 3 A with cable. Price benchmark only; vendor must confirm input and charging configuration. Current budget uses external power, not an unconfirmed battery.</x:v>
+      </x:c>
+      <x:c r="C34" s="29" t="str">
+        <x:v>https://www.adafruit.com/product/4298</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="68" customHeight="1">
+      <x:c r="A35" s="29" t="str">
+        <x:v>GASFILTER</x:v>
+      </x:c>
+      <x:c r="B35" s="29" t="str">
+        <x:v>Gilson ANP1322 SupaTop
+USD 95 per 100. Hydrophobic PTFE, 13 mm, 0.22 um, NONSTERILE, air venting listed. Price proxy for 0.2 um gas-filter requirement, not certified sterile replacement. Two used per device; buying a box costs 100 filters.</x:v>
+      </x:c>
+      <x:c r="C35" s="29" t="str">
+        <x:v>https://www.gilson.com/default/catalog/product/view/id/1204/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="54" customHeight="1">
+      <x:c r="A36" s="29" t="str">
+        <x:v>PTFE</x:v>
+      </x:c>
+      <x:c r="B36" s="29" t="str">
+        <x:v>Tinkersphere 2 mm ID 3 mm OD PTFE
+Search listing USD 4.99; sold length not verified. NTD 200 per 1 m is a separate allowance. Printer-feed tubing is not qualified analytical tubing.</x:v>
+      </x:c>
+      <x:c r="C36" s="29" t="str">
+        <x:v>https://tinkersphere.com/3d-printer-parts-supplies/2015-ptfe-teflon-tube-2mm-id-3mm-od-for-175-mm-filament.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="54" customHeight="1">
+      <x:c r="A37" s="29" t="str">
+        <x:v>COUPLER</x:v>
+      </x:c>
+      <x:c r="B37" s="29" t="str">
+        <x:v>Adafruit 3 mm ID silicone tubing reference
+Related tubing listed USD 2.50 per metre. Budget NTD 150 includes short flexible couplers and matching adapters. Exact ID/OD, Luer interfaces and VOC recovery must be checked; no fit guarantee.</x:v>
+      </x:c>
+      <x:c r="C37" s="29" t="str">
+        <x:v>https://www.adafruit.com/product/4699</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="68" customHeight="1">
+      <x:c r="A38" s="29" t="str">
+        <x:v>OPTIC</x:v>
+      </x:c>
+      <x:c r="B38" s="29" t="str">
+        <x:v>Edmund Optics 67-016 520 nm emission filter
+USD 284, 12.5 mm diameter, substrate 2.00 +/-0.25 mm, mounted. Does NOT fit 5.2x4.2x1.0 mm seat. NTD 12000 is a custom thin-filter budget allowance, not a quote or available drop-in part. Cutting this stock part does not solve its thickness mismatch.</x:v>
+      </x:c>
+      <x:c r="C38" s="29" t="str">
+        <x:v>https://www.edmundoptics.com/p/520nm-cwl-125mm-dia-36nm-bandwidth-od-6-fluorescence-filter/21556/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="54" customHeight="1">
+      <x:c r="A39" s="29" t="str">
+        <x:v>UART</x:v>
+      </x:c>
+      <x:c r="B39" s="29" t="str">
+        <x:v>Adafruit 5335 CP2102N Friend
+USD 5.95 each. Signals 3.3 V; power wire 5 V. Leave VCC disconnected at J3. Cable and jumper wires separate.</x:v>
+      </x:c>
+      <x:c r="C39" s="29" t="str">
+        <x:v>https://www.adafruit.com/product/5335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="68" customHeight="1">
+      <x:c r="A40" s="29" t="str">
+        <x:v>PUMP</x:v>
+      </x:c>
+      <x:c r="B40" s="29" t="str">
+        <x:v>Adafruit 4699 gas pump price benchmark
+USD 7.95 for pump alone. 2.5 L/min, intermittent duty; NOT a selected 3 mL/min continuous source. NTD 5000 system allowance requires a qualified controlled source, bypass/regulation, pressure protection, fittings and supply. Borrow a suitable lab system first.</x:v>
+      </x:c>
+      <x:c r="C40" s="29" t="str">
+        <x:v>https://www.adafruit.com/product/4699</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="68" customHeight="1">
+      <x:c r="A41" s="29" t="str">
+        <x:v>FLOW</x:v>
+      </x:c>
+      <x:c r="B41" s="29" t="str">
+        <x:v>Omega precision rotameter range reference
+FL-320 nominal air range 0.02-15 cc/min. Historical price deliberately not treated as current. NTD 15000 is a planning allowance pending current calibrated meter quote; 3 mL/min must fall within usable range.</x:v>
+      </x:c>
+      <x:c r="C41" s="29" t="str">
+        <x:v>https://br.omega.com/omegaFiles/green/pdf/FL120.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="54" customHeight="1">
+      <x:c r="A42" s="29" t="str">
+        <x:v>DYE</x:v>
+      </x:c>
+      <x:c r="B42" s="29" t="str">
+        <x:v>Sigma 46970 sodium fluorescein
+USD 52.60 per 100 g. Budget includes whole bottle, not a fictitious single-well quantity. Prefer a documented laboratory aliquot. Not an assay-specific or GCaMP-certified standard.</x:v>
+      </x:c>
+      <x:c r="C42" s="29" t="str">
+        <x:v>https://www.sigmaaldrich.com/US/en/product/sigma/46970</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="54" customHeight="1">
+      <x:c r="A43" s="29" t="str">
+        <x:v>VALVE</x:v>
+      </x:c>
+      <x:c r="B43" s="29" t="str">
+        <x:v>Adafruit 4663 FA0520E
+USD 2.95 for 6 V valve alone. NTD 500 system allowance includes driver, flyback diode, supply and fittings. Future only; VOC wetted-material suitability and firmware support unverified.</x:v>
+      </x:c>
+      <x:c r="C43" s="29" t="str">
+        <x:v>https://www.adafruit.com/product/4663</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="54" customHeight="1">
+      <x:c r="A44" s="29" t="str">
+        <x:v>PDMS</x:v>
+      </x:c>
+      <x:c r="B44" s="29" t="str">
+        <x:v>Dow Sylgard 184 0.5 kg kit reference
+Kit identity found; current public price not verified. NTD 6000 planning allowance for kit and basic casting consumables. No claim that PDMS removes water selectively.</x:v>
+      </x:c>
+      <x:c r="C44" s="29" t="str">
+        <x:v>https://labproinc.com/products/dow-sylgard-184-silicone-encapsulant-clear-0-5-kg-kit-184-sil-elast-kit-0-5kg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="68" customHeight="1">
+      <x:c r="A45" s="29" t="str">
+        <x:v>TOOLS</x:v>
+      </x:c>
+      <x:c r="B45" s="29" t="str">
+        <x:v>Local tools and lab access allowance
+Engineering allowances only: hand tools/calipers NTD 1500; DMM 800; scope 10000; pipette/tips 4000; print/post-cure supplies 300. Borrow existing printer, wash/cure equipment, PC, phone, biosafety/cell facilities. Their capital replacement prices are outside this BOM.</x:v>
+      </x:c>
+      <x:c r="C45" s="29" t="str">
+        <x:v>Original planning record; no public price URL.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="40" customHeight="1">
+      <x:c r="A46" s="29" t="str">
+        <x:v>PCB_LED</x:v>
+      </x:c>
+      <x:c r="B46" s="29" t="str">
+        <x:v>DigiKey 155124BS73200
+NTD 17 each at quantity 1.</x:v>
+      </x:c>
+      <x:c r="C46" s="29" t="str">
+        <x:v>https://www.digikey.tw/en/products/detail/w%C3%BCrth-elektronik/155124BS73200/4490035</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="40" customHeight="1">
+      <x:c r="A47" s="29" t="str">
+        <x:v>PCB_PD</x:v>
+      </x:c>
+      <x:c r="B47" s="29" t="str">
+        <x:v>DigiKey VEMD5060X01
+NTD 68 each at quantity 1.</x:v>
+      </x:c>
+      <x:c r="C47" s="29" t="str">
+        <x:v>https://www.digikey.tw/en/products/detail/vishay-semiconductor-opto-division/VEMD5060X01/5879084</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="54" customHeight="1">
+      <x:c r="A48" s="29" t="str">
+        <x:v>PCB_U1</x:v>
+      </x:c>
+      <x:c r="B48" s="29" t="str">
+        <x:v>DigiKey TPS61023 family
+Search results list TPS61023DRLT cut tape NTD 52. Packaging-suffix proxy for vendor TPS61023; exact order code requires confirmation.</x:v>
+      </x:c>
+      <x:c r="C48" s="29" t="str">
+        <x:v>https://www.digikey.tw/en/products/detail/texas-instruments/TPS61023DRLR/11310629</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="40" customHeight="1">
+      <x:c r="A49" s="29" t="str">
+        <x:v>PCB_U2</x:v>
+      </x:c>
+      <x:c r="B49" s="29" t="str">
+        <x:v>DigiKey BQ24074RGTR
+NTD 88 each at quantity 1; RGT package assumed from schematic.</x:v>
+      </x:c>
+      <x:c r="C49" s="29" t="str">
+        <x:v>https://www.digikey.tw/en/products/detail/texas-instruments/BQ24074RGTR/2047269</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="40" customHeight="1">
+      <x:c r="A50" s="29" t="str">
+        <x:v>PCB_U4</x:v>
+      </x:c>
+      <x:c r="B50" s="29" t="str">
+        <x:v>DigiKey ESP32-WROOM-32E-N4
+NTD 181 each. N4 is a price proxy; vendor flash suffix missing.</x:v>
+      </x:c>
+      <x:c r="C50" s="29" t="str">
+        <x:v>https://www.digikey.tw/en/products/detail/espressif-systems/ESP32-WROOM-32E-N4/11613125</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="40" customHeight="1">
+      <x:c r="A51" s="29" t="str">
+        <x:v>PCB_U6</x:v>
+      </x:c>
+      <x:c r="B51" s="29" t="str">
+        <x:v>DigiKey LP5907MFX-3.3/NOPB
+NTD 24 each at quantity 1.</x:v>
+      </x:c>
+      <x:c r="C51" s="29" t="str">
+        <x:v>https://www.digikey.tw/en/products/detail/texas-instruments/LP5907MFX-3-3-NOPB/3906441</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="40" customHeight="1">
+      <x:c r="A52" s="29" t="str">
+        <x:v>PCB_U7</x:v>
+      </x:c>
+      <x:c r="B52" s="29" t="str">
+        <x:v>DigiKey LTC6655BHMS8-2.5#TRPBF
+NTD 628 for cut tape. Packaging proxy for #PBF; listed no stock.</x:v>
+      </x:c>
+      <x:c r="C52" s="29" t="str">
+        <x:v>https://www.digikey.tw/en/products/detail/analog-devices-inc/LTC6655BHMS8-2-5-TRPBF/2181717</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="40" customHeight="1">
+      <x:c r="A53" s="29" t="str">
+        <x:v>PCB_U8</x:v>
+      </x:c>
+      <x:c r="B53" s="29" t="str">
+        <x:v>DigiKey LMP7721MAX/NOPB listing
+Search listing NTD 226 for MAX/NOPB. Vendor LMP7721 suffix missing; package proxy.</x:v>
+      </x:c>
+      <x:c r="C53" s="29" t="str">
+        <x:v>https://www.digikey.tw/en/products/filter/linear/amplifiers/instrumentation-op-amps-buffer-amps/687</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="40" customHeight="1">
+      <x:c r="A54" s="29" t="str">
+        <x:v>PCB_U9</x:v>
+      </x:c>
+      <x:c r="B54" s="29" t="str">
+        <x:v>DigiKey ADS8866IDGS
+NTD 306 each at quantity 1.</x:v>
+      </x:c>
+      <x:c r="C54" s="29" t="str">
+        <x:v>https://www.digikey.tw/zh/products/detail/texas-instruments/ADS8866IDGS/5176196</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="82" customHeight="1">
+      <x:c r="A55" s="29" t="str">
+        <x:v>PCB_MISC</x:v>
+      </x:c>
+      <x:c r="B55" s="29" t="str">
+        <x:v>Unspecified PCB parts allowance
+Generic single-piece budgets, NOT verified quotations: small resistors NTD 1, high-value resistor 30, shunt 5; ceramics 2-8; bulk capacitor 15; LED 2; MOSFET 5; inductor 10; connectors 5-30; switches 5-15; linear regulator 10. Unknown U3 remains unpriced. Do not purchase substitutes without vendor values, packages and ratings.</x:v>
+      </x:c>
+      <x:c r="C55" s="29" t="str">
+        <x:v>Original planning record; no public price URL.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="30" customHeight="1">
+      <x:c r="A56" s="36" t="str">
+        <x:v>Specification-source register</x:v>
+      </x:c>
+      <x:c r="B56" s="36" t="str"/>
+      <x:c r="C56" s="36" t="str"/>
+    </x:row>
+    <x:row r="57" ht="28" customHeight="1">
+      <x:c r="A57" s="29" t="str">
+        <x:v>procurement: CAD</x:v>
+      </x:c>
+      <x:c r="B57" s="29" t="str">
+        <x:v>Existing frozen geometry; read-only audit, no changes.</x:v>
+      </x:c>
+      <x:c r="C57" s="29" t="str">
+        <x:v>Original source identifier: 09_engineering_sources/CAD/aerosense.scad</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="28" customHeight="1">
+      <x:c r="A58" s="29" t="str">
+        <x:v>procurement: STL</x:v>
+      </x:c>
+      <x:c r="B58" s="29" t="str">
+        <x:v>All8 binary STL bounds independently read; exported Z minima are0. Assembly coordinates are separate.</x:v>
+      </x:c>
+      <x:c r="C58" s="29" t="str">
+        <x:v>Original source identifier: 01_print</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="28" customHeight="1">
+      <x:c r="A59" s="29" t="str">
+        <x:v>procurement: ASM</x:v>
+      </x:c>
+      <x:c r="B59" s="29" t="str"/>
+      <x:c r="C59" s="29" t="str">
+        <x:v>Original source identifier: 04_manuals/Assembly_Manual_ZH.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="40" customHeight="1">
+      <x:c r="A60" s="29" t="str">
+        <x:v>procurement: GASKET</x:v>
+      </x:c>
+      <x:c r="B60" s="29" t="str"/>
+      <x:c r="C60" s="29" t="str">
+        <x:v>Original source identifier: 09_engineering_sources/CAD/drawings/gasket_cut_template_1to1.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="28" customHeight="1">
+      <x:c r="A61" s="29" t="str">
+        <x:v>procurement: FLOW</x:v>
+      </x:c>
+      <x:c r="B61" s="29" t="str"/>
+      <x:c r="C61" s="29" t="str">
+        <x:v>Original source identifier: 02_simulation/airflow/Flow_Operation_ZH.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="28" customHeight="1">
+      <x:c r="A62" s="29" t="str">
+        <x:v>procurement: OPTICS</x:v>
+      </x:c>
+      <x:c r="B62" s="29" t="str"/>
+      <x:c r="C62" s="29" t="str">
+        <x:v>Original source identifier: 02_simulation/optics/Analysis_EN.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="28" customHeight="1">
+      <x:c r="A63" s="29" t="str">
+        <x:v>procurement: OPERATION</x:v>
+      </x:c>
+      <x:c r="B63" s="29" t="str"/>
+      <x:c r="C63" s="29" t="str">
+        <x:v>Original source identifier: 03_software/guides/Operation_and_Setup_EN.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="28" customHeight="1">
+      <x:c r="A64" s="29" t="str">
+        <x:v>procurement: VALIDATION</x:v>
+      </x:c>
+      <x:c r="B64" s="29" t="str"/>
+      <x:c r="C64" s="29" t="str">
+        <x:v>Original source identifier: 07_validation/Fluorescence_and_Cell_Test_ZH.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="28" customHeight="1">
+      <x:c r="A65" s="29" t="str">
+        <x:v>procurement: ELEC</x:v>
+      </x:c>
+      <x:c r="B65" s="29" t="str">
+        <x:v>Schematic interpretation supplied by optics audit agent2026-10-06; value/MPN uncertainties retained.</x:v>
+      </x:c>
+      <x:c r="C65" s="29" t="str">
+        <x:v>Original source identifier: 08_reference/NTHU_TEST_BOARD_Schematic.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="28" customHeight="1">
+      <x:c r="A66" s="29" t="str">
+        <x:v>procurement: FAN</x:v>
+      </x:c>
+      <x:c r="B66" s="29" t="str">
+        <x:v>Official SUNON catalogue,printed p32/PDF p32; candidate5V136mA0.68W;frame40±0.5,pitch32±0.3.</x:v>
+      </x:c>
+      <x:c r="C66" s="29" t="str">
+        <x:v>https://www.sunon.com/eu/MANAGE/Docs/WEBCONT/Files/1236/DC%20Fan_20240630(255-E)_s.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="40" customHeight="1">
+      <x:c r="A67" s="29" t="str">
+        <x:v>procurement: SCREW</x:v>
+      </x:c>
+      <x:c r="B67" s="29" t="str">
+        <x:v>Official Bossard M3 ISO4762/DIN912 dimensional reference:head5.5,height3,hex2.5. This30-mm article is a family-dimension reference,not a purchased length or MPN selection.</x:v>
+      </x:c>
+      <x:c r="C67" s="29" t="str">
+        <x:v>https://nederland.bossard.com/en-us/standard-fastening-elements/screws/screws-and-bolts-with-internal-drive/912000a20030030</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="28" customHeight="1">
+      <x:c r="A68" s="29" t="str">
+        <x:v>procurement: PITCH</x:v>
+      </x:c>
+      <x:c r="B68" s="29" t="str">
+        <x:v>Official KIPP coarse metric pitch:M3×0.5.</x:v>
+      </x:c>
+      <x:c r="C68" s="29" t="str">
+        <x:v>https://www.kippusa.com/en-us/measurement-units</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="40" customHeight="1">
+      <x:c r="A69" s="29" t="str">
+        <x:v>procurement: NUT</x:v>
+      </x:c>
+      <x:c r="B69" s="29" t="str">
+        <x:v>Bossard manufacturer datasheet hosted by distributor,BN629 DIN934/~ISO4032:M3,AF5.5,height max2.4. Dimensional evidence,not selected MPN.</x:v>
+      </x:c>
+      <x:c r="C69" s="29" t="str">
+        <x:v>https://media.distrelec.com/Web/Downloads/_t/ds/1241613_eng_tds.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="40" customHeight="1">
+      <x:c r="A70" s="29" t="str">
+        <x:v>procurement: WASHER</x:v>
+      </x:c>
+      <x:c r="B70" s="29" t="str">
+        <x:v>Direct supplier dimensional reference:ID3.2/OD7/thickness0.5. Nylon article is not a final material/MPN selection; PCB insulation choice remains open.</x:v>
+      </x:c>
+      <x:c r="C70" s="29" t="str">
+        <x:v>https://www.accu.co.uk/metric-flat-washers/465682-HPW-3-2-7-0-5-N</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="54" customHeight="1">
+      <x:c r="A71" s="29" t="str">
+        <x:v>PCB: vendor_BOM</x:v>
+      </x:c>
+      <x:c r="B71" s="29" t="str">
+        <x:v>NTHU_TEST_BOARD_BOM.docx, vendor table, 61 rows
+Accessed: 2026-10-06
+SHA256: 3541da4a10afbfc371f4ec7c8094329fea7ed84635b543628252fe67276fa4b8</x:v>
+      </x:c>
+      <x:c r="C71" s="29" t="str">
+        <x:v>Original source identifier: 08_reference/NTHU_TEST_BOARD_BOM.docx</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="54" customHeight="1">
+      <x:c r="A72" s="29" t="str">
+        <x:v>PCB: schematic</x:v>
+      </x:c>
+      <x:c r="B72" s="29" t="str">
+        <x:v>NTHU_TEST_BOARD_Schematic.pdf, version A, 14 September 2026, sheets 1–2
+Accessed: 2026-10-06
+SHA256: c8cfc0600a6d34740c1caac24f37d9eaea6bea59b88278e4258988769939d07e</x:v>
+      </x:c>
+      <x:c r="C72" s="29" t="str">
+        <x:v>Original source identifier: 08_reference/NTHU_TEST_BOARD_Schematic.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="40" customHeight="1">
+      <x:c r="A73" s="29" t="str">
+        <x:v>PCB: TI_TPS61023</x:v>
+      </x:c>
+      <x:c r="B73" s="29" t="str">
+        <x:v>Texas Instruments TPS61023 product information
+Accessed: 2026-10-06</x:v>
+      </x:c>
+      <x:c r="C73" s="29" t="str">
+        <x:v>https://www.ti.com/product/TPS61023</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="40" customHeight="1">
+      <x:c r="A74" s="29" t="str">
+        <x:v>PCB: TI_BQ24074</x:v>
+      </x:c>
+      <x:c r="B74" s="29" t="str">
+        <x:v>Texas Instruments BQ24074 product information
+Accessed: 2026-10-06</x:v>
+      </x:c>
+      <x:c r="C74" s="29" t="str">
+        <x:v>https://www.ti.com/product/BQ24074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="40" customHeight="1">
+      <x:c r="A75" s="29" t="str">
+        <x:v>PCB: TI_LP5907</x:v>
+      </x:c>
+      <x:c r="B75" s="29" t="str">
+        <x:v>Texas Instruments LP5907 datasheet, ordering/package information
+Accessed: 2026-10-06</x:v>
+      </x:c>
+      <x:c r="C75" s="29" t="str">
+        <x:v>https://www.ti.com/lit/ds/symlink/lp5907.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="40" customHeight="1">
+      <x:c r="A76" s="29" t="str">
+        <x:v>PCB: TI_LMP7721</x:v>
+      </x:c>
+      <x:c r="B76" s="29" t="str">
+        <x:v>Texas Instruments LMP7721 product information
+Accessed: 2026-10-06</x:v>
+      </x:c>
+      <x:c r="C76" s="29" t="str">
+        <x:v>https://www.ti.com/product/LMP7721</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="40" customHeight="1">
+      <x:c r="A77" s="29" t="str">
+        <x:v>PCB: TI_ADS8866</x:v>
+      </x:c>
+      <x:c r="B77" s="29" t="str">
+        <x:v>Texas Instruments ADS8866 datasheet, ADS8866IDGS ordering information
+Accessed: 2026-10-06</x:v>
+      </x:c>
+      <x:c r="C77" s="29" t="str">
+        <x:v>https://www.ti.com/lit/ds/symlink/ads8866.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="40" customHeight="1">
+      <x:c r="A78" s="29" t="str">
+        <x:v>PCB: ADI_LTC6655</x:v>
+      </x:c>
+      <x:c r="B78" s="29" t="str">
+        <x:v>Analog Devices LTC6655 / LTC6655LN datasheet
+Accessed: 2026-10-06</x:v>
+      </x:c>
+      <x:c r="C78" s="29" t="str">
+        <x:v>https://www.analog.com/media/en/technical-documentation/data-sheets/LTC6655-6655LN.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="40" customHeight="1">
+      <x:c r="A79" s="29" t="str">
+        <x:v>PCB: ECMOS_EC50117</x:v>
+      </x:c>
+      <x:c r="B79" s="29" t="str">
+        <x:v>E-CMOS EC50117 datasheet 9L05N Rev F004; page 2 EC50117KBG ordering row
+Accessed: 2026-10-06</x:v>
+      </x:c>
+      <x:c r="C79" s="29" t="str">
+        <x:v>https://www.ecmos.com.tw/wp-content/uploads/2022/07/EC50117_9L05N-Rev.F004.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="40" customHeight="1">
+      <x:c r="A80" s="29" t="str">
+        <x:v>PCB: ESPRESSIF_32E</x:v>
+      </x:c>
+      <x:c r="B80" s="29" t="str">
+        <x:v>Espressif ESP32-WROOM-32E / ESP32-WROOM-32UE datasheet
+Accessed: 2026-10-06</x:v>
+      </x:c>
+      <x:c r="C80" s="29" t="str">
+        <x:v>https://www.espressif.com/sites/default/files/documentation/esp32-wroom-32e_esp32-wroom-32ue_datasheet_en.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="40" customHeight="1">
+      <x:c r="A81" s="29" t="str">
+        <x:v>PCB: WURTH_LED</x:v>
+      </x:c>
+      <x:c r="B81" s="29" t="str">
+        <x:v>Würth Elektronik 155124BS73200 datasheet
+Accessed: 2026-10-06</x:v>
+      </x:c>
+      <x:c r="C81" s="29" t="str">
+        <x:v>https://www.we-online.com/components/products/datasheet/155124BS73200.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="40" customHeight="1">
+      <x:c r="A82" s="29" t="str">
+        <x:v>PCB: VISHAY_PD</x:v>
+      </x:c>
+      <x:c r="B82" s="29" t="str">
+        <x:v>Vishay VEMD5060X01 product information, document 84278
+Accessed: 2026-10-06</x:v>
+      </x:c>
+      <x:c r="C82" s="29" t="str">
+        <x:v>https://www.vishay.com/en/product/84278/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="40" customHeight="1">
+      <x:c r="A83" s="29" t="str">
+        <x:v>PCB: AOS_AO3400A</x:v>
+      </x:c>
+      <x:c r="B83" s="29" t="str">
+        <x:v>Alpha &amp; Omega Semiconductor AO3400A datasheet
+Accessed: 2026-10-06</x:v>
+      </x:c>
+      <x:c r="C83" s="29" t="str">
+        <x:v>https://www.aosmd.com/res/data_sheets/AO3400A.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="30" customHeight="1">
+      <x:c r="A84" s="36" t="str">
+        <x:v>Additional purchase provenance</x:v>
+      </x:c>
+      <x:c r="B84" s="36" t="str"/>
+      <x:c r="C84" s="36" t="str"/>
+    </x:row>
+    <x:row r="85" ht="40" customHeight="1">
+      <x:c r="A85" s="29" t="str">
+        <x:v>Historical fields</x:v>
+      </x:c>
+      <x:c r="B85" s="29" t="str">
+        <x:v>These original source fields preserve model/part identifiers and earlier estimates. They do not override active price inputs or add to totals.</x:v>
+      </x:c>
+      <x:c r="C85" s="29" t="str"/>
+    </x:row>
+    <x:row r="86" ht="96" customHeight="1">
+      <x:c r="A86" s="29" t="str">
+        <x:v>F01</x:v>
+      </x:c>
+      <x:c r="B86" s="29" t="str">
+        <x:v>price_source: FAN
+source: RS 2025400 viewed 2026-09-24 incl tax; out of stock then. https://twcn.rs-online.com/web/p/axial-fans/2025400
+low: 161
+high: 161
+source_en: CAD; ASM; FAN</x:v>
+      </x:c>
+      <x:c r="C86" s="29" t="str">
+        <x:v>Historical source fields; active prices are on Purchase.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="82" customHeight="1">
+      <x:c r="A87" s="29" t="str">
+        <x:v>H01</x:v>
+      </x:c>
+      <x:c r="B87" s="29" t="str">
+        <x:v>price_source: FASTENER
+source: Quotation pending; no invented price / 尚待報價，未填假價格
+low: 3
+high: 3
+source_en: CAD; ASM; SCREW; PITCH</x:v>
+      </x:c>
+      <x:c r="C87" s="29" t="str">
+        <x:v>Historical source fields; active prices are on Purchase.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="82" customHeight="1">
+      <x:c r="A88" s="29" t="str">
+        <x:v>H02</x:v>
+      </x:c>
+      <x:c r="B88" s="29" t="str">
+        <x:v>price_source: FASTENER
+source: Quotation pending; no invented price / 尚待報價，未填假價格
+low: 4
+high: 4
+source_en: CAD; ASM; SCREW; PITCH</x:v>
+      </x:c>
+      <x:c r="C88" s="29" t="str">
+        <x:v>Historical source fields; active prices are on Purchase.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="82" customHeight="1">
+      <x:c r="A89" s="29" t="str">
+        <x:v>H03</x:v>
+      </x:c>
+      <x:c r="B89" s="29" t="str">
+        <x:v>price_source: FASTENER
+source: Quotation pending; no invented price / 尚待報價，未填假價格
+low: 6
+high: 6
+source_en: CAD; ASM; SCREW; PITCH</x:v>
+      </x:c>
+      <x:c r="C89" s="29" t="str">
+        <x:v>Historical source fields; active prices are on Purchase.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="82" customHeight="1">
+      <x:c r="A90" s="29" t="str">
+        <x:v>H04</x:v>
+      </x:c>
+      <x:c r="B90" s="29" t="str">
+        <x:v>price_source: FASTENER
+source: Planning allowance, NOT supplier quote / 預算假設，非報價
+low: 2
+high: 2
+source_en: CAD; ASM; NUT</x:v>
+      </x:c>
+      <x:c r="C90" s="29" t="str">
+        <x:v>Historical source fields; active prices are on Purchase.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="82" customHeight="1">
+      <x:c r="A91" s="29" t="str">
+        <x:v>H05</x:v>
+      </x:c>
+      <x:c r="B91" s="29" t="str">
+        <x:v>price_source: FASTENER
+source: Planning allowance, NOT supplier quote / 預算假設，非報價
+low: 1
+high: 1
+source_en: CAD; ASM; WASHER</x:v>
+      </x:c>
+      <x:c r="C91" s="29" t="str">
+        <x:v>Historical source fields; active prices are on Purchase.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="82" customHeight="1">
+      <x:c r="A92" s="29" t="str">
+        <x:v>E01</x:v>
+      </x:c>
+      <x:c r="B92" s="29" t="str">
+        <x:v>price_source: TOOLS
+source: Planning allowance, NOT supplier quote / 預算假設，非報價
+low: 80
+high: 80
+source_en: ASM; ELEC</x:v>
+      </x:c>
+      <x:c r="C92" s="29" t="str">
+        <x:v>Historical source fields; active prices are on Purchase.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="82" customHeight="1">
+      <x:c r="A93" s="29" t="str">
+        <x:v>S01</x:v>
+      </x:c>
+      <x:c r="B93" s="29" t="str">
+        <x:v>price_source: SEAL
+source: Planning allowance, NOT supplier quote / 預算假設，非報價
+low: 150
+high: 150
+source_en: CAD; ASM; GASKET</x:v>
+      </x:c>
+      <x:c r="C93" s="29" t="str">
+        <x:v>Historical source fields; active prices are on Purchase.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="82" customHeight="1">
+      <x:c r="A94" s="29" t="str">
+        <x:v>E02</x:v>
+      </x:c>
+      <x:c r="B94" s="29" t="str">
+        <x:v>price_source: POWER
+source: Quotation pending; no invented price / 尚待報價，未填假價格
+low: 277.9757
+high: 277.9757
+source_en: ELEC; ASM</x:v>
+      </x:c>
+      <x:c r="C94" s="29" t="str">
+        <x:v>Historical source fields; active prices are on Purchase.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="82" customHeight="1">
+      <x:c r="A95" s="29" t="str">
+        <x:v>G01</x:v>
+      </x:c>
+      <x:c r="B95" s="29" t="str">
+        <x:v>price_source: GASFILTER
+source: Quotation pending; no invented price / 尚待報價，未填假價格
+low: 30.21475
+high: 30.21475
+source_en: ASM; FLOW</x:v>
+      </x:c>
+      <x:c r="C95" s="29" t="str">
+        <x:v>Historical source fields; active prices are on Purchase.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="82" customHeight="1">
+      <x:c r="A96" s="29" t="str">
+        <x:v>G02</x:v>
+      </x:c>
+      <x:c r="B96" s="29" t="str">
+        <x:v>price_source: PTFE
+source: Planning allowance, NOT supplier quote / 預算假設，非報價
+low: 200
+high: 200
+source_en: CAD; ASM; FLOW</x:v>
+      </x:c>
+      <x:c r="C96" s="29" t="str">
+        <x:v>Historical source fields; active prices are on Purchase.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" ht="82" customHeight="1">
+      <x:c r="A97" s="29" t="str">
+        <x:v>G03</x:v>
+      </x:c>
+      <x:c r="B97" s="29" t="str">
+        <x:v>price_source: COUPLER
+source: Quotation pending; no invented price / 尚待報價，未填假價格
+low: 150
+high: 150
+source_en: CAD; ASM</x:v>
+      </x:c>
+      <x:c r="C97" s="29" t="str">
+        <x:v>Historical source fields; active prices are on Purchase.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="82" customHeight="1">
+      <x:c r="A98" s="29" t="str">
+        <x:v>O01</x:v>
+      </x:c>
+      <x:c r="B98" s="29" t="str">
+        <x:v>price_source: OPTIC
+source: Quotation pending; no invented price / 尚待報價，未填假價格
+low: 12000
+high: 12000
+source_en: CAD; ASM; OPTICS</x:v>
+      </x:c>
+      <x:c r="C98" s="29" t="str">
+        <x:v>Historical source fields; active prices are on Purchase.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="82" customHeight="1">
+      <x:c r="A99" s="29" t="str">
+        <x:v>P01</x:v>
+      </x:c>
+      <x:c r="B99" s="29" t="str">
+        <x:v>price_source: UART
+source: Quotation pending; no invented price / 尚待報價，未填假價格
+low: 189.23975000000002
+high: 189.23975000000002
+source_en: OPERATION; ELEC</x:v>
+      </x:c>
+      <x:c r="C99" s="29" t="str">
+        <x:v>Historical source fields; active prices are on Purchase.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="82" customHeight="1">
+      <x:c r="A100" s="29" t="str">
+        <x:v>L01</x:v>
+      </x:c>
+      <x:c r="B100" s="29" t="str">
+        <x:v>price_source: PUMP
+source: Quotation pending; no invented price / 尚待報價，未填假價格
+low: 5000
+high: 5000
+source_en: ASM; FLOW</x:v>
+      </x:c>
+      <x:c r="C100" s="29" t="str">
+        <x:v>Historical source fields; active prices are on Purchase.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="82" customHeight="1">
+      <x:c r="A101" s="29" t="str">
+        <x:v>L02</x:v>
+      </x:c>
+      <x:c r="B101" s="29" t="str">
+        <x:v>price_source: TOOLS
+source: Quotation pending; no invented price / 尚待報價，未填假價格
+low: 1500
+high: 1500
+source_en: ASM; SCREW</x:v>
+      </x:c>
+      <x:c r="C101" s="29" t="str">
+        <x:v>Historical source fields; active prices are on Purchase.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="82" customHeight="1">
+      <x:c r="A102" s="29" t="str">
+        <x:v>L03</x:v>
+      </x:c>
+      <x:c r="B102" s="29" t="str">
+        <x:v>price_source: DYE
+source: Quotation pending; no invented price / 尚待報價，未填假價格
+low: 1672.943
+high: 1672.943
+source_en: VALIDATION; OPERATION</x:v>
+      </x:c>
+      <x:c r="C102" s="29" t="str">
+        <x:v>Historical source fields; active prices are on Purchase.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" ht="40" customHeight="1">
+      <x:c r="A103" s="29" t="str">
+        <x:v>P02</x:v>
+      </x:c>
+      <x:c r="B103" s="29" t="str">
+        <x:v>low: 150
+high: 150</x:v>
+      </x:c>
+      <x:c r="C103" s="29" t="str">
+        <x:v>Historical source fields; active prices are on Purchase.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" ht="40" customHeight="1">
+      <x:c r="A104" s="29" t="str">
+        <x:v>L04</x:v>
+      </x:c>
+      <x:c r="B104" s="29" t="str">
+        <x:v>low: 15000
+high: 15000</x:v>
+      </x:c>
+      <x:c r="C104" s="29" t="str">
+        <x:v>Historical source fields; active prices are on Purchase.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" ht="40" customHeight="1">
+      <x:c r="A105" s="29" t="str">
+        <x:v>L05</x:v>
+      </x:c>
+      <x:c r="B105" s="29" t="str">
+        <x:v>low: 800
+high: 800</x:v>
+      </x:c>
+      <x:c r="C105" s="29" t="str">
+        <x:v>Historical source fields; active prices are on Purchase.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" ht="40" customHeight="1">
+      <x:c r="A106" s="29" t="str">
+        <x:v>L06</x:v>
+      </x:c>
+      <x:c r="B106" s="29" t="str">
+        <x:v>low: 10000
+high: 10000</x:v>
+      </x:c>
+      <x:c r="C106" s="29" t="str">
+        <x:v>Historical source fields; active prices are on Purchase.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" ht="40" customHeight="1">
+      <x:c r="A107" s="29" t="str">
+        <x:v>L07</x:v>
+      </x:c>
+      <x:c r="B107" s="29" t="str">
+        <x:v>low: 4000
+high: 4000</x:v>
+      </x:c>
+      <x:c r="C107" s="29" t="str">
+        <x:v>Historical source fields; active prices are on Purchase.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="40" customHeight="1">
+      <x:c r="A108" s="29" t="str">
+        <x:v>L08</x:v>
+      </x:c>
+      <x:c r="B108" s="29" t="str">
+        <x:v>low: 300
+high: 300</x:v>
+      </x:c>
+      <x:c r="C108" s="29" t="str">
+        <x:v>Historical source fields; active prices are on Purchase.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="40" customHeight="1">
+      <x:c r="A109" s="29" t="str">
+        <x:v>FUT01</x:v>
+      </x:c>
+      <x:c r="B109" s="29" t="str">
+        <x:v>low: 6000
+high: 6000</x:v>
+      </x:c>
+      <x:c r="C109" s="29" t="str">
+        <x:v>Historical source fields; active prices are on Purchase.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="40" customHeight="1">
+      <x:c r="A110" s="29" t="str">
+        <x:v>FUT02</x:v>
+      </x:c>
+      <x:c r="B110" s="29" t="str">
+        <x:v>low: 500
+high: 500</x:v>
+      </x:c>
+      <x:c r="C110" s="29" t="str">
+        <x:v>Historical source fields; active prices are on Purchase.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="40" customHeight="1">
+      <x:c r="A111" s="29" t="str">
+        <x:v>FUT03</x:v>
+      </x:c>
+      <x:c r="B111" s="29" t="str">
+        <x:v>low: 1000
+high: 1000</x:v>
+      </x:c>
+      <x:c r="C111" s="29" t="str">
+        <x:v>Historical source fields; active prices are on Purchase.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" ht="30" customHeight="1">
+      <x:c r="A112" s="36" t="str">
+        <x:v>Additional PCB provenance</x:v>
+      </x:c>
+      <x:c r="B112" s="36" t="str"/>
+      <x:c r="C112" s="36" t="str"/>
+    </x:row>
+    <x:row r="113" ht="222" customHeight="1">
+      <x:c r="A113" s="29" t="str">
+        <x:v>1: C1</x:v>
+      </x:c>
+      <x:c r="B113" s="29" t="str">
+        <x:v>status: 規格/MPN未完整
+unit_price: 2
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 1
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"C1","purpose_zh":"U2 OUT 系統供電節點至 GND 的去耦／緩衝電容。","purpose_en":"Decoupling/buffering between the U2 OUT system-supply node and ground.","location_zh":"原理圖第 1 頁：充電／電源路徑","location_en":"Schematic page 1: charger / power path","page":1}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠 BOM 與原理圖皆未填容值。","spec_en":"No capacitance is given in the vendor BOM or schematic.","purpose_zh":"C1: U2 OUT 系統供電節點至 GND 的去耦／緩衝電容。","purpose_en":"C1: Decoupling/buffering between the U2 OUT system-supply node and ground.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、耐壓、容差、介電材質／型式尚未提供；電源電容需另核對有效容值、ESR 與穩定性要求。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, voltage rating, tolerance and dielectric/type are not supplied; power capacitors also require effective-capacitance, ESR and stability checks."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 1</x:v>
+      </x:c>
+      <x:c r="C113" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" ht="222" customHeight="1">
+      <x:c r="A114" s="29" t="str">
+        <x:v>2: C2</x:v>
+      </x:c>
+      <x:c r="B114" s="29" t="str">
+        <x:v>status: 規格/MPN未完整
+unit_price: 2
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 2
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"C2","purpose_zh":"U1 Vin 升壓輸入節點至 GND 的去耦電容。","purpose_en":"Input decoupling from the U1 boost-input node to ground.","location_zh":"原理圖第 1 頁：升壓電源","location_en":"Schematic page 1: boost supply","page":1}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠 BOM 與原理圖皆未填容值。","spec_en":"No capacitance is given in the vendor BOM or schematic.","purpose_zh":"C2: U1 Vin 升壓輸入節點至 GND 的去耦電容。","purpose_en":"C2: Input decoupling from the U1 boost-input node to ground.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、耐壓、容差、介電材質／型式尚未提供；電源電容需另核對有效容值、ESR 與穩定性要求。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, voltage rating, tolerance and dielectric/type are not supplied; power capacitors also require effective-capacitance, ESR and stability checks."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 2</x:v>
+      </x:c>
+      <x:c r="C114" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" ht="250" customHeight="1">
+      <x:c r="A115" s="29" t="str">
+        <x:v>3: C3</x:v>
+      </x:c>
+      <x:c r="B115" s="29" t="str">
+        <x:v>status: 規格/MPN未完整
+unit_price: 2
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 3
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"C3","purpose_zh":"U1 輸出、標為 5V 的節點至 GND 的濾波电容；實際設定仍取決於未提供的 R6/R8。","purpose_en":"Output filtering on the net labelled 5V; the actual setting still depends on unspecified R6/R8.","location_zh":"原理圖第 1 頁：升壓電源","location_en":"Schematic page 1: boost supply","page":1}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠 BOM 與原理圖皆未填容值。","spec_en":"No capacitance is given in the vendor BOM or schematic.","purpose_zh":"C3: U1 輸出、標為 5V 的節點至 GND 的濾波电容；實際設定仍取決於未提供的 R6/R8。","purpose_en":"C3: Output filtering on the net labelled 5V; the actual setting still depends on unspecified R6/R8.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、耐壓、容差、介電材質／型式尚未提供；電源電容需另核對有效容值、ESR 與穩定性要求。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, voltage rating, tolerance and dielectric/type are not supplied; power capacitors also require effective-capacitance, ESR and stability checks."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 3</x:v>
+      </x:c>
+      <x:c r="C115" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" ht="250" customHeight="1">
+      <x:c r="A116" s="29" t="str">
+        <x:v>4: C4</x:v>
+      </x:c>
+      <x:c r="B116" s="29" t="str">
+        <x:v>status: 規格/MPN未完整
+unit_price: 2
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 4
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"C4","purpose_zh":"U1 輸出、標為 5V 的節點至 GND 的濾波电容；實際設定仍取決於未提供的 R6/R8。","purpose_en":"Output filtering on the net labelled 5V; the actual setting still depends on unspecified R6/R8.","location_zh":"原理圖第 1 頁：升壓電源","location_en":"Schematic page 1: boost supply","page":1}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠 BOM 與原理圖皆未填容值。","spec_en":"No capacitance is given in the vendor BOM or schematic.","purpose_zh":"C4: U1 輸出、標為 5V 的節點至 GND 的濾波电容；實際設定仍取決於未提供的 R6/R8。","purpose_en":"C4: Output filtering on the net labelled 5V; the actual setting still depends on unspecified R6/R8.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、耐壓、容差、介電材質／型式尚未提供；電源電容需另核對有效容值、ESR 與穩定性要求。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, voltage rating, tolerance and dielectric/type are not supplied; power capacitors also require effective-capacitance, ESR and stability checks."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 4</x:v>
+      </x:c>
+      <x:c r="C116" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" ht="250" customHeight="1">
+      <x:c r="A117" s="29" t="str">
+        <x:v>5: C5</x:v>
+      </x:c>
+      <x:c r="B117" s="29" t="str">
+        <x:v>status: 規格/MPN未完整
+unit_price: 2
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 5
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"C5","purpose_zh":"U1 輸出、標為 5V 的節點至 GND 的濾波电容；實際設定仍取決於未提供的 R6/R8。","purpose_en":"Output filtering on the net labelled 5V; the actual setting still depends on unspecified R6/R8.","location_zh":"原理圖第 1 頁：升壓電源","location_en":"Schematic page 1: boost supply","page":1}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠 BOM 與原理圖皆未填容值。","spec_en":"No capacitance is given in the vendor BOM or schematic.","purpose_zh":"C5: U1 輸出、標為 5V 的節點至 GND 的濾波电容；實際設定仍取決於未提供的 R6/R8。","purpose_en":"C5: Output filtering on the net labelled 5V; the actual setting still depends on unspecified R6/R8.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、耐壓、容差、介電材質／型式尚未提供；電源電容需另核對有效容值、ESR 與穩定性要求。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, voltage rating, tolerance and dielectric/type are not supplied; power capacitors also require effective-capacitance, ESR and stability checks."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 5</x:v>
+      </x:c>
+      <x:c r="C117" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" ht="222" customHeight="1">
+      <x:c r="A118" s="29" t="str">
+        <x:v>6: C6</x:v>
+      </x:c>
+      <x:c r="B118" s="29" t="str">
+        <x:v>status: 規格/MPN未完整
+unit_price: 2
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 6
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"C6","purpose_zh":"USB 5V_USB 至 GND 的輸入去耦電容。","purpose_en":"Input decoupling from USB 5V_USB to ground.","location_zh":"原理圖第 1 頁：USB／充電輸入","location_en":"Schematic page 1: USB / charger input","page":1}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠 BOM 與原理圖皆未填容值。","spec_en":"No capacitance is given in the vendor BOM or schematic.","purpose_zh":"C6: USB 5V_USB 至 GND 的輸入去耦電容。","purpose_en":"C6: Input decoupling from USB 5V_USB to ground.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、耐壓、容差、介電材質／型式尚未提供；電源電容需另核對有效容值、ESR 與穩定性要求。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, voltage rating, tolerance and dielectric/type are not supplied; power capacitors also require effective-capacitance, ESR and stability checks."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 6</x:v>
+      </x:c>
+      <x:c r="C118" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" ht="236" customHeight="1">
+      <x:c r="A119" s="29" t="str">
+        <x:v>7: C7</x:v>
+      </x:c>
+      <x:c r="B119" s="29" t="str">
+        <x:v>status: 規格/MPN未完整
+unit_price: 2
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 7
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"C7","purpose_zh":"U3 P1 供電節點至 GND 的去耦電容；U3 型號未提供。","purpose_en":"Decoupling from the U3 P1 supply node to ground; U3 is unidentified.","location_zh":"原理圖第 1 頁：U3 電源控制周邊","location_en":"Schematic page 1: U3 power-control circuitry","page":1}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠 BOM 與原理圖皆未填容值。","spec_en":"No capacitance is given in the vendor BOM or schematic.","purpose_zh":"C7: U3 P1 供電節點至 GND 的去耦電容；U3 型號未提供。","purpose_en":"C7: Decoupling from the U3 P1 supply node to ground; U3 is unidentified.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、耐壓、容差、介電材質／型式尚未提供；電源電容需另核對有效容值、ESR 與穩定性要求。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, voltage rating, tolerance and dielectric/type are not supplied; power capacitors also require effective-capacitance, ESR and stability checks."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 7</x:v>
+      </x:c>
+      <x:c r="C119" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" ht="222" customHeight="1">
+      <x:c r="A120" s="29" t="str">
+        <x:v>8: C8</x:v>
+      </x:c>
+      <x:c r="B120" s="29" t="str">
+        <x:v>status: 規格/MPN未完整
+unit_price: 2
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 8
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"C8","purpose_zh":"U2 BAT／J1 電池正端節點至 GND 的電容。","purpose_en":"Capacitor from the U2 BAT / J1 battery-positive node to ground.","location_zh":"原理圖第 1 頁：電池／充電","location_en":"Schematic page 1: battery / charger","page":1}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠 BOM 與原理圖皆未填容值。","spec_en":"No capacitance is given in the vendor BOM or schematic.","purpose_zh":"C8: U2 BAT／J1 電池正端節點至 GND 的電容。","purpose_en":"C8: Capacitor from the U2 BAT / J1 battery-positive node to ground.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、耐壓、容差、介電材質／型式尚未提供；電源電容需另核對有效容值、ESR 與穩定性要求。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, voltage rating, tolerance and dielectric/type are not supplied; power capacitors also require effective-capacitance, ESR and stability checks."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 8</x:v>
+      </x:c>
+      <x:c r="C120" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" ht="250" customHeight="1">
+      <x:c r="A121" s="29" t="str">
+        <x:v>9: C9</x:v>
+      </x:c>
+      <x:c r="B121" s="29" t="str">
+        <x:v>status: 規格/MPN未完整
+unit_price: 2
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 9
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"C9","purpose_zh":"R10/R12 分壓中點、U3 P2 至 GND 的濾波電容；具體控制功能待 U3 型號確認。","purpose_en":"Filtering from the R10/R12 divider midpoint / U3 P2 to ground; control function requires the U3 identity.","location_zh":"原理圖第 1 頁：U3 電源控制周邊","location_en":"Schematic page 1: U3 power-control circuitry","page":1}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠 BOM 與原理圖皆未填容值。","spec_en":"No capacitance is given in the vendor BOM or schematic.","purpose_zh":"C9: R10/R12 分壓中點、U3 P2 至 GND 的濾波電容；具體控制功能待 U3 型號確認。","purpose_en":"C9: Filtering from the R10/R12 divider midpoint / U3 P2 to ground; control function requires the U3 identity.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、耐壓、容差、介電材質／型式尚未提供；電源電容需另核對有效容值、ESR 與穩定性要求。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, voltage rating, tolerance and dielectric/type are not supplied; power capacitors also require effective-capacitance, ESR and stability checks."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 9</x:v>
+      </x:c>
+      <x:c r="C121" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" ht="250" customHeight="1">
+      <x:c r="A122" s="29" t="str">
+        <x:v>10: C10</x:v>
+      </x:c>
+      <x:c r="B122" s="29" t="str">
+        <x:v>status: 規格/MPN未完整
+unit_price: 2
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 10
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"C10","purpose_zh":"U3 P6 至 GND；U3 型號未提供，不能確定其定時／補償等具體功能。","purpose_en":"Connected from U3 P6 to ground; timing/compensation or other function cannot be assigned without its identity.","location_zh":"原理圖第 1 頁：U3 電源控制周邊","location_en":"Schematic page 1: U3 power-control circuitry","page":1}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠 BOM 與原理圖皆未填容值。","spec_en":"No capacitance is given in the vendor BOM or schematic.","purpose_zh":"C10: U3 P6 至 GND；U3 型號未提供，不能確定其定時／補償等具體功能。","purpose_en":"C10: Connected from U3 P6 to ground; timing/compensation or other function cannot be assigned without its identity.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、耐壓、容差、介電材質／型式尚未提供；電源電容需另核對有效容值、ESR 與穩定性要求。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, voltage rating, tolerance and dielectric/type are not supplied; power capacitors also require effective-capacitance, ESR and stability checks."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 10</x:v>
+      </x:c>
+      <x:c r="C122" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" ht="250" customHeight="1">
+      <x:c r="A123" s="29" t="str">
+        <x:v>11: C11</x:v>
+      </x:c>
+      <x:c r="B123" s="29" t="str">
+        <x:v>status: 規格/MPN未完整
+unit_price: 2
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 11
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"C11","purpose_zh":"U3 P4 至 GND；U3 型號未提供，不能確定其定時／補償等具體功能。","purpose_en":"Connected from U3 P4 to ground; timing/compensation or other function cannot be assigned without its identity.","location_zh":"原理圖第 1 頁：U3 電源控制周邊","location_en":"Schematic page 1: U3 power-control circuitry","page":1}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠 BOM 與原理圖皆未填容值。","spec_en":"No capacitance is given in the vendor BOM or schematic.","purpose_zh":"C11: U3 P4 至 GND；U3 型號未提供，不能確定其定時／補償等具體功能。","purpose_en":"C11: Connected from U3 P4 to ground; timing/compensation or other function cannot be assigned without its identity.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、耐壓、容差、介電材質／型式尚未提供；電源電容需另核對有效容值、ESR 與穩定性要求。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, voltage rating, tolerance and dielectric/type are not supplied; power capacitors also require effective-capacitance, ESR and stability checks."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 11</x:v>
+      </x:c>
+      <x:c r="C123" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" ht="222" customHeight="1">
+      <x:c r="A124" s="29" t="str">
+        <x:v>12: C12</x:v>
+      </x:c>
+      <x:c r="B124" s="29" t="str">
+        <x:v>status: 依廠商BOM，封裝/容差仍需確認
+unit_price: 15
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 12
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"C12","purpose_zh":"LED 區 5V 至 GND 的局部儲能電容；原圖有極性符號。","purpose_en":"Local bulk capacitor between LED 5V and ground; the schematic uses a polarized symbol.","location_zh":"原理圖第 2 頁：LEDs","location_en":"Schematic page 2: LEDs","page":2}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠標稱容值 47uF。","spec_en":"Vendor nominal capacitance: 47uF.","purpose_zh":"C12: LED 區 5V 至 GND 的局部儲能電容；原圖有極性符號。","purpose_en":"C12: Local bulk capacitor between LED 5V and ground; the schematic uses a polarized symbol.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、耐壓、容差、介電材質／型式尚未提供；電源電容需另核對有效容值、ESR 與穩定性要求。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, voltage rating, tolerance and dielectric/type are not supplied; power capacitors also require effective-capacitance, ESR and stability checks."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 12</x:v>
+      </x:c>
+      <x:c r="C124" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" ht="236" customHeight="1">
+      <x:c r="A125" s="29" t="str">
+        <x:v>13: C13,C18</x:v>
+      </x:c>
+      <x:c r="B125" s="29" t="str">
+        <x:v>status: 依廠商BOM，封裝/容差仍需確認
+unit_price: 8
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 13
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"C13","purpose_zh":"ESP32 3V3_DIG 供電去耦。","purpose_en":"ESP32 3V3_DIG supply decoupling.","location_zh":"原理圖第 2 頁：ESP32","location_en":"Schematic page 2: ESP32","page":2},{"reference":"C18","purpose_zh":"U5 的 3V3_DIG 輸出電容。","purpose_en":"U5 3V3_DIG output capacitor.","location_zh":"原理圖第 2 頁：3V3 LDO","location_en":"Schematic page 2: 3V3 LDO","page":2}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠標稱容值 22uF。","spec_en":"Vendor nominal capacitance: 22uF.","purpose_zh":"C13: ESP32 3V3_DIG 供電去耦。；C18: U5 的 3V3_DIG 輸出電容。","purpose_en":"C13: ESP32 3V3_DIG supply decoupling.；C18: U5 3V3_DIG output capacitor.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、耐壓、容差、介電材質／型式尚未提供；電源電容需另核對有效容值、ESR 與穩定性要求。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, voltage rating, tolerance and dielectric/type are not supplied; power capacitors also require effective-capacitance, ESR and stability checks."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 13</x:v>
+      </x:c>
+      <x:c r="C125" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" ht="194" customHeight="1">
+      <x:c r="A126" s="29" t="str">
+        <x:v>14: C14,C15,C22,C25</x:v>
+      </x:c>
+      <x:c r="B126" s="29" t="str">
+        <x:v>status: 依廠商BOM，封裝/容差仍需確認
+unit_price: 2
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 14
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"C14","purpose_zh":"ESP32 3V3_DIG 供電去耦。","purpose_en":"ESP32 3V3_DIG supply decoupling.","location_zh":"原理圖第 2 頁：ESP32","location_en":"Schematic page 2: ESP32","page":2},{"reference":"C15","purpose_zh":"跨接 SW2 的 ESP_EN 至 GND，屬復位／啟用節點電容。","purpose_en":"ESP_EN-to-ground capacitor across SW2 in the reset/enable network.","location_zh":"原理圖第 2 頁：ESP32 復位","location_en":"Schematic page 2: ESP32 reset","page":2},{"reference":"C22","purpose_zh":"U7 的 3V3_ANA 輸入去耦。","purpose_en":"U7 3V3_ANA input decoupling.","location_zh":"原理圖第 2 頁：2V5_REF","location_en":"Schematic page 2: 2V5_REF","page":2},{"reference":"C25","purpose_zh":"R31 後方 U8 局部供電至 GND 的電容，與 R31 構成供電濾波。C26 原圖有極性符號。","purpose_en":"Capacitors from the U8 local supply after R31 to ground, forming supply filtering with R31. C26 has a polarized</x:v>
+      </x:c>
+      <x:c r="C126" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" ht="208" customHeight="1">
+      <x:c r="A127" s="29" t="str">
+        <x:v>14: C14,C15,C22,C25 (continued)</x:v>
+      </x:c>
+      <x:c r="B127" s="29" t="str">
+        <x:v> symbol.","location_zh":"原理圖第 2 頁：TIA 供電","location_en":"Schematic page 2: TIA supply","page":2}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠標稱容值 0.1uF。","spec_en":"Vendor nominal capacitance: 0.1uF.","purpose_zh":"C14: ESP32 3V3_DIG 供電去耦。；C15: 跨接 SW2 的 ESP_EN 至 GND，屬復位／啟用節點電容。；C22: U7 的 3V3_ANA 輸入去耦。；C25: R31 後方 U8 局部供電至 GND 的電容，與 R31 構成供電濾波。C26 原圖有極性符號。","purpose_en":"C14: ESP32 3V3_DIG supply decoupling.；C15: ESP_EN-to-ground capacitor across SW2 in the reset/enable network.；C22: U7 3V3_ANA input decoupling.；C25: Capacitors from the U8 local supply after R31 to ground, forming supply filtering with R31. C26 has a polarized symbol.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、耐壓、容差、介電材質／型式尚未提供；電源電容需另核對有效容值、ESR 與穩定性要求。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, voltage rating, tolerance and dielectric/type are not supplied; power capacitors also require effective-capacitance, ESR and stability checks."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 14</x:v>
+      </x:c>
+      <x:c r="C127" s="29" t="str"/>
+    </x:row>
+    <x:row r="128" ht="194" customHeight="1">
+      <x:c r="A128" s="29" t="str">
+        <x:v>15: C16,C17,C23,C28</x:v>
+      </x:c>
+      <x:c r="B128" s="29" t="str">
+        <x:v>status: 依廠商BOM，封裝/容差仍需確認
+unit_price: 8
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 15
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"C16","purpose_zh":"ESP_EN 至 GND，與 R15 構成啟用／復位 RC 網路。","purpose_en":"ESP_EN-to-ground capacitor forming the enable/reset RC network with R15.","location_zh":"原理圖第 2 頁：ESP32 復位","location_en":"Schematic page 2: ESP32 reset","page":2},{"reference":"C17","purpose_zh":"U5 的 5V 輸入去耦。","purpose_en":"U5 5V input decoupling.","location_zh":"原理圖第 2 頁：3V3 LDO","location_en":"Schematic page 2: 3V3 LDO","page":2},{"reference":"C23","purpose_zh":"U7 VREF_2V5 輸出電容。","purpose_en":"U7 VREF_2V5 output capacitor.","location_zh":"原理圖第 2 頁：2V5_REF","location_en":"Schematic page 2: 2V5_REF","page":2},{"reference":"C28","purpose_zh":"與 R34 串聯，形成 VREF_2V5 至 GND 的參考電壓旁路支路。","purpose_en":"In series with R34 in a VREF_2V5-to-ground reference-bypass</x:v>
+      </x:c>
+      <x:c r="C128" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" ht="194" customHeight="1">
+      <x:c r="A129" s="29" t="str">
+        <x:v>15: C16,C17,C23,C28 (continued)</x:v>
+      </x:c>
+      <x:c r="B129" s="29" t="str">
+        <x:v> branch.","location_zh":"原理圖第 2 頁：ADC 參考","location_en":"Schematic page 2: ADC reference","page":2}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠標稱容值 10uF。","spec_en":"Vendor nominal capacitance: 10uF.","purpose_zh":"C16: ESP_EN 至 GND，與 R15 構成啟用／復位 RC 網路。；C17: U5 的 5V 輸入去耦。；C23: U7 VREF_2V5 輸出電容。；C28: 與 R34 串聯，形成 VREF_2V5 至 GND 的參考電壓旁路支路。","purpose_en":"C16: ESP_EN-to-ground capacitor forming the enable/reset RC network with R15.；C17: U5 5V input decoupling.；C23: U7 VREF_2V5 output capacitor.；C28: In series with R34 in a VREF_2V5-to-ground reference-bypass branch.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、耐壓、容差、介電材質／型式尚未提供；電源電容需另核對有效容值、ESR 與穩定性要求。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, voltage rating, tolerance and dielectric/type are not supplied; power capacitors also require effective-capacitance, ESR and stability checks."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 15</x:v>
+      </x:c>
+      <x:c r="C129" s="29" t="str"/>
+    </x:row>
+    <x:row r="130" ht="166" customHeight="1">
+      <x:c r="A130" s="29" t="str">
+        <x:v>16: C19,C20,C27,C29</x:v>
+      </x:c>
+      <x:c r="B130" s="29" t="str">
+        <x:v>status: 依廠商BOM，封裝/容差仍需確認
+unit_price: 2
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 16
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"C19","purpose_zh":"U6 的 5V 輸入去耦。","purpose_en":"U6 5V input decoupling.","location_zh":"原理圖第 2 頁：3V3 LDO","location_en":"Schematic page 2: 3V3 LDO","page":2},{"reference":"C20","purpose_zh":"U6 的 3V3_ANA 輸出電容。","purpose_en":"U6 3V3_ANA output capacitor.","location_zh":"原理圖第 2 頁：3V3 LDO","location_en":"Schematic page 2: 3V3 LDO","page":2},{"reference":"C27","purpose_zh":"U9 DVDD／3V3_DIG 供電去耦。","purpose_en":"U9 DVDD / 3V3_DIG decoupling.","location_zh":"原理圖第 2 頁：ADC","location_en":"Schematic page 2: ADC","page":2},{"reference":"C29","purpose_zh":"U9 AVDD／3V3_ANA 供電去耦。","purpose_en":"U9 AVDD / 3V3_ANA</x:v>
+      </x:c>
+      <x:c r="C130" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" ht="152" customHeight="1">
+      <x:c r="A131" s="29" t="str">
+        <x:v>16: C19,C20,C27,C29 (continued)</x:v>
+      </x:c>
+      <x:c r="B131" s="29" t="str">
+        <x:v> decoupling.","location_zh":"原理圖第 2 頁：ADC","location_en":"Schematic page 2: ADC","page":2}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠標稱容值 1uF。","spec_en":"Vendor nominal capacitance: 1uF.","purpose_zh":"C19: U6 的 5V 輸入去耦。；C20: U6 的 3V3_ANA 輸出電容。；C27: U9 DVDD／3V3_DIG 供電去耦。；C29: U9 AVDD／3V3_ANA 供電去耦。","purpose_en":"C19: U6 5V input decoupling.；C20: U6 3V3_ANA output capacitor.；C27: U9 DVDD / 3V3_DIG decoupling.；C29: U9 AVDD / 3V3_ANA decoupling.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、耐壓、容差、介電材質／型式尚未提供；電源電容需另核對有效容值、ESR 與穩定性要求。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, voltage rating, tolerance and dielectric/type are not supplied; power capacitors also require effective-capacitance, ESR and stability checks."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 16</x:v>
+      </x:c>
+      <x:c r="C131" s="29" t="str"/>
+    </x:row>
+    <x:row r="132" ht="278" customHeight="1">
+      <x:c r="A132" s="29" t="str">
+        <x:v>17: C21</x:v>
+      </x:c>
+      <x:c r="B132" s="29" t="str">
+        <x:v>status: 依廠商BOM，封裝/容差仍需確認
+unit_price: 2
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 17
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"C21","purpose_zh":"與 R27 並聯，從 U8 輸出回授至反相輸入；影響跨阻放大器補償與頻寬。","purpose_en":"In parallel with R27 from U8 output to its inverting input; affects transimpedance compensation and bandwidth.","location_zh":"原理圖第 2 頁：TIA","location_en":"Schematic page 2: TIA","page":2}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠標稱容值 2.2pF。","spec_en":"Vendor nominal capacitance: 2.2pF.","purpose_zh":"C21: 與 R27 並聯，從 U8 輸出回授至反相輸入；影響跨阻放大器補償與頻寬。","purpose_en":"C21: In parallel with R27 from U8 output to its inverting input; affects transimpedance compensation and bandwidth.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、耐壓、容差、介電材質／型式尚未提供；電源電容需另核對有效容值、ESR 與穩定性要求。 2.2 pF 為小訊號回授值，焊墊／走線寄生不可忽略；低漏電與合適介電材質須廠商選定。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, voltage rating, tolerance and dielectric/type are not supplied; power capacitors also require effective-capacitance, ESR and stability checks. At 2.2 pF, pad/trace parasitics matter; the vendor must select suitable low-leakage construction/dielectric."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 17</x:v>
+      </x:c>
+      <x:c r="C132" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" ht="236" customHeight="1">
+      <x:c r="A133" s="29" t="str">
+        <x:v>18: C24</x:v>
+      </x:c>
+      <x:c r="B133" s="29" t="str">
+        <x:v>status: 依廠商BOM，封裝/容差仍需確認
+unit_price: 2
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 18
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"C24","purpose_zh":"跨 ADC_AINP 與 ADC_AINN，與 R29/R36 形成 ADC 輸入濾波網路。","purpose_en":"Across ADC_AINP and ADC_AINN, part of the ADC-input filtering network with R29/R36.","location_zh":"原理圖第 2 頁：TIA／ADC","location_en":"Schematic page 2: TIA / ADC","page":2}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠標稱容值 1000pF。","spec_en":"Vendor nominal capacitance: 1000pF.","purpose_zh":"C24: 跨 ADC_AINP 與 ADC_AINN，與 R29/R36 形成 ADC 輸入濾波網路。","purpose_en":"C24: Across ADC_AINP and ADC_AINN, part of the ADC-input filtering network with R29/R36.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、耐壓、容差、介電材質／型式尚未提供；電源電容需另核對有效容值、ESR 與穩定性要求。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, voltage rating, tolerance and dielectric/type are not supplied; power capacitors also require effective-capacitance, ESR and stability checks."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 18</x:v>
+      </x:c>
+      <x:c r="C133" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" ht="250" customHeight="1">
+      <x:c r="A134" s="29" t="str">
+        <x:v>19: C26</x:v>
+      </x:c>
+      <x:c r="B134" s="29" t="str">
+        <x:v>status: 依廠商BOM，封裝/容差仍需確認
+unit_price: 15
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 19
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"C26","purpose_zh":"R31 後方 U8 局部供電至 GND 的電容，與 R31 構成供電濾波。C26 原圖有極性符號。","purpose_en":"Capacitors from the U8 local supply after R31 to ground, forming supply filtering with R31. C26 has a polarized symbol.","location_zh":"原理圖第 2 頁：TIA 供電","location_en":"Schematic page 2: TIA supply","page":2}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠標稱容值 100uF。","spec_en":"Vendor nominal capacitance: 100uF.","purpose_zh":"C26: R31 後方 U8 局部供電至 GND 的電容，與 R31 構成供電濾波。C26 原圖有極性符號。","purpose_en":"C26: Capacitors from the U8 local supply after R31 to ground, forming supply filtering with R31. C26 has a polarized symbol.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、耐壓、容差、介電材質／型式尚未提供；電源電容需另核對有效容值、ESR 與穩定性要求。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, voltage rating, tolerance and dielectric/type are not supplied; power capacitors also require effective-capacitance, ESR and stability checks."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 19</x:v>
+      </x:c>
+      <x:c r="C134" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" ht="180" customHeight="1">
+      <x:c r="A135" s="29" t="str">
+        <x:v>20: DPS1,DPS2</x:v>
+      </x:c>
+      <x:c r="B135" s="29" t="str">
+        <x:v>status: 規格/MPN未完整
+unit_price: 2
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 20
+source_ids: ["vendor_BOM","schematic"]
+per_reference: []
+orderability: incomplete_component_specification
+details: {"spec_zh":"僅標示 LED；共 2 顆。","spec_en":"Only identified as LED; two devices.","purpose_zh":"DPS1 接 U2 PGOOD、配 R5；DPS2 接 U2 CHG、配 R7，顯示電源／充電狀態。","purpose_en":"DPS1 is connected to U2 PGOOD via R5; DPS2 to U2 CHG via R7 for power/charging status.","missing_zh":"顏色、廠牌／MPN、封裝尺寸／高度、順向電壓／電流與亮度均未提供。","missing_en":"Color, manufacturer/MPN, package size/height, forward voltage/current and brightness are not supplied."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 20</x:v>
+      </x:c>
+      <x:c r="C135" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" ht="236" customHeight="1">
+      <x:c r="A136" s="29" t="str">
+        <x:v>21: D1,D2,D3,D4</x:v>
+      </x:c>
+      <x:c r="B136" s="29" t="str">
+        <x:v>status: 依廠商BOM，封裝/容差仍需確認
+unit_price: 17
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 21
+source_ids: ["vendor_BOM","schematic","WURTH_LED"]
+per_reference: []
+orderability: identified_part_pending_assembly_verification
+details: {"spec_zh":"Würth Elektronik 155124BS73200；1204 側發光 SMD；資料表在 20 mA 下典型峰值 468 nm／主波長 470 nm、視角 120°。","spec_en":"Würth Elektronik 155124BS73200; 1204 side-view SMD; datasheet at 20 mA gives typical peak 468 nm / dominant wavelength 470 nm and 120° viewing angle.","purpose_zh":"D1–D4 由 Q1–Q4 低側開關調變；各有 100 Ω 串聯電阻。GPIO25/26/27/32 對應 LED1/2/3/4。","purpose_en":"D1–D4 are modulated by low-side switches Q1–Q4 with individual 100 Ω series resistors. GPIO25/26/27/32 map to LED1/2/3/4.","missing_zh":"須核對實際焊接方向／高度、光學軸與 well 對位、實際電流及光功率；20 mA 是資料表測試條件，非已驗證板上電流。","missing_en":"Verify assembled orientation/height, optical-axis alignment to wells, operating current and optical power; 20 mA is a datasheet test condition, not a verified board current."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 21</x:v>
+      </x:c>
+      <x:c r="C136" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" ht="236" customHeight="1">
+      <x:c r="A137" s="29" t="str">
+        <x:v>22: D5</x:v>
+      </x:c>
+      <x:c r="B137" s="29" t="str">
+        <x:v>status: 依廠商BOM，封裝/容差仍需確認
+unit_price: 68
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 22
+source_ids: ["vendor_BOM","schematic","VISHAY_PD"]
+per_reference: []
+orderability: identified_part_pending_assembly_verification
+details: {"spec_zh":"Vishay VEMD5060X01；頂視 SMD，外形 5×4×0.9 mm；感光面積 7.5 mm²；可見光至近紅外感測。","spec_en":"Vishay VEMD5060X01; top-view SMD, 5×4×0.9 mm body; 7.5 mm² photosensitive area; visible-to-near-infrared response.","purpose_zh":"D5 是四井共用 PD；陰極連 PD_SUM／U8 反相輸入，陽極接 GND。藍光與綠光皆可被接收，必須搭配光學濾波與空白校正。","purpose_en":"D5 is the single PD shared by four wells; cathode to PD_SUM / U8 inverting input and anode to ground. It detects both blue and green light, requiring optical filtering and blank correction.","missing_zh":"實際感光區中心與封裝中心不可混同；裝配座標、濾片／墊圈遮擋與角度接受度须核對。廠商需確認最終訂購後綴及來料。","missing_en":"Do not equate the active-area center with the package center; verify assembly coordinates, filter/gasket obscuration and angular acceptance. Confirm final order suffix and supplied part."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 22</x:v>
+      </x:c>
+      <x:c r="C137" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" ht="180" customHeight="1">
+      <x:c r="A138" s="29" t="str">
+        <x:v>23: FD1,FD2,FD3,FD4,FD5,FD6,FD
+7,FD8</x:v>
+      </x:c>
+      <x:c r="B138" s="29" t="str">
+        <x:v>status: PCB fiducial，不是採購元件
+unit_price: 0
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 23
+source_ids: ["vendor_BOM","schematic"]
+per_reference: []
+orderability: PCB_feature_not_separate_purchase
+details: {"spec_zh":"FD_040；8 個定位標記。","spec_en":"FD_040; eight fiducials.","purpose_zh":"供 SMT 視覺定位，不是額外焊接的 LED 或感測器。","purpose_en":"Provide vision alignment for SMT assembly; these are not separate LEDs or sensors.","missing_zh":"銅面／阻焊開窗與定位尺寸由製板資料確認；不另購零件。","missing_en":"Confirm copper/solder-mask geometry in fabrication data; do not purchase separate components."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 23</x:v>
+      </x:c>
+      <x:c r="C138" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" ht="194" customHeight="1">
+      <x:c r="A139" s="29" t="str">
+        <x:v>24: H1,H2,H3,H4</x:v>
+      </x:c>
+      <x:c r="B139" s="29" t="str">
+        <x:v>status: PCB孔位，不另當电子零件買
+unit_price: 0
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 24
+source_ids: ["vendor_BOM","schematic"]
+per_reference: []
+orderability: PCB_feature_not_separate_purchase
+details: {"spec_zh":"H1–H4；原廠標示 CON(銅柱孔)。","spec_en":"H1–H4; vendor label CON (standoff holes).","purpose_zh":"PCB 機械固定孔，不是電子連接器；額外螺絲／螺帽見其他材料表，勿重複計價。","purpose_en":"Mechanical PCB fixing holes, not electrical connectors; screws/nuts are listed in the separate materials BOM and must not be counted twice.","missing_zh":"孔徑、鍍孔／非鍍孔、銅箔避讓與裝配間隙須依製板圖／實板確認；本列未指定螺絲尺寸。","missing_en":"Verify diameter, plated/non-plated status, copper keepout and clearance from fabrication drawings/board; this row does not specify a screw size."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 24</x:v>
+      </x:c>
+      <x:c r="C139" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" ht="222" customHeight="1">
+      <x:c r="A140" s="29" t="str">
+        <x:v>25: J1</x:v>
+      </x:c>
+      <x:c r="B140" s="29" t="str">
+        <x:v>status: 規格/MPN未完整
+unit_price: 30
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 25
+source_ids: ["vendor_BOM","schematic","TI_BQ24074"]
+per_reference: []
+orderability: incomplete_component_specification
+details: {"spec_zh":"原廠僅標 Battery_Case；原圖腳1接 BAT，腳2接 GND。","spec_en":"Only Battery_Case is specified; schematic pin 1 connects to BAT and pin 2 to ground.","purpose_zh":"接 U2 BQ24074 單節鋰離子／鋰聚合物 4.2 V 充電架構；不能由此推定為 18650 電池座。","purpose_en":"Connects to the BQ24074 single-cell Li-ion/Li-poly 4.2 V charging architecture; this does not establish an 18650 holder.","missing_zh":"完整MPN、電池尺寸／化學與保護配置、極性標記、安裝孔與含電池高度、額定電流未完整提供；R1–R3/R9 亦未定，先請廠商確認。","missing_en":"MPN, cell size/chemistry/protection, polarity marking, mounting and height with cell, and current rating are incomplete; R1–R3/R9 are also unspecified. Obtain vendor confirmation first."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 25</x:v>
+      </x:c>
+      <x:c r="C140" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" ht="208" customHeight="1">
+      <x:c r="A141" s="29" t="str">
+        <x:v>26: J2</x:v>
+      </x:c>
+      <x:c r="B141" s="29" t="str">
+        <x:v>status: 規格/MPN未完整
+unit_price: 20
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 26
+source_ids: ["vendor_BOM","schematic"]
+per_reference: []
+orderability: incomplete_component_specification
+details: {"spec_zh":"VBUS 接 5V_USB；CC1/CC2 經 R13/R14 至 GND；資料線 D+/D− 與 SBU 未接。","spec_en":"VBUS connects to 5V_USB; CC1/CC2 connect through R13/R14 to ground; D+/D− and SBU are unconnected.","purpose_zh":"提供電源／充電輸入，不能用此孔作原生 USB 韌體燒錄或資料傳输；J3 是 UART 介面。","purpose_en":"Power/charging input, not a native USB programming/data port; J3 provides the UART interface.","missing_zh":"完整MPN、封裝與固定腳、孔口位置／高度、額定電流未給；R13/R14 數值未給，USB-C 供電配置待確認。","missing_en":"MPN, footprint/retention tabs, opening location/height and current rating are absent; R13/R14 values are absent, so confirm USB-C power configuration."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 26</x:v>
+      </x:c>
+      <x:c r="C141" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142" ht="208" customHeight="1">
+      <x:c r="A142" s="29" t="str">
+        <x:v>27: J3</x:v>
+      </x:c>
+      <x:c r="B142" s="29" t="str">
+        <x:v>status: 規格/MPN未完整
+unit_price: 5
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 27
+source_ids: ["vendor_BOM","schematic"]
+per_reference: []
+orderability: incomplete_component_specification
+details: {"spec_zh":"原圖腳1=3V3_DIG、2=ESP32 TXD0、3=ESP32 RXD0、4=GND。","spec_en":"Schematic pin 1=3V3_DIG, 2=ESP32 TXD0, 3=ESP32 RXD0, 4=GND.","purpose_zh":"ESP32 3.3 V UART 燒錄／除錯介面；連接轉接器時 TX/RX 交叉且核對供電，不能將5 V邏輯直接接入。","purpose_en":"ESP32 3.3 V UART programming/debug interface; cross TX/RX and verify power wiring. Do not apply 5 V logic directly.","missing_zh":"廠牌／MPN、針距、直角／直立、針長與高度、對接線材未提供；不能自動假定2.54 mm。","missing_en":"Manufacturer/MPN, pitch, straight/right-angle form, pin length/height and mating cable are unspecified; do not automatically assume 2.54 mm."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 27</x:v>
+      </x:c>
+      <x:c r="C142" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" ht="180" customHeight="1">
+      <x:c r="A143" s="29" t="str">
+        <x:v>28: L1</x:v>
+      </x:c>
+      <x:c r="B143" s="29" t="str">
+        <x:v>status: 規格/MPN未完整
+unit_price: 10
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 28
+source_ids: ["vendor_BOM","schematic","TI_TPS61023"]
+per_reference: []
+orderability: incomplete_component_specification
+details: {"spec_zh":"L1；原廠無電感值／MPN。","spec_en":"L1; inductance and MPN are absent.","purpose_zh":"跨 U1 Vin 與 SW，為 TPS61023 升壓能量儲存元件。","purpose_en":"Between U1 Vin and SW; the TPS61023 boost energy-storage element.","missing_zh":"電感值、飽和／RMS 電流、DCR、屏蔽型式、封裝／高度與完整MPN皆待廠商確認。","missing_en":"Inductance, saturation/RMS current, DCR, shielding, package/height and orderable MPN all require vendor confirmation."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 28</x:v>
+      </x:c>
+      <x:c r="C143" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" ht="208" customHeight="1">
+      <x:c r="A144" s="29" t="str">
+        <x:v>29: Q1,Q2,Q3,Q4</x:v>
+      </x:c>
+      <x:c r="B144" s="29" t="str">
+        <x:v>status: 依廠商BOM，封裝/容差仍需確認
+unit_price: 5
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 29
+source_ids: ["vendor_BOM","schematic","AOS_AO3400A"]
+per_reference: []
+orderability: identified_part_pending_assembly_verification
+details: {"spec_zh":"AOS AO3400A；30 V N-MOSFET，SOT-23；資料表提供低閘極電壓導通規格。","spec_en":"AOS AO3400A; 30 V N-channel MOSFET, SOT-23; low-gate-voltage on-resistance is specified.","purpose_zh":"Q1–Q4 分別作 D1–D4 LED 低側開關；由各 LED_GATE 經串聯電阻驅動，閘極有下拉。","purpose_en":"Q1–Q4 are low-side switches for LEDs D1–D4, driven by LED_GATE through series resistors with gate pull-downs.","missing_zh":"須核對封裝焊盤／腳位、來料及實際 LED 電流／溫升；器件最大額定值不等於板上允許負載。","missing_en":"Verify footprint/pinout, supplied part and operating LED current/temperature; device maximum ratings are not allowable board-load guarantees."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 29</x:v>
+      </x:c>
+      <x:c r="C144" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" ht="222" customHeight="1">
+      <x:c r="A145" s="29" t="str">
+        <x:v>30: R1</x:v>
+      </x:c>
+      <x:c r="B145" s="29" t="str">
+        <x:v>status: 規格/MPN未完整
+unit_price: 1
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 30
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"R1","purpose_zh":"U2 ITERM 至 GND，設定充電終止電流。","purpose_en":"U2 ITERM-to-ground resistor setting charge-termination current.","location_zh":"原理圖第 1 頁：充電／電源路徑","location_en":"Schematic page 1: charger / power path","page":1}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠 BOM 與原理圖皆未填阻值。","spec_en":"No resistance is given in the vendor BOM or schematic.","purpose_zh":"R1: U2 ITERM 至 GND，設定充電終止電流。","purpose_en":"R1: U2 ITERM-to-ground resistor setting charge-termination current.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、功率、容差、溫度係數及最大工作電壓尚未提供。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, power rating, tolerance, temperature coefficient and maximum working voltage are not supplied."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 30</x:v>
+      </x:c>
+      <x:c r="C145" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" ht="208" customHeight="1">
+      <x:c r="A146" s="29" t="str">
+        <x:v>31: R2</x:v>
+      </x:c>
+      <x:c r="B146" s="29" t="str">
+        <x:v>status: 規格/MPN未完整
+unit_price: 1
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 31
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"R2","purpose_zh":"U2 ILIM 至 GND，設定輸入電流限制。","purpose_en":"U2 ILIM-to-ground resistor setting the input-current limit.","location_zh":"原理圖第 1 頁：充電／電源路徑","location_en":"Schematic page 1: charger / power path","page":1}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠 BOM 與原理圖皆未填阻值。","spec_en":"No resistance is given in the vendor BOM or schematic.","purpose_zh":"R2: U2 ILIM 至 GND，設定輸入電流限制。","purpose_en":"R2: U2 ILIM-to-ground resistor setting the input-current limit.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、功率、容差、溫度係數及最大工作電壓尚未提供。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, power rating, tolerance, temperature coefficient and maximum working voltage are not supplied."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 31</x:v>
+      </x:c>
+      <x:c r="C146" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" ht="208" customHeight="1">
+      <x:c r="A147" s="29" t="str">
+        <x:v>32: R3</x:v>
+      </x:c>
+      <x:c r="B147" s="29" t="str">
+        <x:v>status: 規格/MPN未完整
+unit_price: 1
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 32
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"R3","purpose_zh":"U2 ISET 至 GND，設定充電電流。","purpose_en":"U2 ISET-to-ground resistor setting charge current.","location_zh":"原理圖第 1 頁：充電／電源路徑","location_en":"Schematic page 1: charger / power path","page":1}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠 BOM 與原理圖皆未填阻值。","spec_en":"No resistance is given in the vendor BOM or schematic.","purpose_zh":"R3: U2 ISET 至 GND，設定充電電流。","purpose_en":"R3: U2 ISET-to-ground resistor setting charge current.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、功率、容差、溫度係數及最大工作電壓尚未提供。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, power rating, tolerance, temperature coefficient and maximum working voltage are not supplied."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 32</x:v>
+      </x:c>
+      <x:c r="C147" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" ht="208" customHeight="1">
+      <x:c r="A148" s="29" t="str">
+        <x:v>33: R4</x:v>
+      </x:c>
+      <x:c r="B148" s="29" t="str">
+        <x:v>status: 規格/MPN未完整
+unit_price: 1
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 33
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"R4","purpose_zh":"SW1 至 U1 EN／U3 P3 節點的串聯電阻。","purpose_en":"Series resistor from SW1 to the U1 EN / U3 P3 node.","location_zh":"原理圖第 1 頁：電源啟用","location_en":"Schematic page 1: power enable","page":1}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠 BOM 與原理圖皆未填阻值。","spec_en":"No resistance is given in the vendor BOM or schematic.","purpose_zh":"R4: SW1 至 U1 EN／U3 P3 節點的串聯電阻。","purpose_en":"R4: Series resistor from SW1 to the U1 EN / U3 P3 node.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、功率、容差、溫度係數及最大工作電壓尚未提供。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, power rating, tolerance, temperature coefficient and maximum working voltage are not supplied."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 33</x:v>
+      </x:c>
+      <x:c r="C148" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" ht="208" customHeight="1">
+      <x:c r="A149" s="29" t="str">
+        <x:v>34: R5</x:v>
+      </x:c>
+      <x:c r="B149" s="29" t="str">
+        <x:v>status: 規格/MPN未完整
+unit_price: 1
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 34
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"R5","purpose_zh":"DPS1 狀態 LED 的串聯限流電阻。","purpose_en":"Series current-limiting resistor for the DPS1 status LED.","location_zh":"原理圖第 1 頁：充電狀態顯示","location_en":"Schematic page 1: charger status","page":1}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠 BOM 與原理圖皆未填阻值。","spec_en":"No resistance is given in the vendor BOM or schematic.","purpose_zh":"R5: DPS1 狀態 LED 的串聯限流電阻。","purpose_en":"R5: Series current-limiting resistor for the DPS1 status LED.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、功率、容差、溫度係數及最大工作電壓尚未提供。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, power rating, tolerance, temperature coefficient and maximum working voltage are not supplied."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 34</x:v>
+      </x:c>
+      <x:c r="C149" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" ht="222" customHeight="1">
+      <x:c r="A150" s="29" t="str">
+        <x:v>35: R6</x:v>
+      </x:c>
+      <x:c r="B150" s="29" t="str">
+        <x:v>status: 規格/MPN未完整
+unit_price: 1
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 35
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"R6","purpose_zh":"5V 輸出至 U1 FB 的上臂回授電阻；與 R8 決定輸出設定。","purpose_en":"Upper feedback resistor from the 5V output to U1 FB; sets output together with R8.","location_zh":"原理圖第 1 頁：升壓電源","location_en":"Schematic page 1: boost supply","page":1}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠 BOM 與原理圖皆未填阻值。","spec_en":"No resistance is given in the vendor BOM or schematic.","purpose_zh":"R6: 5V 輸出至 U1 FB 的上臂回授電阻；與 R8 決定輸出設定。","purpose_en":"R6: Upper feedback resistor from the 5V output to U1 FB; sets output together with R8.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、功率、容差、溫度係數及最大工作電壓尚未提供。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, power rating, tolerance, temperature coefficient and maximum working voltage are not supplied."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 35</x:v>
+      </x:c>
+      <x:c r="C150" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" ht="208" customHeight="1">
+      <x:c r="A151" s="29" t="str">
+        <x:v>36: R7</x:v>
+      </x:c>
+      <x:c r="B151" s="29" t="str">
+        <x:v>status: 規格/MPN未完整
+unit_price: 1
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 36
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"R7","purpose_zh":"DPS2 充電 LED 的串聯限流電阻。","purpose_en":"Series current-limiting resistor for the DPS2 charging LED.","location_zh":"原理圖第 1 頁：充電狀態顯示","location_en":"Schematic page 1: charger status","page":1}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠 BOM 與原理圖皆未填阻值。","spec_en":"No resistance is given in the vendor BOM or schematic.","purpose_zh":"R7: DPS2 充電 LED 的串聯限流電阻。","purpose_en":"R7: Series current-limiting resistor for the DPS2 charging LED.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、功率、容差、溫度係數及最大工作電壓尚未提供。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, power rating, tolerance, temperature coefficient and maximum working voltage are not supplied."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 36</x:v>
+      </x:c>
+      <x:c r="C151" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" ht="222" customHeight="1">
+      <x:c r="A152" s="29" t="str">
+        <x:v>37: R8</x:v>
+      </x:c>
+      <x:c r="B152" s="29" t="str">
+        <x:v>status: 規格/MPN未完整
+unit_price: 1
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 37
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"R8","purpose_zh":"U1 FB 至 GND 的下臂回授電阻；與 R6 決定輸出設定。","purpose_en":"Lower feedback resistor from U1 FB to ground; sets output together with R6.","location_zh":"原理圖第 1 頁：升壓電源","location_en":"Schematic page 1: boost supply","page":1}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠 BOM 與原理圖皆未填阻值。","spec_en":"No resistance is given in the vendor BOM or schematic.","purpose_zh":"R8: U1 FB 至 GND 的下臂回授電阻；與 R6 決定輸出設定。","purpose_en":"R8: Lower feedback resistor from U1 FB to ground; sets output together with R6.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、功率、容差、溫度係數及最大工作電壓尚未提供。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, power rating, tolerance, temperature coefficient and maximum working voltage are not supplied."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 37</x:v>
+      </x:c>
+      <x:c r="C152" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" ht="236" customHeight="1">
+      <x:c r="A153" s="29" t="str">
+        <x:v>38: R9</x:v>
+      </x:c>
+      <x:c r="B153" s="29" t="str">
+        <x:v>status: 規格/MPN未完整
+unit_price: 1
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 38
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"R9","purpose_zh":"U2 TS 至 GND 的偏壓支路；圖中僅畫電阻，不能宣稱已接電池溫度感測器。","purpose_en":"Bias branch from U2 TS to ground; the drawing only shows a resistor, not a verified battery-temperature sensor.","location_zh":"原理圖第 1 頁：充電 TS","location_en":"Schematic page 1: charger TS","page":1}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠 BOM 與原理圖皆未填阻值。","spec_en":"No resistance is given in the vendor BOM or schematic.","purpose_zh":"R9: U2 TS 至 GND 的偏壓支路；圖中僅畫電阻，不能宣稱已接電池溫度感測器。","purpose_en":"R9: Bias branch from U2 TS to ground; the drawing only shows a resistor, not a verified battery-temperature sensor.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、功率、容差、溫度係數及最大工作電壓尚未提供。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, power rating, tolerance, temperature coefficient and maximum working voltage are not supplied."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 38</x:v>
+      </x:c>
+      <x:c r="C153" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" ht="236" customHeight="1">
+      <x:c r="A154" s="29" t="str">
+        <x:v>39: R10</x:v>
+      </x:c>
+      <x:c r="B154" s="29" t="str">
+        <x:v>status: 規格/MPN未完整
+unit_price: 1
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 39
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"R10","purpose_zh":"系統供電至 U3 P2 的分壓上臂，與 R12/C9 配合；U3 的確切功能未知。","purpose_en":"Upper divider from system supply to U3 P2, used with R12/C9; exact U3 function is unknown.","location_zh":"原理圖第 1 頁：U3 電源控制周邊","location_en":"Schematic page 1: U3 power-control circuitry","page":1}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠 BOM 與原理圖皆未填阻值。","spec_en":"No resistance is given in the vendor BOM or schematic.","purpose_zh":"R10: 系統供電至 U3 P2 的分壓上臂，與 R12/C9 配合；U3 的確切功能未知。","purpose_en":"R10: Upper divider from system supply to U3 P2, used with R12/C9; exact U3 function is unknown.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、功率、容差、溫度係數及最大工作電壓尚未提供。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, power rating, tolerance, temperature coefficient and maximum working voltage are not supplied."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 39</x:v>
+      </x:c>
+      <x:c r="C154" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" ht="208" customHeight="1">
+      <x:c r="A155" s="29" t="str">
+        <x:v>40: R11</x:v>
+      </x:c>
+      <x:c r="B155" s="29" t="str">
+        <x:v>status: 規格/MPN未完整
+unit_price: 1
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 40
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"R11","purpose_zh":"U1 EN／U3 P3 共用節點至 GND 的下拉。","purpose_en":"Pull-down from the common U1 EN / U3 P3 node to ground.","location_zh":"原理圖第 1 頁：電源啟用","location_en":"Schematic page 1: power enable","page":1}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠 BOM 與原理圖皆未填阻值。","spec_en":"No resistance is given in the vendor BOM or schematic.","purpose_zh":"R11: U1 EN／U3 P3 共用節點至 GND 的下拉。","purpose_en":"R11: Pull-down from the common U1 EN / U3 P3 node to ground.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、功率、容差、溫度係數及最大工作電壓尚未提供。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, power rating, tolerance, temperature coefficient and maximum working voltage are not supplied."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 40</x:v>
+      </x:c>
+      <x:c r="C155" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" ht="236" customHeight="1">
+      <x:c r="A156" s="29" t="str">
+        <x:v>41: R12</x:v>
+      </x:c>
+      <x:c r="B156" s="29" t="str">
+        <x:v>status: 規格/MPN未完整
+unit_price: 1
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 41
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"R12","purpose_zh":"U3 P2 至 GND 的分壓下臂，與 R10/C9 配合；U3 的確切功能未知。","purpose_en":"Lower divider from U3 P2 to ground, used with R10/C9; exact U3 function is unknown.","location_zh":"原理圖第 1 頁：U3 電源控制周邊","location_en":"Schematic page 1: U3 power-control circuitry","page":1}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠 BOM 與原理圖皆未填阻值。","spec_en":"No resistance is given in the vendor BOM or schematic.","purpose_zh":"R12: U3 P2 至 GND 的分壓下臂，與 R10/C9 配合；U3 的確切功能未知。","purpose_en":"R12: Lower divider from U3 P2 to ground, used with R10/C9; exact U3 function is unknown.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、功率、容差、溫度係數及最大工作電壓尚未提供。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, power rating, tolerance, temperature coefficient and maximum working voltage are not supplied."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 41</x:v>
+      </x:c>
+      <x:c r="C156" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" ht="236" customHeight="1">
+      <x:c r="A157" s="29" t="str">
+        <x:v>42: R13</x:v>
+      </x:c>
+      <x:c r="B157" s="29" t="str">
+        <x:v>status: 規格/MPN未完整
+unit_price: 1
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 42
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"R13","purpose_zh":"USB-C CC1 至 GND 的下拉電阻。數值未給，不能自行填入典型值。","purpose_en":"USB-C CC1-to-ground pull-down; value is absent and must not be replaced by an assumed typical value.","location_zh":"原理圖第 1 頁：USB-C","location_en":"Schematic page 1: USB-C","page":1}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠 BOM 與原理圖皆未填阻值。","spec_en":"No resistance is given in the vendor BOM or schematic.","purpose_zh":"R13: USB-C CC1 至 GND 的下拉電阻。數值未給，不能自行填入典型值。","purpose_en":"R13: USB-C CC1-to-ground pull-down; value is absent and must not be replaced by an assumed typical value.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、功率、容差、溫度係數及最大工作電壓尚未提供。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, power rating, tolerance, temperature coefficient and maximum working voltage are not supplied."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 42</x:v>
+      </x:c>
+      <x:c r="C157" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" ht="236" customHeight="1">
+      <x:c r="A158" s="29" t="str">
+        <x:v>43: R14</x:v>
+      </x:c>
+      <x:c r="B158" s="29" t="str">
+        <x:v>status: 規格/MPN未完整
+unit_price: 1
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 43
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"R14","purpose_zh":"USB-C CC2 至 GND 的下拉電阻。數值未給，不能自行填入典型值。","purpose_en":"USB-C CC2-to-ground pull-down; value is absent and must not be replaced by an assumed typical value.","location_zh":"原理圖第 1 頁：USB-C","location_en":"Schematic page 1: USB-C","page":1}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠 BOM 與原理圖皆未填阻值。","spec_en":"No resistance is given in the vendor BOM or schematic.","purpose_zh":"R14: USB-C CC2 至 GND 的下拉電阻。數值未給，不能自行填入典型值。","purpose_en":"R14: USB-C CC2-to-ground pull-down; value is absent and must not be replaced by an assumed typical value.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、功率、容差、溫度係數及最大工作電壓尚未提供。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, power rating, tolerance, temperature coefficient and maximum working voltage are not supplied."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 43</x:v>
+      </x:c>
+      <x:c r="C158" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" ht="166" customHeight="1">
+      <x:c r="A159" s="29" t="str">
+        <x:v>44: R15,R28,R35</x:v>
+      </x:c>
+      <x:c r="B159" s="29" t="str">
+        <x:v>status: 依廠商BOM，封裝/容差仍需確認
+unit_price: 1
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 44
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"R15","purpose_zh":"ESP_EN 至 3V3_DIG 的上拉。","purpose_en":"Pull-up from ESP_EN to 3V3_DIG.","location_zh":"原理圖第 2 頁：ESP32 復位","location_en":"Schematic page 2: ESP32 reset","page":2},{"reference":"R28","purpose_zh":"U7 SHDN 至 Vin／3V3_ANA 的上拉。","purpose_en":"Pull-up from U7 SHDN to Vin / 3V3_ANA.","location_zh":"原理圖第 2 頁：2V5_REF","location_en":"Schematic page 2: 2V5_REF","page":2},{"reference":"R35","purpose_zh":"U9 DIN 至 3V3_DIG 的上拉，用於原圖標示的三線 CS 模式設定。","purpose_en":"DIN-to-3V3_DIG pull-up for the three-wire CS-mode configuration labelled in the schematic.","location_zh":"原理圖第 2</x:v>
+      </x:c>
+      <x:c r="C159" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" ht="152" customHeight="1">
+      <x:c r="A160" s="29" t="str">
+        <x:v>44: R15,R28,R35 (continued)</x:v>
+      </x:c>
+      <x:c r="B160" s="29" t="str">
+        <x:v> 頁：ADC","location_en":"Schematic page 2: ADC","page":2}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠標稱阻值 10k。","spec_en":"Vendor nominal resistance: 10k.","purpose_zh":"R15: ESP_EN 至 3V3_DIG 的上拉。；R28: U7 SHDN 至 Vin／3V3_ANA 的上拉。；R35: U9 DIN 至 3V3_DIG 的上拉，用於原圖標示的三線 CS 模式設定。","purpose_en":"R15: Pull-up from ESP_EN to 3V3_DIG.；R28: Pull-up from U7 SHDN to Vin / 3V3_ANA.；R35: DIN-to-3V3_DIG pull-up for the three-wire CS-mode configuration labelled in the schematic.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、功率、容差、溫度係數及最大工作電壓尚未提供。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, power rating, tolerance, temperature coefficient and maximum working voltage are not supplied."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 44</x:v>
+      </x:c>
+      <x:c r="C160" s="29" t="str"/>
+    </x:row>
+    <x:row r="161" ht="264" customHeight="1">
+      <x:c r="A161" s="29" t="str">
+        <x:v>45: R16,R21,R24,R29,R30,R31,R3
+6</x:v>
+      </x:c>
+      <x:c r="B161" s="29" t="str">
+        <x:v>status: 依廠商BOM，封裝/容差仍需確認
+unit_price: 1
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 45
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"R16","purpose_zh":"D1 藍光 LED 的 5V 串聯限流電阻。","purpose_en":"5V series current-limiting resistor for blue LED D1.","location_zh":"原理圖第 2 頁：LEDs","location_en":"Schematic page 2: LEDs","page":2},{"reference":"R21","purpose_zh":"D2 藍光 LED 的 5V 串聯限流電阻。","purpose_en":"5V series current-limiting resistor for blue LED D2.","location_zh":"原理圖第 2 頁：LEDs","location_en":"Schematic page 2: LEDs","page":2},{"reference":"R24","purpose_zh":"D3 藍光 LED 的 5V 串聯限流電阻。","purpose_en":"5V series current-limiting resistor for blue LED D3.","location_zh":"原理圖第 2 頁：LEDs","location_en":"Schematic page 2: LEDs","page":2},{"reference":"R29","purpose_zh":"U8 輸出至 ADC_AINP 的串聯隔離／濾波电阻。","purpose_en":"Series isolation/filtering resistor from U8 output to ADC_AINP.","location_zh":"原理圖第 2 頁：TIA／ADC","location_en":"Schematic page 2: TIA / ADC","page":2},{"reference":"R30","purpose_zh":"D4 藍光 LED 的 5V 串聯限流電阻。","purpose_en":"5V series current-limiting resistor for blue LED D4.","location_zh":"原理圖第 2 頁：LEDs","location_en":"Schematic page 2: LEDs","page":2},{"reference":"R31","purpose_zh":"3V3_ANA 至 U8 局部供電的串聯濾波電阻，搭配 C25/C26。","purpose_en":"Series supply-filter resistor from 3V3_ANA to the U8 local supply, used with C25/C26.","location_zh":"原理圖第 2 頁：TIA</x:v>
+      </x:c>
+      <x:c r="C161" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" ht="264" customHeight="1">
+      <x:c r="A162" s="29" t="str">
+        <x:v>45: R16,R21,R24,R29,R30,R31,R3
+6 (continued)</x:v>
+      </x:c>
+      <x:c r="B162" s="29" t="str">
+        <x:v> 供電","location_en":"Schematic page 2: TIA supply","page":2},{"reference":"R36","purpose_zh":"ADC_AINN 至 GND 的串聯電阻，搭配 R29/C24 的輸入網路。","purpose_en":"Series resistor from ADC_AINN to ground in the R29/C24 input network.","location_zh":"原理圖第 2 頁：TIA／ADC","location_en":"Schematic page 2: TIA / ADC","page":2}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠標稱阻值 100R。","spec_en":"Vendor nominal resistance: 100R.","purpose_zh":"R16: D1 藍光 LED 的 5V 串聯限流電阻。；R21: D2 藍光 LED 的 5V 串聯限流電阻。；R24: D3 藍光 LED 的 5V 串聯限流電阻。；R29: U8 輸出至 ADC_AINP 的串聯隔離／濾波电阻。；R30: D4 藍光 LED 的 5V 串聯限流電阻。；R31: 3V3_ANA 至 U8 局部供電的串聯濾波電阻，搭配 C25/C26。；R36: ADC_AINN 至 GND 的串聯電阻，搭配 R29/C24 的輸入網路。","purpose_en":"R16: 5V series current-limiting resistor for blue LED D1.；R21: 5V series current-limiting resistor for blue LED D2.；R24: 5V series current-limiting resistor for blue LED D3.；R29: Series isolation/filtering resistor from U8 output to ADC_AINP.；R30: 5V series current-limiting resistor for blue LED D4.；R31: Series supply-filter resistor from 3V3_ANA to the U8 local supply, used with C25/C26.；R36: Series resistor from ADC_AINN to ground in the R29/C24 input network.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、功率、容差、溫度係數及最大工作電壓尚未提供。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, power rating, tolerance, temperature coefficient and maximum working voltage are not supplied."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 45</x:v>
+      </x:c>
+      <x:c r="C162" s="29" t="str"/>
+    </x:row>
+    <x:row r="163" ht="180" customHeight="1">
+      <x:c r="A163" s="29" t="str">
+        <x:v>46: R17,R22,R25,R32</x:v>
+      </x:c>
+      <x:c r="B163" s="29" t="str">
+        <x:v>status: 依廠商BOM，封裝/容差仍需確認
+unit_price: 1
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 46
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"R17","purpose_zh":"LED1_GATE 至 Q1 閘極的串聯電阻。","purpose_en":"Series resistor from LED1_GATE to the Q1 gate.","location_zh":"原理圖第 2 頁：LEDs","location_en":"Schematic page 2: LEDs","page":2},{"reference":"R22","purpose_zh":"LED2_GATE 至 Q2 閘極的串聯電阻。","purpose_en":"Series resistor from LED2_GATE to the Q2 gate.","location_zh":"原理圖第 2 頁：LEDs","location_en":"Schematic page 2: LEDs","page":2},{"reference":"R25","purpose_zh":"LED3_GATE 至 Q3 閘極的串聯電阻。","purpose_en":"Series resistor from LED3_GATE to the Q3 gate.","location_zh":"原理圖第 2 頁：LEDs","location_en":"Schematic page 2: LEDs","page":2},{"reference":"R32","purpose_zh":"LED4_GATE 至 Q4 閘極的串聯電阻。","purpose_en":"Series resistor from LED4_GATE to</x:v>
+      </x:c>
+      <x:c r="C163" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" ht="166" customHeight="1">
+      <x:c r="A164" s="29" t="str">
+        <x:v>46: R17,R22,R25,R32 (continued)</x:v>
+      </x:c>
+      <x:c r="B164" s="29" t="str">
+        <x:v> the Q4 gate.","location_zh":"原理圖第 2 頁：LEDs","location_en":"Schematic page 2: LEDs","page":2}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠標稱阻值 220R。","spec_en":"Vendor nominal resistance: 220R.","purpose_zh":"R17: LED1_GATE 至 Q1 閘極的串聯電阻。；R22: LED2_GATE 至 Q2 閘極的串聯電阻。；R25: LED3_GATE 至 Q3 閘極的串聯電阻。；R32: LED4_GATE 至 Q4 閘極的串聯電阻。","purpose_en":"R17: Series resistor from LED1_GATE to the Q1 gate.；R22: Series resistor from LED2_GATE to the Q2 gate.；R25: Series resistor from LED3_GATE to the Q3 gate.；R32: Series resistor from LED4_GATE to the Q4 gate.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、功率、容差、溫度係數及最大工作電壓尚未提供。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, power rating, tolerance, temperature coefficient and maximum working voltage are not supplied."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 46</x:v>
+      </x:c>
+      <x:c r="C164" s="29" t="str"/>
+    </x:row>
+    <x:row r="165" ht="180" customHeight="1">
+      <x:c r="A165" s="29" t="str">
+        <x:v>47: R20,R23,R26,R33</x:v>
+      </x:c>
+      <x:c r="B165" s="29" t="str">
+        <x:v>status: 依廠商BOM，封裝/容差仍需確認
+unit_price: 1
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 47
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"R20","purpose_zh":"Q1 閘極至源極／GND 的下拉。","purpose_en":"Pull-down from the Q1 gate to its source / ground.","location_zh":"原理圖第 2 頁：LEDs","location_en":"Schematic page 2: LEDs","page":2},{"reference":"R23","purpose_zh":"Q2 閘極至源極／GND 的下拉。","purpose_en":"Pull-down from the Q2 gate to its source / ground.","location_zh":"原理圖第 2 頁：LEDs","location_en":"Schematic page 2: LEDs","page":2},{"reference":"R26","purpose_zh":"Q3 閘極至源極／GND 的下拉。","purpose_en":"Pull-down from the Q3 gate to its source / ground.","location_zh":"原理圖第 2 頁：LEDs","location_en":"Schematic page 2: LEDs","page":2},{"reference":"R33","purpose_zh":"Q4 閘極至源極／GND 的下拉。","purpose_en":"Pull-down from the Q4 gate to its</x:v>
+      </x:c>
+      <x:c r="C165" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" ht="180" customHeight="1">
+      <x:c r="A166" s="29" t="str">
+        <x:v>47: R20,R23,R26,R33 (continued)</x:v>
+      </x:c>
+      <x:c r="B166" s="29" t="str">
+        <x:v> source / ground.","location_zh":"原理圖第 2 頁：LEDs","location_en":"Schematic page 2: LEDs","page":2}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠標稱阻值 100k。","spec_en":"Vendor nominal resistance: 100k.","purpose_zh":"R20: Q1 閘極至源極／GND 的下拉。；R23: Q2 閘極至源極／GND 的下拉。；R26: Q3 閘極至源極／GND 的下拉。；R33: Q4 閘極至源極／GND 的下拉。","purpose_en":"R20: Pull-down from the Q1 gate to its source / ground.；R23: Pull-down from the Q2 gate to its source / ground.；R26: Pull-down from the Q3 gate to its source / ground.；R33: Pull-down from the Q4 gate to its source / ground.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、功率、容差、溫度係數及最大工作電壓尚未提供。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, power rating, tolerance, temperature coefficient and maximum working voltage are not supplied."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 47</x:v>
+      </x:c>
+      <x:c r="C166" s="29" t="str"/>
+    </x:row>
+    <x:row r="167" ht="264" customHeight="1">
+      <x:c r="A167" s="29" t="str">
+        <x:v>48: R27</x:v>
+      </x:c>
+      <x:c r="B167" s="29" t="str">
+        <x:v>status: 依廠商BOM，封裝/容差仍需確認
+unit_price: 30
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 48
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"R27","purpose_zh":"U8 輸出至反相輸入的跨阻回授電阻，將 PD 光電流轉成電壓；與 C21 並聯。","purpose_en":"Transimpedance feedback from U8 output to its inverting input, converting PD photocurrent to voltage; in parallel with C21.","location_zh":"原理圖第 2 頁：TIA","location_en":"Schematic page 2: TIA","page":2}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠標稱阻值 100M。","spec_en":"Vendor nominal resistance: 100M.","purpose_zh":"R27: U8 輸出至反相輸入的跨阻回授電阻，將 PD 光電流轉成電壓；與 C21 並聯。","purpose_en":"R27: Transimpedance feedback from U8 output to its inverting input, converting PD photocurrent to voltage; in parallel with C21.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、功率、容差、溫度係數及最大工作電壓尚未提供。 100 MΩ 回授需另核對漏電、清潔／濕度敏感度與雜訊；不可僅凭阻值任選。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, power rating, tolerance, temperature coefficient and maximum working voltage are not supplied. The 100 MΩ feedback also requires leakage, cleaning/humidity and noise review; resistance alone is insufficient."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 48</x:v>
+      </x:c>
+      <x:c r="C167" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" ht="236" customHeight="1">
+      <x:c r="A168" s="29" t="str">
+        <x:v>49: R34</x:v>
+      </x:c>
+      <x:c r="B168" s="29" t="str">
+        <x:v>status: 依廠商BOM，封裝/容差仍需確認
+unit_price: 5
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 49
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"R34","purpose_zh":"與 C28 串聯接於 VREF_2V5 至 GND 旁路支路；不是電流感測電阻，也非串在 ADC 訊號線中。","purpose_en":"In series with C28 in the VREF_2V5-to-ground bypass branch; not a current-sense resistor or series ADC-signal resistor.","location_zh":"原理圖第 2 頁：ADC 參考","location_en":"Schematic page 2: ADC reference","page":2}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠標稱阻值 0.1R。","spec_en":"Vendor nominal resistance: 0.1R.","purpose_zh":"R34: 與 C28 串聯接於 VREF_2V5 至 GND 旁路支路；不是電流感測電阻，也非串在 ADC 訊號線中。","purpose_en":"R34: In series with C28 in the VREF_2V5-to-ground bypass branch; not a current-sense resistor or series ADC-signal resistor.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、功率、容差、溫度係數及最大工作電壓尚未提供。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, power rating, tolerance, temperature coefficient and maximum working voltage are not supplied."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 49</x:v>
+      </x:c>
+      <x:c r="C168" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" ht="264" customHeight="1">
+      <x:c r="A169" s="29" t="str">
+        <x:v>50: R37,R38</x:v>
+      </x:c>
+      <x:c r="B169" s="29" t="str">
+        <x:v>status: 依廠商BOM，封裝/容差仍需確認
+unit_price: 1
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 50
+source_ids: ["vendor_BOM","schematic"]
+per_reference: [{"reference":"R37","purpose_zh":"ESP32 ADC_SCLK 至 U9 SCLK 的串聯電阻。","purpose_en":"Series resistor from ESP32 ADC_SCLK to U9 SCLK.","location_zh":"原理圖第 2 頁：ADC 數位介面","location_en":"Schematic page 2: ADC digital interface","page":2},{"reference":"R38","purpose_zh":"ESP32 ADC_CONVST 至 U9 CONVST 的串聯電阻。","purpose_en":"Series resistor from ESP32 ADC_CONVST to U9 CONVST.","location_zh":"原理圖第 2 頁：ADC 數位介面","location_en":"Schematic page 2: ADC digital interface","page":2}]
+orderability: incomplete_passive_specification
+details: {"spec_zh":"原廠標稱阻值 47R。","spec_en":"Vendor nominal resistance: 47R.","purpose_zh":"R37: ESP32 ADC_SCLK 至 U9 SCLK 的串聯電阻。；R38: ESP32 ADC_CONVST 至 U9 CONVST 的串聯電阻。","purpose_en":"R37: Series resistor from ESP32 ADC_SCLK to U9 SCLK.；R38: Series resistor from ESP32 ADC_CONVST to U9 CONVST.","missing_zh":"廠牌／完整料號、封裝尺寸與高度、功率、容差、溫度係數及最大工作電壓尚未提供。","missing_en":"Manufacturer/orderable MPN, case dimensions/height, power rating, tolerance, temperature coefficient and maximum working voltage are not supplied."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 50</x:v>
+      </x:c>
+      <x:c r="C169" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" ht="208" customHeight="1">
+      <x:c r="A170" s="29" t="str">
+        <x:v>51: SW1</x:v>
+      </x:c>
+      <x:c r="B170" s="29" t="str">
+        <x:v>status: 規格/MPN未完整
+unit_price: 15
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 51
+source_ids: ["vendor_BOM","schematic"]
+per_reference: []
+orderability: incomplete_component_specification
+details: {"spec_zh":"原圖三接點 COMM/B/A；COMM 接系統供電，B 經 R4 接 EN，A 未接。","spec_en":"Three schematic contacts COMM/B/A; COMM is at system supply, B connects through R4 to EN, and A is unconnected.","purpose_zh":"切換 U1 升壓啟用控制；不能據此宣稱切斷 USB 充電器或所有電池電流。","purpose_en":"Switches the U1 boost-enable control; it does not establish isolation of the USB charger or all battery current.","missing_zh":"MPN、實體型式、封裝／操作柄位置與行程、額定值及開孔尺寸未提供。","missing_en":"MPN, physical type, footprint/actuator position and travel, ratings and panel opening are unspecified."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 51</x:v>
+      </x:c>
+      <x:c r="C170" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" ht="180" customHeight="1">
+      <x:c r="A171" s="29" t="str">
+        <x:v>52: SW2,SW3</x:v>
+      </x:c>
+      <x:c r="B171" s="29" t="str">
+        <x:v>status: 規格/MPN未完整
+unit_price: 5
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 52
+source_ids: ["vendor_BOM","schematic"]
+per_reference: []
+orderability: incomplete_component_specification
+details: {"spec_zh":"SW2、SW3；原圖按下時將各訊號接 GND。","spec_en":"SW2 and SW3; each grounds its respective signal when pressed.","purpose_zh":"SW2：ESP_EN 復位；SW3：ESP_IO0 啟動／下載模式選擇。","purpose_en":"SW2: ESP_EN reset; SW3: ESP_IO0 boot/download-mode selection.","missing_zh":"完整MPN、接點規格、封裝尺寸／按壓高度／方向、操作力與壽命未提供。","missing_en":"MPN, contact rating, footprint/actuation height/direction, force and life are unspecified."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 52</x:v>
+      </x:c>
+      <x:c r="C171" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" ht="208" customHeight="1">
+      <x:c r="A172" s="29" t="str">
+        <x:v>53: U1</x:v>
+      </x:c>
+      <x:c r="B172" s="29" t="str">
+        <x:v>status: 依廠商BOM，封裝/容差仍需確認
+unit_price: 52
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 53
+source_ids: ["vendor_BOM","schematic","TI_TPS61023"]
+per_reference: []
+orderability: identified_part_pending_assembly_verification
+details: {"spec_zh":"TI TPS61023；6-pin SOT-563 (DRL)。3.7 A 指開關電流限制，不能當作5 V輸出額定電流。","spec_en":"TI TPS61023; 6-pin SOT-563 (DRL). The 3.7 A figure is a switch-current limit, not a 5 V output-current rating.","purpose_zh":"將充電器 OUT／電池系統供電升壓至圖示5V軌，供 LED 與後級 LDO。","purpose_en":"Boosts the charger OUT / battery-system supply to the rail labelled 5V for LEDs and downstream LDOs.","missing_zh":"完整訂購後綴、L1/C2–C5/R6/R8 等值未完整提供；5V設定、穩定度及風扇可用電流須廠商驗證。","missing_en":"Full ordering suffix and L1/C2–C5/R6/R8 values are incomplete; vendor must validate the 5V setting, stability and available fan current."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 53</x:v>
+      </x:c>
+      <x:c r="C172" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" ht="208" customHeight="1">
+      <x:c r="A173" s="29" t="str">
+        <x:v>54: U2</x:v>
+      </x:c>
+      <x:c r="B173" s="29" t="str">
+        <x:v>status: 依廠商BOM，封裝/容差仍需確認
+unit_price: 88
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 54
+source_ids: ["vendor_BOM","schematic","TI_BQ24074"]
+per_reference: []
+orderability: identified_part_pending_assembly_verification
+details: {"spec_zh":"TI BQ24074；4.2 V 單節 Li-ion/Li-poly 充電器；16-pin VQFN (RGT)，3×3 mm。","spec_en":"TI BQ24074; 4.2 V single-cell Li-ion/Li-poly charger; 16-pin VQFN (RGT), 3×3 mm.","purpose_zh":"接 USB 5V_USB、BAT 電池與 OUT 系統供電；OUT 不是已調節的5 V升壓輸出。","purpose_en":"Interfaces USB 5V_USB, the BAT battery node and OUT system supply; OUT is not the regulated 5V boost output.","missing_zh":"完整訂購後綴、R1/R2/R3/R9 及電池／散熱配置未定；不可將器件1.5 A能力當作本板已設定充電電流。","missing_en":"Full ordering suffix, R1/R2/R3/R9, cell and thermal configuration remain incomplete; the device 1.5 A capability is not the configured board charging current."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 54</x:v>
+      </x:c>
+      <x:c r="C173" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" ht="194" customHeight="1">
+      <x:c r="A174" s="29" t="str">
+        <x:v>55: U3</x:v>
+      </x:c>
+      <x:c r="B174" s="29" t="str">
+        <x:v>status: 規格/MPN未完整
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 55
+source_ids: ["vendor_BOM","schematic"]
+per_reference: []
+orderability: unidentified_component
+details: {"spec_zh":"原廠僅有 U3、P1–P6；無型號或功能名稱。","spec_en":"Only U3 and P1–P6 are provided; no MPN or functional identity.","purpose_zh":"P1 接系統供電、P5 接 GND、P2 接 R10/R12/C9、P3 接升壓 EN，P4/P6 各接電容至GND。功能必須由廠商確認。","purpose_en":"P1 connects to system supply, P5 to ground, P2 to R10/R12/C9, P3 to boost EN, and P4/P6 each to a capacitor to ground. Vendor identification is required.","missing_zh":"IC 類型、完整MPN、供電／輸出額定值、腳位定義、封裝與周邊值皆未定；不能指定替代料。","missing_en":"IC type, MPN, supply/output ratings, pin functions, package and external values are unknown; no substitute can be specified."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 55</x:v>
+      </x:c>
+      <x:c r="C174" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" ht="222" customHeight="1">
+      <x:c r="A175" s="29" t="str">
+        <x:v>56: U4</x:v>
+      </x:c>
+      <x:c r="B175" s="29" t="str">
+        <x:v>status: 依廠商BOM，封裝/容差仍需確認
+unit_price: 181
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 56
+source_ids: ["vendor_BOM","schematic","ESPRESSIF_32E"]
+per_reference: []
+orderability: identified_part_pending_assembly_verification
+details: {"spec_zh":"Espressif ESP32-WROOM-32E；2.4 GHz 無線、3.3 V 系統模組；32E 為板載 PCB 天線版本。","spec_en":"Espressif ESP32-WROOM-32E; 2.4 GHz wireless module for a 3.3 V system; 32E uses an onboard PCB antenna.","purpose_zh":"控制四路 LED、讀取 ADS8866 並提供網路介面；原圖 UART 在 J3。","purpose_en":"Controls four LED channels, reads ADS8866 and provides networking; schematic UART is available at J3.","missing_zh":"需確認完整容量／溫度等訂購後綴、實際焊接高度與天線禁布／外殼空間；不要把32E誤當具外接天線座的32UE。","missing_en":"Confirm the full flash/temperature ordering variant, assembled height and antenna keepout/enclosure clearance; do not confuse 32E with the external-antenna-connector 32UE."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 56</x:v>
+      </x:c>
+      <x:c r="C175" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" ht="208" customHeight="1">
+      <x:c r="A176" s="29" t="str">
+        <x:v>57: U5</x:v>
+      </x:c>
+      <x:c r="B176" s="29" t="str">
+        <x:v>status: 依廠商BOM，封裝/容差仍需確認
+unit_price: 10
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 57
+source_ids: ["vendor_BOM","schematic","ECMOS_EC50117"]
+per_reference: []
+orderability: identified_part_pending_assembly_verification
+details: {"spec_zh":"E-CMOS EC50117KBG；官方訂購表確認固定3.3 V、SOT-223；系列標稱1 A能力。","spec_en":"E-CMOS EC50117KBG; manufacturer ordering table identifies fixed 3.3 V, SOT-223; series nominal 1 A capability.","purpose_zh":"5V 輸入轉為 3V3_DIG，供 ESP32 與數位電路。","purpose_en":"Converts the 5V input to 3V3_DIG for ESP32 and digital circuitry.","missing_zh":"實際可用電流取決於壓差、PCB散熱與負載；須核對 C17/C18 型式、穩定性與組裝封裝，不能宣稱本板可持續供1 A。","missing_en":"Available current depends on dropout, PCB cooling and load; verify C17/C18 type, stability and assembled package. Continuous 1 A board output is not established."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 57</x:v>
+      </x:c>
+      <x:c r="C176" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" ht="208" customHeight="1">
+      <x:c r="A177" s="29" t="str">
+        <x:v>58: U6</x:v>
+      </x:c>
+      <x:c r="B177" s="29" t="str">
+        <x:v>status: 依廠商BOM，封裝/容差仍需確認
+unit_price: 24
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 58
+source_ids: ["vendor_BOM","schematic","TI_LP5907"]
+per_reference: []
+orderability: identified_part_pending_assembly_verification
+details: {"spec_zh":"TI LP5907MFX-3.3/NOPB；固定3.3 V、250 mA 器件額定能力；5-pin SOT-23 (DBV)。","spec_en":"TI LP5907MFX-3.3/NOPB; fixed 3.3 V, 250 mA device capability; 5-pin SOT-23 (DBV).","purpose_zh":"將5V轉為3V3_ANA，供類比前端、ADC類比電源及參考電壓IC；EN 接輸入。","purpose_en":"Generates 3V3_ANA from 5V for the analog front end, ADC analog supply and reference IC; EN is tied to input.","missing_zh":"須核對C19/C20有效容值、穩定性、熱耗散與封裝焊盘；額定250 mA不是全系統驗證結果。","missing_en":"Verify effective C19/C20 capacitance, stability, dissipation and footprint; the 250 mA rating is not a whole-system validation result."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 58</x:v>
+      </x:c>
+      <x:c r="C177" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" ht="208" customHeight="1">
+      <x:c r="A178" s="29" t="str">
+        <x:v>59: U7</x:v>
+      </x:c>
+      <x:c r="B178" s="29" t="str">
+        <x:v>status: 依廠商BOM，封裝/容差仍需確認
+unit_price: 628
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 59
+source_ids: ["vendor_BOM","schematic","ADI_LTC6655"]
+per_reference: []
+orderability: identified_part_pending_assembly_verification
+details: {"spec_zh":"Analog Devices LTC6655BHMS8-2.5#PBF；2.5 V 輸出、8-pin MSOP。","spec_en":"Analog Devices LTC6655BHMS8-2.5#PBF; 2.5 V output, 8-pin MSOP.","purpose_zh":"由3V3_ANA產生VREF_2V5，供U9 ADC参考；SHDN經R28上拉，輸出force/sense腳於圖中相接。","purpose_en":"Generates VREF_2V5 from 3V3_ANA for U9; SHDN is pulled up by R28 and output force/sense pins are joined in the schematic.","missing_zh":"須核對C22/C23型式、負載／穩定性、佈線與ADC實際參考電壓；不可把名義2.5 V當作已校準量測。","missing_en":"Verify C22/C23 type, load/stability, layout and measured ADC reference voltage; nominal 2.5 V is not a calibrated measurement."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 59</x:v>
+      </x:c>
+      <x:c r="C178" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" ht="208" customHeight="1">
+      <x:c r="A179" s="29" t="str">
+        <x:v>60: U8</x:v>
+      </x:c>
+      <x:c r="B179" s="29" t="str">
+        <x:v>status: 依廠商BOM，封裝/容差仍需確認
+unit_price: 226
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 60
+source_ids: ["vendor_BOM","schematic","TI_LMP7721"]
+per_reference: []
+orderability: identified_part_pending_assembly_verification
+details: {"spec_zh":"TI LMP7721；單運算放大器、8-pin SOIC (D)，供電範圍1.8–5.5 V。","spec_en":"TI LMP7721; single amplifier, 8-pin SOIC (D), 1.8–5.5 V supply range.","purpose_zh":"U8以R27=100 MΩ／C21=2.2 pF跨阻回授讀取D5；非反相端接GND，供電經R31/C25/C26濾波。","purpose_en":"U8 reads D5 using R27=100 MΩ / C21=2.2 pF transimpedance feedback; its non-inverting input is grounded and supply is filtered by R31/C25/C26.","missing_zh":"完整訂購後綴、實際封裝與低漏電佈線／清潔、穩定性和接近地電位輸出範圍需驗證；此表不等於TIA性能驗證。","missing_en":"Confirm full ordering suffix, package, low-leakage layout/cleanliness, stability and near-ground output range; this BOM is not TIA performance validation."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 60</x:v>
+      </x:c>
+      <x:c r="C179" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" ht="208" customHeight="1">
+      <x:c r="A180" s="29" t="str">
+        <x:v>61: U9</x:v>
+      </x:c>
+      <x:c r="B180" s="29" t="str">
+        <x:v>status: 依廠商BOM，封裝/容差仍需確認
+unit_price: 306
+source: NTHU_TEST_BOARD_BOM.docx vendor table row 61
+source_ids: ["vendor_BOM","schematic","TI_ADS8866"]
+per_reference: []
+orderability: identified_part_pending_assembly_verification
+details: {"spec_zh":"TI ADS8866IDGS；16-bit、100 kSPS 器件上限，10-pin VSSOP (DGS)；外接參考。","spec_en":"TI ADS8866IDGS; 16-bit, 100 kSPS device limit, 10-pin VSSOP (DGS); external reference.","purpose_zh":"取樣TIA輸出；AVDD=3V3_ANA、DVDD=3V3_DIG、REF=VREF_2V5；SCLK/DOUT/CONVST接ESP32。","purpose_en":"Samples TIA output; AVDD=3V3_ANA, DVDD=3V3_DIG, REF=VREF_2V5; SCLK/DOUT/CONVST interface to ESP32.","missing_zh":"需確認實際取樣率／時序、ADC輸入建立時間與雜訊、參考與電源去耦；100 kSPS不是目前韌體已驗證的取樣性能。","missing_en":"Verify actual sampling/timing, input settling/noise and reference/supply decoupling; 100 kSPS is not verified current firmware performance."}
+original_source: NTHU_TEST_BOARD_BOM.docx vendor table row 61</x:v>
+      </x:c>
+      <x:c r="C180" s="29" t="str">
+        <x:v>Original vendor/source fields; active estimate and missing specifications remain on PCB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" ht="30" customHeight="1">
+      <x:c r="A181" s="36" t="str">
+        <x:v>Print geometry and file identity</x:v>
+      </x:c>
+      <x:c r="B181" s="36" t="str"/>
+      <x:c r="C181" s="36" t="str"/>
+    </x:row>
+    <x:row r="182" ht="110" customHeight="1">
+      <x:c r="A182" s="29" t="str">
+        <x:v>01_base_BLACK.stl</x:v>
+      </x:c>
+      <x:c r="B182" s="29" t="str">
+        <x:v>Batch: P1
+Triangles: 7248; connected components: 1; watertight edges: true
+Mesh volume: 78.13914674155713 cm3
+Assembly minimum: -54, -56, 0 mm
+Assembly maximum: 54, 52, 43.29999923706055 mm
+Size: 108, 108, 43.29999923706055 mm
+Degenerate triangles removed in original export: 0</x:v>
+      </x:c>
+      <x:c r="C182" s="29" t="str">
+        <x:v>SHA256: dd90fa4a126e02d6523114ea447e4f24aaf27826d7a456a111bd6cf6feee2b22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183" ht="110" customHeight="1">
+      <x:c r="A183" s="29" t="str">
+        <x:v>02_black_hood_BLACK.stl</x:v>
+      </x:c>
+      <x:c r="B183" s="29" t="str">
+        <x:v>Batch: P2
+Triangles: 1976; connected components: 1; watertight edges: true
+Mesh volume: 28.76661897830055 cm3
+Assembly minimum: -54, -56, 40.79999923706055 mm
+Assembly maximum: 54, 52, 64 mm
+Size: 108, 108, 23.200000762939453 mm
+Degenerate triangles removed in original export: 0</x:v>
+      </x:c>
+      <x:c r="C183" s="29" t="str">
+        <x:v>SHA256: c45b0cded88cfa45070e5f04c933d58ffb0aead62d7ea7d8899ca5c906f7f557</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184" ht="110" customHeight="1">
+      <x:c r="A184" s="29" t="str">
+        <x:v>03_gas_lid_BLACK.stl</x:v>
+      </x:c>
+      <x:c r="B184" s="29" t="str">
+        <x:v>Batch: P2
+Triangles: 3372; connected components: 1; watertight edges: true
+Mesh volume: 29.53238239220095 cm3
+Assembly minimum: -54, -56, 57.900001525878906 mm
+Assembly maximum: 54, 52, 66 mm
+Size: 108, 108, 8.099998474121094 mm
+Degenerate triangles removed in original export: 2</x:v>
+      </x:c>
+      <x:c r="C184" s="29" t="str">
+        <x:v>SHA256: eb1af20eb3458d72ddc2b2a70a6b206e97616f6d677a2dc703a870ec99c691dd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185" ht="110" customHeight="1">
+      <x:c r="A185" s="29" t="str">
+        <x:v>04_well_NE_CLEAR.stl</x:v>
+      </x:c>
+      <x:c r="B185" s="29" t="str">
+        <x:v>Batch: P3
+Triangles: 40; connected components: 1; watertight edges: true
+Mesh volume: 0.11564499290465757 cm3
+Assembly minimum: 0.7999992370605469, 0.75, 42.5 mm
+Assembly maximum: 6.5, 5.25, 55.5 mm
+Size: 5.700000762939453, 4.5, 13 mm
+Degenerate triangles removed in original export: 0</x:v>
+      </x:c>
+      <x:c r="C185" s="29" t="str">
+        <x:v>SHA256: b349bc6ee902d8bdb5c7e42d39c7ebe928e01e4c2a883a2d869645bee29c86c7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186" ht="110" customHeight="1">
+      <x:c r="A186" s="29" t="str">
+        <x:v>05_well_NW_CLEAR.stl</x:v>
+      </x:c>
+      <x:c r="B186" s="29" t="str">
+        <x:v>Batch: P3
+Triangles: 40; connected components: 1; watertight edges: true
+Mesh volume: 0.1156449929046576 cm3
+Assembly minimum: -6.5, 0.75, 42.5 mm
+Assembly maximum: -0.7999992370605469, 5.25, 55.5 mm
+Size: 5.700000762939453, 4.5, 13 mm
+Degenerate triangles removed in original export: 0</x:v>
+      </x:c>
+      <x:c r="C186" s="29" t="str">
+        <x:v>SHA256: c4d0085d0fd145611bef334bfc3ec3b513f1340f9608a29822ac0ccd709bb790</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" ht="110" customHeight="1">
+      <x:c r="A187" s="29" t="str">
+        <x:v>06_well_SW_CLEAR.stl</x:v>
+      </x:c>
+      <x:c r="B187" s="29" t="str">
+        <x:v>Batch: P3
+Triangles: 40; connected components: 1; watertight edges: true
+Mesh volume: 0.11564499290465756 cm3
+Assembly minimum: -6.5, -5.25, 42.5 mm
+Assembly maximum: -0.7999992370605469, -0.75, 55.5 mm
+Size: 5.700000762939453, 4.5, 13 mm
+Degenerate triangles removed in original export: 0</x:v>
+      </x:c>
+      <x:c r="C187" s="29" t="str">
+        <x:v>SHA256: fec68336b7a5b404f66f46e0a54f6d66ed84ff590e85e4793ce028ff90a10fb2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188" ht="110" customHeight="1">
+      <x:c r="A188" s="29" t="str">
+        <x:v>07_well_SE_CLEAR.stl</x:v>
+      </x:c>
+      <x:c r="B188" s="29" t="str">
+        <x:v>Batch: P3
+Triangles: 40; connected components: 1; watertight edges: true
+Mesh volume: 0.11564499290465757 cm3
+Assembly minimum: 0.7999992370605469, -5.25, 42.5 mm
+Assembly maximum: 6.5, -0.75, 55.5 mm
+Size: 5.700000762939453, 4.5, 13 mm
+Degenerate triangles removed in original export: 0</x:v>
+      </x:c>
+      <x:c r="C188" s="29" t="str">
+        <x:v>SHA256: 64930ddaca73a7cfd28599e3525a9e77f26db9e8bbb255e126343b579945a363</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189" ht="110" customHeight="1">
+      <x:c r="A189" s="29" t="str">
+        <x:v>08_gas_compression_plate_B
+LACK.stl</x:v>
+      </x:c>
+      <x:c r="B189" s="29" t="str">
+        <x:v>Batch: P2
+Triangles: 92; connected components: 1; watertight edges: true
+Mesh volume: 0.37824025512696247 cm3
+Assembly minimum: -10, -9, 56.099998474121094 mm
+Assembly maximum: 10, 9, 57.29999923706055 mm
+Size: 20, 18, 1.2000007629394531 mm
+Degenerate triangles removed in original export: 0</x:v>
+      </x:c>
+      <x:c r="C189" s="29" t="str">
+        <x:v>SHA256: 8255ef667a516ba1fd46389974d341523e5bcee4bc5f81e6805fa2f3b864ef64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" ht="28" customHeight="1">
+      <x:c r="A190" s="29" t="str">
+        <x:v>01_base_BLACK.ctb</x:v>
+      </x:c>
+      <x:c r="B190" s="29" t="str">
+        <x:v>Sliced print file. Retained bytes match the source file before folder consolidation.</x:v>
+      </x:c>
+      <x:c r="C190" s="29" t="str">
+        <x:v>SHA256: 1d05971e924c78ade7c83b0acae26120e2dddff5b3b52b35064b252af4ad474b</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191" ht="28" customHeight="1">
+      <x:c r="A191" s="29" t="str">
+        <x:v>020308_parts.ctb</x:v>
+      </x:c>
+      <x:c r="B191" s="29" t="str">
+        <x:v>Sliced print file. Retained bytes match the source file before folder consolidation.</x:v>
+      </x:c>
+      <x:c r="C191" s="29" t="str">
+        <x:v>SHA256: f76017570fd0f2680b0245193d79bfe6ccc4f6919abb938166f5a0cc9a814a6e</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192" ht="28" customHeight="1">
+      <x:c r="A192" s="29" t="str">
+        <x:v>0407_wells.ctb</x:v>
+      </x:c>
+      <x:c r="B192" s="29" t="str">
+        <x:v>Sliced print file. Retained bytes match the source file before folder consolidation.</x:v>
+      </x:c>
+      <x:c r="C192" s="29" t="str">
+        <x:v>SHA256: cec360f96ba4704f76ac404b8af52bdb09c2033c37464cb0cb0512ec80cab98d</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193" ht="30" customHeight="1">
+      <x:c r="A193" s="36" t="str">
+        <x:v>Pricing policy</x:v>
+      </x:c>
+      <x:c r="B193" s="36" t="str"/>
+      <x:c r="C193" s="36" t="str"/>
+    </x:row>
+    <x:row r="194" ht="28" customHeight="1">
+      <x:c r="A194" s="29" t="str">
+        <x:v>quantity_basis</x:v>
+      </x:c>
+      <x:c r="B194" s="29" t="str">
+        <x:v>Small-quantity retail; listings, proxies and allowances explicitly distinguished</x:v>
+      </x:c>
+      <x:c r="C194" s="29" t="str"/>
+    </x:row>
+    <x:row r="195" ht="28" customHeight="1">
+      <x:c r="A195" s="29" t="str">
+        <x:v>tax_shipping</x:v>
+      </x:c>
+      <x:c r="B195" s="29" t="str">
+        <x:v>Shipping, import duties and taxes not included unless source explicitly states included</x:v>
+      </x:c>
+      <x:c r="C195" s="29" t="str"/>
+    </x:row>
+    <x:row r="196" ht="28" customHeight="1">
+      <x:c r="A196" s="29" t="str">
+        <x:v>PCBA</x:v>
+      </x:c>
+      <x:c r="B196" s="29" t="str">
+        <x:v>Use quoted allocation once; do not add PCB component estimate again</x:v>
+      </x:c>
+      <x:c r="C196" s="29" t="str"/>
+    </x:row>
+    <x:row r="197" ht="28" customHeight="1">
+      <x:c r="A197" s="29" t="str">
+        <x:v>printing</x:v>
+      </x:c>
+      <x:c r="B197" s="29" t="str">
+        <x:v>Preserve user formula and source amounts; no extra bottle cost or machine charge added</x:v>
+      </x:c>
+      <x:c r="C197" s="29" t="str"/>
+    </x:row>
+    <x:row r="198" ht="28" customHeight="1">
+      <x:c r="A198" s="29" t="str">
+        <x:v>future</x:v>
+      </x:c>
+      <x:c r="B198" s="29" t="str">
+        <x:v>Excluded from current device and development totals</x:v>
+      </x:c>
+      <x:c r="C198" s="29" t="str"/>
+    </x:row>
+    <x:row r="199" ht="28" customHeight="1">
+      <x:c r="A199" s="29" t="str">
+        <x:v>missing</x:v>
+      </x:c>
+      <x:c r="B199" s="29" t="str">
+        <x:v>Unidentified U3 not assigned a false price; custom optical filter not order-ready</x:v>
+      </x:c>
+      <x:c r="C199" s="29" t="str"/>
+    </x:row>
+    <x:row r="200" ht="28" customHeight="1">
+      <x:c r="A200" s="29" t="str">
+        <x:v>owned</x:v>
+      </x:c>
+      <x:c r="B200" s="29" t="str">
+        <x:v>owned_qty editable. Borrowed items can reduce new purchase budget without making material value zero.</x:v>
+      </x:c>
+      <x:c r="C200" s="29" t="str"/>
+    </x:row>
+    <x:row r="201" ht="40" customHeight="1">
+      <x:c r="A201" s="29" t="str">
+        <x:v>PCB quote scope</x:v>
+      </x:c>
+      <x:c r="B201" s="29" t="str">
+        <x:v>User quotation including design and setup; per-board allocation is not repeat-production pricing</x:v>
+      </x:c>
+      <x:c r="C201" s="29" t="str">
+        <x:v>Original source quotation: NTD 131250 for 2 boards. English allocation is converted to USD.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202" ht="40" customHeight="1">
+      <x:c r="A202" s="29" t="str">
+        <x:v>FX source record</x:v>
+      </x:c>
+      <x:c r="B202" s="29" t="str">
+        <x:v>31.805 NTD per USD; source date 2026-10-05 15:13; recorded 2026-10-08.
+Bank of Taiwan displayed USD spot selling snapshot; comparison and budgeting only</x:v>
+      </x:c>
+      <x:c r="C202" s="29" t="str">
+        <x:v>https://www.bot.com.tw/tw/personal-banking/foreign-exchange</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203" ht="30" customHeight="1">
+      <x:c r="A203" s="36" t="str">
+        <x:v>Historical verification record</x:v>
+      </x:c>
+      <x:c r="B203" s="36" t="str"/>
+      <x:c r="C203" s="36" t="str"/>
+    </x:row>
+    <x:row r="204" ht="40" customHeight="1">
+      <x:c r="A204" s="29" t="str">
+        <x:v>Scope</x:v>
+      </x:c>
+      <x:c r="B204" s="29" t="str">
+        <x:v>The fields below describe the earlier published workbook, before this consolidation. Prior hashes identify that earlier version. They do not claim a native Excel run.</x:v>
+      </x:c>
+      <x:c r="C204" s="29" t="str"/>
+    </x:row>
+    <x:row r="205" ht="28" customHeight="1">
+      <x:c r="A205" s="29" t="str">
+        <x:v>date</x:v>
+      </x:c>
+      <x:c r="B205" s="29" t="str">
+        <x:v>2026-10-11</x:v>
+      </x:c>
+      <x:c r="C205" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206" ht="28" customHeight="1">
+      <x:c r="A206" s="29" t="str">
+        <x:v>currency</x:v>
+      </x:c>
+      <x:c r="B206" s="29" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="C206" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207" ht="28" customHeight="1">
+      <x:c r="A207" s="29" t="str">
+        <x:v>conversion_NTD_per_USD</x:v>
+      </x:c>
+      <x:c r="B207" s="29" t="str">
+        <x:v>31.805</x:v>
+      </x:c>
+      <x:c r="C207" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208" ht="28" customHeight="1">
+      <x:c r="A208" s="29" t="str">
+        <x:v>conversion_source_date</x:v>
+      </x:c>
+      <x:c r="B208" s="29" t="str">
+        <x:v>2026-10-05 15:13</x:v>
+      </x:c>
+      <x:c r="C208" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209" ht="40" customHeight="1">
+      <x:c r="A209" s="29" t="str">
+        <x:v>conversion_policy</x:v>
+      </x:c>
+      <x:c r="B209" s="29" t="str">
+        <x:v>Fixed converted USD budget inputs. Source NTD appears only in provenance notes; input/quantity formulas are in USD. No live FX refresh claimed.</x:v>
+      </x:c>
+      <x:c r="C209" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210" ht="28" customHeight="1">
+      <x:c r="A210" s="29" t="str">
+        <x:v>formula_engine</x:v>
+      </x:c>
+      <x:c r="B210" s="29" t="str">
+        <x:v>artifact-tool</x:v>
+      </x:c>
+      <x:c r="C210" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211" ht="40" customHeight="1">
+      <x:c r="A211" s="29" t="str">
+        <x:v>native_Excel_execution_ver
+ified</x:v>
+      </x:c>
+      <x:c r="B211" s="29" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="C211" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212" ht="28" customHeight="1">
+      <x:c r="A212" s="29" t="str">
+        <x:v>print_count</x:v>
+      </x:c>
+      <x:c r="B212" s="29" t="str">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C212" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213" ht="28" customHeight="1">
+      <x:c r="A213" s="29" t="str">
+        <x:v>PCB_rows</x:v>
+      </x:c>
+      <x:c r="B213" s="29" t="str">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C213" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214" ht="28" customHeight="1">
+      <x:c r="A214" s="29" t="str">
+        <x:v>purchase_rows</x:v>
+      </x:c>
+      <x:c r="B214" s="29" t="str">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C214" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215" ht="28" customHeight="1">
+      <x:c r="A215" s="29" t="str">
+        <x:v>required_rows</x:v>
+      </x:c>
+      <x:c r="B215" s="29" t="str">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C215" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216" ht="28" customHeight="1">
+      <x:c r="A216" s="29" t="str">
+        <x:v>developer_rows</x:v>
+      </x:c>
+      <x:c r="B216" s="29" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C216" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217" ht="28" customHeight="1">
+      <x:c r="A217" s="29" t="str">
+        <x:v>future_rows</x:v>
+      </x:c>
+      <x:c r="B217" s="29" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C217" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218" ht="28" customHeight="1">
+      <x:c r="A218" s="29" t="str">
+        <x:v>calculated_print_total_USD</x:v>
+      </x:c>
+      <x:c r="B218" s="29" t="str">
+        <x:v>35.06950479484358</x:v>
+      </x:c>
+      <x:c r="C218" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="219" ht="40" customHeight="1">
+      <x:c r="A219" s="29" t="str">
+        <x:v>required_purchases_used_US
+D</x:v>
+      </x:c>
+      <x:c r="B219" s="29" t="str">
+        <x:v>412.9352365980192</x:v>
+      </x:c>
+      <x:c r="C219" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="220" ht="28" customHeight="1">
+      <x:c r="A220" s="29" t="str">
+        <x:v>required_nonPCB_USD</x:v>
+      </x:c>
+      <x:c r="B220" s="29" t="str">
+        <x:v>448.00474139286274</x:v>
+      </x:c>
+      <x:c r="C220" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221" ht="28" customHeight="1">
+      <x:c r="A221" s="29" t="str">
+        <x:v>PCB_quote_total_USD</x:v>
+      </x:c>
+      <x:c r="B221" s="29" t="str">
+        <x:v>4126.709636849552</x:v>
+      </x:c>
+      <x:c r="C221" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="222" ht="28" customHeight="1">
+      <x:c r="A222" s="29" t="str">
+        <x:v>PCB_allocation_USD</x:v>
+      </x:c>
+      <x:c r="B222" s="29" t="str">
+        <x:v>2063.354818424776</x:v>
+      </x:c>
+      <x:c r="C222" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223" ht="28" customHeight="1">
+      <x:c r="A223" s="29" t="str">
+        <x:v>required_budget_USD</x:v>
+      </x:c>
+      <x:c r="B223" s="29" t="str">
+        <x:v>2511.359559817639</x:v>
+      </x:c>
+      <x:c r="C223" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224" ht="28" customHeight="1">
+      <x:c r="A224" s="29" t="str">
+        <x:v>required_new_packs_USD</x:v>
+      </x:c>
+      <x:c r="B224" s="29" t="str">
+        <x:v>512.5122056280459</x:v>
+      </x:c>
+      <x:c r="C224" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="225" ht="28" customHeight="1">
+      <x:c r="A225" s="29" t="str">
+        <x:v>developer_budget_USD</x:v>
+      </x:c>
+      <x:c r="B225" s="29" t="str">
+        <x:v>1214.0286983178744</x:v>
+      </x:c>
+      <x:c r="C225" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226" ht="28" customHeight="1">
+      <x:c r="A226" s="29" t="str">
+        <x:v>developer_new_packs_USD</x:v>
+      </x:c>
+      <x:c r="B226" s="29" t="str">
+        <x:v>1214.0286983178744</x:v>
+      </x:c>
+      <x:c r="C226" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227" ht="28" customHeight="1">
+      <x:c r="A227" s="29" t="str">
+        <x:v>future_budget_USD</x:v>
+      </x:c>
+      <x:c r="B227" s="29" t="str">
+        <x:v>235.8119792485458</x:v>
+      </x:c>
+      <x:c r="C227" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="228" ht="28" customHeight="1">
+      <x:c r="A228" s="29" t="str">
+        <x:v>PCB_priced_materials_USD</x:v>
+      </x:c>
+      <x:c r="B228" s="29" t="str">
+        <x:v>61.436880993554496</x:v>
+      </x:c>
+      <x:c r="C228" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="229" ht="28" customHeight="1">
+      <x:c r="A229" s="29" t="str">
+        <x:v>PCB_unpriced_rows</x:v>
+      </x:c>
+      <x:c r="B229" s="29" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C229" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="230" ht="28" customHeight="1">
+      <x:c r="A230" s="29" t="str">
+        <x:v>complete_cost</x:v>
+      </x:c>
+      <x:c r="B230" s="29" t="str">
+        <x:v>Not order-ready; proxies and allowances included</x:v>
+      </x:c>
+      <x:c r="C230" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="231" ht="40" customHeight="1">
+      <x:c r="A231" s="29" t="str">
+        <x:v>formula_total_matches_inde
+pendent_calculation</x:v>
+      </x:c>
+      <x:c r="B231" s="29" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="C231" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232" ht="28" customHeight="1">
+      <x:c r="A232" s="29" t="str">
+        <x:v>blank_vs_zero_test_passed</x:v>
+      </x:c>
+      <x:c r="B232" s="29" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="C232" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="233" ht="28" customHeight="1">
+      <x:c r="A233" s="29" t="str">
+        <x:v>pack_vs_usage_test_passed</x:v>
+      </x:c>
+      <x:c r="B233" s="29" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="C233" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="234" ht="28" customHeight="1">
+      <x:c r="A234" s="29" t="str">
+        <x:v>owned_quantity_test_passed</x:v>
+      </x:c>
+      <x:c r="B234" s="29" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="C234" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="235" ht="40" customHeight="1">
+      <x:c r="A235" s="29" t="str">
+        <x:v>USD_input_recalculation_pa
+ssed</x:v>
+      </x:c>
+      <x:c r="B235" s="29" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="C235" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="236" ht="28" customHeight="1">
+      <x:c r="A236" s="29" t="str">
+        <x:v>zero_pack_divisor_rejected</x:v>
+      </x:c>
+      <x:c r="B236" s="29" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="C236" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="237" ht="28" customHeight="1">
+      <x:c r="A237" s="29" t="str">
+        <x:v>zero_PCB_divisor_rejected</x:v>
+      </x:c>
+      <x:c r="B237" s="29" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="C237" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="238" ht="28" customHeight="1">
+      <x:c r="A238" s="29" t="str">
+        <x:v>missing_resin_rejected</x:v>
+      </x:c>
+      <x:c r="B238" s="29" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="C238" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="239" ht="28" customHeight="1">
+      <x:c r="A239" s="29" t="str">
+        <x:v>printed_geometry_preserved</x:v>
+      </x:c>
+      <x:c r="B239" s="29" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="C239" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="240" ht="28" customHeight="1">
+      <x:c r="A240" s="29" t="str">
+        <x:v>ZH_deliverables_unchanged</x:v>
+      </x:c>
+      <x:c r="B240" s="29" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="C240" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="241" ht="28" customHeight="1">
+      <x:c r="A241" s="29" t="str">
+        <x:v>formula_error_scan</x:v>
+      </x:c>
+      <x:c r="B241" s="29" t="str">
+        <x:v>{"kind":"notice","message":"Cell search matched 0 entries."}</x:v>
+      </x:c>
+      <x:c r="C241" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="242" ht="28" customHeight="1">
+      <x:c r="A242" s="29" t="str">
+        <x:v>public_workbook_sha256</x:v>
+      </x:c>
+      <x:c r="B242" s="29" t="str">
+        <x:v>8e6c482fc1ea55bad41929827f2f45c013c33a037fc3ca0d7844b90ac3ca0966</x:v>
+      </x:c>
+      <x:c r="C242" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="243" ht="28" customHeight="1">
+      <x:c r="A243" s="29" t="str">
+        <x:v>visual_QA_passed</x:v>
+      </x:c>
+      <x:c r="B243" s="29" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="C243" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="244" ht="28" customHeight="1">
+      <x:c r="A244" s="29" t="str">
+        <x:v>rendered_sheets</x:v>
+      </x:c>
+      <x:c r="B244" s="29" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C244" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="245" ht="54" customHeight="1">
+      <x:c r="A245" s="29" t="str">
+        <x:v>visual_QA</x:v>
+      </x:c>
+      <x:c r="B245" s="29" t="str">
+        <x:v>Inspected all four affected views: USD Summary, Purchase price/quantity calculations, PCB price columns and print-batch calculations. Labels and prices are readable; no clipped costs or formula errors. Printed worksheet preserved. Native Excel execution is not claimed.</x:v>
+      </x:c>
+      <x:c r="C245" s="29" t="str">
+        <x:v>Previous validation record.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>